--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU307"/>
+  <dimension ref="A1:AU310"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G19">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G33">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G73">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G80">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="O83">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="P83">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O84">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="P84">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G103">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G106">
@@ -17583,17 +17583,17 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N106">
-        <v>1.68</v>
+        <v>3.46</v>
       </c>
       <c r="O106">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="P106">
-        <v>4.8</v>
+        <v>2.03</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G108">
@@ -17909,17 +17909,17 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G137">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G172">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="O173">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="P173">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB173">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB174">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="O175">
-        <v>3.54</v>
+        <v>7.04</v>
       </c>
       <c r="P175">
-        <v>3.52</v>
+        <v>14.3</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-22 13:45:00</t>
+          <t>2026-08-22 13:30:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-22 13:45:00</t>
+          <t>2026-08-22 13:30:00</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O177">
-        <v>3.13</v>
+        <v>3.54</v>
       </c>
       <c r="P177">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB177">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-22 14:00:00</t>
+          <t>2026-08-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -29276,12 +29276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O178">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P178">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB178">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-22 14:00:00</t>
+          <t>2026-08-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29607,22 +29607,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29688,10 +29688,10 @@
         <v>0</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Iraklis 1908 U19</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Iraklis 1908 U19</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G196">
@@ -32373,12 +32373,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-08-22 14:15:00</t>
+          <t>2026-08-22 14:00:00</t>
         </is>
       </c>
     </row>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-08-22 14:30:00</t>
+          <t>2026-08-22 14:00:00</t>
         </is>
       </c>
     </row>
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-08-22 14:30:00</t>
+          <t>2026-08-22 14:15:00</t>
         </is>
       </c>
     </row>
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G200">
@@ -33025,12 +33025,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-08-22 15:00:00</t>
+          <t>2026-08-22 14:30:00</t>
         </is>
       </c>
     </row>
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-22 15:00:00</t>
+          <t>2026-08-22 14:30:00</t>
         </is>
       </c>
     </row>
@@ -33356,22 +33356,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,22 +34171,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G208">
@@ -34209,7 +34209,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G209">
@@ -34492,12 +34492,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G210">
@@ -34535,7 +34535,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N210">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>2026-08-22 15:15:00</t>
+          <t>2026-08-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -34655,12 +34655,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G211">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-08-22 15:15:00</t>
+          <t>2026-08-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G212">
@@ -34981,12 +34981,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-08-22 15:30:00</t>
+          <t>2026-08-22 15:15:00</t>
         </is>
       </c>
     </row>
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-08-22 15:30:00</t>
+          <t>2026-08-22 15:15:00</t>
         </is>
       </c>
     </row>
@@ -35312,22 +35312,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,22 +35475,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,22 +35638,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,22 +36290,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,22 +36453,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,22 +36616,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,22 +36779,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G224">
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O225">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P225">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-08-22 15:45:00</t>
+          <t>2026-08-22 15:30:00</t>
         </is>
       </c>
     </row>
@@ -37100,12 +37100,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O226">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P226">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-08-22 15:45:00</t>
+          <t>2026-08-22 15:30:00</t>
         </is>
       </c>
     </row>
@@ -37263,27 +37263,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O227">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P227">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-08-22 15:45:00</t>
+          <t>2026-08-22 15:30:00</t>
         </is>
       </c>
     </row>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="O228">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P228">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>5.42</v>
+        <v>2.65</v>
       </c>
       <c r="O229">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="P229">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37675,10 +37675,10 @@
         <v>0</v>
       </c>
       <c r="AA229">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB229">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC229">
         <v>0</v>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.72</v>
+        <v>3.58</v>
       </c>
       <c r="O230">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="P230">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37838,10 +37838,10 @@
         <v>0</v>
       </c>
       <c r="AA230">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB230">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC230">
         <v>0</v>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38164,10 +38164,10 @@
         <v>0</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC232">
         <v>0</v>
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="O233">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P233">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38327,10 +38327,10 @@
         <v>0</v>
       </c>
       <c r="AA233">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB233">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC233">
         <v>0</v>
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-08-22 16:00:00</t>
+          <t>2026-08-22 15:45:00</t>
         </is>
       </c>
     </row>
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O234">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P234">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38490,10 +38490,10 @@
         <v>0</v>
       </c>
       <c r="AA234">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB234">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC234">
         <v>0</v>
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-08-22 16:00:00</t>
+          <t>2026-08-22 15:45:00</t>
         </is>
       </c>
     </row>
@@ -38567,12 +38567,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O235">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P235">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38653,10 +38653,10 @@
         <v>0</v>
       </c>
       <c r="AA235">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB235">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC235">
         <v>0</v>
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-08-22 16:00:00</t>
+          <t>2026-08-22 15:45:00</t>
         </is>
       </c>
     </row>
@@ -38735,22 +38735,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38816,10 +38816,10 @@
         <v>0</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC236">
         <v>0</v>
@@ -38898,22 +38898,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -38979,10 +38979,10 @@
         <v>0</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC237">
         <v>0</v>
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>0</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC238">
         <v>0</v>
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O239">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P239">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB239">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,22 +39550,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,22 +39713,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,10 +39794,10 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC242">
         <v>0</v>
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,22 +40039,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,22 +40365,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O248">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P248">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O249">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P249">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41012,12 +41012,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G250">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>2026-08-22 16:30:00</t>
+          <t>2026-08-22 16:00:00</t>
         </is>
       </c>
     </row>
@@ -41175,12 +41175,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-08-22 16:30:00</t>
+          <t>2026-08-22 16:00:00</t>
         </is>
       </c>
     </row>
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-08-22 16:30:00</t>
+          <t>2026-08-22 16:00:00</t>
         </is>
       </c>
     </row>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G253">
@@ -41664,27 +41664,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-08-22 17:00:00</t>
+          <t>2026-08-22 16:30:00</t>
         </is>
       </c>
     </row>
@@ -41827,27 +41827,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G255">
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-08-22 17:00:00</t>
+          <t>2026-08-22 16:30:00</t>
         </is>
       </c>
     </row>
@@ -41990,27 +41990,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G256">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-08-22 17:00:00</t>
+          <t>2026-08-22 16:30:00</t>
         </is>
       </c>
     </row>
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-08-22 17:30:00</t>
+          <t>2026-08-22 17:00:00</t>
         </is>
       </c>
     </row>
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-08-22 18:00:00</t>
+          <t>2026-08-22 17:00:00</t>
         </is>
       </c>
     </row>
@@ -42479,12 +42479,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G259">
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-08-22 18:15:00</t>
+          <t>2026-08-22 17:00:00</t>
         </is>
       </c>
     </row>
@@ -42642,12 +42642,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-08-22 18:30:00</t>
+          <t>2026-08-22 17:30:00</t>
         </is>
       </c>
     </row>
@@ -42805,12 +42805,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O261">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P261">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-08-22 18:30:00</t>
+          <t>2026-08-22 18:00:00</t>
         </is>
       </c>
     </row>
@@ -42968,12 +42968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-08-22 18:30:00</t>
+          <t>2026-08-22 18:15:00</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43457,12 +43457,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-08-22 19:30:00</t>
+          <t>2026-08-22 18:30:00</t>
         </is>
       </c>
     </row>
@@ -43620,12 +43620,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-08-22 19:30:00</t>
+          <t>2026-08-22 18:30:00</t>
         </is>
       </c>
     </row>
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-08-22 19:30:00</t>
+          <t>2026-08-22 18:30:00</t>
         </is>
       </c>
     </row>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-08-22 20:00:00</t>
+          <t>2026-08-22 19:30:00</t>
         </is>
       </c>
     </row>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-08-22 20:00:00</t>
+          <t>2026-08-22 19:30:00</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-08-22 20:00:00</t>
+          <t>2026-08-22 19:30:00</t>
         </is>
       </c>
     </row>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G272">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O273">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P273">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-08-22 20:30:00</t>
+          <t>2026-08-22 20:00:00</t>
         </is>
       </c>
     </row>
@@ -44924,7 +44924,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-08-22 20:30:00</t>
+          <t>2026-08-22 20:00:00</t>
         </is>
       </c>
     </row>
@@ -45087,12 +45087,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G275">
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-08-22 20:30:00</t>
+          <t>2026-08-22 20:00:00</t>
         </is>
       </c>
     </row>
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O278">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P278">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O279">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P279">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.99</v>
+        <v>2.56</v>
       </c>
       <c r="O281">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="P281">
-        <v>3.79</v>
+        <v>2.69</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46554,12 +46554,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-08-22 21:00:00</t>
+          <t>2026-08-22 20:30:00</t>
         </is>
       </c>
     </row>
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-08-22 21:00:00</t>
+          <t>2026-08-22 20:30:00</t>
         </is>
       </c>
     </row>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-08-22 21:00:00</t>
+          <t>2026-08-22 20:30:00</t>
         </is>
       </c>
     </row>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,22 +47211,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G288">
@@ -47374,22 +47374,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G289">
@@ -47537,22 +47537,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G295">
@@ -48510,27 +48510,27 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O296">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P296">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-08-22 21:30:00</t>
+          <t>2026-08-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -48673,27 +48673,27 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O297">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P297">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-08-22 21:30:00</t>
+          <t>2026-08-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -48836,27 +48836,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O298">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P298">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-08-22 21:30:00</t>
+          <t>2026-08-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-08-22 21:45:00</t>
+          <t>2026-08-22 21:30:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-08-22 22:00:00</t>
+          <t>2026-08-22 21:30:00</t>
         </is>
       </c>
     </row>
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-08-22 22:00:00</t>
+          <t>2026-08-22 21:30:00</t>
         </is>
       </c>
     </row>
@@ -49488,12 +49488,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-08-22 22:00:00</t>
+          <t>2026-08-22 21:45:00</t>
         </is>
       </c>
     </row>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-08-22 22:30:00</t>
+          <t>2026-08-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -49814,7 +49814,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G304">
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-08-22 23:00:00</t>
+          <t>2026-08-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G305">
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-08-22 23:30:00</t>
+          <t>2026-08-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -50140,7 +50140,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G306">
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-08-22 23:30:00</t>
+          <t>2026-08-22 22:30:00</t>
         </is>
       </c>
     </row>
@@ -50303,156 +50303,645 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="G307">
+        <v>0</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>0</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
+        <v>0</v>
+      </c>
+      <c r="P307">
+        <v>0</v>
+      </c>
+      <c r="Q307">
+        <v>0</v>
+      </c>
+      <c r="R307">
+        <v>0</v>
+      </c>
+      <c r="S307">
+        <v>0</v>
+      </c>
+      <c r="T307">
+        <v>0</v>
+      </c>
+      <c r="U307">
+        <v>0</v>
+      </c>
+      <c r="V307">
+        <v>0</v>
+      </c>
+      <c r="W307">
+        <v>0</v>
+      </c>
+      <c r="X307">
+        <v>0</v>
+      </c>
+      <c r="Y307">
+        <v>0</v>
+      </c>
+      <c r="Z307">
+        <v>0</v>
+      </c>
+      <c r="AA307">
+        <v>0</v>
+      </c>
+      <c r="AB307">
+        <v>0</v>
+      </c>
+      <c r="AC307">
+        <v>0</v>
+      </c>
+      <c r="AD307">
+        <v>0</v>
+      </c>
+      <c r="AE307">
+        <v>0</v>
+      </c>
+      <c r="AF307">
+        <v>0</v>
+      </c>
+      <c r="AG307">
+        <v>0</v>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ307">
+        <v>0</v>
+      </c>
+      <c r="AK307">
+        <v>0</v>
+      </c>
+      <c r="AL307">
+        <v>0</v>
+      </c>
+      <c r="AM307">
+        <v>-1</v>
+      </c>
+      <c r="AN307">
+        <v>-1</v>
+      </c>
+      <c r="AO307">
+        <v>-1</v>
+      </c>
+      <c r="AP307">
+        <v>-1</v>
+      </c>
+      <c r="AQ307">
+        <v>0</v>
+      </c>
+      <c r="AR307">
+        <v>0</v>
+      </c>
+      <c r="AS307">
+        <v>0</v>
+      </c>
+      <c r="AT307">
+        <v>0</v>
+      </c>
+      <c r="AU307" t="inlineStr">
+        <is>
+          <t>2026-08-22 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
+      <c r="C308" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D308" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G308">
+        <v>0</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308">
+        <v>0</v>
+      </c>
+      <c r="P308">
+        <v>0</v>
+      </c>
+      <c r="Q308">
+        <v>0</v>
+      </c>
+      <c r="R308">
+        <v>0</v>
+      </c>
+      <c r="S308">
+        <v>0</v>
+      </c>
+      <c r="T308">
+        <v>0</v>
+      </c>
+      <c r="U308">
+        <v>0</v>
+      </c>
+      <c r="V308">
+        <v>0</v>
+      </c>
+      <c r="W308">
+        <v>0</v>
+      </c>
+      <c r="X308">
+        <v>0</v>
+      </c>
+      <c r="Y308">
+        <v>0</v>
+      </c>
+      <c r="Z308">
+        <v>0</v>
+      </c>
+      <c r="AA308">
+        <v>0</v>
+      </c>
+      <c r="AB308">
+        <v>0</v>
+      </c>
+      <c r="AC308">
+        <v>0</v>
+      </c>
+      <c r="AD308">
+        <v>0</v>
+      </c>
+      <c r="AE308">
+        <v>0</v>
+      </c>
+      <c r="AF308">
+        <v>0</v>
+      </c>
+      <c r="AG308">
+        <v>0</v>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ308">
+        <v>0</v>
+      </c>
+      <c r="AK308">
+        <v>0</v>
+      </c>
+      <c r="AL308">
+        <v>0</v>
+      </c>
+      <c r="AM308">
+        <v>-1</v>
+      </c>
+      <c r="AN308">
+        <v>-1</v>
+      </c>
+      <c r="AO308">
+        <v>-1</v>
+      </c>
+      <c r="AP308">
+        <v>-1</v>
+      </c>
+      <c r="AQ308">
+        <v>0</v>
+      </c>
+      <c r="AR308">
+        <v>0</v>
+      </c>
+      <c r="AS308">
+        <v>0</v>
+      </c>
+      <c r="AT308">
+        <v>0</v>
+      </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>2026-08-22 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="G309">
+        <v>0</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N309">
+        <v>0</v>
+      </c>
+      <c r="O309">
+        <v>0</v>
+      </c>
+      <c r="P309">
+        <v>0</v>
+      </c>
+      <c r="Q309">
+        <v>0</v>
+      </c>
+      <c r="R309">
+        <v>0</v>
+      </c>
+      <c r="S309">
+        <v>0</v>
+      </c>
+      <c r="T309">
+        <v>0</v>
+      </c>
+      <c r="U309">
+        <v>0</v>
+      </c>
+      <c r="V309">
+        <v>0</v>
+      </c>
+      <c r="W309">
+        <v>0</v>
+      </c>
+      <c r="X309">
+        <v>0</v>
+      </c>
+      <c r="Y309">
+        <v>0</v>
+      </c>
+      <c r="Z309">
+        <v>0</v>
+      </c>
+      <c r="AA309">
+        <v>0</v>
+      </c>
+      <c r="AB309">
+        <v>0</v>
+      </c>
+      <c r="AC309">
+        <v>0</v>
+      </c>
+      <c r="AD309">
+        <v>0</v>
+      </c>
+      <c r="AE309">
+        <v>0</v>
+      </c>
+      <c r="AF309">
+        <v>0</v>
+      </c>
+      <c r="AG309">
+        <v>0</v>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ309">
+        <v>0</v>
+      </c>
+      <c r="AK309">
+        <v>0</v>
+      </c>
+      <c r="AL309">
+        <v>0</v>
+      </c>
+      <c r="AM309">
+        <v>-1</v>
+      </c>
+      <c r="AN309">
+        <v>-1</v>
+      </c>
+      <c r="AO309">
+        <v>-1</v>
+      </c>
+      <c r="AP309">
+        <v>-1</v>
+      </c>
+      <c r="AQ309">
+        <v>0</v>
+      </c>
+      <c r="AR309">
+        <v>0</v>
+      </c>
+      <c r="AS309">
+        <v>0</v>
+      </c>
+      <c r="AT309">
+        <v>0</v>
+      </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>2026-08-22 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
+      <c r="F310" t="inlineStr">
         <is>
           <t>Colorado Rapids</t>
         </is>
       </c>
-      <c r="G307">
-        <v>0</v>
-      </c>
-      <c r="H307">
-        <v>0</v>
-      </c>
-      <c r="I307">
-        <v>0</v>
-      </c>
-      <c r="J307">
-        <v>0</v>
-      </c>
-      <c r="K307">
-        <v>0</v>
-      </c>
-      <c r="L307">
-        <v>0</v>
-      </c>
-      <c r="M307" t="inlineStr">
+      <c r="G310">
+        <v>0</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>0</v>
+      </c>
+      <c r="M310" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N307">
-        <v>0</v>
-      </c>
-      <c r="O307">
-        <v>0</v>
-      </c>
-      <c r="P307">
-        <v>0</v>
-      </c>
-      <c r="Q307">
-        <v>0</v>
-      </c>
-      <c r="R307">
-        <v>0</v>
-      </c>
-      <c r="S307">
-        <v>0</v>
-      </c>
-      <c r="T307">
-        <v>0</v>
-      </c>
-      <c r="U307">
-        <v>0</v>
-      </c>
-      <c r="V307">
-        <v>0</v>
-      </c>
-      <c r="W307">
-        <v>0</v>
-      </c>
-      <c r="X307">
-        <v>0</v>
-      </c>
-      <c r="Y307">
-        <v>0</v>
-      </c>
-      <c r="Z307">
-        <v>0</v>
-      </c>
-      <c r="AA307">
-        <v>0</v>
-      </c>
-      <c r="AB307">
-        <v>0</v>
-      </c>
-      <c r="AC307">
-        <v>0</v>
-      </c>
-      <c r="AD307">
-        <v>0</v>
-      </c>
-      <c r="AE307">
-        <v>0</v>
-      </c>
-      <c r="AF307">
-        <v>0</v>
-      </c>
-      <c r="AG307">
-        <v>0</v>
-      </c>
-      <c r="AH307" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI307" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ307">
-        <v>0</v>
-      </c>
-      <c r="AK307">
-        <v>0</v>
-      </c>
-      <c r="AL307">
-        <v>0</v>
-      </c>
-      <c r="AM307">
-        <v>-1</v>
-      </c>
-      <c r="AN307">
-        <v>-1</v>
-      </c>
-      <c r="AO307">
-        <v>-1</v>
-      </c>
-      <c r="AP307">
-        <v>-1</v>
-      </c>
-      <c r="AQ307">
-        <v>0</v>
-      </c>
-      <c r="AR307">
-        <v>0</v>
-      </c>
-      <c r="AS307">
-        <v>0</v>
-      </c>
-      <c r="AT307">
-        <v>0</v>
-      </c>
-      <c r="AU307" t="inlineStr">
+      <c r="N310">
+        <v>0</v>
+      </c>
+      <c r="O310">
+        <v>0</v>
+      </c>
+      <c r="P310">
+        <v>0</v>
+      </c>
+      <c r="Q310">
+        <v>0</v>
+      </c>
+      <c r="R310">
+        <v>0</v>
+      </c>
+      <c r="S310">
+        <v>0</v>
+      </c>
+      <c r="T310">
+        <v>0</v>
+      </c>
+      <c r="U310">
+        <v>0</v>
+      </c>
+      <c r="V310">
+        <v>0</v>
+      </c>
+      <c r="W310">
+        <v>0</v>
+      </c>
+      <c r="X310">
+        <v>0</v>
+      </c>
+      <c r="Y310">
+        <v>0</v>
+      </c>
+      <c r="Z310">
+        <v>0</v>
+      </c>
+      <c r="AA310">
+        <v>0</v>
+      </c>
+      <c r="AB310">
+        <v>0</v>
+      </c>
+      <c r="AC310">
+        <v>0</v>
+      </c>
+      <c r="AD310">
+        <v>0</v>
+      </c>
+      <c r="AE310">
+        <v>0</v>
+      </c>
+      <c r="AF310">
+        <v>0</v>
+      </c>
+      <c r="AG310">
+        <v>0</v>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ310">
+        <v>0</v>
+      </c>
+      <c r="AK310">
+        <v>0</v>
+      </c>
+      <c r="AL310">
+        <v>0</v>
+      </c>
+      <c r="AM310">
+        <v>-1</v>
+      </c>
+      <c r="AN310">
+        <v>-1</v>
+      </c>
+      <c r="AO310">
+        <v>-1</v>
+      </c>
+      <c r="AP310">
+        <v>-1</v>
+      </c>
+      <c r="AQ310">
+        <v>0</v>
+      </c>
+      <c r="AR310">
+        <v>0</v>
+      </c>
+      <c r="AS310">
+        <v>0</v>
+      </c>
+      <c r="AT310">
+        <v>0</v>
+      </c>
+      <c r="AU310" t="inlineStr">
         <is>
           <t>2026-08-22 23:30:00</t>
         </is>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G19">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G33">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G184">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G185">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G198">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G225">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="O282">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="P282">
-        <v>2.7</v>
+        <v>3.79</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O283">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P283">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G284">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G285">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G298">

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G198">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G223">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G298">

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G19">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G223">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="O229">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P229">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.58</v>
+        <v>2.65</v>
       </c>
       <c r="O230">
-        <v>3.88</v>
+        <v>3.35</v>
       </c>
       <c r="P230">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="O231">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P231">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q247">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.07</v>
+        <v>2.82</v>
       </c>
       <c r="O76">
-        <v>3.76</v>
+        <v>3.43</v>
       </c>
       <c r="P76">
-        <v>3.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.82</v>
+        <v>2.07</v>
       </c>
       <c r="O77">
-        <v>3.43</v>
+        <v>3.76</v>
       </c>
       <c r="P77">
-        <v>2.7</v>
+        <v>3.76</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G108">
@@ -17909,17 +17909,17 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N108">
-        <v>5.76</v>
+        <v>1.68</v>
       </c>
       <c r="O108">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="P108">
-        <v>1.49</v>
+        <v>4.8</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB108">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G109">
@@ -18072,17 +18072,17 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N109">
-        <v>1.68</v>
+        <v>5.76</v>
       </c>
       <c r="O109">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P109">
-        <v>4.8</v>
+        <v>1.49</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21544,10 +21544,10 @@
         <v>0</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE130">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G137">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G146">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G148">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G162">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G198">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G274">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G278">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O281">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P281">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O282">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P282">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O286">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P286">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q286">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O83">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="P83">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="O84">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="P84">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="O102">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="P102">
-        <v>2.56</v>
+        <v>4.45</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AB102">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="O103">
-        <v>4.05</v>
+        <v>3.62</v>
       </c>
       <c r="P103">
-        <v>4.45</v>
+        <v>2.56</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AB103">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N106">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N107">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.24</v>
+        <v>4.76</v>
       </c>
       <c r="O175">
-        <v>7.04</v>
+        <v>3.73</v>
       </c>
       <c r="P175">
-        <v>14.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="AB175">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>4.76</v>
+        <v>1.24</v>
       </c>
       <c r="O176">
-        <v>3.73</v>
+        <v>7.04</v>
       </c>
       <c r="P176">
-        <v>1.86</v>
+        <v>14.3</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
+        <v>1.61</v>
+      </c>
+      <c r="AB176">
         <v>2.15</v>
-      </c>
-      <c r="AB176">
-        <v>1.62</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Iraklis 1908 U19</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>3.98</v>
+        <v>1.19</v>
       </c>
       <c r="O187">
-        <v>3.04</v>
+        <v>6.05</v>
       </c>
       <c r="P187">
-        <v>2.05</v>
+        <v>16</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Iraklis 1908 U19</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.19</v>
+        <v>3.98</v>
       </c>
       <c r="O188">
-        <v>6.05</v>
+        <v>3.04</v>
       </c>
       <c r="P188">
-        <v>16</v>
+        <v>2.05</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G198">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G274">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O310">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P310">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q310">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G162">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>4.76</v>
+        <v>1.24</v>
       </c>
       <c r="O175">
-        <v>3.73</v>
+        <v>7.04</v>
       </c>
       <c r="P175">
-        <v>1.86</v>
+        <v>14.3</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
+        <v>1.61</v>
+      </c>
+      <c r="AB175">
         <v>2.15</v>
-      </c>
-      <c r="AB175">
-        <v>1.62</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.24</v>
+        <v>4.76</v>
       </c>
       <c r="O176">
-        <v>7.04</v>
+        <v>3.73</v>
       </c>
       <c r="P176">
-        <v>14.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="AB176">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q248">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="O23">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P23">
-        <v>2.92</v>
+        <v>3.61</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="O24">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P24">
-        <v>3.61</v>
+        <v>2.92</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
       <c r="O97">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="P97">
-        <v>4.75</v>
+        <v>2.28</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,7 +16159,7 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB97">
         <v>1.78</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.03</v>
+        <v>4.89</v>
       </c>
       <c r="O98">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="P98">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AB98">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="O99">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="P99">
-        <v>3.54</v>
+        <v>4.45</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB99">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>4.89</v>
+        <v>2.47</v>
       </c>
       <c r="O100">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P100">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB100">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O101">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="P101">
-        <v>3.96</v>
+        <v>4.75</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB101">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="O102">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="P102">
-        <v>4.45</v>
+        <v>3.54</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB102">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.47</v>
+        <v>1.85</v>
       </c>
       <c r="O103">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="P103">
-        <v>2.56</v>
+        <v>3.96</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AB103">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N106">
@@ -17596,34 +17596,34 @@
         <v>2.03</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
         <v>1.9</v>
@@ -17632,19 +17632,19 @@
         <v>1.9</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N107">
@@ -17759,34 +17759,34 @@
         <v>7.55</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA107">
         <v>1.61</v>
@@ -17795,19 +17795,19 @@
         <v>2.3</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="O111">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="P111">
-        <v>5.86</v>
+        <v>6.5</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="O112">
-        <v>4.55</v>
+        <v>3.14</v>
       </c>
       <c r="P112">
-        <v>6.5</v>
+        <v>3.16</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="O113">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P113">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P114">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O115">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="P115">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="O116">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P116">
-        <v>2.81</v>
+        <v>2.37</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O117">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.76</v>
+        <v>1.51</v>
       </c>
       <c r="O118">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="P118">
-        <v>2.37</v>
+        <v>5.86</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N122">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28716,10 +28716,10 @@
         <v>0</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE174">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G196">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G198">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34584,10 +34584,10 @@
         <v>0</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE210">
         <v>0</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.65</v>
+        <v>3.58</v>
       </c>
       <c r="O230">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="P230">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>3.58</v>
+        <v>2.65</v>
       </c>
       <c r="O231">
-        <v>3.88</v>
+        <v>3.35</v>
       </c>
       <c r="P231">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38490,10 +38490,10 @@
         <v>0</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC234">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49737,10 +49737,10 @@
         <v>0</v>
       </c>
       <c r="AA303">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB303">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC303">
         <v>0</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q307">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G56">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G67">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kelantan</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G70">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G106">
@@ -17583,68 +17583,68 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N106">
-        <v>3.46</v>
+        <v>1.68</v>
       </c>
       <c r="O106">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="P106">
-        <v>2.03</v>
+        <v>4.8</v>
       </c>
       <c r="Q106">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S106">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T106">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U106">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V106">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W106">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X106">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA106">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB106">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC106">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD106">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK106">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G107">
@@ -17746,68 +17746,68 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N107">
-        <v>1.33</v>
+        <v>5.76</v>
       </c>
       <c r="O107">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="P107">
-        <v>7.55</v>
+        <v>1.49</v>
       </c>
       <c r="Q107">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S107">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T107">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U107">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V107">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W107">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z107">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA107">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC107">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD107">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE107">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF107">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK107">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="O108">
-        <v>3.8</v>
+        <v>4.65</v>
       </c>
       <c r="P108">
+        <v>7.55</v>
+      </c>
+      <c r="Q108">
+        <v>1.86</v>
+      </c>
+      <c r="R108">
+        <v>2.41</v>
+      </c>
+      <c r="S108">
+        <v>1.28</v>
+      </c>
+      <c r="T108">
+        <v>3.34</v>
+      </c>
+      <c r="U108">
+        <v>2.34</v>
+      </c>
+      <c r="V108">
+        <v>1.53</v>
+      </c>
+      <c r="W108">
+        <v>1.09</v>
+      </c>
+      <c r="X108">
+        <v>1.03</v>
+      </c>
+      <c r="Y108">
+        <v>1.17</v>
+      </c>
+      <c r="Z108">
         <v>4.8</v>
       </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
-      <c r="T108">
-        <v>0</v>
-      </c>
-      <c r="U108">
-        <v>0</v>
-      </c>
-      <c r="V108">
-        <v>0</v>
-      </c>
-      <c r="W108">
-        <v>0</v>
-      </c>
-      <c r="X108">
-        <v>0</v>
-      </c>
-      <c r="Y108">
-        <v>0</v>
-      </c>
-      <c r="Z108">
-        <v>0</v>
-      </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>5.76</v>
+        <v>3.46</v>
       </c>
       <c r="O109">
-        <v>4.4</v>
+        <v>3.44</v>
       </c>
       <c r="P109">
-        <v>1.49</v>
+        <v>2.03</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA109">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB109">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="P117">
-        <v>2.81</v>
+        <v>5.86</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="O118">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="P118">
-        <v>5.86</v>
+        <v>2.81</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G298">

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU310"/>
+  <dimension ref="A1:AU313"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G108">
@@ -17909,68 +17909,68 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N108">
-        <v>1.33</v>
+        <v>3.46</v>
       </c>
       <c r="O108">
-        <v>4.65</v>
+        <v>3.44</v>
       </c>
       <c r="P108">
-        <v>7.55</v>
+        <v>2.03</v>
       </c>
       <c r="Q108">
-        <v>1.86</v>
+        <v>3.9</v>
       </c>
       <c r="R108">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S108">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T108">
-        <v>3.34</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="V108">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W108">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y108">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z108">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB108">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC108">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="AD108">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>3</v>
+        <v>1.29</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G109">
@@ -18072,68 +18072,68 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N109">
-        <v>3.46</v>
+        <v>1.33</v>
       </c>
       <c r="O109">
-        <v>3.44</v>
+        <v>4.65</v>
       </c>
       <c r="P109">
-        <v>2.03</v>
+        <v>7.55</v>
       </c>
       <c r="Q109">
-        <v>3.9</v>
+        <v>1.86</v>
       </c>
       <c r="R109">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="U109">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="V109">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X109">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z109">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA109">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB109">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC109">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD109">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE109">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG109">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK109">
-        <v>1.29</v>
+        <v>3</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Hatta</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O120">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB120">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC122">
         <v>0</v>
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G123">
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-22 11:15:00</t>
+          <t>2026-08-22 11:00:00</t>
         </is>
       </c>
     </row>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-22 11:30:00</t>
+          <t>2026-08-22 11:00:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G126">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-22 11:30:00</t>
+          <t>2026-08-22 11:15:00</t>
         </is>
       </c>
     </row>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21544,10 +21544,10 @@
         <v>0</v>
       </c>
       <c r="AC130">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD130">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE130">
         <v>0</v>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G131">
@@ -21778,27 +21778,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21870,10 +21870,10 @@
         <v>0</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-22 12:00:00</t>
+          <t>2026-08-22 11:30:00</t>
         </is>
       </c>
     </row>
@@ -21941,27 +21941,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G133">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-22 12:00:00</t>
+          <t>2026-08-22 11:30:00</t>
         </is>
       </c>
     </row>
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G140">
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O141">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="P141">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="AA141">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB141">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC141">
         <v>0</v>
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-22 12:15:00</t>
+          <t>2026-08-22 12:00:00</t>
         </is>
       </c>
     </row>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O142">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P142">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-22 12:30:00</t>
+          <t>2026-08-22 12:00:00</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-22 12:30:00</t>
+          <t>2026-08-22 12:15:00</t>
         </is>
       </c>
     </row>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>3.24</v>
+        <v>2.01</v>
       </c>
       <c r="O144">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB144">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O149">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P149">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G152">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-08-22 12:45:00</t>
+          <t>2026-08-22 12:30:00</t>
         </is>
       </c>
     </row>
@@ -25201,12 +25201,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G153">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-08-22 13:00:00</t>
+          <t>2026-08-22 12:30:00</t>
         </is>
       </c>
     </row>
@@ -25364,12 +25364,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G154">
@@ -25515,7 +25515,7 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>2026-08-22 13:00:00</t>
+          <t>2026-08-22 12:45:00</t>
         </is>
       </c>
     </row>
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O156">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P156">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26184,22 +26184,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G159">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O164">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P164">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27162,7 +27162,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="O166">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P166">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G167">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-08-22 13:10:00</t>
+          <t>2026-08-22 13:00:00</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-22 13:15:00</t>
+          <t>2026-08-22 13:00:00</t>
         </is>
       </c>
     </row>
@@ -27809,27 +27809,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G169">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-22 13:30:00</t>
+          <t>2026-08-22 13:10:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O170">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P170">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB170">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-22 13:30:00</t>
+          <t>2026-08-22 13:15:00</t>
         </is>
       </c>
     </row>
@@ -28140,22 +28140,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G173">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28716,10 +28716,10 @@
         <v>0</v>
       </c>
       <c r="AC174">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD174">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE174">
         <v>0</v>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="O175">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="P175">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB175">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>4.76</v>
+        <v>1.27</v>
       </c>
       <c r="O176">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="P176">
-        <v>1.86</v>
+        <v>7.85</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,16 +29036,16 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB176">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE176">
         <v>0</v>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="O177">
-        <v>3.54</v>
+        <v>7.04</v>
       </c>
       <c r="P177">
-        <v>3.52</v>
+        <v>14.3</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-22 13:45:00</t>
+          <t>2026-08-22 13:30:00</t>
         </is>
       </c>
     </row>
@@ -29276,12 +29276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.65</v>
+        <v>4.76</v>
       </c>
       <c r="O178">
-        <v>3.45</v>
+        <v>3.73</v>
       </c>
       <c r="P178">
-        <v>2.68</v>
+        <v>1.86</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB178">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-22 13:45:00</t>
+          <t>2026-08-22 13:30:00</t>
         </is>
       </c>
     </row>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O179">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P179">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB179">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-22 14:00:00</t>
+          <t>2026-08-22 13:35:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="O180">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="P180">
-        <v>3.23</v>
+        <v>3.52</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29688,10 +29688,10 @@
         <v>0</v>
       </c>
       <c r="AA180">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB180">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-22 14:00:00</t>
+          <t>2026-08-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-22 14:00:00</t>
+          <t>2026-08-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30014,10 +30014,10 @@
         <v>0</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC182">
         <v>0</v>
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC183">
         <v>0</v>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Iraklis 1908 U19</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O187">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="P187">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="O188">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P188">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Iraklis 1908 U19</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G198">
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-08-22 14:15:00</t>
+          <t>2026-08-22 14:00:00</t>
         </is>
       </c>
     </row>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-08-22 14:30:00</t>
+          <t>2026-08-22 14:00:00</t>
         </is>
       </c>
     </row>
@@ -33025,12 +33025,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-08-22 14:30:00</t>
+          <t>2026-08-22 14:00:00</t>
         </is>
       </c>
     </row>
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-22 14:30:00</t>
+          <t>2026-08-22 14:15:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-22 15:00:00</t>
+          <t>2026-08-22 14:30:00</t>
         </is>
       </c>
     </row>
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G204">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-08-22 15:00:00</t>
+          <t>2026-08-22 14:30:00</t>
         </is>
       </c>
     </row>
@@ -33677,27 +33677,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-08-22 15:00:00</t>
+          <t>2026-08-22 14:30:00</t>
         </is>
       </c>
     </row>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O207">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P207">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G210">
@@ -34535,17 +34535,17 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N210">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="O210">
-        <v>5.04</v>
+        <v>4.9</v>
       </c>
       <c r="P210">
-        <v>6.27</v>
+        <v>7.37</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34584,10 +34584,10 @@
         <v>0</v>
       </c>
       <c r="AC210">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD210">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE210">
         <v>0</v>
@@ -34660,22 +34660,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G211">
@@ -34818,12 +34818,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G212">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-08-22 15:15:00</t>
+          <t>2026-08-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -34981,12 +34981,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G213">
@@ -35024,17 +35024,17 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N213">
-        <v>2.97</v>
+        <v>1.46</v>
       </c>
       <c r="O213">
-        <v>3.28</v>
+        <v>5.04</v>
       </c>
       <c r="P213">
-        <v>2.32</v>
+        <v>6.27</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35073,10 +35073,10 @@
         <v>0</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE213">
         <v>0</v>
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-08-22 15:15:00</t>
+          <t>2026-08-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-08-22 15:15:00</t>
+          <t>2026-08-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-08-22 15:30:00</t>
+          <t>2026-08-22 15:15:00</t>
         </is>
       </c>
     </row>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="O216">
-        <v>3.62</v>
+        <v>3.28</v>
       </c>
       <c r="P216">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-08-22 15:30:00</t>
+          <t>2026-08-22 15:15:00</t>
         </is>
       </c>
     </row>
@@ -35633,12 +35633,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G217">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-08-22 15:30:00</t>
+          <t>2026-08-22 15:15:00</t>
         </is>
       </c>
     </row>
@@ -35801,22 +35801,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,22 +35964,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36127,22 +36127,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,22 +36779,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,22 +36942,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,22 +37105,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O226">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P226">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37268,22 +37268,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O227">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P227">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O228">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P228">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-08-22 15:45:00</t>
+          <t>2026-08-22 15:30:00</t>
         </is>
       </c>
     </row>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O229">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P229">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-08-22 15:45:00</t>
+          <t>2026-08-22 15:30:00</t>
         </is>
       </c>
     </row>
@@ -37752,27 +37752,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="O230">
-        <v>3.88</v>
+        <v>3.38</v>
       </c>
       <c r="P230">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-08-22 15:45:00</t>
+          <t>2026-08-22 15:30:00</t>
         </is>
       </c>
     </row>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="O231">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="P231">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>5.42</v>
+        <v>2.2</v>
       </c>
       <c r="O232">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="P232">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38164,10 +38164,10 @@
         <v>0</v>
       </c>
       <c r="AA232">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB232">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC232">
         <v>0</v>
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.72</v>
+        <v>3.58</v>
       </c>
       <c r="O233">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="P233">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38327,10 +38327,10 @@
         <v>0</v>
       </c>
       <c r="AA233">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB233">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC233">
         <v>0</v>
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="O234">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P234">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38490,10 +38490,10 @@
         <v>0</v>
       </c>
       <c r="AA234">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB234">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC234">
         <v>0</v>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38653,10 +38653,10 @@
         <v>0</v>
       </c>
       <c r="AA235">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB235">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC235">
         <v>0</v>
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="O236">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P236">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38816,10 +38816,10 @@
         <v>0</v>
       </c>
       <c r="AA236">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB236">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC236">
         <v>0</v>
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-08-22 16:00:00</t>
+          <t>2026-08-22 15:45:00</t>
         </is>
       </c>
     </row>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="O237">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P237">
-        <v>2.76</v>
+        <v>2.39</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -38979,10 +38979,10 @@
         <v>0</v>
       </c>
       <c r="AA237">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB237">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC237">
         <v>0</v>
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-08-22 16:00:00</t>
+          <t>2026-08-22 15:45:00</t>
         </is>
       </c>
     </row>
@@ -39056,12 +39056,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O238">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P238">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>0</v>
       </c>
       <c r="AA238">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB238">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC238">
         <v>0</v>
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-08-22 16:00:00</t>
+          <t>2026-08-22 15:45:00</t>
         </is>
       </c>
     </row>
@@ -39224,22 +39224,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39387,22 +39387,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39468,10 +39468,10 @@
         <v>0</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC240">
         <v>0</v>
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="O241">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="P241">
-        <v>6.54</v>
+        <v>3.19</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39631,10 +39631,10 @@
         <v>0</v>
       </c>
       <c r="AA241">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB241">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC241">
         <v>0</v>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O242">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P242">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,10 +39794,10 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB242">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC242">
         <v>0</v>
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,22 +40039,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40202,22 +40202,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="O245">
-        <v>5.5</v>
+        <v>4.46</v>
       </c>
       <c r="P245">
-        <v>13.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,22 +40528,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O247">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P247">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="O248">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="P248">
-        <v>4.37</v>
+        <v>13.6</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40854,22 +40854,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.6</v>
+        <v>3.04</v>
       </c>
       <c r="O250">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="P250">
-        <v>4.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="O251">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P251">
-        <v>4.56</v>
+        <v>4.37</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O252">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P252">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-08-22 16:30:00</t>
+          <t>2026-08-22 16:00:00</t>
         </is>
       </c>
     </row>
@@ -41664,12 +41664,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-08-22 16:30:00</t>
+          <t>2026-08-22 16:00:00</t>
         </is>
       </c>
     </row>
@@ -41827,12 +41827,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-08-22 16:30:00</t>
+          <t>2026-08-22 16:00:00</t>
         </is>
       </c>
     </row>
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O256">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="P256">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42153,27 +42153,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-08-22 17:00:00</t>
+          <t>2026-08-22 16:30:00</t>
         </is>
       </c>
     </row>
@@ -42316,27 +42316,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-08-22 17:00:00</t>
+          <t>2026-08-22 16:30:00</t>
         </is>
       </c>
     </row>
@@ -42479,27 +42479,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P259">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-08-22 17:00:00</t>
+          <t>2026-08-22 16:30:00</t>
         </is>
       </c>
     </row>
@@ -42642,12 +42642,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-08-22 17:30:00</t>
+          <t>2026-08-22 17:00:00</t>
         </is>
       </c>
     </row>
@@ -42805,12 +42805,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-08-22 18:00:00</t>
+          <t>2026-08-22 17:00:00</t>
         </is>
       </c>
     </row>
@@ -42968,12 +42968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-08-22 18:15:00</t>
+          <t>2026-08-22 17:00:00</t>
         </is>
       </c>
     </row>
@@ -43131,12 +43131,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-08-22 18:30:00</t>
+          <t>2026-08-22 17:30:00</t>
         </is>
       </c>
     </row>
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O264">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P264">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-08-22 18:30:00</t>
+          <t>2026-08-22 18:00:00</t>
         </is>
       </c>
     </row>
@@ -43457,12 +43457,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-08-22 18:30:00</t>
+          <t>2026-08-22 18:15:00</t>
         </is>
       </c>
     </row>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G266">
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-08-22 19:30:00</t>
+          <t>2026-08-22 18:30:00</t>
         </is>
       </c>
     </row>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-08-22 19:30:00</t>
+          <t>2026-08-22 18:30:00</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-08-22 19:30:00</t>
+          <t>2026-08-22 18:30:00</t>
         </is>
       </c>
     </row>
@@ -44435,12 +44435,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O271">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P271">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-08-22 20:00:00</t>
+          <t>2026-08-22 19:30:00</t>
         </is>
       </c>
     </row>
@@ -44598,12 +44598,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O272">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P272">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-08-22 20:00:00</t>
+          <t>2026-08-22 19:30:00</t>
         </is>
       </c>
     </row>
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O273">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P273">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-08-22 20:00:00</t>
+          <t>2026-08-22 19:30:00</t>
         </is>
       </c>
     </row>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="O274">
-        <v>4.17</v>
+        <v>3.1</v>
       </c>
       <c r="P274">
-        <v>4.99</v>
+        <v>2.4</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45250,12 +45250,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="O276">
-        <v>3.27</v>
+        <v>2.73</v>
       </c>
       <c r="P276">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-08-22 20:30:00</t>
+          <t>2026-08-22 20:00:00</t>
         </is>
       </c>
     </row>
@@ -45413,7 +45413,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="O277">
-        <v>4.85</v>
+        <v>4.17</v>
       </c>
       <c r="P277">
-        <v>7.05</v>
+        <v>4.99</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-08-22 20:30:00</t>
+          <t>2026-08-22 20:00:00</t>
         </is>
       </c>
     </row>
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O278">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P278">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-08-22 20:30:00</t>
+          <t>2026-08-22 20:00:00</t>
         </is>
       </c>
     </row>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="O281">
-        <v>5.09</v>
+        <v>4.4</v>
       </c>
       <c r="P281">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O282">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P282">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O283">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P283">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.56</v>
+        <v>1.5</v>
       </c>
       <c r="O284">
-        <v>3.73</v>
+        <v>5.09</v>
       </c>
       <c r="P284">
-        <v>2.69</v>
+        <v>6.02</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O285">
-        <v>3.79</v>
+        <v>4.05</v>
       </c>
       <c r="P285">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>3.52</v>
+        <v>2.44</v>
       </c>
       <c r="O286">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="P286">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-08-22 21:00:00</t>
+          <t>2026-08-22 20:30:00</t>
         </is>
       </c>
     </row>
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.45</v>
+        <v>1.99</v>
       </c>
       <c r="O288">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="P288">
-        <v>5.84</v>
+        <v>3.79</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-08-22 21:00:00</t>
+          <t>2026-08-22 20:30:00</t>
         </is>
       </c>
     </row>
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-08-22 21:00:00</t>
+          <t>2026-08-22 20:30:00</t>
         </is>
       </c>
     </row>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G290">
@@ -47700,22 +47700,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47863,22 +47863,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G292">
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G298">
@@ -48999,27 +48999,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O299">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P299">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-08-22 21:30:00</t>
+          <t>2026-08-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,27 +49162,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O300">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P300">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-08-22 21:30:00</t>
+          <t>2026-08-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O301">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P301">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-08-22 21:30:00</t>
+          <t>2026-08-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -49488,12 +49488,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.31</v>
+        <v>1.81</v>
       </c>
       <c r="O302">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="P302">
-        <v>2.51</v>
+        <v>4.58</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-08-22 21:45:00</t>
+          <t>2026-08-22 21:30:00</t>
         </is>
       </c>
     </row>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.76</v>
+        <v>2.76</v>
       </c>
       <c r="O303">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P303">
-        <v>3.97</v>
+        <v>2.53</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49737,10 +49737,10 @@
         <v>0</v>
       </c>
       <c r="AA303">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB303">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC303">
         <v>0</v>
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-08-22 22:00:00</t>
+          <t>2026-08-22 21:30:00</t>
         </is>
       </c>
     </row>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-08-22 22:00:00</t>
+          <t>2026-08-22 21:30:00</t>
         </is>
       </c>
     </row>
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-08-22 22:00:00</t>
+          <t>2026-08-22 21:45:00</t>
         </is>
       </c>
     </row>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="O306">
-        <v>4.55</v>
+        <v>3.58</v>
       </c>
       <c r="P306">
-        <v>5.99</v>
+        <v>3.97</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50226,10 +50226,10 @@
         <v>0</v>
       </c>
       <c r="AA306">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB306">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC306">
         <v>0</v>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-08-22 22:30:00</t>
+          <t>2026-08-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -50303,7 +50303,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O307">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P307">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-08-22 23:00:00</t>
+          <t>2026-08-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -50466,12 +50466,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O308">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="P308">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-08-22 23:30:00</t>
+          <t>2026-08-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -50629,7 +50629,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="O309">
-        <v>4.01</v>
+        <v>4.55</v>
       </c>
       <c r="P309">
-        <v>3.44</v>
+        <v>5.99</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-08-22 23:30:00</t>
+          <t>2026-08-22 22:30:00</t>
         </is>
       </c>
     </row>
@@ -50792,156 +50792,645 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="G310">
+        <v>0</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>0</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N310">
+        <v>2.59</v>
+      </c>
+      <c r="O310">
+        <v>3.18</v>
+      </c>
+      <c r="P310">
+        <v>2.44</v>
+      </c>
+      <c r="Q310">
+        <v>0</v>
+      </c>
+      <c r="R310">
+        <v>0</v>
+      </c>
+      <c r="S310">
+        <v>0</v>
+      </c>
+      <c r="T310">
+        <v>0</v>
+      </c>
+      <c r="U310">
+        <v>0</v>
+      </c>
+      <c r="V310">
+        <v>0</v>
+      </c>
+      <c r="W310">
+        <v>0</v>
+      </c>
+      <c r="X310">
+        <v>0</v>
+      </c>
+      <c r="Y310">
+        <v>0</v>
+      </c>
+      <c r="Z310">
+        <v>0</v>
+      </c>
+      <c r="AA310">
+        <v>0</v>
+      </c>
+      <c r="AB310">
+        <v>0</v>
+      </c>
+      <c r="AC310">
+        <v>0</v>
+      </c>
+      <c r="AD310">
+        <v>0</v>
+      </c>
+      <c r="AE310">
+        <v>0</v>
+      </c>
+      <c r="AF310">
+        <v>0</v>
+      </c>
+      <c r="AG310">
+        <v>0</v>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ310">
+        <v>0</v>
+      </c>
+      <c r="AK310">
+        <v>0</v>
+      </c>
+      <c r="AL310">
+        <v>0</v>
+      </c>
+      <c r="AM310">
+        <v>-1</v>
+      </c>
+      <c r="AN310">
+        <v>-1</v>
+      </c>
+      <c r="AO310">
+        <v>-1</v>
+      </c>
+      <c r="AP310">
+        <v>-1</v>
+      </c>
+      <c r="AQ310">
+        <v>0</v>
+      </c>
+      <c r="AR310">
+        <v>0</v>
+      </c>
+      <c r="AS310">
+        <v>0</v>
+      </c>
+      <c r="AT310">
+        <v>0</v>
+      </c>
+      <c r="AU310" t="inlineStr">
+        <is>
+          <t>2026-08-22 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
+      <c r="C311" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
+      <c r="D311" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G311">
+        <v>0</v>
+      </c>
+      <c r="H311">
+        <v>0</v>
+      </c>
+      <c r="I311">
+        <v>0</v>
+      </c>
+      <c r="J311">
+        <v>0</v>
+      </c>
+      <c r="K311">
+        <v>0</v>
+      </c>
+      <c r="L311">
+        <v>0</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N311">
+        <v>1.48</v>
+      </c>
+      <c r="O311">
+        <v>4.98</v>
+      </c>
+      <c r="P311">
+        <v>6.42</v>
+      </c>
+      <c r="Q311">
+        <v>0</v>
+      </c>
+      <c r="R311">
+        <v>0</v>
+      </c>
+      <c r="S311">
+        <v>0</v>
+      </c>
+      <c r="T311">
+        <v>0</v>
+      </c>
+      <c r="U311">
+        <v>0</v>
+      </c>
+      <c r="V311">
+        <v>0</v>
+      </c>
+      <c r="W311">
+        <v>0</v>
+      </c>
+      <c r="X311">
+        <v>0</v>
+      </c>
+      <c r="Y311">
+        <v>0</v>
+      </c>
+      <c r="Z311">
+        <v>0</v>
+      </c>
+      <c r="AA311">
+        <v>0</v>
+      </c>
+      <c r="AB311">
+        <v>0</v>
+      </c>
+      <c r="AC311">
+        <v>0</v>
+      </c>
+      <c r="AD311">
+        <v>0</v>
+      </c>
+      <c r="AE311">
+        <v>0</v>
+      </c>
+      <c r="AF311">
+        <v>0</v>
+      </c>
+      <c r="AG311">
+        <v>0</v>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ311">
+        <v>0</v>
+      </c>
+      <c r="AK311">
+        <v>0</v>
+      </c>
+      <c r="AL311">
+        <v>0</v>
+      </c>
+      <c r="AM311">
+        <v>-1</v>
+      </c>
+      <c r="AN311">
+        <v>-1</v>
+      </c>
+      <c r="AO311">
+        <v>-1</v>
+      </c>
+      <c r="AP311">
+        <v>-1</v>
+      </c>
+      <c r="AQ311">
+        <v>0</v>
+      </c>
+      <c r="AR311">
+        <v>0</v>
+      </c>
+      <c r="AS311">
+        <v>0</v>
+      </c>
+      <c r="AT311">
+        <v>0</v>
+      </c>
+      <c r="AU311" t="inlineStr">
+        <is>
+          <t>2026-08-22 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="G312">
+        <v>0</v>
+      </c>
+      <c r="H312">
+        <v>0</v>
+      </c>
+      <c r="I312">
+        <v>0</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>0</v>
+      </c>
+      <c r="L312">
+        <v>0</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N312">
+        <v>2.04</v>
+      </c>
+      <c r="O312">
+        <v>4.01</v>
+      </c>
+      <c r="P312">
+        <v>3.44</v>
+      </c>
+      <c r="Q312">
+        <v>0</v>
+      </c>
+      <c r="R312">
+        <v>0</v>
+      </c>
+      <c r="S312">
+        <v>0</v>
+      </c>
+      <c r="T312">
+        <v>0</v>
+      </c>
+      <c r="U312">
+        <v>0</v>
+      </c>
+      <c r="V312">
+        <v>0</v>
+      </c>
+      <c r="W312">
+        <v>0</v>
+      </c>
+      <c r="X312">
+        <v>0</v>
+      </c>
+      <c r="Y312">
+        <v>0</v>
+      </c>
+      <c r="Z312">
+        <v>0</v>
+      </c>
+      <c r="AA312">
+        <v>0</v>
+      </c>
+      <c r="AB312">
+        <v>0</v>
+      </c>
+      <c r="AC312">
+        <v>0</v>
+      </c>
+      <c r="AD312">
+        <v>0</v>
+      </c>
+      <c r="AE312">
+        <v>0</v>
+      </c>
+      <c r="AF312">
+        <v>0</v>
+      </c>
+      <c r="AG312">
+        <v>0</v>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ312">
+        <v>0</v>
+      </c>
+      <c r="AK312">
+        <v>0</v>
+      </c>
+      <c r="AL312">
+        <v>0</v>
+      </c>
+      <c r="AM312">
+        <v>-1</v>
+      </c>
+      <c r="AN312">
+        <v>-1</v>
+      </c>
+      <c r="AO312">
+        <v>-1</v>
+      </c>
+      <c r="AP312">
+        <v>-1</v>
+      </c>
+      <c r="AQ312">
+        <v>0</v>
+      </c>
+      <c r="AR312">
+        <v>0</v>
+      </c>
+      <c r="AS312">
+        <v>0</v>
+      </c>
+      <c r="AT312">
+        <v>0</v>
+      </c>
+      <c r="AU312" t="inlineStr">
+        <is>
+          <t>2026-08-22 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
+      <c r="F313" t="inlineStr">
         <is>
           <t>Colorado Rapids</t>
         </is>
       </c>
-      <c r="G310">
-        <v>0</v>
-      </c>
-      <c r="H310">
-        <v>0</v>
-      </c>
-      <c r="I310">
-        <v>0</v>
-      </c>
-      <c r="J310">
-        <v>0</v>
-      </c>
-      <c r="K310">
-        <v>0</v>
-      </c>
-      <c r="L310">
-        <v>0</v>
-      </c>
-      <c r="M310" t="inlineStr">
+      <c r="G313">
+        <v>0</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
+      <c r="L313">
+        <v>0</v>
+      </c>
+      <c r="M313" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N310">
+      <c r="N313">
         <v>2.03</v>
       </c>
-      <c r="O310">
+      <c r="O313">
         <v>3.99</v>
       </c>
-      <c r="P310">
+      <c r="P313">
         <v>3.47</v>
       </c>
-      <c r="Q310">
-        <v>0</v>
-      </c>
-      <c r="R310">
-        <v>0</v>
-      </c>
-      <c r="S310">
-        <v>0</v>
-      </c>
-      <c r="T310">
-        <v>0</v>
-      </c>
-      <c r="U310">
-        <v>0</v>
-      </c>
-      <c r="V310">
-        <v>0</v>
-      </c>
-      <c r="W310">
-        <v>0</v>
-      </c>
-      <c r="X310">
-        <v>0</v>
-      </c>
-      <c r="Y310">
-        <v>0</v>
-      </c>
-      <c r="Z310">
-        <v>0</v>
-      </c>
-      <c r="AA310">
-        <v>0</v>
-      </c>
-      <c r="AB310">
-        <v>0</v>
-      </c>
-      <c r="AC310">
-        <v>0</v>
-      </c>
-      <c r="AD310">
-        <v>0</v>
-      </c>
-      <c r="AE310">
-        <v>0</v>
-      </c>
-      <c r="AF310">
-        <v>0</v>
-      </c>
-      <c r="AG310">
-        <v>0</v>
-      </c>
-      <c r="AH310" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI310" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ310">
-        <v>0</v>
-      </c>
-      <c r="AK310">
-        <v>0</v>
-      </c>
-      <c r="AL310">
-        <v>0</v>
-      </c>
-      <c r="AM310">
-        <v>-1</v>
-      </c>
-      <c r="AN310">
-        <v>-1</v>
-      </c>
-      <c r="AO310">
-        <v>-1</v>
-      </c>
-      <c r="AP310">
-        <v>-1</v>
-      </c>
-      <c r="AQ310">
-        <v>0</v>
-      </c>
-      <c r="AR310">
-        <v>0</v>
-      </c>
-      <c r="AS310">
-        <v>0</v>
-      </c>
-      <c r="AT310">
-        <v>0</v>
-      </c>
-      <c r="AU310" t="inlineStr">
+      <c r="Q313">
+        <v>0</v>
+      </c>
+      <c r="R313">
+        <v>0</v>
+      </c>
+      <c r="S313">
+        <v>0</v>
+      </c>
+      <c r="T313">
+        <v>0</v>
+      </c>
+      <c r="U313">
+        <v>0</v>
+      </c>
+      <c r="V313">
+        <v>0</v>
+      </c>
+      <c r="W313">
+        <v>0</v>
+      </c>
+      <c r="X313">
+        <v>0</v>
+      </c>
+      <c r="Y313">
+        <v>0</v>
+      </c>
+      <c r="Z313">
+        <v>0</v>
+      </c>
+      <c r="AA313">
+        <v>0</v>
+      </c>
+      <c r="AB313">
+        <v>0</v>
+      </c>
+      <c r="AC313">
+        <v>0</v>
+      </c>
+      <c r="AD313">
+        <v>0</v>
+      </c>
+      <c r="AE313">
+        <v>0</v>
+      </c>
+      <c r="AF313">
+        <v>0</v>
+      </c>
+      <c r="AG313">
+        <v>0</v>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ313">
+        <v>0</v>
+      </c>
+      <c r="AK313">
+        <v>0</v>
+      </c>
+      <c r="AL313">
+        <v>0</v>
+      </c>
+      <c r="AM313">
+        <v>-1</v>
+      </c>
+      <c r="AN313">
+        <v>-1</v>
+      </c>
+      <c r="AO313">
+        <v>-1</v>
+      </c>
+      <c r="AP313">
+        <v>-1</v>
+      </c>
+      <c r="AQ313">
+        <v>0</v>
+      </c>
+      <c r="AR313">
+        <v>0</v>
+      </c>
+      <c r="AS313">
+        <v>0</v>
+      </c>
+      <c r="AT313">
+        <v>0</v>
+      </c>
+      <c r="AU313" t="inlineStr">
         <is>
           <t>2026-08-22 23:30:00</t>
         </is>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="O117">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>5.86</v>
+        <v>2.81</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="O118">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="P118">
-        <v>2.81</v>
+        <v>5.86</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>3.12</v>
+        <v>1.55</v>
       </c>
       <c r="O276">
-        <v>2.73</v>
+        <v>4.17</v>
       </c>
       <c r="P276">
-        <v>2.42</v>
+        <v>4.99</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.55</v>
+        <v>3.12</v>
       </c>
       <c r="O277">
-        <v>4.17</v>
+        <v>2.73</v>
       </c>
       <c r="P277">
-        <v>4.99</v>
+        <v>2.42</v>
       </c>
       <c r="Q277">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P87">
-        <v>4.52</v>
+        <v>3.81</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB87">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="O88">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P88">
-        <v>3.81</v>
+        <v>3.3</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,14 +14816,14 @@
         </is>
       </c>
       <c r="N89">
+        <v>3.65</v>
+      </c>
+      <c r="O89">
+        <v>3.5</v>
+      </c>
+      <c r="P89">
         <v>1.95</v>
       </c>
-      <c r="O89">
-        <v>3.4</v>
-      </c>
-      <c r="P89">
-        <v>3.75</v>
-      </c>
       <c r="Q89">
         <v>0</v>
       </c>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="O90">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P90">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.65</v>
+        <v>1.7</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P92">
-        <v>1.95</v>
+        <v>5</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="O93">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="P93">
-        <v>2.74</v>
+        <v>3.37</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="O101">
-        <v>3.72</v>
+        <v>3.54</v>
       </c>
       <c r="P101">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB101">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O102">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="P102">
-        <v>3.54</v>
+        <v>3.96</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AB102">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O103">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="P103">
-        <v>3.96</v>
+        <v>4.75</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB103">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="O112">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="O113">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P113">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O114">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="P114">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O115">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P115">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="O116">
-        <v>3.54</v>
+        <v>3.14</v>
       </c>
       <c r="P116">
-        <v>2.37</v>
+        <v>3.16</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P117">
-        <v>2.81</v>
+        <v>2.37</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC141">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Iraklis 1908 U19</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.19</v>
+        <v>3.98</v>
       </c>
       <c r="O190">
-        <v>6.05</v>
+        <v>3.04</v>
       </c>
       <c r="P190">
-        <v>16</v>
+        <v>2.05</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>3.98</v>
+        <v>1.19</v>
       </c>
       <c r="O191">
-        <v>3.04</v>
+        <v>6.05</v>
       </c>
       <c r="P191">
-        <v>2.05</v>
+        <v>16</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q217">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -31415,7 +31415,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Iraklis 1908 U19</t>
         </is>
       </c>
       <c r="G191">

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P16">
-        <v>2.69</v>
+        <v>2.07</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="O40">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="O41">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -31415,7 +31415,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Iraklis 1908 U19</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G191">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G299">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G301">

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G47">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34246,10 +34246,10 @@
         <v>0</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA208">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36528,10 +36528,10 @@
         <v>0</v>
       </c>
       <c r="Y222">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z222">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA222">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36691,10 +36691,10 @@
         <v>0</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA223">
         <v>0</v>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36854,10 +36854,10 @@
         <v>0</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA224">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37017,10 +37017,10 @@
         <v>0</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA225">
         <v>0</v>
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37180,10 +37180,10 @@
         <v>0</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA226">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40603,10 +40603,10 @@
         <v>0</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA247">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q308">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU313"/>
+  <dimension ref="A1:AU314"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G135">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G163">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O165">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="P165">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="O166">
-        <v>3.1</v>
+        <v>5.35</v>
       </c>
       <c r="P166">
-        <v>3.19</v>
+        <v>10.1</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O168">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P168">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-22 13:10:00</t>
+          <t>2026-08-22 13:00:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G170">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-22 13:15:00</t>
+          <t>2026-08-22 13:10:00</t>
         </is>
       </c>
     </row>
@@ -28135,27 +28135,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-22 13:30:00</t>
+          <t>2026-08-22 13:15:00</t>
         </is>
       </c>
     </row>
@@ -28303,22 +28303,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O172">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P172">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB172">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O176">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P176">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29042,10 +29042,10 @@
         <v>0</v>
       </c>
       <c r="AC176">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD176">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE176">
         <v>0</v>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O177">
-        <v>7.04</v>
+        <v>5.4</v>
       </c>
       <c r="P177">
-        <v>14.3</v>
+        <v>7.85</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,16 +29199,16 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB177">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>4.76</v>
+        <v>1.24</v>
       </c>
       <c r="O178">
-        <v>3.73</v>
+        <v>7.04</v>
       </c>
       <c r="P178">
-        <v>1.86</v>
+        <v>14.3</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
+        <v>1.61</v>
+      </c>
+      <c r="AB178">
         <v>2.15</v>
-      </c>
-      <c r="AB178">
-        <v>1.62</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-22 13:35:00</t>
+          <t>2026-08-22 13:30:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O180">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P180">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-22 13:45:00</t>
+          <t>2026-08-22 13:35:00</t>
         </is>
       </c>
     </row>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O181">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="P181">
-        <v>2.68</v>
+        <v>3.52</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB181">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29928,12 +29928,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="O182">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="P182">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30014,10 +30014,10 @@
         <v>0</v>
       </c>
       <c r="AA182">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB182">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AC182">
         <v>0</v>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2026-08-22 14:00:00</t>
+          <t>2026-08-22 13:45:00</t>
         </is>
       </c>
     </row>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="O183">
-        <v>3.38</v>
+        <v>3.13</v>
       </c>
       <c r="P183">
-        <v>3.23</v>
+        <v>3.85</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AB183">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="AC183">
         <v>0</v>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30585,22 +30585,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O186">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P186">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="O190">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P190">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.19</v>
+        <v>3.98</v>
       </c>
       <c r="O191">
-        <v>6.05</v>
+        <v>3.04</v>
       </c>
       <c r="P191">
-        <v>16</v>
+        <v>2.05</v>
       </c>
       <c r="Q191">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S191">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T191">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U191">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V191">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W191">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y191">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z191">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="AA191">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB191">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC191">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD191">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE191">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF191">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG191">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK191">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S192">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T192">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U192">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V192">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W192">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X192">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC192">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE192">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG192">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK192">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O194">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P194">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB194">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G199">
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-22 14:15:00</t>
+          <t>2026-08-22 14:00:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-22 14:30:00</t>
+          <t>2026-08-22 14:15:00</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O204">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="P204">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33682,7 +33682,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-08-22 15:00:00</t>
+          <t>2026-08-22 14:30:00</t>
         </is>
       </c>
     </row>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,22 +34171,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O208">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P208">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34246,10 +34246,10 @@
         <v>0</v>
       </c>
       <c r="Y208">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z208">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA208">
         <v>0</v>
@@ -34334,22 +34334,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34409,10 +34409,10 @@
         <v>0</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA209">
         <v>0</v>
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O210">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P210">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34660,22 +34660,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34823,22 +34823,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G213">
@@ -35024,17 +35024,17 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N213">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O213">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="P213">
-        <v>6.27</v>
+        <v>0</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35073,10 +35073,10 @@
         <v>0</v>
       </c>
       <c r="AC213">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD213">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE213">
         <v>0</v>
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G214">
@@ -35187,17 +35187,17 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35236,10 +35236,10 @@
         <v>0</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE214">
         <v>0</v>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-08-22 15:15:00</t>
+          <t>2026-08-22 15:00:00</t>
         </is>
       </c>
     </row>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.97</v>
+        <v>1.41</v>
       </c>
       <c r="O216">
-        <v>3.28</v>
+        <v>4.65</v>
       </c>
       <c r="P216">
-        <v>2.32</v>
+        <v>5.73</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.26</v>
+        <v>2.97</v>
       </c>
       <c r="O217">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="P217">
-        <v>11</v>
+        <v>2.32</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35796,12 +35796,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-08-22 15:30:00</t>
+          <t>2026-08-22 15:15:00</t>
         </is>
       </c>
     </row>
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O219">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P219">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36290,22 +36290,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O222">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P222">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36528,10 +36528,10 @@
         <v>0</v>
       </c>
       <c r="Y222">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z222">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA222">
         <v>0</v>
@@ -37268,22 +37268,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37343,10 +37343,10 @@
         <v>0</v>
       </c>
       <c r="Y227">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z227">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O229">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P229">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37757,22 +37757,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O230">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="P230">
-        <v>2.13</v>
+        <v>3.22</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37915,27 +37915,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O231">
-        <v>3.74</v>
+        <v>3.38</v>
       </c>
       <c r="P231">
-        <v>2.82</v>
+        <v>2.13</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-08-22 15:45:00</t>
+          <t>2026-08-22 15:30:00</t>
         </is>
       </c>
     </row>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="O232">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P232">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="O233">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P233">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.65</v>
+        <v>3.58</v>
       </c>
       <c r="O234">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="P234">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>5.42</v>
+        <v>2.65</v>
       </c>
       <c r="O235">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="P235">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38653,10 +38653,10 @@
         <v>0</v>
       </c>
       <c r="AA235">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB235">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.72</v>
+        <v>5.42</v>
       </c>
       <c r="O236">
-        <v>3.2</v>
+        <v>3.77</v>
       </c>
       <c r="P236">
-        <v>2.99</v>
+        <v>1.77</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38816,10 +38816,10 @@
         <v>0</v>
       </c>
       <c r="AA236">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB236">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC236">
         <v>0</v>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="O237">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P237">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -38979,10 +38979,10 @@
         <v>0</v>
       </c>
       <c r="AA237">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AB237">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>0</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC238">
         <v>0</v>
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O239">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P239">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB239">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-08-22 16:00:00</t>
+          <t>2026-08-22 15:45:00</t>
         </is>
       </c>
     </row>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="O240">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P240">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39468,10 +39468,10 @@
         <v>0</v>
       </c>
       <c r="AA240">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB240">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC240">
         <v>0</v>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.22</v>
+        <v>2.59</v>
       </c>
       <c r="O241">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P241">
-        <v>3.19</v>
+        <v>2.76</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39631,10 +39631,10 @@
         <v>0</v>
       </c>
       <c r="AA241">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB241">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC241">
         <v>0</v>
@@ -39713,22 +39713,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,10 +39794,10 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC242">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,22 +40039,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O244">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P244">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40202,22 +40202,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O245">
-        <v>4.46</v>
+        <v>3.95</v>
       </c>
       <c r="P245">
-        <v>7.5</v>
+        <v>6.54</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB245">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O247">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P247">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40603,10 +40603,10 @@
         <v>0</v>
       </c>
       <c r="Y247">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z247">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA247">
         <v>0</v>
@@ -40691,22 +40691,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.23</v>
+        <v>2.15</v>
       </c>
       <c r="O248">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="P248">
-        <v>13.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40766,10 +40766,10 @@
         <v>0</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA248">
         <v>0</v>
@@ -40854,22 +40854,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41017,22 +41017,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O250">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P250">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.81</v>
+        <v>3.04</v>
       </c>
       <c r="O251">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P251">
-        <v>4.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O253">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P253">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O254">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="P254">
-        <v>4.56</v>
+        <v>4.75</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="O255">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P255">
-        <v>3.15</v>
+        <v>4.56</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -41990,12 +41990,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-08-22 16:30:00</t>
+          <t>2026-08-22 16:00:00</t>
         </is>
       </c>
     </row>
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O259">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="P259">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42642,27 +42642,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-08-22 17:00:00</t>
+          <t>2026-08-22 16:30:00</t>
         </is>
       </c>
     </row>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G261">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G262">
@@ -43131,12 +43131,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-08-22 17:30:00</t>
+          <t>2026-08-22 17:00:00</t>
         </is>
       </c>
     </row>
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-08-22 18:00:00</t>
+          <t>2026-08-22 17:30:00</t>
         </is>
       </c>
     </row>
@@ -43457,12 +43457,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-08-22 18:15:00</t>
+          <t>2026-08-22 18:00:00</t>
         </is>
       </c>
     </row>
@@ -43620,12 +43620,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-08-22 18:30:00</t>
+          <t>2026-08-22 18:15:00</t>
         </is>
       </c>
     </row>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O267">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P267">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G269">
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G270">
@@ -44435,12 +44435,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-08-22 19:30:00</t>
+          <t>2026-08-22 18:30:00</t>
         </is>
       </c>
     </row>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G273">
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-08-22 20:00:00</t>
+          <t>2026-08-22 19:30:00</t>
         </is>
       </c>
     </row>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="O275">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P275">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="O276">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="P276">
-        <v>4.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>3.12</v>
+        <v>1.55</v>
       </c>
       <c r="O277">
-        <v>2.73</v>
+        <v>4.17</v>
       </c>
       <c r="P277">
-        <v>2.42</v>
+        <v>4.99</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45739,12 +45739,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O279">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P279">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-08-22 20:30:00</t>
+          <t>2026-08-22 20:00:00</t>
         </is>
       </c>
     </row>
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>1.33</v>
+        <v>2.96</v>
       </c>
       <c r="O280">
-        <v>4.85</v>
+        <v>3.27</v>
       </c>
       <c r="P280">
-        <v>7.05</v>
+        <v>2.51</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="O281">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="P281">
-        <v>6.11</v>
+        <v>7.05</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O283">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P283">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O284">
-        <v>5.09</v>
+        <v>3.76</v>
       </c>
       <c r="P284">
-        <v>6.02</v>
+        <v>3.57</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="O285">
-        <v>4.05</v>
+        <v>5.09</v>
       </c>
       <c r="P285">
-        <v>3.58</v>
+        <v>6.02</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="O286">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P286">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="O287">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="P287">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.99</v>
+        <v>2.56</v>
       </c>
       <c r="O288">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="P288">
-        <v>3.79</v>
+        <v>2.69</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-08-22 21:00:00</t>
+          <t>2026-08-22 20:30:00</t>
         </is>
       </c>
     </row>
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O291">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P291">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -48026,7 +48026,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,22 +48189,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G299">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G301">
@@ -49488,27 +49488,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O302">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P302">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-08-22 21:30:00</t>
+          <t>2026-08-22 21:00:00</t>
         </is>
       </c>
     </row>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.76</v>
+        <v>1.81</v>
       </c>
       <c r="O303">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P303">
-        <v>2.53</v>
+        <v>4.58</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="O304">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P304">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="O305">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P305">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-08-22 21:45:00</t>
+          <t>2026-08-22 21:30:00</t>
         </is>
       </c>
     </row>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="O306">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P306">
-        <v>3.97</v>
+        <v>2.51</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50226,10 +50226,10 @@
         <v>0</v>
       </c>
       <c r="AA306">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB306">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC306">
         <v>0</v>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-08-22 22:00:00</t>
+          <t>2026-08-22 21:45:00</t>
         </is>
       </c>
     </row>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -50389,10 +50389,10 @@
         <v>0</v>
       </c>
       <c r="AA307">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB307">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC307">
         <v>0</v>
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O308">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P308">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50629,12 +50629,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="O309">
-        <v>4.55</v>
+        <v>2.7</v>
       </c>
       <c r="P309">
-        <v>5.99</v>
+        <v>2.88</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-08-22 22:30:00</t>
+          <t>2026-08-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -50792,12 +50792,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.59</v>
+        <v>1.55</v>
       </c>
       <c r="O310">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P310">
-        <v>2.44</v>
+        <v>5.99</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-08-22 23:00:00</t>
+          <t>2026-08-22 22:30:00</t>
         </is>
       </c>
     </row>
@@ -50955,12 +50955,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.48</v>
+        <v>2.59</v>
       </c>
       <c r="O311">
-        <v>4.98</v>
+        <v>3.18</v>
       </c>
       <c r="P311">
-        <v>6.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q311">
         <v>0</v>
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-08-22 23:30:00</t>
+          <t>2026-08-22 23:00:00</t>
         </is>
       </c>
     </row>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O312">
-        <v>4.01</v>
+        <v>4.98</v>
       </c>
       <c r="P312">
-        <v>3.44</v>
+        <v>6.42</v>
       </c>
       <c r="Q312">
         <v>0</v>
@@ -51296,141 +51296,304 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="G313">
+        <v>0</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
+      <c r="L313">
+        <v>0</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N313">
+        <v>2.04</v>
+      </c>
+      <c r="O313">
+        <v>4.01</v>
+      </c>
+      <c r="P313">
+        <v>3.44</v>
+      </c>
+      <c r="Q313">
+        <v>0</v>
+      </c>
+      <c r="R313">
+        <v>0</v>
+      </c>
+      <c r="S313">
+        <v>0</v>
+      </c>
+      <c r="T313">
+        <v>0</v>
+      </c>
+      <c r="U313">
+        <v>0</v>
+      </c>
+      <c r="V313">
+        <v>0</v>
+      </c>
+      <c r="W313">
+        <v>0</v>
+      </c>
+      <c r="X313">
+        <v>0</v>
+      </c>
+      <c r="Y313">
+        <v>0</v>
+      </c>
+      <c r="Z313">
+        <v>0</v>
+      </c>
+      <c r="AA313">
+        <v>0</v>
+      </c>
+      <c r="AB313">
+        <v>0</v>
+      </c>
+      <c r="AC313">
+        <v>0</v>
+      </c>
+      <c r="AD313">
+        <v>0</v>
+      </c>
+      <c r="AE313">
+        <v>0</v>
+      </c>
+      <c r="AF313">
+        <v>0</v>
+      </c>
+      <c r="AG313">
+        <v>0</v>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ313">
+        <v>0</v>
+      </c>
+      <c r="AK313">
+        <v>0</v>
+      </c>
+      <c r="AL313">
+        <v>0</v>
+      </c>
+      <c r="AM313">
+        <v>-1</v>
+      </c>
+      <c r="AN313">
+        <v>-1</v>
+      </c>
+      <c r="AO313">
+        <v>-1</v>
+      </c>
+      <c r="AP313">
+        <v>-1</v>
+      </c>
+      <c r="AQ313">
+        <v>0</v>
+      </c>
+      <c r="AR313">
+        <v>0</v>
+      </c>
+      <c r="AS313">
+        <v>0</v>
+      </c>
+      <c r="AT313">
+        <v>0</v>
+      </c>
+      <c r="AU313" t="inlineStr">
+        <is>
+          <t>2026-08-22 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr">
+      <c r="F314" t="inlineStr">
         <is>
           <t>Colorado Rapids</t>
         </is>
       </c>
-      <c r="G313">
-        <v>0</v>
-      </c>
-      <c r="H313">
-        <v>0</v>
-      </c>
-      <c r="I313">
-        <v>0</v>
-      </c>
-      <c r="J313">
-        <v>0</v>
-      </c>
-      <c r="K313">
-        <v>0</v>
-      </c>
-      <c r="L313">
-        <v>0</v>
-      </c>
-      <c r="M313" t="inlineStr">
+      <c r="G314">
+        <v>0</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
+      <c r="L314">
+        <v>0</v>
+      </c>
+      <c r="M314" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N313">
+      <c r="N314">
         <v>2.03</v>
       </c>
-      <c r="O313">
+      <c r="O314">
         <v>3.99</v>
       </c>
-      <c r="P313">
+      <c r="P314">
         <v>3.47</v>
       </c>
-      <c r="Q313">
-        <v>0</v>
-      </c>
-      <c r="R313">
-        <v>0</v>
-      </c>
-      <c r="S313">
-        <v>0</v>
-      </c>
-      <c r="T313">
-        <v>0</v>
-      </c>
-      <c r="U313">
-        <v>0</v>
-      </c>
-      <c r="V313">
-        <v>0</v>
-      </c>
-      <c r="W313">
-        <v>0</v>
-      </c>
-      <c r="X313">
-        <v>0</v>
-      </c>
-      <c r="Y313">
-        <v>0</v>
-      </c>
-      <c r="Z313">
-        <v>0</v>
-      </c>
-      <c r="AA313">
-        <v>0</v>
-      </c>
-      <c r="AB313">
-        <v>0</v>
-      </c>
-      <c r="AC313">
-        <v>0</v>
-      </c>
-      <c r="AD313">
-        <v>0</v>
-      </c>
-      <c r="AE313">
-        <v>0</v>
-      </c>
-      <c r="AF313">
-        <v>0</v>
-      </c>
-      <c r="AG313">
-        <v>0</v>
-      </c>
-      <c r="AH313" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI313" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ313">
-        <v>0</v>
-      </c>
-      <c r="AK313">
-        <v>0</v>
-      </c>
-      <c r="AL313">
-        <v>0</v>
-      </c>
-      <c r="AM313">
-        <v>-1</v>
-      </c>
-      <c r="AN313">
-        <v>-1</v>
-      </c>
-      <c r="AO313">
-        <v>-1</v>
-      </c>
-      <c r="AP313">
-        <v>-1</v>
-      </c>
-      <c r="AQ313">
-        <v>0</v>
-      </c>
-      <c r="AR313">
-        <v>0</v>
-      </c>
-      <c r="AS313">
-        <v>0</v>
-      </c>
-      <c r="AT313">
-        <v>0</v>
-      </c>
-      <c r="AU313" t="inlineStr">
+      <c r="Q314">
+        <v>0</v>
+      </c>
+      <c r="R314">
+        <v>0</v>
+      </c>
+      <c r="S314">
+        <v>0</v>
+      </c>
+      <c r="T314">
+        <v>0</v>
+      </c>
+      <c r="U314">
+        <v>0</v>
+      </c>
+      <c r="V314">
+        <v>0</v>
+      </c>
+      <c r="W314">
+        <v>0</v>
+      </c>
+      <c r="X314">
+        <v>0</v>
+      </c>
+      <c r="Y314">
+        <v>0</v>
+      </c>
+      <c r="Z314">
+        <v>0</v>
+      </c>
+      <c r="AA314">
+        <v>0</v>
+      </c>
+      <c r="AB314">
+        <v>0</v>
+      </c>
+      <c r="AC314">
+        <v>0</v>
+      </c>
+      <c r="AD314">
+        <v>0</v>
+      </c>
+      <c r="AE314">
+        <v>0</v>
+      </c>
+      <c r="AF314">
+        <v>0</v>
+      </c>
+      <c r="AG314">
+        <v>0</v>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ314">
+        <v>0</v>
+      </c>
+      <c r="AK314">
+        <v>0</v>
+      </c>
+      <c r="AL314">
+        <v>0</v>
+      </c>
+      <c r="AM314">
+        <v>-1</v>
+      </c>
+      <c r="AN314">
+        <v>-1</v>
+      </c>
+      <c r="AO314">
+        <v>-1</v>
+      </c>
+      <c r="AP314">
+        <v>-1</v>
+      </c>
+      <c r="AQ314">
+        <v>0</v>
+      </c>
+      <c r="AR314">
+        <v>0</v>
+      </c>
+      <c r="AS314">
+        <v>0</v>
+      </c>
+      <c r="AT314">
+        <v>0</v>
+      </c>
+      <c r="AU314" t="inlineStr">
         <is>
           <t>2026-08-22 23:30:00</t>
         </is>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q283">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kelantan</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G69">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.76</v>
+        <v>1.51</v>
       </c>
       <c r="O117">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="P117">
-        <v>2.37</v>
+        <v>5.86</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.51</v>
+        <v>2.76</v>
       </c>
       <c r="O118">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="P118">
-        <v>5.86</v>
+        <v>2.37</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC125">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21701,10 +21701,10 @@
         <v>0</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC131">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42891,10 +42891,10 @@
         <v>0</v>
       </c>
       <c r="AA261">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB261">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC261">
         <v>0</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O312">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P312">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q312">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.55</v>
+        <v>2.01</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="P27">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="R27">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="U27">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>2.94</v>
+        <v>4.44</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>1.74</v>
+        <v>2.21</v>
       </c>
       <c r="AC27">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF27">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.01</v>
+        <v>2.55</v>
       </c>
       <c r="O28">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="Q28">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="U28">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
+        <v>1.31</v>
+      </c>
+      <c r="Z28">
+        <v>2.94</v>
+      </c>
+      <c r="AA28">
+        <v>2.1</v>
+      </c>
+      <c r="AB28">
+        <v>1.74</v>
+      </c>
+      <c r="AC28">
+        <v>3.3</v>
+      </c>
+      <c r="AD28">
         <v>1.22</v>
       </c>
-      <c r="Z28">
-        <v>4.44</v>
-      </c>
-      <c r="AA28">
-        <v>1.7</v>
-      </c>
-      <c r="AB28">
-        <v>2.21</v>
-      </c>
-      <c r="AC28">
-        <v>2.72</v>
-      </c>
-      <c r="AD28">
-        <v>1.45</v>
-      </c>
       <c r="AE28">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG28">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.99</v>
+        <v>1.48</v>
       </c>
       <c r="O29">
-        <v>3.48</v>
+        <v>4.25</v>
       </c>
       <c r="P29">
-        <v>1.78</v>
+        <v>5.32</v>
       </c>
       <c r="Q29">
+        <v>1.97</v>
+      </c>
+      <c r="R29">
+        <v>2.48</v>
+      </c>
+      <c r="S29">
+        <v>1.25</v>
+      </c>
+      <c r="T29">
+        <v>3.5</v>
+      </c>
+      <c r="U29">
+        <v>2.18</v>
+      </c>
+      <c r="V29">
+        <v>1.52</v>
+      </c>
+      <c r="W29">
+        <v>1.1</v>
+      </c>
+      <c r="X29">
+        <v>1.03</v>
+      </c>
+      <c r="Y29">
+        <v>1.13</v>
+      </c>
+      <c r="Z29">
         <v>4.5</v>
       </c>
-      <c r="R29">
-        <v>2.23</v>
-      </c>
-      <c r="S29">
-        <v>1.36</v>
-      </c>
-      <c r="T29">
-        <v>2.88</v>
-      </c>
-      <c r="U29">
+      <c r="AA29">
+        <v>1.56</v>
+      </c>
+      <c r="AB29">
+        <v>2.17</v>
+      </c>
+      <c r="AC29">
+        <v>2.38</v>
+      </c>
+      <c r="AD29">
+        <v>1.46</v>
+      </c>
+      <c r="AE29">
+        <v>1.2</v>
+      </c>
+      <c r="AF29">
+        <v>1.66</v>
+      </c>
+      <c r="AG29">
+        <v>2.05</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.14</v>
+      </c>
+      <c r="AK29">
         <v>2.5</v>
-      </c>
-      <c r="V29">
-        <v>1.38</v>
-      </c>
-      <c r="W29">
-        <v>1.04</v>
-      </c>
-      <c r="X29">
-        <v>1.06</v>
-      </c>
-      <c r="Y29">
-        <v>1.25</v>
-      </c>
-      <c r="Z29">
-        <v>3.3</v>
-      </c>
-      <c r="AA29">
-        <v>1.94</v>
-      </c>
-      <c r="AB29">
-        <v>1.76</v>
-      </c>
-      <c r="AC29">
-        <v>3</v>
-      </c>
-      <c r="AD29">
-        <v>1.3</v>
-      </c>
-      <c r="AE29">
-        <v>1.06</v>
-      </c>
-      <c r="AF29">
-        <v>1.77</v>
-      </c>
-      <c r="AG29">
-        <v>1.9</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.2</v>
-      </c>
-      <c r="AK29">
-        <v>1.14</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.81</v>
+        <v>2.06</v>
       </c>
       <c r="O30">
-        <v>4.05</v>
+        <v>3.62</v>
       </c>
       <c r="P30">
-        <v>1.55</v>
+        <v>2.96</v>
       </c>
       <c r="Q30">
-        <v>4.35</v>
+        <v>2.6</v>
       </c>
       <c r="R30">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S30">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
         <v>2.33</v>
@@ -5226,13 +5226,13 @@
         <v>1.46</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
         <v>3.75</v>
@@ -5247,32 +5247,32 @@
         <v>2.6</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE30">
         <v>1.16</v>
       </c>
       <c r="AF30">
+        <v>1.58</v>
+      </c>
+      <c r="AG30">
+        <v>2.18</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.21</v>
+      </c>
+      <c r="AK30">
         <v>1.66</v>
-      </c>
-      <c r="AG30">
-        <v>2.05</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.18</v>
-      </c>
-      <c r="AK30">
-        <v>1.13</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,58 +5362,58 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.48</v>
+        <v>4.81</v>
       </c>
       <c r="O31">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="P31">
-        <v>5.32</v>
+        <v>1.55</v>
       </c>
       <c r="Q31">
-        <v>1.97</v>
+        <v>4.35</v>
       </c>
       <c r="R31">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U31">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="V31">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA31">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AB31">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD31">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
         <v>1.66</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>2.5</v>
+        <v>1.13</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.06</v>
+        <v>3.99</v>
       </c>
       <c r="O32">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="P32">
-        <v>2.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q32">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
+        <v>1.36</v>
+      </c>
+      <c r="T32">
+        <v>2.88</v>
+      </c>
+      <c r="U32">
+        <v>2.5</v>
+      </c>
+      <c r="V32">
+        <v>1.38</v>
+      </c>
+      <c r="W32">
+        <v>1.04</v>
+      </c>
+      <c r="X32">
+        <v>1.06</v>
+      </c>
+      <c r="Y32">
         <v>1.25</v>
       </c>
-      <c r="T32">
-        <v>3.6</v>
-      </c>
-      <c r="U32">
-        <v>2.33</v>
-      </c>
-      <c r="V32">
-        <v>1.46</v>
-      </c>
-      <c r="W32">
-        <v>1.15</v>
-      </c>
-      <c r="X32">
-        <v>1.01</v>
-      </c>
-      <c r="Y32">
+      <c r="Z32">
+        <v>3.3</v>
+      </c>
+      <c r="AA32">
+        <v>1.94</v>
+      </c>
+      <c r="AB32">
+        <v>1.76</v>
+      </c>
+      <c r="AC32">
+        <v>3</v>
+      </c>
+      <c r="AD32">
+        <v>1.3</v>
+      </c>
+      <c r="AE32">
+        <v>1.06</v>
+      </c>
+      <c r="AF32">
+        <v>1.77</v>
+      </c>
+      <c r="AG32">
+        <v>1.9</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.2</v>
       </c>
-      <c r="Z32">
-        <v>3.75</v>
-      </c>
-      <c r="AA32">
-        <v>1.65</v>
-      </c>
-      <c r="AB32">
-        <v>2</v>
-      </c>
-      <c r="AC32">
-        <v>2.6</v>
-      </c>
-      <c r="AD32">
-        <v>1.49</v>
-      </c>
-      <c r="AE32">
-        <v>1.16</v>
-      </c>
-      <c r="AF32">
-        <v>1.58</v>
-      </c>
-      <c r="AG32">
-        <v>2.18</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.21</v>
-      </c>
       <c r="AK32">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,46 +6503,46 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="Q38">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="R38">
+        <v>1.96</v>
+      </c>
+      <c r="S38">
+        <v>1.4</v>
+      </c>
+      <c r="T38">
+        <v>2.69</v>
+      </c>
+      <c r="U38">
+        <v>2.9</v>
+      </c>
+      <c r="V38">
+        <v>1.35</v>
+      </c>
+      <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.3</v>
+      </c>
+      <c r="Z38">
+        <v>3</v>
+      </c>
+      <c r="AA38">
         <v>2.05</v>
-      </c>
-      <c r="S38">
-        <v>1.42</v>
-      </c>
-      <c r="T38">
-        <v>2.65</v>
-      </c>
-      <c r="U38">
-        <v>2.95</v>
-      </c>
-      <c r="V38">
-        <v>1.34</v>
-      </c>
-      <c r="W38">
-        <v>1.04</v>
-      </c>
-      <c r="X38">
-        <v>1.06</v>
-      </c>
-      <c r="Y38">
-        <v>1.36</v>
-      </c>
-      <c r="Z38">
-        <v>3.14</v>
-      </c>
-      <c r="AA38">
-        <v>2.1</v>
       </c>
       <c r="AB38">
         <v>1.7</v>
@@ -6551,17 +6551,17 @@
         <v>3.8</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
         <v>1.04</v>
       </c>
       <c r="AF38">
+        <v>1.77</v>
+      </c>
+      <c r="AG38">
         <v>1.91</v>
       </c>
-      <c r="AG38">
-        <v>1.83</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK38">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P39">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="R39">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3</v>
+        <v>3.76</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AC39">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
       <c r="AD39">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG39">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="O40">
+        <v>3.25</v>
+      </c>
+      <c r="P40">
+        <v>4</v>
+      </c>
+      <c r="Q40">
+        <v>2.6</v>
+      </c>
+      <c r="R40">
+        <v>2.05</v>
+      </c>
+      <c r="S40">
+        <v>1.42</v>
+      </c>
+      <c r="T40">
+        <v>2.65</v>
+      </c>
+      <c r="U40">
+        <v>2.95</v>
+      </c>
+      <c r="V40">
+        <v>1.34</v>
+      </c>
+      <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
+        <v>1.06</v>
+      </c>
+      <c r="Y40">
+        <v>1.36</v>
+      </c>
+      <c r="Z40">
+        <v>3.14</v>
+      </c>
+      <c r="AA40">
+        <v>2.1</v>
+      </c>
+      <c r="AB40">
+        <v>1.7</v>
+      </c>
+      <c r="AC40">
         <v>3.8</v>
       </c>
-      <c r="P40">
-        <v>6</v>
-      </c>
-      <c r="Q40">
-        <v>2.2</v>
-      </c>
-      <c r="R40">
-        <v>2.34</v>
-      </c>
-      <c r="S40">
-        <v>1.33</v>
-      </c>
-      <c r="T40">
-        <v>3.1</v>
-      </c>
-      <c r="U40">
-        <v>2.5</v>
-      </c>
-      <c r="V40">
-        <v>1.46</v>
-      </c>
-      <c r="W40">
-        <v>1.1</v>
-      </c>
-      <c r="X40">
-        <v>1.03</v>
-      </c>
-      <c r="Y40">
-        <v>1.22</v>
-      </c>
-      <c r="Z40">
-        <v>3.76</v>
-      </c>
-      <c r="AA40">
-        <v>1.73</v>
-      </c>
-      <c r="AB40">
-        <v>2.01</v>
-      </c>
-      <c r="AC40">
-        <v>2.81</v>
-      </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.82</v>
+        <v>2.85</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R41">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="U41">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB41">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC41">
         <v>3.12</v>
       </c>
       <c r="AD41">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
         <v>1.74</v>
       </c>
       <c r="AG41">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
+        <v>1.82</v>
+      </c>
+      <c r="O42">
+        <v>3.6</v>
+      </c>
+      <c r="P42">
+        <v>4.33</v>
+      </c>
+      <c r="Q42">
+        <v>2.82</v>
+      </c>
+      <c r="R42">
+        <v>2.18</v>
+      </c>
+      <c r="S42">
+        <v>1.36</v>
+      </c>
+      <c r="T42">
         <v>2.85</v>
       </c>
-      <c r="O42">
-        <v>3.5</v>
-      </c>
-      <c r="P42">
-        <v>2.4</v>
-      </c>
-      <c r="Q42">
-        <v>2.9</v>
-      </c>
-      <c r="R42">
-        <v>2.07</v>
-      </c>
-      <c r="S42">
-        <v>1.4</v>
-      </c>
-      <c r="T42">
-        <v>3.02</v>
-      </c>
       <c r="U42">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA42">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC42">
         <v>3.12</v>
       </c>
       <c r="AD42">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
         <v>1.74</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="O70">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P70">
-        <v>3.82</v>
+        <v>2.89</v>
       </c>
       <c r="Q70">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R70">
+        <v>2.38</v>
+      </c>
+      <c r="S70">
+        <v>1.26</v>
+      </c>
+      <c r="T70">
+        <v>3.4</v>
+      </c>
+      <c r="U70">
+        <v>2.38</v>
+      </c>
+      <c r="V70">
+        <v>1.55</v>
+      </c>
+      <c r="W70">
+        <v>1.11</v>
+      </c>
+      <c r="X70">
+        <v>1.03</v>
+      </c>
+      <c r="Y70">
+        <v>1.17</v>
+      </c>
+      <c r="Z70">
+        <v>4.3</v>
+      </c>
+      <c r="AA70">
+        <v>1.58</v>
+      </c>
+      <c r="AB70">
         <v>2.2</v>
       </c>
-      <c r="S70">
-        <v>1.31</v>
-      </c>
-      <c r="T70">
-        <v>3.02</v>
-      </c>
-      <c r="U70">
-        <v>2.5</v>
-      </c>
-      <c r="V70">
+      <c r="AC70">
+        <v>2.43</v>
+      </c>
+      <c r="AD70">
         <v>1.44</v>
       </c>
-      <c r="W70">
-        <v>1.08</v>
-      </c>
-      <c r="X70">
-        <v>1</v>
-      </c>
-      <c r="Y70">
-        <v>1.19</v>
-      </c>
-      <c r="Z70">
-        <v>3.74</v>
-      </c>
-      <c r="AA70">
-        <v>1.68</v>
-      </c>
-      <c r="AB70">
-        <v>1.96</v>
-      </c>
-      <c r="AC70">
-        <v>2.7</v>
-      </c>
-      <c r="AD70">
-        <v>1.37</v>
-      </c>
       <c r="AE70">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF70">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,65 +11882,65 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="O71">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="P71">
-        <v>2.65</v>
+        <v>3.82</v>
       </c>
       <c r="Q71">
-        <v>2.97</v>
+        <v>2.34</v>
       </c>
       <c r="R71">
+        <v>2.2</v>
+      </c>
+      <c r="S71">
+        <v>1.31</v>
+      </c>
+      <c r="T71">
+        <v>3.02</v>
+      </c>
+      <c r="U71">
+        <v>2.5</v>
+      </c>
+      <c r="V71">
+        <v>1.44</v>
+      </c>
+      <c r="W71">
+        <v>1.08</v>
+      </c>
+      <c r="X71">
+        <v>1</v>
+      </c>
+      <c r="Y71">
+        <v>1.19</v>
+      </c>
+      <c r="Z71">
+        <v>3.74</v>
+      </c>
+      <c r="AA71">
+        <v>1.68</v>
+      </c>
+      <c r="AB71">
+        <v>1.96</v>
+      </c>
+      <c r="AC71">
+        <v>2.7</v>
+      </c>
+      <c r="AD71">
+        <v>1.37</v>
+      </c>
+      <c r="AE71">
+        <v>1.1</v>
+      </c>
+      <c r="AF71">
+        <v>1.65</v>
+      </c>
+      <c r="AG71">
         <v>2.08</v>
       </c>
-      <c r="S71">
-        <v>1.36</v>
-      </c>
-      <c r="T71">
-        <v>2.78</v>
-      </c>
-      <c r="U71">
-        <v>2.7</v>
-      </c>
-      <c r="V71">
-        <v>1.38</v>
-      </c>
-      <c r="W71">
-        <v>1.07</v>
-      </c>
-      <c r="X71">
-        <v>1.01</v>
-      </c>
-      <c r="Y71">
-        <v>1.26</v>
-      </c>
-      <c r="Z71">
-        <v>3.2</v>
-      </c>
-      <c r="AA71">
-        <v>1.89</v>
-      </c>
-      <c r="AB71">
-        <v>1.81</v>
-      </c>
-      <c r="AC71">
-        <v>3.08</v>
-      </c>
-      <c r="AD71">
-        <v>1.28</v>
-      </c>
-      <c r="AE71">
-        <v>1.07</v>
-      </c>
-      <c r="AF71">
-        <v>1.69</v>
-      </c>
-      <c r="AG71">
-        <v>2</v>
-      </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AK71">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="O72">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="Q72">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="R72">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S72">
+        <v>1.36</v>
+      </c>
+      <c r="T72">
+        <v>2.78</v>
+      </c>
+      <c r="U72">
+        <v>2.7</v>
+      </c>
+      <c r="V72">
+        <v>1.38</v>
+      </c>
+      <c r="W72">
+        <v>1.07</v>
+      </c>
+      <c r="X72">
+        <v>1.01</v>
+      </c>
+      <c r="Y72">
         <v>1.26</v>
       </c>
-      <c r="T72">
-        <v>3.4</v>
-      </c>
-      <c r="U72">
-        <v>2.38</v>
-      </c>
-      <c r="V72">
-        <v>1.55</v>
-      </c>
-      <c r="W72">
-        <v>1.11</v>
-      </c>
-      <c r="X72">
-        <v>1.03</v>
-      </c>
-      <c r="Y72">
-        <v>1.17</v>
-      </c>
       <c r="Z72">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA72">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AB72">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AC72">
-        <v>2.43</v>
+        <v>3.08</v>
       </c>
       <c r="AD72">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AE72">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
+        <v>1.69</v>
+      </c>
+      <c r="AG72">
+        <v>2</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>1.37</v>
+      </c>
+      <c r="AK72">
         <v>1.5</v>
-      </c>
-      <c r="AG72">
-        <v>2.38</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.25</v>
-      </c>
-      <c r="AK72">
-        <v>1.75</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="O85">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>3.81</v>
+        <v>3.3</v>
       </c>
       <c r="Q85">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="R85">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
         <v>1.36</v>
       </c>
       <c r="T85">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="U85">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V85">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W85">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z85">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="AA85">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB85">
         <v>1.8</v>
       </c>
       <c r="AC85">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD85">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG85">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="O86">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P86">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="Q86">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S86">
         <v>1.36</v>
       </c>
       <c r="T86">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="U86">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V86">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z86">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA86">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB86">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC86">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD86">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF86">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG86">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AK86">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="O87">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="Q87">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R87">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T87">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U87">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W87">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y87">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z87">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA87">
+        <v>1.93</v>
+      </c>
+      <c r="AB87">
         <v>1.85</v>
       </c>
-      <c r="AB87">
-        <v>1.87</v>
-      </c>
       <c r="AC87">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD87">
+        <v>1.33</v>
+      </c>
+      <c r="AE87">
+        <v>1.11</v>
+      </c>
+      <c r="AF87">
+        <v>1.73</v>
+      </c>
+      <c r="AG87">
+        <v>1.95</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.27</v>
       </c>
-      <c r="AE87">
-        <v>1.07</v>
-      </c>
-      <c r="AF87">
-        <v>1.67</v>
-      </c>
-      <c r="AG87">
-        <v>2.05</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.42</v>
-      </c>
       <c r="AK87">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="O88">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="Q88">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R88">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S88">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T88">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U88">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="V88">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W88">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X88">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z88">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AA88">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB88">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC88">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD88">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF88">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG88">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
+        <v>2.4</v>
+      </c>
+      <c r="O89">
+        <v>3.3</v>
+      </c>
+      <c r="P89">
+        <v>2.8</v>
+      </c>
+      <c r="Q89">
+        <v>2.78</v>
+      </c>
+      <c r="R89">
+        <v>2.04</v>
+      </c>
+      <c r="S89">
+        <v>1.39</v>
+      </c>
+      <c r="T89">
+        <v>2.9</v>
+      </c>
+      <c r="U89">
+        <v>2.62</v>
+      </c>
+      <c r="V89">
+        <v>1.4</v>
+      </c>
+      <c r="W89">
+        <v>1.04</v>
+      </c>
+      <c r="X89">
+        <v>1.01</v>
+      </c>
+      <c r="Y89">
+        <v>1.29</v>
+      </c>
+      <c r="Z89">
+        <v>3.4</v>
+      </c>
+      <c r="AA89">
+        <v>1.93</v>
+      </c>
+      <c r="AB89">
+        <v>1.85</v>
+      </c>
+      <c r="AC89">
+        <v>3.25</v>
+      </c>
+      <c r="AD89">
+        <v>1.3</v>
+      </c>
+      <c r="AE89">
+        <v>1.06</v>
+      </c>
+      <c r="AF89">
         <v>1.7</v>
       </c>
-      <c r="O89">
-        <v>3.6</v>
-      </c>
-      <c r="P89">
-        <v>5</v>
-      </c>
-      <c r="Q89">
-        <v>2.38</v>
-      </c>
-      <c r="R89">
-        <v>2.1</v>
-      </c>
-      <c r="S89">
-        <v>1.42</v>
-      </c>
-      <c r="T89">
-        <v>2.62</v>
-      </c>
-      <c r="U89">
-        <v>3</v>
-      </c>
-      <c r="V89">
-        <v>1.36</v>
-      </c>
-      <c r="W89">
-        <v>1.03</v>
-      </c>
-      <c r="X89">
-        <v>1.02</v>
-      </c>
-      <c r="Y89">
-        <v>1.31</v>
-      </c>
-      <c r="Z89">
-        <v>2.92</v>
-      </c>
-      <c r="AA89">
-        <v>2.1</v>
-      </c>
-      <c r="AB89">
-        <v>1.71</v>
-      </c>
-      <c r="AC89">
-        <v>3.5</v>
-      </c>
-      <c r="AD89">
-        <v>1.25</v>
-      </c>
-      <c r="AE89">
-        <v>1.04</v>
-      </c>
-      <c r="AF89">
-        <v>1.91</v>
-      </c>
       <c r="AG89">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK89">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,61 +15142,61 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="O91">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="P91">
-        <v>3.37</v>
+        <v>4.52</v>
       </c>
       <c r="Q91">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
+        <v>1.33</v>
+      </c>
+      <c r="T91">
+        <v>3</v>
+      </c>
+      <c r="U91">
+        <v>2.5</v>
+      </c>
+      <c r="V91">
+        <v>1.45</v>
+      </c>
+      <c r="W91">
+        <v>1.07</v>
+      </c>
+      <c r="X91">
+        <v>1</v>
+      </c>
+      <c r="Y91">
+        <v>1.28</v>
+      </c>
+      <c r="Z91">
+        <v>3.65</v>
+      </c>
+      <c r="AA91">
+        <v>1.82</v>
+      </c>
+      <c r="AB91">
+        <v>1.87</v>
+      </c>
+      <c r="AC91">
+        <v>2.88</v>
+      </c>
+      <c r="AD91">
         <v>1.38</v>
       </c>
-      <c r="T91">
-        <v>2.8</v>
-      </c>
-      <c r="U91">
-        <v>2.75</v>
-      </c>
-      <c r="V91">
-        <v>1.39</v>
-      </c>
-      <c r="W91">
-        <v>1.08</v>
-      </c>
-      <c r="X91">
-        <v>1.01</v>
-      </c>
-      <c r="Y91">
-        <v>1.3</v>
-      </c>
-      <c r="Z91">
-        <v>3.3</v>
-      </c>
-      <c r="AA91">
-        <v>1.95</v>
-      </c>
-      <c r="AB91">
-        <v>1.8</v>
-      </c>
-      <c r="AC91">
-        <v>3.28</v>
-      </c>
-      <c r="AD91">
-        <v>1.25</v>
-      </c>
       <c r="AE91">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF91">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG91">
         <v>1.95</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,58 +15305,58 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="O92">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P92">
-        <v>2.8</v>
+        <v>3.81</v>
       </c>
       <c r="Q92">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="R92">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="S92">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T92">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U92">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="V92">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W92">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z92">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="AA92">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB92">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC92">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD92">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE92">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
         <v>1.7</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK92">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,61 +15468,61 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="O93">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="P93">
-        <v>4.52</v>
+        <v>3.37</v>
       </c>
       <c r="Q93">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="R93">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T93">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U93">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V93">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W93">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z93">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA93">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AB93">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC93">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AD93">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE93">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG93">
         <v>1.95</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="O97">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="P97">
-        <v>2.56</v>
+        <v>3.54</v>
       </c>
       <c r="Q97">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S97">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T97">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U97">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V97">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W97">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y97">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="AA97">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB97">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC97">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="AD97">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE97">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF97">
         <v>1.65</v>
       </c>
       <c r="AG97">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.3</v>
       </c>
       <c r="AK97">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
+        <v>3.03</v>
+      </c>
+      <c r="O98">
+        <v>3.35</v>
+      </c>
+      <c r="P98">
+        <v>2.28</v>
+      </c>
+      <c r="Q98">
+        <v>3.9</v>
+      </c>
+      <c r="R98">
+        <v>2.05</v>
+      </c>
+      <c r="S98">
+        <v>1.37</v>
+      </c>
+      <c r="T98">
+        <v>2.8</v>
+      </c>
+      <c r="U98">
+        <v>3.01</v>
+      </c>
+      <c r="V98">
+        <v>1.38</v>
+      </c>
+      <c r="W98">
+        <v>1.05</v>
+      </c>
+      <c r="X98">
+        <v>1.03</v>
+      </c>
+      <c r="Y98">
+        <v>1.33</v>
+      </c>
+      <c r="Z98">
+        <v>3.45</v>
+      </c>
+      <c r="AA98">
         <v>1.99</v>
       </c>
-      <c r="O98">
-        <v>3.54</v>
-      </c>
-      <c r="P98">
-        <v>3.54</v>
-      </c>
-      <c r="Q98">
-        <v>2.45</v>
-      </c>
-      <c r="R98">
-        <v>2.15</v>
-      </c>
-      <c r="S98">
-        <v>1.34</v>
-      </c>
-      <c r="T98">
-        <v>2.94</v>
-      </c>
-      <c r="U98">
-        <v>2.6</v>
-      </c>
-      <c r="V98">
-        <v>1.45</v>
-      </c>
-      <c r="W98">
-        <v>1.11</v>
-      </c>
-      <c r="X98">
-        <v>1</v>
-      </c>
-      <c r="Y98">
+      <c r="AB98">
+        <v>1.78</v>
+      </c>
+      <c r="AC98">
+        <v>3.3</v>
+      </c>
+      <c r="AD98">
         <v>1.25</v>
       </c>
-      <c r="Z98">
-        <v>3.35</v>
-      </c>
-      <c r="AA98">
-        <v>1.75</v>
-      </c>
-      <c r="AB98">
-        <v>1.95</v>
-      </c>
-      <c r="AC98">
-        <v>2.78</v>
-      </c>
-      <c r="AD98">
-        <v>1.33</v>
-      </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF98">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG98">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
+        <v>1.71</v>
+      </c>
+      <c r="AK98">
         <v>1.3</v>
-      </c>
-      <c r="AK98">
-        <v>1.82</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>3.03</v>
+        <v>2.47</v>
       </c>
       <c r="O102">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="P102">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="Q102">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T102">
+        <v>3.2</v>
+      </c>
+      <c r="U102">
         <v>2.8</v>
       </c>
-      <c r="U102">
-        <v>3.01</v>
-      </c>
       <c r="V102">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W102">
+        <v>1.06</v>
+      </c>
+      <c r="X102">
         <v>1.05</v>
       </c>
-      <c r="X102">
-        <v>1.03</v>
-      </c>
       <c r="Y102">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z102">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="AA102">
+        <v>1.78</v>
+      </c>
+      <c r="AB102">
         <v>1.99</v>
-      </c>
-      <c r="AB102">
-        <v>1.78</v>
       </c>
       <c r="AC102">
         <v>3.3</v>
       </c>
       <c r="AD102">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF102">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG102">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="AK102">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G106">
@@ -17583,68 +17583,68 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N106">
-        <v>3.46</v>
+        <v>1.33</v>
       </c>
       <c r="O106">
-        <v>3.44</v>
+        <v>4.65</v>
       </c>
       <c r="P106">
-        <v>2.03</v>
+        <v>7.55</v>
       </c>
       <c r="Q106">
-        <v>3.9</v>
+        <v>1.86</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="S106">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T106">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="U106">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="V106">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W106">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X106">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA106">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB106">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC106">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD106">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE106">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF106">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK106">
-        <v>1.29</v>
+        <v>3</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G107">
@@ -17746,68 +17746,68 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N107">
+        <v>2.37</v>
+      </c>
+      <c r="O107">
+        <v>3.34</v>
+      </c>
+      <c r="P107">
+        <v>2.89</v>
+      </c>
+      <c r="Q107">
+        <v>2.66</v>
+      </c>
+      <c r="R107">
+        <v>2.12</v>
+      </c>
+      <c r="S107">
         <v>1.33</v>
       </c>
-      <c r="O107">
-        <v>4.65</v>
-      </c>
-      <c r="P107">
-        <v>7.55</v>
-      </c>
-      <c r="Q107">
-        <v>1.86</v>
-      </c>
-      <c r="R107">
-        <v>2.41</v>
-      </c>
-      <c r="S107">
-        <v>1.28</v>
-      </c>
       <c r="T107">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="U107">
-        <v>2.34</v>
+        <v>2.67</v>
       </c>
       <c r="V107">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W107">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z107">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA107">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AB107">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AC107">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AD107">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AE107">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,58 +17913,58 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.68</v>
+        <v>3.46</v>
       </c>
       <c r="O108">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="P108">
-        <v>4.8</v>
+        <v>2.03</v>
       </c>
       <c r="Q108">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="R108">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S108">
+        <v>1.37</v>
+      </c>
+      <c r="T108">
+        <v>2.85</v>
+      </c>
+      <c r="U108">
+        <v>2.69</v>
+      </c>
+      <c r="V108">
+        <v>1.41</v>
+      </c>
+      <c r="W108">
+        <v>1.06</v>
+      </c>
+      <c r="X108">
+        <v>1.05</v>
+      </c>
+      <c r="Y108">
+        <v>1.25</v>
+      </c>
+      <c r="Z108">
+        <v>3.5</v>
+      </c>
+      <c r="AA108">
+        <v>1.9</v>
+      </c>
+      <c r="AB108">
+        <v>1.9</v>
+      </c>
+      <c r="AC108">
+        <v>3.2</v>
+      </c>
+      <c r="AD108">
         <v>1.3</v>
       </c>
-      <c r="T108">
-        <v>3.2</v>
-      </c>
-      <c r="U108">
-        <v>2.4</v>
-      </c>
-      <c r="V108">
-        <v>1.5</v>
-      </c>
-      <c r="W108">
+      <c r="AE108">
         <v>1.08</v>
-      </c>
-      <c r="X108">
-        <v>1</v>
-      </c>
-      <c r="Y108">
-        <v>1.23</v>
-      </c>
-      <c r="Z108">
-        <v>3.95</v>
-      </c>
-      <c r="AA108">
-        <v>1.8</v>
-      </c>
-      <c r="AB108">
-        <v>2.04</v>
-      </c>
-      <c r="AC108">
-        <v>2.8</v>
-      </c>
-      <c r="AD108">
-        <v>1.4</v>
-      </c>
-      <c r="AE108">
-        <v>1.15</v>
       </c>
       <c r="AF108">
         <v>1.7</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="O109">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="P109">
-        <v>2.89</v>
+        <v>4.8</v>
       </c>
       <c r="Q109">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="R109">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="U109">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="V109">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y109">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z109">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AA109">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB109">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC109">
         <v>2.8</v>
       </c>
       <c r="AD109">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE109">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF109">
         <v>1.7</v>
       </c>
       <c r="AG109">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O110">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P110">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="Q110">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="R110">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="S110">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="U110">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="V110">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>3.54</v>
+        <v>3.27</v>
       </c>
       <c r="AA110">
+        <v>2.06</v>
+      </c>
+      <c r="AB110">
+        <v>1.72</v>
+      </c>
+      <c r="AC110">
+        <v>3.3</v>
+      </c>
+      <c r="AD110">
+        <v>1.28</v>
+      </c>
+      <c r="AE110">
+        <v>1.03</v>
+      </c>
+      <c r="AF110">
         <v>1.8</v>
       </c>
-      <c r="AB110">
-        <v>1.98</v>
-      </c>
-      <c r="AC110">
-        <v>2.8</v>
-      </c>
-      <c r="AD110">
-        <v>1.34</v>
-      </c>
-      <c r="AE110">
-        <v>1.13</v>
-      </c>
-      <c r="AF110">
-        <v>1.62</v>
-      </c>
       <c r="AG110">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK110">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="O111">
         <v>3.3</v>
       </c>
       <c r="P111">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="Q111">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="R111">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S111">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T111">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U111">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="V111">
         <v>1.36</v>
       </c>
       <c r="W111">
+        <v>1.06</v>
+      </c>
+      <c r="X111">
         <v>1.02</v>
       </c>
-      <c r="X111">
-        <v>1</v>
-      </c>
       <c r="Y111">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z111">
-        <v>3.27</v>
+        <v>2.93</v>
       </c>
       <c r="AA111">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB111">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC111">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD111">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE111">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG111">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,28 +18565,28 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O112">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="P112">
-        <v>2.78</v>
+        <v>3.16</v>
       </c>
       <c r="Q112">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R112">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S112">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T112">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="U112">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V112">
         <v>1.35</v>
@@ -18595,34 +18595,34 @@
         <v>1.05</v>
       </c>
       <c r="X112">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z112">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="AA112">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB112">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC112">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AD112">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE112">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG112">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK112">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O113">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P113">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="Q113">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="R113">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S113">
         <v>1.35</v>
       </c>
       <c r="T113">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U113">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V113">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X113">
         <v>1.05</v>
       </c>
       <c r="Y113">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA113">
         <v>1.8</v>
       </c>
       <c r="AB113">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC113">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AD113">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE113">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF113">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG113">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="O114">
+        <v>4.25</v>
+      </c>
+      <c r="P114">
+        <v>5.86</v>
+      </c>
+      <c r="Q114">
+        <v>2.1</v>
+      </c>
+      <c r="R114">
+        <v>2.14</v>
+      </c>
+      <c r="S114">
+        <v>1.29</v>
+      </c>
+      <c r="T114">
         <v>3.3</v>
       </c>
-      <c r="P114">
-        <v>2.56</v>
-      </c>
-      <c r="Q114">
-        <v>3.2</v>
-      </c>
-      <c r="R114">
-        <v>2.05</v>
-      </c>
-      <c r="S114">
-        <v>1.39</v>
-      </c>
-      <c r="T114">
-        <v>2.69</v>
-      </c>
       <c r="U114">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="V114">
+        <v>1.48</v>
+      </c>
+      <c r="W114">
+        <v>1.1</v>
+      </c>
+      <c r="X114">
+        <v>1.04</v>
+      </c>
+      <c r="Y114">
+        <v>1.25</v>
+      </c>
+      <c r="Z114">
+        <v>3.7</v>
+      </c>
+      <c r="AA114">
+        <v>1.79</v>
+      </c>
+      <c r="AB114">
+        <v>1.95</v>
+      </c>
+      <c r="AC114">
+        <v>2.95</v>
+      </c>
+      <c r="AD114">
         <v>1.36</v>
       </c>
-      <c r="W114">
-        <v>1.06</v>
-      </c>
-      <c r="X114">
-        <v>1.02</v>
-      </c>
-      <c r="Y114">
-        <v>1.29</v>
-      </c>
-      <c r="Z114">
-        <v>2.93</v>
-      </c>
-      <c r="AA114">
-        <v>2</v>
-      </c>
-      <c r="AB114">
-        <v>1.85</v>
-      </c>
-      <c r="AC114">
-        <v>3.38</v>
-      </c>
-      <c r="AD114">
-        <v>1.24</v>
-      </c>
       <c r="AE114">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF114">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG114">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK114">
-        <v>1.51</v>
+        <v>2.25</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="O115">
-        <v>4.25</v>
+        <v>3.38</v>
       </c>
       <c r="P115">
-        <v>5.86</v>
+        <v>2.78</v>
       </c>
       <c r="Q115">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="R115">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S115">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U115">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="V115">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W115">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y115">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z115">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA115">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB115">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC115">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AD115">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE115">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF115">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG115">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK115">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,80 +19217,80 @@
         </is>
       </c>
       <c r="N116">
+        <v>2.4</v>
+      </c>
+      <c r="O116">
+        <v>3.38</v>
+      </c>
+      <c r="P116">
+        <v>2.78</v>
+      </c>
+      <c r="Q116">
+        <v>3</v>
+      </c>
+      <c r="R116">
+        <v>2.1</v>
+      </c>
+      <c r="S116">
         <v>1.44</v>
       </c>
-      <c r="O116">
-        <v>4.55</v>
-      </c>
-      <c r="P116">
-        <v>6.5</v>
-      </c>
-      <c r="Q116">
+      <c r="T116">
+        <v>2.57</v>
+      </c>
+      <c r="U116">
+        <v>3.04</v>
+      </c>
+      <c r="V116">
+        <v>1.35</v>
+      </c>
+      <c r="W116">
+        <v>1.05</v>
+      </c>
+      <c r="X116">
+        <v>1.05</v>
+      </c>
+      <c r="Y116">
+        <v>1.3</v>
+      </c>
+      <c r="Z116">
+        <v>2.82</v>
+      </c>
+      <c r="AA116">
+        <v>2.1</v>
+      </c>
+      <c r="AB116">
+        <v>1.72</v>
+      </c>
+      <c r="AC116">
+        <v>3.75</v>
+      </c>
+      <c r="AD116">
+        <v>1.26</v>
+      </c>
+      <c r="AE116">
+        <v>1.05</v>
+      </c>
+      <c r="AF116">
+        <v>1.8</v>
+      </c>
+      <c r="AG116">
         <v>1.95</v>
       </c>
-      <c r="R116">
-        <v>2.4</v>
-      </c>
-      <c r="S116">
-        <v>1.29</v>
-      </c>
-      <c r="T116">
-        <v>3.4</v>
-      </c>
-      <c r="U116">
-        <v>2.47</v>
-      </c>
-      <c r="V116">
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116">
+        <v>1.32</v>
+      </c>
+      <c r="AK116">
         <v>1.53</v>
-      </c>
-      <c r="W116">
-        <v>1.11</v>
-      </c>
-      <c r="X116">
-        <v>1.01</v>
-      </c>
-      <c r="Y116">
-        <v>1.2</v>
-      </c>
-      <c r="Z116">
-        <v>4.5</v>
-      </c>
-      <c r="AA116">
-        <v>1.67</v>
-      </c>
-      <c r="AB116">
-        <v>2.2</v>
-      </c>
-      <c r="AC116">
-        <v>2.5</v>
-      </c>
-      <c r="AD116">
-        <v>1.44</v>
-      </c>
-      <c r="AE116">
-        <v>1.15</v>
-      </c>
-      <c r="AF116">
-        <v>1.7</v>
-      </c>
-      <c r="AG116">
-        <v>2.05</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.19</v>
-      </c>
-      <c r="AK116">
-        <v>2.6</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="O117">
-        <v>3.14</v>
+        <v>4.55</v>
       </c>
       <c r="P117">
-        <v>3.16</v>
+        <v>6.5</v>
       </c>
       <c r="Q117">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="R117">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="T117">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U117">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="V117">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA117">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AB117">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC117">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD117">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE117">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF117">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK117">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,80 +22803,80 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="O138">
-        <v>3.38</v>
+        <v>4.8</v>
       </c>
       <c r="P138">
-        <v>4.45</v>
+        <v>1.39</v>
       </c>
       <c r="Q138">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="R138">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="S138">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T138">
-        <v>2.95</v>
+        <v>3.36</v>
       </c>
       <c r="U138">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="V138">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W138">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X138">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y138">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z138">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA138">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB138">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AC138">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="AD138">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE138">
+        <v>1.17</v>
+      </c>
+      <c r="AF138">
+        <v>1.74</v>
+      </c>
+      <c r="AG138">
+        <v>2</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
         <v>1.15</v>
       </c>
-      <c r="AF138">
-        <v>1.55</v>
-      </c>
-      <c r="AG138">
-        <v>2.26</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>1.22</v>
-      </c>
       <c r="AK138">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,80 +22966,80 @@
         </is>
       </c>
       <c r="N139">
-        <v>6.5</v>
+        <v>3.95</v>
       </c>
       <c r="O139">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P139">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="Q139">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="R139">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="S139">
+        <v>1.4</v>
+      </c>
+      <c r="T139">
+        <v>2.75</v>
+      </c>
+      <c r="U139">
+        <v>2.66</v>
+      </c>
+      <c r="V139">
+        <v>1.36</v>
+      </c>
+      <c r="W139">
+        <v>1.05</v>
+      </c>
+      <c r="X139">
+        <v>1.02</v>
+      </c>
+      <c r="Y139">
+        <v>1.3</v>
+      </c>
+      <c r="Z139">
+        <v>3.4</v>
+      </c>
+      <c r="AA139">
+        <v>1.88</v>
+      </c>
+      <c r="AB139">
+        <v>1.88</v>
+      </c>
+      <c r="AC139">
+        <v>3.05</v>
+      </c>
+      <c r="AD139">
+        <v>1.28</v>
+      </c>
+      <c r="AE139">
+        <v>1.08</v>
+      </c>
+      <c r="AF139">
+        <v>1.8</v>
+      </c>
+      <c r="AG139">
+        <v>1.95</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>1.3</v>
+      </c>
+      <c r="AK139">
         <v>1.25</v>
-      </c>
-      <c r="T139">
-        <v>3.36</v>
-      </c>
-      <c r="U139">
-        <v>2.25</v>
-      </c>
-      <c r="V139">
-        <v>1.57</v>
-      </c>
-      <c r="W139">
-        <v>1.12</v>
-      </c>
-      <c r="X139">
-        <v>1.03</v>
-      </c>
-      <c r="Y139">
-        <v>1.13</v>
-      </c>
-      <c r="Z139">
-        <v>4.4</v>
-      </c>
-      <c r="AA139">
-        <v>1.62</v>
-      </c>
-      <c r="AB139">
-        <v>2.22</v>
-      </c>
-      <c r="AC139">
-        <v>2.34</v>
-      </c>
-      <c r="AD139">
-        <v>1.44</v>
-      </c>
-      <c r="AE139">
-        <v>1.17</v>
-      </c>
-      <c r="AF139">
-        <v>1.74</v>
-      </c>
-      <c r="AG139">
-        <v>2</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>1.15</v>
-      </c>
-      <c r="AK139">
-        <v>1.07</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>3.95</v>
+        <v>1.8</v>
       </c>
       <c r="O140">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P140">
-        <v>1.87</v>
+        <v>4.45</v>
       </c>
       <c r="Q140">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="R140">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S140">
+        <v>1.34</v>
+      </c>
+      <c r="T140">
+        <v>2.95</v>
+      </c>
+      <c r="U140">
+        <v>2.61</v>
+      </c>
+      <c r="V140">
+        <v>1.5</v>
+      </c>
+      <c r="W140">
+        <v>1.08</v>
+      </c>
+      <c r="X140">
+        <v>1.04</v>
+      </c>
+      <c r="Y140">
+        <v>1.22</v>
+      </c>
+      <c r="Z140">
+        <v>4.15</v>
+      </c>
+      <c r="AA140">
+        <v>1.65</v>
+      </c>
+      <c r="AB140">
+        <v>2.17</v>
+      </c>
+      <c r="AC140">
+        <v>2.42</v>
+      </c>
+      <c r="AD140">
         <v>1.4</v>
       </c>
-      <c r="T140">
-        <v>2.75</v>
-      </c>
-      <c r="U140">
-        <v>2.66</v>
-      </c>
-      <c r="V140">
-        <v>1.36</v>
-      </c>
-      <c r="W140">
-        <v>1.05</v>
-      </c>
-      <c r="X140">
-        <v>1.02</v>
-      </c>
-      <c r="Y140">
-        <v>1.3</v>
-      </c>
-      <c r="Z140">
-        <v>3.4</v>
-      </c>
-      <c r="AA140">
-        <v>1.88</v>
-      </c>
-      <c r="AB140">
-        <v>1.88</v>
-      </c>
-      <c r="AC140">
-        <v>3.05</v>
-      </c>
-      <c r="AD140">
-        <v>1.28</v>
-      </c>
       <c r="AE140">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF140">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG140">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK140">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G205">

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.97</v>
+        <v>2.55</v>
       </c>
       <c r="O26">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q26">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R26">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U26">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z26">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="AA26">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AC26">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD26">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.01</v>
+        <v>3.97</v>
       </c>
       <c r="O27">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="P27">
-        <v>3.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q27">
-        <v>2.54</v>
+        <v>4.2</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
+        <v>1.32</v>
+      </c>
+      <c r="Z27">
+        <v>3.35</v>
+      </c>
+      <c r="AA27">
+        <v>1.94</v>
+      </c>
+      <c r="AB27">
+        <v>1.79</v>
+      </c>
+      <c r="AC27">
+        <v>3.5</v>
+      </c>
+      <c r="AD27">
+        <v>1.27</v>
+      </c>
+      <c r="AE27">
+        <v>1.06</v>
+      </c>
+      <c r="AF27">
+        <v>1.75</v>
+      </c>
+      <c r="AG27">
+        <v>1.95</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.83</v>
+      </c>
+      <c r="AK27">
         <v>1.22</v>
-      </c>
-      <c r="Z27">
-        <v>4.44</v>
-      </c>
-      <c r="AA27">
-        <v>1.7</v>
-      </c>
-      <c r="AB27">
-        <v>2.21</v>
-      </c>
-      <c r="AC27">
-        <v>2.72</v>
-      </c>
-      <c r="AD27">
-        <v>1.45</v>
-      </c>
-      <c r="AE27">
-        <v>1.18</v>
-      </c>
-      <c r="AF27">
-        <v>1.62</v>
-      </c>
-      <c r="AG27">
-        <v>2.04</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.27</v>
-      </c>
-      <c r="AK27">
-        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.55</v>
+        <v>2.01</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="P28">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="Q28">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="U28">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>2.94</v>
+        <v>4.44</v>
       </c>
       <c r="AA28">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>1.74</v>
+        <v>2.21</v>
       </c>
       <c r="AC28">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>5.46</v>
       </c>
       <c r="P51">
-        <v>2.55</v>
+        <v>7.03</v>
       </c>
       <c r="Q51">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S51">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="V51">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="Z51">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
       <c r="AA51">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AB51">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="AC51">
-        <v>2.38</v>
+        <v>1.68</v>
       </c>
       <c r="AD51">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AE51">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AF51">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AG51">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="O52">
-        <v>5.46</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>7.03</v>
+        <v>2.55</v>
       </c>
       <c r="Q52">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="Z52">
-        <v>7.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA52">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AB52">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="AC52">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="AD52">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AE52">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AF52">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AG52">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>2.8</v>
+        <v>1.37</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G66">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,31 +16446,31 @@
         </is>
       </c>
       <c r="N99">
-        <v>4.89</v>
+        <v>2.47</v>
       </c>
       <c r="O99">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P99">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q99">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="R99">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S99">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U99">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="V99">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W99">
         <v>1.06</v>
@@ -16479,28 +16479,28 @@
         <v>1.05</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z99">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AA99">
+        <v>1.78</v>
+      </c>
+      <c r="AB99">
+        <v>1.99</v>
+      </c>
+      <c r="AC99">
+        <v>3.3</v>
+      </c>
+      <c r="AD99">
+        <v>1.3</v>
+      </c>
+      <c r="AE99">
+        <v>1.09</v>
+      </c>
+      <c r="AF99">
         <v>1.65</v>
-      </c>
-      <c r="AB99">
-        <v>2.1</v>
-      </c>
-      <c r="AC99">
-        <v>2.88</v>
-      </c>
-      <c r="AD99">
-        <v>1.38</v>
-      </c>
-      <c r="AE99">
-        <v>1.1</v>
-      </c>
-      <c r="AF99">
-        <v>1.68</v>
       </c>
       <c r="AG99">
         <v>2.1</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="O100">
-        <v>5.4</v>
+        <v>3.72</v>
       </c>
       <c r="P100">
-        <v>11.3</v>
+        <v>4.75</v>
       </c>
       <c r="Q100">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="R100">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="S100">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="T100">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="U100">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="V100">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="W100">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y100">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z100">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AA100">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB100">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC100">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="AD100">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF100">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG100">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.7</v>
+        <v>4.89</v>
       </c>
       <c r="O101">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="P101">
-        <v>4.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q101">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="R101">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S101">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T101">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U101">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="V101">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
         <v>1.05</v>
       </c>
       <c r="Y101">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z101">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA101">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB101">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC101">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD101">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE101">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF101">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG101">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.47</v>
+        <v>1.26</v>
       </c>
       <c r="O102">
-        <v>3.62</v>
+        <v>5.4</v>
       </c>
       <c r="P102">
-        <v>2.56</v>
+        <v>11.3</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="R102">
+        <v>2.48</v>
+      </c>
+      <c r="S102">
+        <v>1.26</v>
+      </c>
+      <c r="T102">
+        <v>3.6</v>
+      </c>
+      <c r="U102">
+        <v>2.34</v>
+      </c>
+      <c r="V102">
+        <v>1.51</v>
+      </c>
+      <c r="W102">
+        <v>1.12</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.16</v>
+      </c>
+      <c r="Z102">
+        <v>4.33</v>
+      </c>
+      <c r="AA102">
+        <v>1.57</v>
+      </c>
+      <c r="AB102">
         <v>2.2</v>
       </c>
-      <c r="S102">
-        <v>1.3</v>
-      </c>
-      <c r="T102">
-        <v>3.2</v>
-      </c>
-      <c r="U102">
-        <v>2.8</v>
-      </c>
-      <c r="V102">
-        <v>1.42</v>
-      </c>
-      <c r="W102">
-        <v>1.06</v>
-      </c>
-      <c r="X102">
-        <v>1.05</v>
-      </c>
-      <c r="Y102">
-        <v>1.23</v>
-      </c>
-      <c r="Z102">
-        <v>3.44</v>
-      </c>
-      <c r="AA102">
-        <v>1.78</v>
-      </c>
-      <c r="AB102">
-        <v>1.99</v>
-      </c>
       <c r="AC102">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="AD102">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE102">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF102">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG102">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK102">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="O112">
-        <v>3.14</v>
+        <v>3.44</v>
       </c>
       <c r="P112">
-        <v>3.16</v>
+        <v>2.69</v>
       </c>
       <c r="Q112">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="R112">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="S112">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="T112">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="U112">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="V112">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W112">
+        <v>1.07</v>
+      </c>
+      <c r="X112">
         <v>1.05</v>
       </c>
-      <c r="X112">
-        <v>1.06</v>
-      </c>
       <c r="Y112">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="Z112">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA112">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AB112">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AC112">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="AD112">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AE112">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF112">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG112">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.44</v>
+        <v>1.44</v>
       </c>
       <c r="O113">
-        <v>3.44</v>
+        <v>4.55</v>
       </c>
       <c r="P113">
-        <v>2.69</v>
+        <v>6.5</v>
       </c>
       <c r="Q113">
-        <v>3.07</v>
+        <v>1.95</v>
       </c>
       <c r="R113">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T113">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U113">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V113">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W113">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z113">
-        <v>3.54</v>
+        <v>4.5</v>
       </c>
       <c r="AA113">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB113">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC113">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD113">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE113">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF113">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK113">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="O114">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="P114">
-        <v>5.86</v>
+        <v>3.16</v>
       </c>
       <c r="Q114">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R114">
+        <v>2</v>
+      </c>
+      <c r="S114">
+        <v>1.46</v>
+      </c>
+      <c r="T114">
+        <v>2.53</v>
+      </c>
+      <c r="U114">
+        <v>3.2</v>
+      </c>
+      <c r="V114">
+        <v>1.35</v>
+      </c>
+      <c r="W114">
+        <v>1.05</v>
+      </c>
+      <c r="X114">
+        <v>1.06</v>
+      </c>
+      <c r="Y114">
+        <v>1.37</v>
+      </c>
+      <c r="Z114">
+        <v>2.85</v>
+      </c>
+      <c r="AA114">
         <v>2.14</v>
       </c>
-      <c r="S114">
-        <v>1.29</v>
-      </c>
-      <c r="T114">
-        <v>3.3</v>
-      </c>
-      <c r="U114">
-        <v>2.45</v>
-      </c>
-      <c r="V114">
-        <v>1.48</v>
-      </c>
-      <c r="W114">
-        <v>1.1</v>
-      </c>
-      <c r="X114">
-        <v>1.04</v>
-      </c>
-      <c r="Y114">
-        <v>1.25</v>
-      </c>
-      <c r="Z114">
-        <v>3.7</v>
-      </c>
-      <c r="AA114">
-        <v>1.79</v>
-      </c>
       <c r="AB114">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC114">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="AD114">
+        <v>1.22</v>
+      </c>
+      <c r="AE114">
+        <v>1.07</v>
+      </c>
+      <c r="AF114">
+        <v>1.84</v>
+      </c>
+      <c r="AG114">
+        <v>1.85</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
         <v>1.36</v>
       </c>
-      <c r="AE114">
-        <v>1.14</v>
-      </c>
-      <c r="AF114">
-        <v>1.75</v>
-      </c>
-      <c r="AG114">
-        <v>1.9</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.15</v>
-      </c>
       <c r="AK114">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="O116">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="P116">
-        <v>2.78</v>
+        <v>5.86</v>
       </c>
       <c r="Q116">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R116">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S116">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T116">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="U116">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="V116">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W116">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y116">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z116">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="AA116">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AB116">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC116">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="AD116">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE116">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF116">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG116">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK116">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,80 +19380,80 @@
         </is>
       </c>
       <c r="N117">
+        <v>2.4</v>
+      </c>
+      <c r="O117">
+        <v>3.38</v>
+      </c>
+      <c r="P117">
+        <v>2.78</v>
+      </c>
+      <c r="Q117">
+        <v>3</v>
+      </c>
+      <c r="R117">
+        <v>2.1</v>
+      </c>
+      <c r="S117">
         <v>1.44</v>
       </c>
-      <c r="O117">
-        <v>4.55</v>
-      </c>
-      <c r="P117">
-        <v>6.5</v>
-      </c>
-      <c r="Q117">
+      <c r="T117">
+        <v>2.57</v>
+      </c>
+      <c r="U117">
+        <v>3.04</v>
+      </c>
+      <c r="V117">
+        <v>1.35</v>
+      </c>
+      <c r="W117">
+        <v>1.05</v>
+      </c>
+      <c r="X117">
+        <v>1.05</v>
+      </c>
+      <c r="Y117">
+        <v>1.3</v>
+      </c>
+      <c r="Z117">
+        <v>2.82</v>
+      </c>
+      <c r="AA117">
+        <v>2.1</v>
+      </c>
+      <c r="AB117">
+        <v>1.72</v>
+      </c>
+      <c r="AC117">
+        <v>3.75</v>
+      </c>
+      <c r="AD117">
+        <v>1.26</v>
+      </c>
+      <c r="AE117">
+        <v>1.05</v>
+      </c>
+      <c r="AF117">
+        <v>1.8</v>
+      </c>
+      <c r="AG117">
         <v>1.95</v>
       </c>
-      <c r="R117">
-        <v>2.4</v>
-      </c>
-      <c r="S117">
-        <v>1.29</v>
-      </c>
-      <c r="T117">
-        <v>3.4</v>
-      </c>
-      <c r="U117">
-        <v>2.47</v>
-      </c>
-      <c r="V117">
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ117">
+        <v>1.32</v>
+      </c>
+      <c r="AK117">
         <v>1.53</v>
-      </c>
-      <c r="W117">
-        <v>1.11</v>
-      </c>
-      <c r="X117">
-        <v>1.01</v>
-      </c>
-      <c r="Y117">
-        <v>1.2</v>
-      </c>
-      <c r="Z117">
-        <v>4.5</v>
-      </c>
-      <c r="AA117">
-        <v>1.67</v>
-      </c>
-      <c r="AB117">
-        <v>2.2</v>
-      </c>
-      <c r="AC117">
-        <v>2.5</v>
-      </c>
-      <c r="AD117">
-        <v>1.44</v>
-      </c>
-      <c r="AE117">
-        <v>1.15</v>
-      </c>
-      <c r="AF117">
-        <v>1.7</v>
-      </c>
-      <c r="AG117">
-        <v>2.05</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.19</v>
-      </c>
-      <c r="AK117">
-        <v>2.6</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.95</v>
+        <v>1.8</v>
       </c>
       <c r="O139">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P139">
-        <v>1.87</v>
+        <v>4.45</v>
       </c>
       <c r="Q139">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="R139">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S139">
+        <v>1.34</v>
+      </c>
+      <c r="T139">
+        <v>2.95</v>
+      </c>
+      <c r="U139">
+        <v>2.61</v>
+      </c>
+      <c r="V139">
+        <v>1.5</v>
+      </c>
+      <c r="W139">
+        <v>1.08</v>
+      </c>
+      <c r="X139">
+        <v>1.04</v>
+      </c>
+      <c r="Y139">
+        <v>1.22</v>
+      </c>
+      <c r="Z139">
+        <v>4.15</v>
+      </c>
+      <c r="AA139">
+        <v>1.65</v>
+      </c>
+      <c r="AB139">
+        <v>2.17</v>
+      </c>
+      <c r="AC139">
+        <v>2.42</v>
+      </c>
+      <c r="AD139">
         <v>1.4</v>
       </c>
-      <c r="T139">
-        <v>2.75</v>
-      </c>
-      <c r="U139">
-        <v>2.66</v>
-      </c>
-      <c r="V139">
-        <v>1.36</v>
-      </c>
-      <c r="W139">
-        <v>1.05</v>
-      </c>
-      <c r="X139">
-        <v>1.02</v>
-      </c>
-      <c r="Y139">
-        <v>1.3</v>
-      </c>
-      <c r="Z139">
-        <v>3.4</v>
-      </c>
-      <c r="AA139">
-        <v>1.88</v>
-      </c>
-      <c r="AB139">
-        <v>1.88</v>
-      </c>
-      <c r="AC139">
-        <v>3.05</v>
-      </c>
-      <c r="AD139">
-        <v>1.28</v>
-      </c>
       <c r="AE139">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF139">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG139">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK139">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
+        <v>3.95</v>
+      </c>
+      <c r="O140">
+        <v>3.5</v>
+      </c>
+      <c r="P140">
+        <v>1.87</v>
+      </c>
+      <c r="Q140">
+        <v>4.5</v>
+      </c>
+      <c r="R140">
+        <v>2.11</v>
+      </c>
+      <c r="S140">
+        <v>1.4</v>
+      </c>
+      <c r="T140">
+        <v>2.75</v>
+      </c>
+      <c r="U140">
+        <v>2.66</v>
+      </c>
+      <c r="V140">
+        <v>1.36</v>
+      </c>
+      <c r="W140">
+        <v>1.05</v>
+      </c>
+      <c r="X140">
+        <v>1.02</v>
+      </c>
+      <c r="Y140">
+        <v>1.3</v>
+      </c>
+      <c r="Z140">
+        <v>3.4</v>
+      </c>
+      <c r="AA140">
+        <v>1.88</v>
+      </c>
+      <c r="AB140">
+        <v>1.88</v>
+      </c>
+      <c r="AC140">
+        <v>3.05</v>
+      </c>
+      <c r="AD140">
+        <v>1.28</v>
+      </c>
+      <c r="AE140">
+        <v>1.08</v>
+      </c>
+      <c r="AF140">
         <v>1.8</v>
       </c>
-      <c r="O140">
-        <v>3.38</v>
-      </c>
-      <c r="P140">
-        <v>4.45</v>
-      </c>
-      <c r="Q140">
-        <v>2.4</v>
-      </c>
-      <c r="R140">
-        <v>2.09</v>
-      </c>
-      <c r="S140">
-        <v>1.34</v>
-      </c>
-      <c r="T140">
-        <v>2.95</v>
-      </c>
-      <c r="U140">
-        <v>2.61</v>
-      </c>
-      <c r="V140">
-        <v>1.5</v>
-      </c>
-      <c r="W140">
-        <v>1.08</v>
-      </c>
-      <c r="X140">
-        <v>1.04</v>
-      </c>
-      <c r="Y140">
-        <v>1.22</v>
-      </c>
-      <c r="Z140">
-        <v>4.15</v>
-      </c>
-      <c r="AA140">
-        <v>1.65</v>
-      </c>
-      <c r="AB140">
-        <v>2.17</v>
-      </c>
-      <c r="AC140">
-        <v>2.42</v>
-      </c>
-      <c r="AD140">
-        <v>1.4</v>
-      </c>
-      <c r="AE140">
-        <v>1.15</v>
-      </c>
-      <c r="AF140">
-        <v>1.55</v>
-      </c>
       <c r="AG140">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK140">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -27865,10 +27865,10 @@
         <v>3.19</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -27877,43 +27877,43 @@
         <v>0</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X169">
         <v>0</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE169">
         <v>0</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -28028,55 +28028,55 @@
         <v>5.58</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28191,55 +28191,55 @@
         <v>3.15</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R171">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S171">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T171">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U171">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V171">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W171">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X171">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y171">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z171">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD171">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE171">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF171">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG171">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK171">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -29495,40 +29495,40 @@
         <v>7.85</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC179">
         <v>1.79</v>
@@ -29537,13 +29537,13 @@
         <v>1.89</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="O227">
+        <v>2.7</v>
+      </c>
+      <c r="P227">
+        <v>2.7</v>
+      </c>
+      <c r="Q227">
+        <v>0</v>
+      </c>
+      <c r="R227">
+        <v>0</v>
+      </c>
+      <c r="S227">
+        <v>0</v>
+      </c>
+      <c r="T227">
+        <v>0</v>
+      </c>
+      <c r="U227">
+        <v>0</v>
+      </c>
+      <c r="V227">
+        <v>0</v>
+      </c>
+      <c r="W227">
+        <v>0</v>
+      </c>
+      <c r="X227">
+        <v>0</v>
+      </c>
+      <c r="Y227">
+        <v>1.6</v>
+      </c>
+      <c r="Z227">
+        <v>2.2</v>
+      </c>
+      <c r="AA227">
         <v>3.1</v>
       </c>
-      <c r="P227">
-        <v>2.9</v>
-      </c>
-      <c r="Q227">
-        <v>3.05</v>
-      </c>
-      <c r="R227">
-        <v>2.05</v>
-      </c>
-      <c r="S227">
-        <v>1.49</v>
-      </c>
-      <c r="T227">
-        <v>2.36</v>
-      </c>
-      <c r="U227">
-        <v>3.1</v>
-      </c>
-      <c r="V227">
-        <v>1.26</v>
-      </c>
-      <c r="W227">
-        <v>1.01</v>
-      </c>
-      <c r="X227">
-        <v>1.11</v>
-      </c>
-      <c r="Y227">
-        <v>1.47</v>
-      </c>
-      <c r="Z227">
-        <v>2.45</v>
-      </c>
-      <c r="AA227">
-        <v>2.5</v>
-      </c>
       <c r="AB227">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC227">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD227">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF227">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG227">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK227">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,80 +37473,80 @@
         </is>
       </c>
       <c r="N228">
+        <v>2.3</v>
+      </c>
+      <c r="O228">
         <v>2.75</v>
       </c>
-      <c r="O228">
-        <v>2.7</v>
-      </c>
       <c r="P228">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y228">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Z228">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA228">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AB228">
+        <v>1.33</v>
+      </c>
+      <c r="AC228">
+        <v>6.4</v>
+      </c>
+      <c r="AD228">
+        <v>1.05</v>
+      </c>
+      <c r="AE228">
+        <v>1.02</v>
+      </c>
+      <c r="AF228">
+        <v>2.38</v>
+      </c>
+      <c r="AG228">
+        <v>1.53</v>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ228">
+        <v>1.4</v>
+      </c>
+      <c r="AK228">
         <v>1.36</v>
-      </c>
-      <c r="AC228">
-        <v>0</v>
-      </c>
-      <c r="AD228">
-        <v>0</v>
-      </c>
-      <c r="AE228">
-        <v>0</v>
-      </c>
-      <c r="AF228">
-        <v>0</v>
-      </c>
-      <c r="AG228">
-        <v>0</v>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ228">
-        <v>0</v>
-      </c>
-      <c r="AK228">
-        <v>0</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,37 +37636,37 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O229">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P229">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q229">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R229">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="S229">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="T229">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U229">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="V229">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W229">
         <v>1.02</v>
       </c>
       <c r="X229">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y229">
         <v>1.71</v>
@@ -37675,25 +37675,25 @@
         <v>2</v>
       </c>
       <c r="AA229">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AB229">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC229">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="AD229">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE229">
         <v>1.02</v>
       </c>
       <c r="AF229">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG229">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>1.4</v>
       </c>
       <c r="AK229">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="O230">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="P230">
-        <v>3</v>
+        <v>4.15</v>
       </c>
       <c r="Q230">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="R230">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S230">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="T230">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U230">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="V230">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W230">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X230">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Y230">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z230">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA230">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="AB230">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AC230">
-        <v>6.25</v>
+        <v>5.35</v>
       </c>
       <c r="AD230">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE230">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF230">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AG230">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AK230">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="O231">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P231">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q231">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="R231">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="S231">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="T231">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="U231">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="V231">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="W231">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X231">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y231">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="Z231">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AA231">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AB231">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AC231">
-        <v>5.35</v>
+        <v>4.25</v>
       </c>
       <c r="AD231">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE231">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF231">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG231">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AK231">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -42046,10 +42046,10 @@
         <v>4.37</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S256">
         <v>0</v>
@@ -42058,34 +42058,34 @@
         <v>0</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X256">
         <v>0</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE256">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="O259">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P259">
-        <v>4.56</v>
+        <v>3.15</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X259">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE259">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="O260">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P260">
-        <v>3.15</v>
+        <v>4.56</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL260">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.01</v>
+        <v>3.97</v>
       </c>
       <c r="O27">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="P27">
-        <v>3.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q27">
-        <v>2.54</v>
+        <v>4.2</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
+        <v>1.32</v>
+      </c>
+      <c r="Z27">
+        <v>3.35</v>
+      </c>
+      <c r="AA27">
+        <v>1.94</v>
+      </c>
+      <c r="AB27">
+        <v>1.79</v>
+      </c>
+      <c r="AC27">
+        <v>3.5</v>
+      </c>
+      <c r="AD27">
+        <v>1.27</v>
+      </c>
+      <c r="AE27">
+        <v>1.06</v>
+      </c>
+      <c r="AF27">
+        <v>1.75</v>
+      </c>
+      <c r="AG27">
+        <v>1.95</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.83</v>
+      </c>
+      <c r="AK27">
         <v>1.22</v>
-      </c>
-      <c r="Z27">
-        <v>4.44</v>
-      </c>
-      <c r="AA27">
-        <v>1.7</v>
-      </c>
-      <c r="AB27">
-        <v>2.21</v>
-      </c>
-      <c r="AC27">
-        <v>2.72</v>
-      </c>
-      <c r="AD27">
-        <v>1.45</v>
-      </c>
-      <c r="AE27">
-        <v>1.18</v>
-      </c>
-      <c r="AF27">
-        <v>1.62</v>
-      </c>
-      <c r="AG27">
-        <v>2.04</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.27</v>
-      </c>
-      <c r="AK27">
-        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.97</v>
+        <v>2.01</v>
       </c>
       <c r="O29">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="P29">
-        <v>1.9</v>
+        <v>3.48</v>
       </c>
       <c r="Q29">
-        <v>4.2</v>
+        <v>2.54</v>
       </c>
       <c r="R29">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="U29">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.35</v>
+        <v>4.44</v>
       </c>
       <c r="AA29">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB29">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AC29">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="AD29">
+        <v>1.45</v>
+      </c>
+      <c r="AE29">
+        <v>1.18</v>
+      </c>
+      <c r="AF29">
+        <v>1.62</v>
+      </c>
+      <c r="AG29">
+        <v>2.04</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.27</v>
       </c>
-      <c r="AE29">
-        <v>1.06</v>
-      </c>
-      <c r="AF29">
-        <v>1.75</v>
-      </c>
-      <c r="AG29">
-        <v>1.95</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.83</v>
-      </c>
       <c r="AK29">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="U42">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AA42">
         <v>1.73</v>
       </c>
       <c r="AB42">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC42">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG42">
         <v>2</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.82</v>
+      </c>
+      <c r="O43">
+        <v>3.6</v>
+      </c>
+      <c r="P43">
+        <v>4.33</v>
+      </c>
+      <c r="Q43">
+        <v>2.82</v>
+      </c>
+      <c r="R43">
+        <v>2.18</v>
+      </c>
+      <c r="S43">
+        <v>1.36</v>
+      </c>
+      <c r="T43">
         <v>2.85</v>
       </c>
-      <c r="O43">
-        <v>3.5</v>
-      </c>
-      <c r="P43">
-        <v>2.4</v>
-      </c>
-      <c r="Q43">
-        <v>2.9</v>
-      </c>
-      <c r="R43">
-        <v>2.07</v>
-      </c>
-      <c r="S43">
-        <v>1.4</v>
-      </c>
-      <c r="T43">
-        <v>3.02</v>
-      </c>
       <c r="U43">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V43">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA43">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB43">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC43">
         <v>3.12</v>
       </c>
       <c r="AD43">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
         <v>1.74</v>
       </c>
       <c r="AG43">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O44">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q44">
+        <v>2.3</v>
+      </c>
+      <c r="R44">
+        <v>2.2</v>
+      </c>
+      <c r="S44">
+        <v>1.35</v>
+      </c>
+      <c r="T44">
+        <v>2.94</v>
+      </c>
+      <c r="U44">
+        <v>2.7</v>
+      </c>
+      <c r="V44">
+        <v>1.44</v>
+      </c>
+      <c r="W44">
+        <v>1.08</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.21</v>
+      </c>
+      <c r="Z44">
+        <v>3.8</v>
+      </c>
+      <c r="AA44">
+        <v>1.73</v>
+      </c>
+      <c r="AB44">
+        <v>1.95</v>
+      </c>
+      <c r="AC44">
         <v>2.82</v>
       </c>
-      <c r="R44">
-        <v>2.18</v>
-      </c>
-      <c r="S44">
-        <v>1.36</v>
-      </c>
-      <c r="T44">
-        <v>2.85</v>
-      </c>
-      <c r="U44">
-        <v>2.75</v>
-      </c>
-      <c r="V44">
-        <v>1.36</v>
-      </c>
-      <c r="W44">
-        <v>1.05</v>
-      </c>
-      <c r="X44">
-        <v>1.05</v>
-      </c>
-      <c r="Y44">
-        <v>1.3</v>
-      </c>
-      <c r="Z44">
-        <v>3.4</v>
-      </c>
-      <c r="AA44">
-        <v>1.75</v>
-      </c>
-      <c r="AB44">
-        <v>1.93</v>
-      </c>
-      <c r="AC44">
-        <v>3.12</v>
-      </c>
       <c r="AD44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="O52">
-        <v>5.46</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>7.03</v>
+        <v>2.55</v>
       </c>
       <c r="Q52">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="Z52">
-        <v>7.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA52">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AB52">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="AC52">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="AD52">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AE52">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AF52">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AG52">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>2.8</v>
+        <v>1.37</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>5.46</v>
       </c>
       <c r="P53">
-        <v>2.55</v>
+        <v>7.03</v>
       </c>
       <c r="Q53">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="R53">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S53">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="U53">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="V53">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="Z53">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
       <c r="AA53">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AB53">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="AC53">
-        <v>2.38</v>
+        <v>1.68</v>
       </c>
       <c r="AD53">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AE53">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AF53">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AG53">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="O57">
-        <v>3.48</v>
+        <v>3.82</v>
       </c>
       <c r="P57">
-        <v>4.13</v>
+        <v>4.94</v>
       </c>
       <c r="Q57">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R57">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S57">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U57">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="V57">
         <v>1.4</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
+        <v>1.25</v>
+      </c>
+      <c r="Z57">
+        <v>3.6</v>
+      </c>
+      <c r="AA57">
+        <v>1.79</v>
+      </c>
+      <c r="AB57">
+        <v>1.92</v>
+      </c>
+      <c r="AC57">
+        <v>3.1</v>
+      </c>
+      <c r="AD57">
         <v>1.33</v>
       </c>
-      <c r="Z57">
-        <v>3.25</v>
-      </c>
-      <c r="AA57">
-        <v>1.87</v>
-      </c>
-      <c r="AB57">
-        <v>1.83</v>
-      </c>
-      <c r="AC57">
-        <v>2.99</v>
-      </c>
-      <c r="AD57">
-        <v>1.29</v>
-      </c>
       <c r="AE57">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF57">
         <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="O58">
-        <v>3.82</v>
+        <v>3.48</v>
       </c>
       <c r="P58">
-        <v>4.94</v>
+        <v>4.13</v>
       </c>
       <c r="Q58">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="R58">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U58">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V58">
         <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y58">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z58">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA58">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AB58">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC58">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AD58">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
         <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="O71">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P71">
-        <v>2.89</v>
+        <v>3.82</v>
       </c>
       <c r="Q71">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S71">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T71">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="U71">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V71">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z71">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA71">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AB71">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AC71">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD71">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG71">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK71">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="O72">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>3.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q72">
-        <v>2.34</v>
+        <v>2.97</v>
       </c>
       <c r="R72">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S72">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T72">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="U72">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V72">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z72">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA72">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AB72">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AC72">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD72">
+        <v>1.28</v>
+      </c>
+      <c r="AE72">
+        <v>1.07</v>
+      </c>
+      <c r="AF72">
+        <v>1.69</v>
+      </c>
+      <c r="AG72">
+        <v>2</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.37</v>
       </c>
-      <c r="AE72">
-        <v>1.1</v>
-      </c>
-      <c r="AF72">
-        <v>1.65</v>
-      </c>
-      <c r="AG72">
-        <v>2.08</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.21</v>
-      </c>
       <c r="AK72">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
+        <v>2.13</v>
+      </c>
+      <c r="O73">
+        <v>3.52</v>
+      </c>
+      <c r="P73">
+        <v>2.89</v>
+      </c>
+      <c r="Q73">
+        <v>2.4</v>
+      </c>
+      <c r="R73">
         <v>2.38</v>
       </c>
-      <c r="O73">
-        <v>3.2</v>
-      </c>
-      <c r="P73">
-        <v>2.65</v>
-      </c>
-      <c r="Q73">
-        <v>2.97</v>
-      </c>
-      <c r="R73">
-        <v>2.08</v>
-      </c>
       <c r="S73">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T73">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="V73">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W73">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z73">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA73">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AB73">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AC73">
-        <v>3.08</v>
+        <v>2.43</v>
       </c>
       <c r="AD73">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE73">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF73">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,61 +15305,61 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="O92">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="P92">
-        <v>4.52</v>
+        <v>3.37</v>
       </c>
       <c r="Q92">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T92">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U92">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V92">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X92">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z92">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA92">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC92">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AD92">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE92">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF92">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG92">
         <v>1.95</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="O93">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P93">
-        <v>3.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q93">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="R93">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T93">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U93">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="V93">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W93">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X93">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z93">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AA93">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AB93">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC93">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD93">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE93">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF93">
         <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK93">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="O94">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="P94">
-        <v>3.37</v>
+        <v>3.81</v>
       </c>
       <c r="Q94">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="R94">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="S94">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V94">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y94">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z94">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AA94">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB94">
         <v>1.8</v>
       </c>
       <c r="AC94">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD94">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE94">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF94">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG94">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK94">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>4.89</v>
+        <v>3.03</v>
       </c>
       <c r="O100">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="P100">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="Q100">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S100">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T100">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U100">
-        <v>2.55</v>
+        <v>3.01</v>
       </c>
       <c r="V100">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W100">
+        <v>1.05</v>
+      </c>
+      <c r="X100">
+        <v>1.03</v>
+      </c>
+      <c r="Y100">
+        <v>1.33</v>
+      </c>
+      <c r="Z100">
+        <v>3.45</v>
+      </c>
+      <c r="AA100">
+        <v>1.99</v>
+      </c>
+      <c r="AB100">
+        <v>1.78</v>
+      </c>
+      <c r="AC100">
+        <v>3.3</v>
+      </c>
+      <c r="AD100">
+        <v>1.25</v>
+      </c>
+      <c r="AE100">
         <v>1.06</v>
       </c>
-      <c r="X100">
-        <v>1.05</v>
-      </c>
-      <c r="Y100">
-        <v>1.21</v>
-      </c>
-      <c r="Z100">
-        <v>3.62</v>
-      </c>
-      <c r="AA100">
-        <v>1.65</v>
-      </c>
-      <c r="AB100">
-        <v>2.1</v>
-      </c>
-      <c r="AC100">
-        <v>2.88</v>
-      </c>
-      <c r="AD100">
-        <v>1.38</v>
-      </c>
-      <c r="AE100">
-        <v>1.1</v>
-      </c>
       <c r="AF100">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AG100">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="AK100">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,28 +16772,28 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.85</v>
+        <v>2.47</v>
       </c>
       <c r="O101">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="P101">
-        <v>3.96</v>
+        <v>2.56</v>
       </c>
       <c r="Q101">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="R101">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S101">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V101">
         <v>1.42</v>
@@ -16805,31 +16805,31 @@
         <v>1.05</v>
       </c>
       <c r="Y101">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z101">
+        <v>3.44</v>
+      </c>
+      <c r="AA101">
+        <v>1.78</v>
+      </c>
+      <c r="AB101">
+        <v>1.99</v>
+      </c>
+      <c r="AC101">
         <v>3.3</v>
-      </c>
-      <c r="AA101">
-        <v>1.91</v>
-      </c>
-      <c r="AB101">
-        <v>1.85</v>
-      </c>
-      <c r="AC101">
-        <v>3.05</v>
       </c>
       <c r="AD101">
         <v>1.3</v>
       </c>
       <c r="AE101">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF101">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.26</v>
+        <v>4.89</v>
       </c>
       <c r="O102">
-        <v>5.4</v>
+        <v>3.74</v>
       </c>
       <c r="P102">
-        <v>11.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q102">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="R102">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S102">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T102">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="U102">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V102">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y102">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z102">
-        <v>4.33</v>
+        <v>3.62</v>
       </c>
       <c r="AA102">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB102">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC102">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AD102">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE102">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF102">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AG102">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.47</v>
+        <v>1.26</v>
       </c>
       <c r="O103">
-        <v>3.62</v>
+        <v>5.4</v>
       </c>
       <c r="P103">
-        <v>2.56</v>
+        <v>11.3</v>
       </c>
       <c r="Q103">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="R103">
+        <v>2.48</v>
+      </c>
+      <c r="S103">
+        <v>1.26</v>
+      </c>
+      <c r="T103">
+        <v>3.6</v>
+      </c>
+      <c r="U103">
+        <v>2.34</v>
+      </c>
+      <c r="V103">
+        <v>1.51</v>
+      </c>
+      <c r="W103">
+        <v>1.12</v>
+      </c>
+      <c r="X103">
+        <v>1.02</v>
+      </c>
+      <c r="Y103">
+        <v>1.16</v>
+      </c>
+      <c r="Z103">
+        <v>4.33</v>
+      </c>
+      <c r="AA103">
+        <v>1.57</v>
+      </c>
+      <c r="AB103">
         <v>2.2</v>
       </c>
-      <c r="S103">
-        <v>1.3</v>
-      </c>
-      <c r="T103">
-        <v>3.2</v>
-      </c>
-      <c r="U103">
-        <v>2.8</v>
-      </c>
-      <c r="V103">
-        <v>1.42</v>
-      </c>
-      <c r="W103">
-        <v>1.06</v>
-      </c>
-      <c r="X103">
-        <v>1.05</v>
-      </c>
-      <c r="Y103">
-        <v>1.23</v>
-      </c>
-      <c r="Z103">
-        <v>3.44</v>
-      </c>
-      <c r="AA103">
-        <v>1.78</v>
-      </c>
-      <c r="AB103">
-        <v>1.99</v>
-      </c>
       <c r="AC103">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="AD103">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE103">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF103">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK103">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.03</v>
+        <v>1.85</v>
       </c>
       <c r="O104">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="P104">
-        <v>2.28</v>
+        <v>3.96</v>
       </c>
       <c r="Q104">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="R104">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S104">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T104">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U104">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="V104">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W104">
+        <v>1.06</v>
+      </c>
+      <c r="X104">
         <v>1.05</v>
       </c>
-      <c r="X104">
-        <v>1.03</v>
-      </c>
       <c r="Y104">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z104">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA104">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AB104">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD104">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF104">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AG104">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="AK104">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.68</v>
+        <v>5.76</v>
       </c>
       <c r="O108">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P108">
-        <v>4.8</v>
+        <v>1.49</v>
       </c>
       <c r="Q108">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="R108">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T108">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="U108">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="V108">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W108">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X108">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z108">
-        <v>3.95</v>
+        <v>5.03</v>
       </c>
       <c r="AA108">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB108">
-        <v>2.04</v>
+        <v>2.37</v>
       </c>
       <c r="AC108">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD108">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE108">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF108">
         <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK108">
-        <v>2.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>5.76</v>
+        <v>1.68</v>
       </c>
       <c r="O110">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="P110">
-        <v>1.49</v>
+        <v>4.8</v>
       </c>
       <c r="Q110">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="R110">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="U110">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V110">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>5.03</v>
+        <v>3.95</v>
       </c>
       <c r="AA110">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB110">
-        <v>2.37</v>
+        <v>2.04</v>
       </c>
       <c r="AC110">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD110">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AE110">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF110">
         <v>1.7</v>
       </c>
       <c r="AG110">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="O116">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="P116">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="Q116">
+        <v>3</v>
+      </c>
+      <c r="R116">
+        <v>2.19</v>
+      </c>
+      <c r="S116">
+        <v>1.25</v>
+      </c>
+      <c r="T116">
         <v>3.22</v>
       </c>
-      <c r="R116">
-        <v>2.25</v>
-      </c>
-      <c r="S116">
-        <v>1.35</v>
-      </c>
-      <c r="T116">
-        <v>3</v>
-      </c>
       <c r="U116">
-        <v>2.73</v>
+        <v>2.39</v>
       </c>
       <c r="V116">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA116">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB116">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC116">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="AD116">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AE116">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF116">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG116">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AK116">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="O117">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="P117">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="Q117">
+        <v>3.22</v>
+      </c>
+      <c r="R117">
+        <v>2.25</v>
+      </c>
+      <c r="S117">
+        <v>1.35</v>
+      </c>
+      <c r="T117">
         <v>3</v>
       </c>
-      <c r="R117">
-        <v>2.19</v>
-      </c>
-      <c r="S117">
-        <v>1.25</v>
-      </c>
-      <c r="T117">
-        <v>3.22</v>
-      </c>
       <c r="U117">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="V117">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W117">
+        <v>1.06</v>
+      </c>
+      <c r="X117">
+        <v>1.05</v>
+      </c>
+      <c r="Y117">
+        <v>1.26</v>
+      </c>
+      <c r="Z117">
+        <v>3.8</v>
+      </c>
+      <c r="AA117">
+        <v>1.8</v>
+      </c>
+      <c r="AB117">
+        <v>1.93</v>
+      </c>
+      <c r="AC117">
+        <v>3.05</v>
+      </c>
+      <c r="AD117">
+        <v>1.37</v>
+      </c>
+      <c r="AE117">
         <v>1.11</v>
       </c>
-      <c r="X117">
-        <v>1.01</v>
-      </c>
-      <c r="Y117">
-        <v>1.15</v>
-      </c>
-      <c r="Z117">
-        <v>4.25</v>
-      </c>
-      <c r="AA117">
-        <v>1.63</v>
-      </c>
-      <c r="AB117">
-        <v>2.23</v>
-      </c>
-      <c r="AC117">
-        <v>2.45</v>
-      </c>
-      <c r="AD117">
-        <v>1.52</v>
-      </c>
-      <c r="AE117">
-        <v>1.14</v>
-      </c>
       <c r="AF117">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AG117">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AK117">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O229">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P229">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q229">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="R229">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="S229">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="T229">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="U229">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="V229">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="W229">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X229">
+        <v>1.11</v>
+      </c>
+      <c r="Y229">
+        <v>1.47</v>
+      </c>
+      <c r="Z229">
+        <v>2.45</v>
+      </c>
+      <c r="AA229">
+        <v>2.5</v>
+      </c>
+      <c r="AB229">
+        <v>1.5</v>
+      </c>
+      <c r="AC229">
+        <v>4.25</v>
+      </c>
+      <c r="AD229">
         <v>1.15</v>
       </c>
-      <c r="Y229">
-        <v>1.67</v>
-      </c>
-      <c r="Z229">
-        <v>2.07</v>
-      </c>
-      <c r="AA229">
-        <v>2.97</v>
-      </c>
-      <c r="AB229">
-        <v>1.3</v>
-      </c>
-      <c r="AC229">
-        <v>7</v>
-      </c>
-      <c r="AD229">
-        <v>1.1</v>
-      </c>
       <c r="AE229">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF229">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG229">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK229">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O230">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="P230">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q230">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="R230">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="S230">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="T230">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="U230">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="V230">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="W230">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X230">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y230">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="Z230">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="AA230">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="AB230">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AC230">
-        <v>4.25</v>
+        <v>7</v>
       </c>
       <c r="AD230">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE230">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF230">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG230">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
+        <v>1.44</v>
+      </c>
+      <c r="AK230">
         <v>1.4</v>
-      </c>
-      <c r="AK230">
-        <v>1.49</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,19 +38777,19 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="O236">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P236">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="Q236">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="R236">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="S236">
         <v>1.34</v>
@@ -38798,37 +38798,37 @@
         <v>3.28</v>
       </c>
       <c r="U236">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="V236">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W236">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X236">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y236">
         <v>1.22</v>
       </c>
       <c r="Z236">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA236">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB236">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC236">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD236">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE236">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF236">
         <v>1.62</v>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AK236">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,31 +38940,31 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="O237">
+        <v>3.88</v>
+      </c>
+      <c r="P237">
+        <v>2.09</v>
+      </c>
+      <c r="Q237">
         <v>3.4</v>
       </c>
-      <c r="P237">
-        <v>3.1</v>
-      </c>
-      <c r="Q237">
-        <v>2.63</v>
-      </c>
       <c r="R237">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S237">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T237">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U237">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V237">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W237">
         <v>1.08</v>
@@ -38979,19 +38979,19 @@
         <v>3.9</v>
       </c>
       <c r="AA237">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB237">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC237">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD237">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE237">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF237">
         <v>1.62</v>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK237">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>3.58</v>
+        <v>2.65</v>
       </c>
       <c r="O238">
-        <v>3.88</v>
+        <v>3.35</v>
       </c>
       <c r="P238">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="Q238">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R238">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S238">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T238">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U238">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="V238">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W238">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X238">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y238">
         <v>1.22</v>
       </c>
       <c r="Z238">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA238">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB238">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC238">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD238">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE238">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF238">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG238">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>1.29</v>
       </c>
       <c r="AK238">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,34 +39266,34 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="O239">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="P239">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
       <c r="Q239">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="R239">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S239">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T239">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U239">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="V239">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W239">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X239">
         <v>1.02</v>
@@ -39302,28 +39302,28 @@
         <v>1.22</v>
       </c>
       <c r="Z239">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA239">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB239">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC239">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AD239">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE239">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF239">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG239">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AK239">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,16 +47905,16 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.99</v>
+        <v>2.56</v>
       </c>
       <c r="O292">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="P292">
-        <v>3.79</v>
+        <v>2.69</v>
       </c>
       <c r="Q292">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="R292">
         <v>2.38</v>
@@ -47926,10 +47926,10 @@
         <v>3.6</v>
       </c>
       <c r="U292">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V292">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W292">
         <v>1.09</v>
@@ -47938,31 +47938,31 @@
         <v>1.03</v>
       </c>
       <c r="Y292">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z292">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA292">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB292">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC292">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD292">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE292">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF292">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG292">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK292">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,58 +48068,58 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.56</v>
+        <v>1.5</v>
       </c>
       <c r="O293">
-        <v>3.73</v>
+        <v>5.09</v>
       </c>
       <c r="P293">
-        <v>2.69</v>
+        <v>6.02</v>
       </c>
       <c r="Q293">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="R293">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="S293">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T293">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U293">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="V293">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="W293">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X293">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z293">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AA293">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AB293">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="AC293">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="AD293">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AE293">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AF293">
         <v>1.53</v>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK293">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,80 +48394,80 @@
         </is>
       </c>
       <c r="N295">
+        <v>1.99</v>
+      </c>
+      <c r="O295">
+        <v>3.79</v>
+      </c>
+      <c r="P295">
+        <v>3.79</v>
+      </c>
+      <c r="Q295">
+        <v>2.25</v>
+      </c>
+      <c r="R295">
+        <v>2.38</v>
+      </c>
+      <c r="S295">
+        <v>1.25</v>
+      </c>
+      <c r="T295">
+        <v>3.6</v>
+      </c>
+      <c r="U295">
+        <v>2.4</v>
+      </c>
+      <c r="V295">
         <v>1.5</v>
       </c>
-      <c r="O295">
-        <v>5.09</v>
-      </c>
-      <c r="P295">
-        <v>6.02</v>
-      </c>
-      <c r="Q295">
-        <v>1.7</v>
-      </c>
-      <c r="R295">
-        <v>2.8</v>
-      </c>
-      <c r="S295">
-        <v>1.15</v>
-      </c>
-      <c r="T295">
-        <v>4.1</v>
-      </c>
-      <c r="U295">
-        <v>1.85</v>
-      </c>
-      <c r="V295">
+      <c r="W295">
+        <v>1.09</v>
+      </c>
+      <c r="X295">
+        <v>1.03</v>
+      </c>
+      <c r="Y295">
+        <v>1.18</v>
+      </c>
+      <c r="Z295">
+        <v>4.4</v>
+      </c>
+      <c r="AA295">
+        <v>1.62</v>
+      </c>
+      <c r="AB295">
+        <v>2.2</v>
+      </c>
+      <c r="AC295">
+        <v>2.5</v>
+      </c>
+      <c r="AD295">
+        <v>1.44</v>
+      </c>
+      <c r="AE295">
+        <v>1.17</v>
+      </c>
+      <c r="AF295">
+        <v>1.57</v>
+      </c>
+      <c r="AG295">
+        <v>2.3</v>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ295">
+        <v>1.22</v>
+      </c>
+      <c r="AK295">
         <v>1.91</v>
-      </c>
-      <c r="W295">
-        <v>1.2</v>
-      </c>
-      <c r="X295">
-        <v>1.01</v>
-      </c>
-      <c r="Y295">
-        <v>1.06</v>
-      </c>
-      <c r="Z295">
-        <v>8</v>
-      </c>
-      <c r="AA295">
-        <v>1.3</v>
-      </c>
-      <c r="AB295">
-        <v>3.65</v>
-      </c>
-      <c r="AC295">
-        <v>1.82</v>
-      </c>
-      <c r="AD295">
-        <v>1.85</v>
-      </c>
-      <c r="AE295">
-        <v>1.36</v>
-      </c>
-      <c r="AF295">
-        <v>1.53</v>
-      </c>
-      <c r="AG295">
-        <v>2.4</v>
-      </c>
-      <c r="AH295" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI295" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ295">
-        <v>1.13</v>
-      </c>
-      <c r="AK295">
-        <v>3.3</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O308">
-        <v>4.98</v>
+        <v>4.01</v>
       </c>
       <c r="P308">
-        <v>6.42</v>
+        <v>3.44</v>
       </c>
       <c r="Q308">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="R308">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="S308">
         <v>1.2</v>
       </c>
       <c r="T308">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="U308">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V308">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="W308">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X308">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z308">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AA308">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB308">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AC308">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AD308">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE308">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF308">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG308">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK308">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O309">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="P309">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="Q309">
         <v>2.4</v>
       </c>
       <c r="R309">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S309">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T309">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U309">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V309">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W309">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X309">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y309">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z309">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA309">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB309">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AC309">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AD309">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE309">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF309">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG309">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>1.22</v>
       </c>
       <c r="AK309">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,80 +50839,80 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="O310">
-        <v>3.99</v>
+        <v>4.98</v>
       </c>
       <c r="P310">
-        <v>3.47</v>
+        <v>6.42</v>
       </c>
       <c r="Q310">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="R310">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S310">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T310">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="U310">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="V310">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="W310">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X310">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y310">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z310">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="AA310">
+        <v>1.36</v>
+      </c>
+      <c r="AB310">
+        <v>2.9</v>
+      </c>
+      <c r="AC310">
+        <v>1.95</v>
+      </c>
+      <c r="AD310">
+        <v>1.8</v>
+      </c>
+      <c r="AE310">
+        <v>1.3</v>
+      </c>
+      <c r="AF310">
         <v>1.45</v>
       </c>
-      <c r="AB310">
-        <v>2.35</v>
-      </c>
-      <c r="AC310">
-        <v>2.38</v>
-      </c>
-      <c r="AD310">
-        <v>1.53</v>
-      </c>
-      <c r="AE310">
-        <v>1.22</v>
-      </c>
-      <c r="AF310">
-        <v>1.5</v>
-      </c>
       <c r="AG310">
+        <v>2.46</v>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ310">
+        <v>1.14</v>
+      </c>
+      <c r="AK310">
         <v>2.45</v>
-      </c>
-      <c r="AH310" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI310" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ310">
-        <v>1.22</v>
-      </c>
-      <c r="AK310">
-        <v>1.8</v>
       </c>
       <c r="AL310">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.97</v>
+        <v>2.55</v>
       </c>
       <c r="O27">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U27">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z27">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="AA27">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AC27">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD27">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG27">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.55</v>
+        <v>3.97</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="P28">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="Q28">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z28">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AA28">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB28">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AC28">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
+        <v>1.27</v>
+      </c>
+      <c r="AE28">
+        <v>1.06</v>
+      </c>
+      <c r="AF28">
+        <v>1.75</v>
+      </c>
+      <c r="AG28">
+        <v>1.95</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.83</v>
+      </c>
+      <c r="AK28">
         <v>1.22</v>
-      </c>
-      <c r="AE28">
-        <v>1.05</v>
-      </c>
-      <c r="AF28">
-        <v>1.68</v>
-      </c>
-      <c r="AG28">
-        <v>1.93</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.33</v>
-      </c>
-      <c r="AK28">
-        <v>1.49</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R35">
         <v>2.14</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U35">
         <v>2.5</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
         <v>1</v>
@@ -6050,28 +6050,28 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="AA35">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC35">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
         <v>1.43</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="O87">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="Q87">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R87">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T87">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U87">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W87">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y87">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z87">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA87">
+        <v>1.93</v>
+      </c>
+      <c r="AB87">
         <v>1.85</v>
       </c>
-      <c r="AB87">
-        <v>1.87</v>
-      </c>
       <c r="AC87">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD87">
+        <v>1.33</v>
+      </c>
+      <c r="AE87">
+        <v>1.11</v>
+      </c>
+      <c r="AF87">
+        <v>1.73</v>
+      </c>
+      <c r="AG87">
+        <v>1.95</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.27</v>
       </c>
-      <c r="AE87">
-        <v>1.07</v>
-      </c>
-      <c r="AF87">
-        <v>1.67</v>
-      </c>
-      <c r="AG87">
-        <v>2.05</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.42</v>
-      </c>
       <c r="AK87">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,40 +14653,40 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O88">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P88">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q88">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="R88">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="S88">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T88">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U88">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V88">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X88">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z88">
         <v>3.4</v>
@@ -14698,35 +14698,35 @@
         <v>1.85</v>
       </c>
       <c r="AC88">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD88">
+        <v>1.3</v>
+      </c>
+      <c r="AE88">
+        <v>1.06</v>
+      </c>
+      <c r="AF88">
+        <v>1.7</v>
+      </c>
+      <c r="AG88">
+        <v>2.05</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
         <v>1.33</v>
       </c>
-      <c r="AE88">
-        <v>1.11</v>
-      </c>
-      <c r="AF88">
-        <v>1.73</v>
-      </c>
-      <c r="AG88">
-        <v>1.95</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.27</v>
-      </c>
       <c r="AK88">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.7</v>
+        <v>3.65</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="Q89">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S89">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="U89">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W89">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y89">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z89">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AA89">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB89">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AC89">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD89">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG89">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="O90">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P90">
+        <v>3.37</v>
+      </c>
+      <c r="Q90">
+        <v>2.62</v>
+      </c>
+      <c r="R90">
+        <v>2.1</v>
+      </c>
+      <c r="S90">
+        <v>1.38</v>
+      </c>
+      <c r="T90">
         <v>2.8</v>
       </c>
-      <c r="Q90">
-        <v>2.78</v>
-      </c>
-      <c r="R90">
-        <v>2.04</v>
-      </c>
-      <c r="S90">
+      <c r="U90">
+        <v>2.75</v>
+      </c>
+      <c r="V90">
         <v>1.39</v>
       </c>
-      <c r="T90">
-        <v>2.9</v>
-      </c>
-      <c r="U90">
-        <v>2.62</v>
-      </c>
-      <c r="V90">
-        <v>1.4</v>
-      </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
+        <v>1.3</v>
+      </c>
+      <c r="Z90">
+        <v>3.3</v>
+      </c>
+      <c r="AA90">
+        <v>1.95</v>
+      </c>
+      <c r="AB90">
+        <v>1.8</v>
+      </c>
+      <c r="AC90">
+        <v>3.28</v>
+      </c>
+      <c r="AD90">
+        <v>1.25</v>
+      </c>
+      <c r="AE90">
+        <v>1.1</v>
+      </c>
+      <c r="AF90">
+        <v>1.74</v>
+      </c>
+      <c r="AG90">
+        <v>1.95</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
         <v>1.29</v>
       </c>
-      <c r="Z90">
-        <v>3.4</v>
-      </c>
-      <c r="AA90">
-        <v>1.93</v>
-      </c>
-      <c r="AB90">
-        <v>1.85</v>
-      </c>
-      <c r="AC90">
-        <v>3.25</v>
-      </c>
-      <c r="AD90">
-        <v>1.3</v>
-      </c>
-      <c r="AE90">
-        <v>1.06</v>
-      </c>
-      <c r="AF90">
+      <c r="AK90">
         <v>1.7</v>
-      </c>
-      <c r="AG90">
-        <v>2.05</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.33</v>
-      </c>
-      <c r="AK90">
-        <v>1.46</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,61 +15142,61 @@
         </is>
       </c>
       <c r="N91">
+        <v>1.68</v>
+      </c>
+      <c r="O91">
+        <v>3.9</v>
+      </c>
+      <c r="P91">
+        <v>4.52</v>
+      </c>
+      <c r="Q91">
+        <v>2.38</v>
+      </c>
+      <c r="R91">
+        <v>2.2</v>
+      </c>
+      <c r="S91">
+        <v>1.33</v>
+      </c>
+      <c r="T91">
+        <v>3</v>
+      </c>
+      <c r="U91">
+        <v>2.5</v>
+      </c>
+      <c r="V91">
+        <v>1.45</v>
+      </c>
+      <c r="W91">
+        <v>1.07</v>
+      </c>
+      <c r="X91">
+        <v>1</v>
+      </c>
+      <c r="Y91">
+        <v>1.28</v>
+      </c>
+      <c r="Z91">
         <v>3.65</v>
       </c>
-      <c r="O91">
-        <v>3.5</v>
-      </c>
-      <c r="P91">
-        <v>1.95</v>
-      </c>
-      <c r="Q91">
-        <v>3.8</v>
-      </c>
-      <c r="R91">
-        <v>2.06</v>
-      </c>
-      <c r="S91">
-        <v>1.36</v>
-      </c>
-      <c r="T91">
-        <v>2.93</v>
-      </c>
-      <c r="U91">
-        <v>2.73</v>
-      </c>
-      <c r="V91">
-        <v>1.39</v>
-      </c>
-      <c r="W91">
-        <v>1.05</v>
-      </c>
-      <c r="X91">
-        <v>1.05</v>
-      </c>
-      <c r="Y91">
-        <v>1.29</v>
-      </c>
-      <c r="Z91">
-        <v>3.4</v>
-      </c>
       <c r="AA91">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB91">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC91">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD91">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF91">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG91">
         <v>1.95</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="O92">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P92">
-        <v>3.37</v>
+        <v>5</v>
       </c>
       <c r="Q92">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="R92">
         <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T92">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U92">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V92">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W92">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z92">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AA92">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB92">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC92">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD92">
         <v>1.25</v>
       </c>
       <c r="AE92">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF92">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK92">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="O93">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P93">
-        <v>4.52</v>
+        <v>2.74</v>
       </c>
       <c r="Q93">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="R93">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T93">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U93">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V93">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W93">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z93">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AA93">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB93">
         <v>1.87</v>
       </c>
       <c r="AC93">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD93">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE93">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AK93">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.03</v>
+        <v>2.47</v>
       </c>
       <c r="O100">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="P100">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="Q100">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="R100">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S100">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
+        <v>3.2</v>
+      </c>
+      <c r="U100">
         <v>2.8</v>
       </c>
-      <c r="U100">
-        <v>3.01</v>
-      </c>
       <c r="V100">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W100">
+        <v>1.06</v>
+      </c>
+      <c r="X100">
         <v>1.05</v>
       </c>
-      <c r="X100">
-        <v>1.03</v>
-      </c>
       <c r="Y100">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z100">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="AA100">
+        <v>1.78</v>
+      </c>
+      <c r="AB100">
         <v>1.99</v>
-      </c>
-      <c r="AB100">
-        <v>1.78</v>
       </c>
       <c r="AC100">
         <v>3.3</v>
       </c>
       <c r="AD100">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE100">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF100">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG100">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,28 +16772,28 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.47</v>
+        <v>1.85</v>
       </c>
       <c r="O101">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="P101">
-        <v>2.56</v>
+        <v>3.96</v>
       </c>
       <c r="Q101">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="R101">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S101">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U101">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V101">
         <v>1.42</v>
@@ -16805,31 +16805,31 @@
         <v>1.05</v>
       </c>
       <c r="Y101">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z101">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA101">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AB101">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AC101">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD101">
         <v>1.3</v>
       </c>
       <c r="AE101">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF101">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG101">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK101">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>4.89</v>
+        <v>1.26</v>
       </c>
       <c r="O102">
-        <v>3.74</v>
+        <v>5.4</v>
       </c>
       <c r="P102">
-        <v>1.68</v>
+        <v>11.3</v>
       </c>
       <c r="Q102">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="R102">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S102">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T102">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="U102">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V102">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X102">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z102">
-        <v>3.62</v>
+        <v>4.33</v>
       </c>
       <c r="AA102">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB102">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC102">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="AD102">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE102">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF102">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG102">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK102">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.26</v>
+        <v>3.03</v>
       </c>
       <c r="O103">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="P103">
-        <v>11.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q103">
-        <v>1.79</v>
+        <v>3.9</v>
       </c>
       <c r="R103">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="S103">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="T103">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="U103">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="V103">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W103">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z103">
-        <v>4.33</v>
+        <v>3.45</v>
       </c>
       <c r="AA103">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="AB103">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC103">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="AD103">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE103">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG103">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="AK103">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,31 +17261,31 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.85</v>
+        <v>4.89</v>
       </c>
       <c r="O104">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="P104">
-        <v>3.96</v>
+        <v>1.68</v>
       </c>
       <c r="Q104">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="R104">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S104">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T104">
         <v>2.94</v>
       </c>
       <c r="U104">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V104">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W104">
         <v>1.06</v>
@@ -17294,31 +17294,31 @@
         <v>1.05</v>
       </c>
       <c r="Y104">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z104">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA104">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB104">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC104">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD104">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE104">
         <v>1.1</v>
       </c>
       <c r="AF104">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,58 +18076,58 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.46</v>
+        <v>1.68</v>
       </c>
       <c r="O109">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="P109">
-        <v>2.03</v>
+        <v>4.8</v>
       </c>
       <c r="Q109">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="R109">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U109">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="V109">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y109">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z109">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA109">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB109">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AC109">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD109">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE109">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF109">
         <v>1.7</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,58 +18239,58 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.68</v>
+        <v>3.46</v>
       </c>
       <c r="O110">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="P110">
-        <v>4.8</v>
+        <v>2.03</v>
       </c>
       <c r="Q110">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="R110">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S110">
+        <v>1.37</v>
+      </c>
+      <c r="T110">
+        <v>2.85</v>
+      </c>
+      <c r="U110">
+        <v>2.69</v>
+      </c>
+      <c r="V110">
+        <v>1.41</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.05</v>
+      </c>
+      <c r="Y110">
+        <v>1.25</v>
+      </c>
+      <c r="Z110">
+        <v>3.5</v>
+      </c>
+      <c r="AA110">
+        <v>1.9</v>
+      </c>
+      <c r="AB110">
+        <v>1.9</v>
+      </c>
+      <c r="AC110">
+        <v>3.2</v>
+      </c>
+      <c r="AD110">
         <v>1.3</v>
       </c>
-      <c r="T110">
-        <v>3.2</v>
-      </c>
-      <c r="U110">
-        <v>2.4</v>
-      </c>
-      <c r="V110">
-        <v>1.5</v>
-      </c>
-      <c r="W110">
+      <c r="AE110">
         <v>1.08</v>
-      </c>
-      <c r="X110">
-        <v>1</v>
-      </c>
-      <c r="Y110">
-        <v>1.23</v>
-      </c>
-      <c r="Z110">
-        <v>3.95</v>
-      </c>
-      <c r="AA110">
-        <v>1.8</v>
-      </c>
-      <c r="AB110">
-        <v>2.04</v>
-      </c>
-      <c r="AC110">
-        <v>2.8</v>
-      </c>
-      <c r="AD110">
-        <v>1.4</v>
-      </c>
-      <c r="AE110">
-        <v>1.15</v>
       </c>
       <c r="AF110">
         <v>1.7</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,65 +19543,65 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="O118">
-        <v>4.25</v>
+        <v>3.38</v>
       </c>
       <c r="P118">
-        <v>5.86</v>
+        <v>2.78</v>
       </c>
       <c r="Q118">
+        <v>3</v>
+      </c>
+      <c r="R118">
         <v>2.1</v>
       </c>
-      <c r="R118">
-        <v>2.14</v>
-      </c>
       <c r="S118">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T118">
-        <v>3.3</v>
+        <v>2.57</v>
       </c>
       <c r="U118">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="V118">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W118">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y118">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z118">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="AA118">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AB118">
+        <v>1.72</v>
+      </c>
+      <c r="AC118">
+        <v>3.75</v>
+      </c>
+      <c r="AD118">
+        <v>1.26</v>
+      </c>
+      <c r="AE118">
+        <v>1.05</v>
+      </c>
+      <c r="AF118">
+        <v>1.8</v>
+      </c>
+      <c r="AG118">
         <v>1.95</v>
       </c>
-      <c r="AC118">
-        <v>2.95</v>
-      </c>
-      <c r="AD118">
-        <v>1.36</v>
-      </c>
-      <c r="AE118">
-        <v>1.14</v>
-      </c>
-      <c r="AF118">
-        <v>1.75</v>
-      </c>
-      <c r="AG118">
-        <v>1.9</v>
-      </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK118">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="O119">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="P119">
-        <v>2.78</v>
+        <v>5.86</v>
       </c>
       <c r="Q119">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R119">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S119">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T119">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="U119">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="V119">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W119">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X119">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y119">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z119">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="AA119">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AB119">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC119">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="AD119">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE119">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF119">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG119">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK119">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U211">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V211">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W211">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z211">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG211">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,31 +47579,31 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="O290">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P290">
-        <v>3.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q290">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="R290">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S290">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T290">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="U290">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="V290">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W290">
         <v>1.2</v>
@@ -47612,13 +47612,13 @@
         <v>1.02</v>
       </c>
       <c r="Y290">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z290">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA290">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB290">
         <v>2.87</v>
@@ -47633,10 +47633,10 @@
         <v>1.3</v>
       </c>
       <c r="AF290">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG290">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK290">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="O291">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="P291">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Q291">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R291">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S291">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T291">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="U291">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V291">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="W291">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X291">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y291">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z291">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AA291">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AB291">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="AC291">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AD291">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AE291">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF291">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AG291">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>1.25</v>
       </c>
       <c r="AK291">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,58 +47905,58 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.56</v>
+        <v>1.5</v>
       </c>
       <c r="O292">
-        <v>3.73</v>
+        <v>5.09</v>
       </c>
       <c r="P292">
-        <v>2.69</v>
+        <v>6.02</v>
       </c>
       <c r="Q292">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="R292">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="S292">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T292">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U292">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="V292">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="W292">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X292">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z292">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AA292">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AB292">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="AC292">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="AD292">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AE292">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AF292">
         <v>1.53</v>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK292">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,31 +48068,31 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.5</v>
+        <v>3.52</v>
       </c>
       <c r="O293">
-        <v>5.09</v>
+        <v>3.98</v>
       </c>
       <c r="P293">
-        <v>6.02</v>
+        <v>2.02</v>
       </c>
       <c r="Q293">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="R293">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="S293">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T293">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U293">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V293">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="W293">
         <v>1.2</v>
@@ -48101,31 +48101,31 @@
         <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z293">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA293">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB293">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="AC293">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AD293">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE293">
+        <v>1.33</v>
+      </c>
+      <c r="AF293">
         <v>1.36</v>
       </c>
-      <c r="AF293">
-        <v>1.53</v>
-      </c>
       <c r="AG293">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="AK293">
-        <v>3.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>3.52</v>
+        <v>1.99</v>
       </c>
       <c r="O294">
-        <v>3.98</v>
+        <v>3.79</v>
       </c>
       <c r="P294">
-        <v>2.02</v>
+        <v>3.79</v>
       </c>
       <c r="Q294">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="R294">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S294">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T294">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="U294">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="V294">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W294">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X294">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y294">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z294">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AA294">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AB294">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AC294">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AD294">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AE294">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF294">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG294">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AK294">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,64 +48394,64 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O295">
-        <v>3.79</v>
+        <v>4.05</v>
       </c>
       <c r="P295">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="Q295">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R295">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S295">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T295">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="U295">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="V295">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W295">
+        <v>1.2</v>
+      </c>
+      <c r="X295">
+        <v>1.02</v>
+      </c>
+      <c r="Y295">
         <v>1.09</v>
       </c>
-      <c r="X295">
-        <v>1.03</v>
-      </c>
-      <c r="Y295">
-        <v>1.18</v>
-      </c>
       <c r="Z295">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AA295">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AB295">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="AC295">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AD295">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AE295">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF295">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG295">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK295">
         <v>1.91</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>3.2</v>
+        <v>2.09</v>
       </c>
       <c r="Q18">
-        <v>2.9</v>
+        <v>3.96</v>
       </c>
       <c r="R18">
+        <v>2.1</v>
+      </c>
+      <c r="S18">
+        <v>1.39</v>
+      </c>
+      <c r="T18">
+        <v>2.66</v>
+      </c>
+      <c r="U18">
+        <v>2.88</v>
+      </c>
+      <c r="V18">
+        <v>1.34</v>
+      </c>
+      <c r="W18">
+        <v>1.04</v>
+      </c>
+      <c r="X18">
+        <v>1.06</v>
+      </c>
+      <c r="Y18">
+        <v>1.3</v>
+      </c>
+      <c r="Z18">
+        <v>3.1</v>
+      </c>
+      <c r="AA18">
         <v>2</v>
       </c>
-      <c r="S18">
-        <v>1.44</v>
-      </c>
-      <c r="T18">
-        <v>2.5</v>
-      </c>
-      <c r="U18">
-        <v>3.08</v>
-      </c>
-      <c r="V18">
+      <c r="AB18">
+        <v>1.73</v>
+      </c>
+      <c r="AC18">
+        <v>3.6</v>
+      </c>
+      <c r="AD18">
+        <v>1.25</v>
+      </c>
+      <c r="AE18">
+        <v>1.08</v>
+      </c>
+      <c r="AF18">
+        <v>1.75</v>
+      </c>
+      <c r="AG18">
+        <v>1.95</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.33</v>
+      </c>
+      <c r="AK18">
         <v>1.3</v>
-      </c>
-      <c r="W18">
-        <v>1.02</v>
-      </c>
-      <c r="X18">
-        <v>1.08</v>
-      </c>
-      <c r="Y18">
-        <v>1.36</v>
-      </c>
-      <c r="Z18">
-        <v>2.8</v>
-      </c>
-      <c r="AA18">
-        <v>2.2</v>
-      </c>
-      <c r="AB18">
-        <v>1.6</v>
-      </c>
-      <c r="AC18">
-        <v>4</v>
-      </c>
-      <c r="AD18">
-        <v>1.2</v>
-      </c>
-      <c r="AE18">
-        <v>1.03</v>
-      </c>
-      <c r="AF18">
-        <v>1.91</v>
-      </c>
-      <c r="AG18">
-        <v>1.8</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.28</v>
-      </c>
-      <c r="AK18">
-        <v>1.57</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
+        <v>3.05</v>
+      </c>
+      <c r="P19">
         <v>3.2</v>
       </c>
-      <c r="P19">
-        <v>2.09</v>
-      </c>
       <c r="Q19">
-        <v>3.96</v>
+        <v>2.9</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y19">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB19">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC19">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="O39">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q39">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="R39">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="U39">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.06</v>
       </c>
       <c r="Y39">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC39">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG39">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q40">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="R40">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="U40">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V40">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
         <v>1.06</v>
       </c>
       <c r="Y40">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z40">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA40">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC40">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
         <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK40">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P43">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q43">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S43">
+        <v>1.35</v>
+      </c>
+      <c r="T43">
+        <v>2.94</v>
+      </c>
+      <c r="U43">
+        <v>2.45</v>
+      </c>
+      <c r="V43">
+        <v>1.44</v>
+      </c>
+      <c r="W43">
+        <v>1.11</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.21</v>
+      </c>
+      <c r="Z43">
+        <v>3.62</v>
+      </c>
+      <c r="AA43">
+        <v>1.77</v>
+      </c>
+      <c r="AB43">
+        <v>2</v>
+      </c>
+      <c r="AC43">
+        <v>2.82</v>
+      </c>
+      <c r="AD43">
         <v>1.36</v>
       </c>
-      <c r="T43">
-        <v>2.9</v>
-      </c>
-      <c r="U43">
-        <v>2.77</v>
-      </c>
-      <c r="V43">
-        <v>1.39</v>
-      </c>
-      <c r="W43">
-        <v>1.08</v>
-      </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
-      <c r="Y43">
-        <v>1.31</v>
-      </c>
-      <c r="Z43">
-        <v>3.3</v>
-      </c>
-      <c r="AA43">
-        <v>1.93</v>
-      </c>
-      <c r="AB43">
-        <v>1.8</v>
-      </c>
-      <c r="AC43">
-        <v>3.3</v>
-      </c>
-      <c r="AD43">
-        <v>1.33</v>
-      </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="O44">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q44">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R44">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U44">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="V44">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z44">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="AA44">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AB44">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC44">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="AD44">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
+        <v>1.7</v>
+      </c>
+      <c r="AG44">
+        <v>2.01</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.3</v>
+      </c>
+      <c r="AK44">
         <v>1.67</v>
-      </c>
-      <c r="AG44">
-        <v>2.1</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.26</v>
-      </c>
-      <c r="AK44">
-        <v>1.95</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P50">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.61</v>
       </c>
       <c r="R50">
         <v>2.45</v>
@@ -8477,46 +8477,46 @@
         <v>1.2</v>
       </c>
       <c r="T50">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="V50">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W50">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA50">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AB50">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AC50">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD50">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AE50">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF50">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG50">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK50">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="O51">
+        <v>3.9</v>
+      </c>
+      <c r="P51">
         <v>3.45</v>
       </c>
-      <c r="P51">
-        <v>2.6</v>
-      </c>
       <c r="Q51">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
         <v>2.45</v>
@@ -8640,46 +8640,46 @@
         <v>1.2</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U51">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="V51">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W51">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z51">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA51">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AB51">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AC51">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD51">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE51">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF51">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG51">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>2.46</v>
       </c>
       <c r="Q52">
-        <v>1.87</v>
+        <v>2.72</v>
       </c>
       <c r="R52">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="V52">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z52">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA52">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB52">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC52">
-        <v>1.67</v>
+        <v>2.53</v>
       </c>
       <c r="AD52">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AE52">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AF52">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK52">
-        <v>2.58</v>
+        <v>1.35</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P53">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="Q53">
-        <v>2.72</v>
+        <v>1.87</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="U53">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="V53">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z53">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA53">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB53">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="AC53">
-        <v>2.53</v>
+        <v>1.67</v>
       </c>
       <c r="AD53">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AE53">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AF53">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG53">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>1.35</v>
+        <v>2.58</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10913,10 +10913,10 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -10925,10 +10925,10 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -10937,31 +10937,31 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE65">
         <v>0</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,10 +11076,10 @@
         <v>0</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -11088,10 +11088,10 @@
         <v>0</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -11106,25 +11106,25 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE66">
         <v>0</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>0</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -11251,10 +11251,10 @@
         <v>0</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -11269,25 +11269,25 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O100">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
+        <v>2.15</v>
+      </c>
+      <c r="Q100">
+        <v>3.85</v>
+      </c>
+      <c r="R100">
+        <v>2.1</v>
+      </c>
+      <c r="S100">
+        <v>1.4</v>
+      </c>
+      <c r="T100">
+        <v>2.75</v>
+      </c>
+      <c r="U100">
         <v>2.8</v>
       </c>
-      <c r="Q100">
-        <v>2.88</v>
-      </c>
-      <c r="R100">
-        <v>2.15</v>
-      </c>
-      <c r="S100">
-        <v>1.35</v>
-      </c>
-      <c r="T100">
-        <v>3</v>
-      </c>
-      <c r="U100">
-        <v>2.76</v>
-      </c>
       <c r="V100">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z100">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="AA100">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AB100">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AC100">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="AD100">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE100">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF100">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG100">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK100">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="O101">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P101">
-        <v>3.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q101">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="R101">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="S101">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T101">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="U101">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="V101">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z101">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="AA101">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AB101">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AC101">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="AD101">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE101">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF101">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AG101">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK101">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,65 +16935,65 @@
         </is>
       </c>
       <c r="N102">
-        <v>3.3</v>
+        <v>4.13</v>
       </c>
       <c r="O102">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q102">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R102">
+        <v>2.25</v>
+      </c>
+      <c r="S102">
+        <v>1.33</v>
+      </c>
+      <c r="T102">
+        <v>2.82</v>
+      </c>
+      <c r="U102">
+        <v>2.59</v>
+      </c>
+      <c r="V102">
+        <v>1.44</v>
+      </c>
+      <c r="W102">
+        <v>1.11</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.25</v>
+      </c>
+      <c r="Z102">
+        <v>3.8</v>
+      </c>
+      <c r="AA102">
+        <v>1.78</v>
+      </c>
+      <c r="AB102">
+        <v>2.04</v>
+      </c>
+      <c r="AC102">
+        <v>2.9</v>
+      </c>
+      <c r="AD102">
+        <v>1.35</v>
+      </c>
+      <c r="AE102">
+        <v>1.13</v>
+      </c>
+      <c r="AF102">
+        <v>1.67</v>
+      </c>
+      <c r="AG102">
         <v>2.1</v>
       </c>
-      <c r="S102">
-        <v>1.4</v>
-      </c>
-      <c r="T102">
-        <v>2.75</v>
-      </c>
-      <c r="U102">
-        <v>2.8</v>
-      </c>
-      <c r="V102">
-        <v>1.38</v>
-      </c>
-      <c r="W102">
-        <v>1.04</v>
-      </c>
-      <c r="X102">
-        <v>1.04</v>
-      </c>
-      <c r="Y102">
-        <v>1.28</v>
-      </c>
-      <c r="Z102">
-        <v>3.08</v>
-      </c>
-      <c r="AA102">
-        <v>2.07</v>
-      </c>
-      <c r="AB102">
-        <v>1.77</v>
-      </c>
-      <c r="AC102">
-        <v>3.5</v>
-      </c>
-      <c r="AD102">
-        <v>1.25</v>
-      </c>
-      <c r="AE102">
-        <v>1.06</v>
-      </c>
-      <c r="AF102">
-        <v>1.75</v>
-      </c>
-      <c r="AG102">
-        <v>1.95</v>
-      </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
+        <v>2.4</v>
+      </c>
+      <c r="O103">
+        <v>3.3</v>
+      </c>
+      <c r="P103">
+        <v>2.8</v>
+      </c>
+      <c r="Q103">
+        <v>2.88</v>
+      </c>
+      <c r="R103">
+        <v>2.15</v>
+      </c>
+      <c r="S103">
+        <v>1.35</v>
+      </c>
+      <c r="T103">
+        <v>3</v>
+      </c>
+      <c r="U103">
+        <v>2.76</v>
+      </c>
+      <c r="V103">
+        <v>1.42</v>
+      </c>
+      <c r="W103">
+        <v>1.05</v>
+      </c>
+      <c r="X103">
+        <v>1</v>
+      </c>
+      <c r="Y103">
+        <v>1.23</v>
+      </c>
+      <c r="Z103">
+        <v>3.44</v>
+      </c>
+      <c r="AA103">
+        <v>1.85</v>
+      </c>
+      <c r="AB103">
+        <v>1.91</v>
+      </c>
+      <c r="AC103">
+        <v>2.94</v>
+      </c>
+      <c r="AD103">
         <v>1.36</v>
       </c>
-      <c r="O103">
-        <v>5</v>
-      </c>
-      <c r="P103">
-        <v>7.7</v>
-      </c>
-      <c r="Q103">
-        <v>1.76</v>
-      </c>
-      <c r="R103">
-        <v>2.5</v>
-      </c>
-      <c r="S103">
-        <v>1.26</v>
-      </c>
-      <c r="T103">
-        <v>3.35</v>
-      </c>
-      <c r="U103">
-        <v>2.34</v>
-      </c>
-      <c r="V103">
-        <v>1.5</v>
-      </c>
-      <c r="W103">
+      <c r="AE103">
         <v>1.08</v>
       </c>
-      <c r="X103">
-        <v>1.03</v>
-      </c>
-      <c r="Y103">
-        <v>1.16</v>
-      </c>
-      <c r="Z103">
-        <v>4.2</v>
-      </c>
-      <c r="AA103">
-        <v>1.61</v>
-      </c>
-      <c r="AB103">
-        <v>2.15</v>
-      </c>
-      <c r="AC103">
-        <v>2.53</v>
-      </c>
-      <c r="AD103">
-        <v>1.41</v>
-      </c>
-      <c r="AE103">
-        <v>1.18</v>
-      </c>
       <c r="AF103">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AG103">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK103">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>4.13</v>
+        <v>1.9</v>
       </c>
       <c r="O104">
+        <v>3.45</v>
+      </c>
+      <c r="P104">
         <v>3.6</v>
       </c>
-      <c r="P104">
-        <v>1.84</v>
-      </c>
       <c r="Q104">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="R104">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S104">
         <v>1.33</v>
       </c>
       <c r="T104">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="U104">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="V104">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W104">
+        <v>1.06</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104">
+        <v>1.3</v>
+      </c>
+      <c r="Z104">
+        <v>3.53</v>
+      </c>
+      <c r="AA104">
+        <v>1.86</v>
+      </c>
+      <c r="AB104">
+        <v>1.81</v>
+      </c>
+      <c r="AC104">
+        <v>3.3</v>
+      </c>
+      <c r="AD104">
+        <v>1.32</v>
+      </c>
+      <c r="AE104">
         <v>1.11</v>
       </c>
-      <c r="X104">
-        <v>1.02</v>
-      </c>
-      <c r="Y104">
-        <v>1.25</v>
-      </c>
-      <c r="Z104">
-        <v>3.8</v>
-      </c>
-      <c r="AA104">
-        <v>1.78</v>
-      </c>
-      <c r="AB104">
-        <v>2.04</v>
-      </c>
-      <c r="AC104">
-        <v>2.9</v>
-      </c>
-      <c r="AD104">
-        <v>1.35</v>
-      </c>
-      <c r="AE104">
-        <v>1.13</v>
-      </c>
       <c r="AF104">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,61 +18076,61 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="O109">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P109">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="Q109">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="R109">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S109">
+        <v>1.33</v>
+      </c>
+      <c r="T109">
+        <v>2.85</v>
+      </c>
+      <c r="U109">
+        <v>2.69</v>
+      </c>
+      <c r="V109">
+        <v>1.44</v>
+      </c>
+      <c r="W109">
+        <v>1.1</v>
+      </c>
+      <c r="X109">
+        <v>1.05</v>
+      </c>
+      <c r="Y109">
+        <v>1.25</v>
+      </c>
+      <c r="Z109">
+        <v>3.6</v>
+      </c>
+      <c r="AA109">
+        <v>1.87</v>
+      </c>
+      <c r="AB109">
+        <v>1.85</v>
+      </c>
+      <c r="AC109">
+        <v>3.1</v>
+      </c>
+      <c r="AD109">
         <v>1.3</v>
       </c>
-      <c r="T109">
-        <v>3.2</v>
-      </c>
-      <c r="U109">
-        <v>2.4</v>
-      </c>
-      <c r="V109">
-        <v>1.5</v>
-      </c>
-      <c r="W109">
+      <c r="AE109">
         <v>1.08</v>
       </c>
-      <c r="X109">
-        <v>1.01</v>
-      </c>
-      <c r="Y109">
-        <v>1.19</v>
-      </c>
-      <c r="Z109">
-        <v>3.9</v>
-      </c>
-      <c r="AA109">
-        <v>1.75</v>
-      </c>
-      <c r="AB109">
-        <v>2.04</v>
-      </c>
-      <c r="AC109">
-        <v>2.8</v>
-      </c>
-      <c r="AD109">
-        <v>1.39</v>
-      </c>
-      <c r="AE109">
-        <v>1.14</v>
-      </c>
       <c r="AF109">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG109">
         <v>2.05</v>
@@ -18149,7 +18149,7 @@
         <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,61 +18239,61 @@
         </is>
       </c>
       <c r="N110">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P110">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="Q110">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="R110">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U110">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="V110">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z110">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA110">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC110">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD110">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE110">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG110">
         <v>2.05</v>
@@ -18312,7 +18312,7 @@
         <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -22812,34 +22812,34 @@
         <v>4</v>
       </c>
       <c r="Q138">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="R138">
         <v>2.15</v>
       </c>
       <c r="S138">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T138">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U138">
         <v>3.1</v>
       </c>
       <c r="V138">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W138">
         <v>1.06</v>
       </c>
       <c r="X138">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y138">
         <v>1.4</v>
       </c>
       <c r="Z138">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AA138">
         <v>2.3</v>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK138">
         <v>1.83</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G162">
@@ -32586,10 +32586,10 @@
         <v>1.94</v>
       </c>
       <c r="O198">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="P198">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32622,10 +32622,10 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB198">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC198">
         <v>0</v>
@@ -32746,28 +32746,28 @@
         </is>
       </c>
       <c r="N199">
-        <v>3.73</v>
+        <v>3</v>
       </c>
       <c r="O199">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="P199">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q199">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="R199">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S199">
         <v>1.43</v>
       </c>
       <c r="T199">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="U199">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V199">
         <v>1.36</v>
@@ -32776,34 +32776,34 @@
         <v>1.05</v>
       </c>
       <c r="X199">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y199">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z199">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AA199">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="AB199">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC199">
         <v>3.24</v>
       </c>
       <c r="AD199">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE199">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF199">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG199">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
+        <v>1.36</v>
+      </c>
+      <c r="AK199">
         <v>1.33</v>
-      </c>
-      <c r="AK199">
-        <v>1.3</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -35028,43 +35028,43 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="O213">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P213">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q213">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="R213">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="S213">
         <v>1.57</v>
       </c>
       <c r="T213">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U213">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="V213">
         <v>1.16</v>
       </c>
       <c r="W213">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X213">
         <v>1.13</v>
       </c>
       <c r="Y213">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z213">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA213">
         <v>2.8</v>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AK213">
         <v>1.75</v>
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O227">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P227">
+        <v>3.8</v>
+      </c>
+      <c r="Q227">
         <v>3</v>
       </c>
-      <c r="Q227">
-        <v>2.88</v>
-      </c>
       <c r="R227">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="S227">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="T227">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="U227">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="V227">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W227">
         <v>1.02</v>
       </c>
       <c r="X227">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y227">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Z227">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA227">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AB227">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC227">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="AD227">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE227">
         <v>1.02</v>
       </c>
       <c r="AF227">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AG227">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK227">
         <v>1.62</v>
@@ -37482,43 +37482,43 @@
         <v>4.15</v>
       </c>
       <c r="Q228">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R228">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="S228">
         <v>1.61</v>
       </c>
       <c r="T228">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U228">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="V228">
         <v>1.19</v>
       </c>
       <c r="W228">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X228">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y228">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z228">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA228">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="AB228">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC228">
-        <v>5.35</v>
+        <v>6</v>
       </c>
       <c r="AD228">
         <v>1.09</v>
@@ -37527,10 +37527,10 @@
         <v>1.03</v>
       </c>
       <c r="AF228">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AG228">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK228">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O229">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P229">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q229">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="R229">
         <v>2.05</v>
       </c>
       <c r="S229">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T229">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U229">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="V229">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W229">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X229">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y229">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z229">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AA229">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB229">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC229">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD229">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE229">
         <v>1.01</v>
       </c>
       <c r="AF229">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG229">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK229">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37802,28 +37802,28 @@
         <v>2.7</v>
       </c>
       <c r="O230">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P230">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q230">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="R230">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="S230">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="T230">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U230">
         <v>4.2</v>
       </c>
       <c r="V230">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W230">
         <v>1.03</v>
@@ -37832,31 +37832,31 @@
         <v>1.15</v>
       </c>
       <c r="Y230">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Z230">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AA230">
         <v>2.97</v>
       </c>
       <c r="AB230">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC230">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="AD230">
         <v>1.1</v>
       </c>
       <c r="AE230">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF230">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG230">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK230">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,16 +37962,16 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O231">
+        <v>2.7</v>
+      </c>
+      <c r="P231">
         <v>2.75</v>
       </c>
-      <c r="P231">
-        <v>3.25</v>
-      </c>
       <c r="Q231">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="R231">
         <v>1.73</v>
@@ -37980,13 +37980,13 @@
         <v>1.69</v>
       </c>
       <c r="T231">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U231">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="V231">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W231">
         <v>1.02</v>
@@ -37995,16 +37995,16 @@
         <v>1.1</v>
       </c>
       <c r="Y231">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z231">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AA231">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AB231">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC231">
         <v>6.4</v>
@@ -38016,7 +38016,7 @@
         <v>1.02</v>
       </c>
       <c r="AF231">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AG231">
         <v>1.53</v>
@@ -38032,7 +38032,7 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK231">
         <v>1.36</v>
@@ -41385,58 +41385,58 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O252">
         <v>2.8</v>
       </c>
       <c r="P252">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q252">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="R252">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="S252">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T252">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="U252">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V252">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W252">
         <v>1.03</v>
       </c>
       <c r="X252">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y252">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z252">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AA252">
         <v>2.97</v>
       </c>
       <c r="AB252">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC252">
-        <v>5.2</v>
+        <v>6.55</v>
       </c>
       <c r="AD252">
         <v>1.11</v>
       </c>
       <c r="AE252">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF252">
         <v>2.4</v>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK252">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,80 +42526,80 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="O259">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P259">
-        <v>4.56</v>
+        <v>3.15</v>
       </c>
       <c r="Q259">
-        <v>2.38</v>
+        <v>3.06</v>
       </c>
       <c r="R259">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S259">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T259">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="U259">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="V259">
+        <v>1.3</v>
+      </c>
+      <c r="W259">
+        <v>1.02</v>
+      </c>
+      <c r="X259">
+        <v>1.05</v>
+      </c>
+      <c r="Y259">
+        <v>1.38</v>
+      </c>
+      <c r="Z259">
+        <v>2.62</v>
+      </c>
+      <c r="AA259">
+        <v>2.23</v>
+      </c>
+      <c r="AB259">
+        <v>1.57</v>
+      </c>
+      <c r="AC259">
+        <v>3.96</v>
+      </c>
+      <c r="AD259">
+        <v>1.17</v>
+      </c>
+      <c r="AE259">
+        <v>1.02</v>
+      </c>
+      <c r="AF259">
+        <v>1.88</v>
+      </c>
+      <c r="AG259">
+        <v>1.79</v>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ259">
         <v>1.31</v>
       </c>
-      <c r="W259">
-        <v>1.03</v>
-      </c>
-      <c r="X259">
-        <v>1.02</v>
-      </c>
-      <c r="Y259">
-        <v>1.31</v>
-      </c>
-      <c r="Z259">
-        <v>2.92</v>
-      </c>
-      <c r="AA259">
-        <v>2.04</v>
-      </c>
-      <c r="AB259">
-        <v>1.68</v>
-      </c>
-      <c r="AC259">
-        <v>3.5</v>
-      </c>
-      <c r="AD259">
-        <v>1.22</v>
-      </c>
-      <c r="AE259">
-        <v>1.04</v>
-      </c>
-      <c r="AF259">
-        <v>1.9</v>
-      </c>
-      <c r="AG259">
-        <v>1.78</v>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ259">
-        <v>1.13</v>
-      </c>
       <c r="AK259">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="O260">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P260">
-        <v>3.15</v>
+        <v>4.56</v>
       </c>
       <c r="Q260">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="R260">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S260">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T260">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="U260">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="V260">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W260">
+        <v>1.03</v>
+      </c>
+      <c r="X260">
         <v>1.02</v>
       </c>
-      <c r="X260">
-        <v>1.05</v>
-      </c>
       <c r="Y260">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z260">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AA260">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="AB260">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AC260">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="AD260">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE260">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF260">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG260">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AK260">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G265">
@@ -43513,71 +43513,71 @@
         <v>0</v>
       </c>
       <c r="Q265">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R265">
+        <v>2.1</v>
+      </c>
+      <c r="S265">
+        <v>1.33</v>
+      </c>
+      <c r="T265">
+        <v>3</v>
+      </c>
+      <c r="U265">
+        <v>2.75</v>
+      </c>
+      <c r="V265">
+        <v>1.4</v>
+      </c>
+      <c r="W265">
+        <v>1.1</v>
+      </c>
+      <c r="X265">
+        <v>1.03</v>
+      </c>
+      <c r="Y265">
+        <v>1.25</v>
+      </c>
+      <c r="Z265">
+        <v>3.5</v>
+      </c>
+      <c r="AA265">
+        <v>1.8</v>
+      </c>
+      <c r="AB265">
         <v>1.91</v>
       </c>
-      <c r="S265">
-        <v>1.5</v>
-      </c>
-      <c r="T265">
-        <v>2.5</v>
-      </c>
-      <c r="U265">
-        <v>3.5</v>
-      </c>
-      <c r="V265">
+      <c r="AC265">
+        <v>3.2</v>
+      </c>
+      <c r="AD265">
+        <v>1.3</v>
+      </c>
+      <c r="AE265">
+        <v>1.11</v>
+      </c>
+      <c r="AF265">
+        <v>1.65</v>
+      </c>
+      <c r="AG265">
+        <v>2.13</v>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ265">
         <v>1.25</v>
       </c>
-      <c r="W265">
-        <v>1.04</v>
-      </c>
-      <c r="X265">
-        <v>1.06</v>
-      </c>
-      <c r="Y265">
-        <v>1.5</v>
-      </c>
-      <c r="Z265">
-        <v>2.5</v>
-      </c>
-      <c r="AA265">
-        <v>2.63</v>
-      </c>
-      <c r="AB265">
-        <v>1.44</v>
-      </c>
-      <c r="AC265">
-        <v>5</v>
-      </c>
-      <c r="AD265">
-        <v>1.14</v>
-      </c>
-      <c r="AE265">
-        <v>1.03</v>
-      </c>
-      <c r="AF265">
-        <v>2.2</v>
-      </c>
-      <c r="AG265">
-        <v>1.61</v>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ265">
-        <v>1.3</v>
-      </c>
       <c r="AK265">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G266">
@@ -43676,71 +43676,71 @@
         <v>0</v>
       </c>
       <c r="Q266">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R266">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S266">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="T266">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U266">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V266">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W266">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X266">
+        <v>1.06</v>
+      </c>
+      <c r="Y266">
+        <v>1.5</v>
+      </c>
+      <c r="Z266">
+        <v>2.5</v>
+      </c>
+      <c r="AA266">
+        <v>2.63</v>
+      </c>
+      <c r="AB266">
+        <v>1.44</v>
+      </c>
+      <c r="AC266">
+        <v>5</v>
+      </c>
+      <c r="AD266">
+        <v>1.14</v>
+      </c>
+      <c r="AE266">
         <v>1.03</v>
       </c>
-      <c r="Y266">
-        <v>1.25</v>
-      </c>
-      <c r="Z266">
-        <v>3.5</v>
-      </c>
-      <c r="AA266">
-        <v>1.8</v>
-      </c>
-      <c r="AB266">
-        <v>1.91</v>
-      </c>
-      <c r="AC266">
-        <v>3.2</v>
-      </c>
-      <c r="AD266">
+      <c r="AF266">
+        <v>2.2</v>
+      </c>
+      <c r="AG266">
+        <v>1.61</v>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ266">
         <v>1.3</v>
       </c>
-      <c r="AE266">
-        <v>1.11</v>
-      </c>
-      <c r="AF266">
-        <v>1.65</v>
-      </c>
-      <c r="AG266">
-        <v>2.13</v>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ266">
-        <v>1.25</v>
-      </c>
       <c r="AK266">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -45632,55 +45632,55 @@
         <v>2.99</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z278">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O308">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="P308">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="Q308">
         <v>2.4</v>
       </c>
       <c r="R308">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S308">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T308">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U308">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V308">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W308">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X308">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y308">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z308">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA308">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB308">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AC308">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AD308">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE308">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF308">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG308">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>1.22</v>
       </c>
       <c r="AK308">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,80 +50676,80 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="O309">
-        <v>3.99</v>
+        <v>4.98</v>
       </c>
       <c r="P309">
-        <v>3.47</v>
+        <v>6.42</v>
       </c>
       <c r="Q309">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="R309">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S309">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T309">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="U309">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="V309">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="W309">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X309">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z309">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="AA309">
+        <v>1.36</v>
+      </c>
+      <c r="AB309">
+        <v>2.9</v>
+      </c>
+      <c r="AC309">
+        <v>1.95</v>
+      </c>
+      <c r="AD309">
+        <v>1.8</v>
+      </c>
+      <c r="AE309">
+        <v>1.3</v>
+      </c>
+      <c r="AF309">
         <v>1.45</v>
       </c>
-      <c r="AB309">
-        <v>2.35</v>
-      </c>
-      <c r="AC309">
-        <v>2.38</v>
-      </c>
-      <c r="AD309">
-        <v>1.53</v>
-      </c>
-      <c r="AE309">
-        <v>1.22</v>
-      </c>
-      <c r="AF309">
-        <v>1.5</v>
-      </c>
       <c r="AG309">
+        <v>2.46</v>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ309">
+        <v>1.14</v>
+      </c>
+      <c r="AK309">
         <v>2.45</v>
-      </c>
-      <c r="AH309" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI309" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ309">
-        <v>1.22</v>
-      </c>
-      <c r="AK309">
-        <v>1.8</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O310">
-        <v>4.98</v>
+        <v>4.01</v>
       </c>
       <c r="P310">
-        <v>6.42</v>
+        <v>3.44</v>
       </c>
       <c r="Q310">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="R310">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="S310">
         <v>1.2</v>
       </c>
       <c r="T310">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="U310">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V310">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="W310">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X310">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y310">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z310">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AA310">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB310">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AC310">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AD310">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE310">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF310">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG310">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK310">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AL310">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.98</v>
+        <v>4.1</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P31">
-        <v>3.15</v>
+        <v>1.71</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3.42</v>
+        <v>2.78</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>4.86</v>
+        <v>3.25</v>
       </c>
       <c r="AA31">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AB31">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD31">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AG31">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AK31">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="Q32">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="R32">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="AA32">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC32">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD32">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>1.62</v>
+        <v>3.15</v>
       </c>
       <c r="Q33">
-        <v>4.65</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
         <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>4.05</v>
+        <v>4.86</v>
       </c>
       <c r="AA33">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AB33">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD33">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
         <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AG33">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,65 +12045,65 @@
         </is>
       </c>
       <c r="N72">
+        <v>1.9</v>
+      </c>
+      <c r="O72">
+        <v>3.6</v>
+      </c>
+      <c r="P72">
+        <v>3.45</v>
+      </c>
+      <c r="Q72">
+        <v>2.42</v>
+      </c>
+      <c r="R72">
+        <v>2.43</v>
+      </c>
+      <c r="S72">
+        <v>1.25</v>
+      </c>
+      <c r="T72">
+        <v>3.4</v>
+      </c>
+      <c r="U72">
+        <v>2.29</v>
+      </c>
+      <c r="V72">
+        <v>1.55</v>
+      </c>
+      <c r="W72">
+        <v>1.12</v>
+      </c>
+      <c r="X72">
+        <v>1.03</v>
+      </c>
+      <c r="Y72">
+        <v>1.18</v>
+      </c>
+      <c r="Z72">
+        <v>4.52</v>
+      </c>
+      <c r="AA72">
+        <v>1.58</v>
+      </c>
+      <c r="AB72">
+        <v>2.19</v>
+      </c>
+      <c r="AC72">
+        <v>2.43</v>
+      </c>
+      <c r="AD72">
+        <v>1.44</v>
+      </c>
+      <c r="AE72">
+        <v>1.18</v>
+      </c>
+      <c r="AF72">
+        <v>1.53</v>
+      </c>
+      <c r="AG72">
         <v>2.38</v>
       </c>
-      <c r="O72">
-        <v>3.2</v>
-      </c>
-      <c r="P72">
-        <v>2.65</v>
-      </c>
-      <c r="Q72">
-        <v>2.95</v>
-      </c>
-      <c r="R72">
-        <v>2.14</v>
-      </c>
-      <c r="S72">
-        <v>1.33</v>
-      </c>
-      <c r="T72">
-        <v>3</v>
-      </c>
-      <c r="U72">
-        <v>2.66</v>
-      </c>
-      <c r="V72">
-        <v>1.39</v>
-      </c>
-      <c r="W72">
-        <v>1.07</v>
-      </c>
-      <c r="X72">
-        <v>1.01</v>
-      </c>
-      <c r="Y72">
-        <v>1.25</v>
-      </c>
-      <c r="Z72">
-        <v>3.28</v>
-      </c>
-      <c r="AA72">
-        <v>1.89</v>
-      </c>
-      <c r="AB72">
-        <v>1.83</v>
-      </c>
-      <c r="AC72">
-        <v>3.08</v>
-      </c>
-      <c r="AD72">
-        <v>1.28</v>
-      </c>
-      <c r="AE72">
-        <v>1.08</v>
-      </c>
-      <c r="AF72">
-        <v>1.68</v>
-      </c>
-      <c r="AG72">
-        <v>2.04</v>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q73">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="R73">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="S73">
+        <v>1.33</v>
+      </c>
+      <c r="T73">
+        <v>3</v>
+      </c>
+      <c r="U73">
+        <v>2.66</v>
+      </c>
+      <c r="V73">
+        <v>1.39</v>
+      </c>
+      <c r="W73">
+        <v>1.07</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
         <v>1.25</v>
       </c>
-      <c r="T73">
-        <v>3.4</v>
-      </c>
-      <c r="U73">
-        <v>2.29</v>
-      </c>
-      <c r="V73">
-        <v>1.55</v>
-      </c>
-      <c r="W73">
-        <v>1.12</v>
-      </c>
-      <c r="X73">
-        <v>1.03</v>
-      </c>
-      <c r="Y73">
-        <v>1.18</v>
-      </c>
       <c r="Z73">
-        <v>4.52</v>
+        <v>3.28</v>
       </c>
       <c r="AA73">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AB73">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AC73">
-        <v>2.43</v>
+        <v>3.08</v>
       </c>
       <c r="AD73">
+        <v>1.28</v>
+      </c>
+      <c r="AE73">
+        <v>1.08</v>
+      </c>
+      <c r="AF73">
+        <v>1.68</v>
+      </c>
+      <c r="AG73">
+        <v>2.04</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>1.34</v>
+      </c>
+      <c r="AK73">
         <v>1.44</v>
-      </c>
-      <c r="AE73">
-        <v>1.18</v>
-      </c>
-      <c r="AF73">
-        <v>1.53</v>
-      </c>
-      <c r="AG73">
-        <v>2.38</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.29</v>
-      </c>
-      <c r="AK73">
-        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P93">
-        <v>3.8</v>
+        <v>2.68</v>
       </c>
       <c r="Q93">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="R93">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S93">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T93">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="U93">
-        <v>3.12</v>
+        <v>2.58</v>
       </c>
       <c r="V93">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W93">
         <v>1.07</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z93">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA93">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AB93">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AC93">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD93">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AG93">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK93">
-        <v>2.01</v>
+        <v>1.52</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="O94">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P94">
-        <v>2.68</v>
+        <v>3.8</v>
       </c>
       <c r="Q94">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="R94">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S94">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="U94">
-        <v>2.58</v>
+        <v>3.12</v>
       </c>
       <c r="V94">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W94">
         <v>1.07</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z94">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA94">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AB94">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AC94">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD94">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF94">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.36</v>
+        <v>4.13</v>
       </c>
       <c r="O101">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P101">
-        <v>7.7</v>
+        <v>1.84</v>
       </c>
       <c r="Q101">
-        <v>1.76</v>
+        <v>4.2</v>
       </c>
       <c r="R101">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S101">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T101">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="U101">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="V101">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z101">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA101">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AB101">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC101">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="AD101">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE101">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF101">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,61 +16935,61 @@
         </is>
       </c>
       <c r="N102">
-        <v>4.13</v>
+        <v>2.4</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q102">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S102">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T102">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U102">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z102">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA102">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB102">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AC102">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AD102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE102">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG102">
         <v>2.1</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK102">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,80 +17098,80 @@
         </is>
       </c>
       <c r="N103">
+        <v>1.9</v>
+      </c>
+      <c r="O103">
+        <v>3.45</v>
+      </c>
+      <c r="P103">
+        <v>3.6</v>
+      </c>
+      <c r="Q103">
         <v>2.4</v>
       </c>
-      <c r="O103">
-        <v>3.3</v>
-      </c>
-      <c r="P103">
-        <v>2.8</v>
-      </c>
-      <c r="Q103">
-        <v>2.88</v>
-      </c>
       <c r="R103">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S103">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T103">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U103">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="V103">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W103">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
         <v>1</v>
       </c>
       <c r="Y103">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z103">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="AA103">
+        <v>1.86</v>
+      </c>
+      <c r="AB103">
+        <v>1.81</v>
+      </c>
+      <c r="AC103">
+        <v>3.3</v>
+      </c>
+      <c r="AD103">
+        <v>1.32</v>
+      </c>
+      <c r="AE103">
+        <v>1.11</v>
+      </c>
+      <c r="AF103">
+        <v>1.75</v>
+      </c>
+      <c r="AG103">
+        <v>1.93</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103">
+        <v>1.29</v>
+      </c>
+      <c r="AK103">
         <v>1.85</v>
-      </c>
-      <c r="AB103">
-        <v>1.91</v>
-      </c>
-      <c r="AC103">
-        <v>2.94</v>
-      </c>
-      <c r="AD103">
-        <v>1.36</v>
-      </c>
-      <c r="AE103">
-        <v>1.08</v>
-      </c>
-      <c r="AF103">
-        <v>1.7</v>
-      </c>
-      <c r="AG103">
-        <v>2.1</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>1.33</v>
-      </c>
-      <c r="AK103">
-        <v>1.55</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="O104">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P104">
-        <v>3.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q104">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="R104">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="S104">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T104">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="U104">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="V104">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z104">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="AA104">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AB104">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AC104">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="AD104">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF104">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AG104">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK104">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G106">
@@ -17583,68 +17583,68 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N106">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="O106">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="Q106">
-        <v>1.75</v>
+        <v>2.64</v>
       </c>
       <c r="R106">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S106">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="U106">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V106">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W106">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA106">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AB106">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC106">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="AD106">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AE106">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG106">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>2.93</v>
+        <v>1.65</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,65 +17750,65 @@
         </is>
       </c>
       <c r="N107">
+        <v>5.75</v>
+      </c>
+      <c r="O107">
+        <v>4.5</v>
+      </c>
+      <c r="P107">
+        <v>1.5</v>
+      </c>
+      <c r="Q107">
+        <v>5.75</v>
+      </c>
+      <c r="R107">
+        <v>2.45</v>
+      </c>
+      <c r="S107">
+        <v>1.25</v>
+      </c>
+      <c r="T107">
+        <v>3.7</v>
+      </c>
+      <c r="U107">
+        <v>2.27</v>
+      </c>
+      <c r="V107">
+        <v>1.6</v>
+      </c>
+      <c r="W107">
+        <v>1.11</v>
+      </c>
+      <c r="X107">
+        <v>1.02</v>
+      </c>
+      <c r="Y107">
+        <v>1.17</v>
+      </c>
+      <c r="Z107">
+        <v>5.03</v>
+      </c>
+      <c r="AA107">
+        <v>1.49</v>
+      </c>
+      <c r="AB107">
+        <v>2.47</v>
+      </c>
+      <c r="AC107">
+        <v>2.35</v>
+      </c>
+      <c r="AD107">
+        <v>1.57</v>
+      </c>
+      <c r="AE107">
+        <v>1.2</v>
+      </c>
+      <c r="AF107">
+        <v>1.63</v>
+      </c>
+      <c r="AG107">
         <v>2.15</v>
       </c>
-      <c r="O107">
-        <v>3.4</v>
-      </c>
-      <c r="P107">
-        <v>3.25</v>
-      </c>
-      <c r="Q107">
-        <v>2.64</v>
-      </c>
-      <c r="R107">
-        <v>2.3</v>
-      </c>
-      <c r="S107">
-        <v>1.36</v>
-      </c>
-      <c r="T107">
-        <v>2.9</v>
-      </c>
-      <c r="U107">
-        <v>2.5</v>
-      </c>
-      <c r="V107">
-        <v>1.44</v>
-      </c>
-      <c r="W107">
-        <v>1.08</v>
-      </c>
-      <c r="X107">
-        <v>1.05</v>
-      </c>
-      <c r="Y107">
-        <v>1.25</v>
-      </c>
-      <c r="Z107">
-        <v>3.6</v>
-      </c>
-      <c r="AA107">
-        <v>1.9</v>
-      </c>
-      <c r="AB107">
-        <v>1.85</v>
-      </c>
-      <c r="AC107">
-        <v>2.8</v>
-      </c>
-      <c r="AD107">
-        <v>1.31</v>
-      </c>
-      <c r="AE107">
-        <v>1.1</v>
-      </c>
-      <c r="AF107">
-        <v>1.7</v>
-      </c>
-      <c r="AG107">
-        <v>2.1</v>
-      </c>
       <c r="AH107" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>1.65</v>
+        <v>1.14</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G108">
@@ -17909,68 +17909,68 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N108">
-        <v>5.75</v>
+        <v>1.38</v>
       </c>
       <c r="O108">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="P108">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="Q108">
-        <v>5.75</v>
+        <v>1.75</v>
       </c>
       <c r="R108">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S108">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T108">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="U108">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V108">
         <v>1.6</v>
       </c>
       <c r="W108">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X108">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z108">
-        <v>5.03</v>
+        <v>4.75</v>
       </c>
       <c r="AA108">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AB108">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AC108">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AD108">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE108">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF108">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AG108">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK108">
-        <v>1.14</v>
+        <v>2.93</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,61 +18076,61 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="O109">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P109">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="Q109">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="R109">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U109">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="V109">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z109">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA109">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB109">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC109">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD109">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE109">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF109">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG109">
         <v>2.05</v>
@@ -18149,7 +18149,7 @@
         <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,61 +18239,61 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="O110">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="Q110">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="R110">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S110">
+        <v>1.33</v>
+      </c>
+      <c r="T110">
+        <v>2.85</v>
+      </c>
+      <c r="U110">
+        <v>2.69</v>
+      </c>
+      <c r="V110">
+        <v>1.44</v>
+      </c>
+      <c r="W110">
+        <v>1.1</v>
+      </c>
+      <c r="X110">
+        <v>1.05</v>
+      </c>
+      <c r="Y110">
+        <v>1.25</v>
+      </c>
+      <c r="Z110">
+        <v>3.6</v>
+      </c>
+      <c r="AA110">
+        <v>1.87</v>
+      </c>
+      <c r="AB110">
+        <v>1.85</v>
+      </c>
+      <c r="AC110">
+        <v>3.1</v>
+      </c>
+      <c r="AD110">
         <v>1.3</v>
       </c>
-      <c r="T110">
-        <v>3.2</v>
-      </c>
-      <c r="U110">
-        <v>2.4</v>
-      </c>
-      <c r="V110">
-        <v>1.5</v>
-      </c>
-      <c r="W110">
+      <c r="AE110">
         <v>1.08</v>
       </c>
-      <c r="X110">
-        <v>1.01</v>
-      </c>
-      <c r="Y110">
-        <v>1.19</v>
-      </c>
-      <c r="Z110">
-        <v>3.9</v>
-      </c>
-      <c r="AA110">
-        <v>1.75</v>
-      </c>
-      <c r="AB110">
-        <v>2.04</v>
-      </c>
-      <c r="AC110">
-        <v>2.8</v>
-      </c>
-      <c r="AD110">
-        <v>1.39</v>
-      </c>
-      <c r="AE110">
-        <v>1.14</v>
-      </c>
       <c r="AF110">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG110">
         <v>2.05</v>
@@ -18312,7 +18312,7 @@
         <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="O227">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="P227">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="Q227">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="R227">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="S227">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="T227">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="U227">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="V227">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W227">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X227">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Y227">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="Z227">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AA227">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AB227">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AC227">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AD227">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE227">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF227">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG227">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AK227">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O228">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P228">
-        <v>4.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q228">
-        <v>2.68</v>
+        <v>3.06</v>
       </c>
       <c r="R228">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S228">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="T228">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U228">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="V228">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="W228">
+        <v>1.04</v>
+      </c>
+      <c r="X228">
+        <v>1.1</v>
+      </c>
+      <c r="Y228">
+        <v>1.44</v>
+      </c>
+      <c r="Z228">
+        <v>2.63</v>
+      </c>
+      <c r="AA228">
+        <v>2.3</v>
+      </c>
+      <c r="AB228">
+        <v>1.51</v>
+      </c>
+      <c r="AC228">
+        <v>4.2</v>
+      </c>
+      <c r="AD228">
+        <v>1.17</v>
+      </c>
+      <c r="AE228">
         <v>1.01</v>
       </c>
-      <c r="X228">
-        <v>1.12</v>
-      </c>
-      <c r="Y228">
-        <v>1.57</v>
-      </c>
-      <c r="Z228">
-        <v>2.3</v>
-      </c>
-      <c r="AA228">
-        <v>3.1</v>
-      </c>
-      <c r="AB228">
-        <v>1.4</v>
-      </c>
-      <c r="AC228">
-        <v>6</v>
-      </c>
-      <c r="AD228">
-        <v>1.09</v>
-      </c>
-      <c r="AE228">
-        <v>1.03</v>
-      </c>
       <c r="AF228">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AG228">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>1.36</v>
       </c>
       <c r="AK228">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O229">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P229">
         <v>2.75</v>
       </c>
       <c r="Q229">
-        <v>3.06</v>
+        <v>3.64</v>
       </c>
       <c r="R229">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="S229">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="T229">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U229">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="V229">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="W229">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X229">
+        <v>1.15</v>
+      </c>
+      <c r="Y229">
+        <v>1.56</v>
+      </c>
+      <c r="Z229">
+        <v>2.1</v>
+      </c>
+      <c r="AA229">
+        <v>2.97</v>
+      </c>
+      <c r="AB229">
+        <v>1.33</v>
+      </c>
+      <c r="AC229">
+        <v>5.2</v>
+      </c>
+      <c r="AD229">
         <v>1.1</v>
       </c>
-      <c r="Y229">
-        <v>1.44</v>
-      </c>
-      <c r="Z229">
-        <v>2.63</v>
-      </c>
-      <c r="AA229">
-        <v>2.3</v>
-      </c>
-      <c r="AB229">
-        <v>1.51</v>
-      </c>
-      <c r="AC229">
-        <v>4.2</v>
-      </c>
-      <c r="AD229">
-        <v>1.17</v>
-      </c>
       <c r="AE229">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF229">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AG229">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>1.36</v>
       </c>
       <c r="AK229">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
+        <v>2.62</v>
+      </c>
+      <c r="O230">
         <v>2.7</v>
-      </c>
-      <c r="O230">
-        <v>2.62</v>
       </c>
       <c r="P230">
         <v>2.75</v>
       </c>
       <c r="Q230">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="R230">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S230">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="T230">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U230">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="V230">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W230">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X230">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y230">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="Z230">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AA230">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AB230">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC230">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AD230">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE230">
         <v>1.02</v>
       </c>
       <c r="AF230">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AG230">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
+        <v>1.35</v>
+      </c>
+      <c r="AK230">
         <v>1.36</v>
-      </c>
-      <c r="AK230">
-        <v>1.37</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="O231">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P231">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q231">
-        <v>3.81</v>
+        <v>3</v>
       </c>
       <c r="R231">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S231">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="T231">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="U231">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="V231">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W231">
         <v>1.02</v>
       </c>
       <c r="X231">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y231">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Z231">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AA231">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AB231">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC231">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD231">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE231">
         <v>1.02</v>
       </c>
       <c r="AF231">
-        <v>2.23</v>
+        <v>2.57</v>
       </c>
       <c r="AG231">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AK231">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -40640,7 +40640,7 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK247">
         <v>1.85</v>
@@ -41059,58 +41059,58 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="O250">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="P250">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q250">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R250">
         <v>2.4</v>
       </c>
       <c r="S250">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T250">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U250">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V250">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W250">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X250">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y250">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z250">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA250">
         <v>1.75</v>
       </c>
       <c r="AB250">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC250">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD250">
         <v>1.36</v>
       </c>
       <c r="AE250">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF250">
         <v>1.95</v>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK250">
         <v>2.8</v>
@@ -41711,31 +41711,31 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O254">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="P254">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q254">
         <v>1.77</v>
       </c>
       <c r="R254">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S254">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T254">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="U254">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V254">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W254">
         <v>1.1</v>
@@ -41750,22 +41750,22 @@
         <v>3.6</v>
       </c>
       <c r="AA254">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB254">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC254">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AD254">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE254">
         <v>1.11</v>
       </c>
       <c r="AF254">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG254">
         <v>1.6</v>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK254">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,19 +41874,19 @@
         </is>
       </c>
       <c r="N255">
-        <v>3.04</v>
+        <v>1.81</v>
       </c>
       <c r="O255">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P255">
-        <v>2.35</v>
+        <v>4.37</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S255">
         <v>0</v>
@@ -41895,34 +41895,34 @@
         <v>0</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X255">
         <v>0</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE255">
         <v>0</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,19 +42037,19 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.81</v>
+        <v>3.04</v>
       </c>
       <c r="O256">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P256">
-        <v>4.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q256">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R256">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S256">
         <v>0</v>
@@ -42058,34 +42058,34 @@
         <v>0</v>
       </c>
       <c r="U256">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V256">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W256">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X256">
         <v>0</v>
       </c>
       <c r="Y256">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z256">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA256">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB256">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC256">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD256">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE256">
         <v>0</v>
@@ -44159,13 +44159,13 @@
         <v>1.8</v>
       </c>
       <c r="O269">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P269">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="Q269">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R269">
         <v>2.09</v>
@@ -44177,13 +44177,13 @@
         <v>2.88</v>
       </c>
       <c r="U269">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V269">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W269">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X269">
         <v>1.06</v>
@@ -44192,16 +44192,16 @@
         <v>1.35</v>
       </c>
       <c r="Z269">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA269">
         <v>2.05</v>
       </c>
       <c r="AB269">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC269">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AD269">
         <v>1.25</v>
@@ -44210,7 +44210,7 @@
         <v>1.08</v>
       </c>
       <c r="AF269">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG269">
         <v>1.8</v>
@@ -44645,31 +44645,31 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="O272">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="P272">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q272">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="R272">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S272">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T272">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U272">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V272">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W272">
         <v>1.05</v>
@@ -44681,28 +44681,28 @@
         <v>1.3</v>
       </c>
       <c r="Z272">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA272">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB272">
         <v>1.75</v>
       </c>
       <c r="AC272">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AD272">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE272">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF272">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG272">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>1.3</v>
       </c>
       <c r="AK272">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44974,25 +44974,25 @@
         <v>1.96</v>
       </c>
       <c r="O274">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P274">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="Q274">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R274">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S274">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="T274">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U274">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V274">
         <v>1.23</v>
@@ -45001,34 +45001,34 @@
         <v>1.05</v>
       </c>
       <c r="X274">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y274">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z274">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA274">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB274">
         <v>1.5</v>
       </c>
       <c r="AC274">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD274">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE274">
         <v>1.04</v>
       </c>
       <c r="AF274">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AG274">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK274">
         <v>1.73</v>
@@ -45134,34 +45134,34 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O275">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P275">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q275">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R275">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S275">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T275">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="U275">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V275">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W275">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X275">
         <v>1.1</v>
@@ -45173,7 +45173,7 @@
         <v>2.45</v>
       </c>
       <c r="AA275">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB275">
         <v>1.48</v>
@@ -45182,16 +45182,16 @@
         <v>5.25</v>
       </c>
       <c r="AD275">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE275">
         <v>1</v>
       </c>
       <c r="AF275">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG275">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK275">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,65 +49209,65 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="O300">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P300">
-        <v>4.58</v>
+        <v>3.75</v>
       </c>
       <c r="Q300">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="R300">
         <v>2.3</v>
       </c>
       <c r="S300">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T300">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U300">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="V300">
         <v>1.53</v>
       </c>
       <c r="W300">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X300">
         <v>1.03</v>
       </c>
       <c r="Y300">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z300">
         <v>4.5</v>
       </c>
       <c r="AA300">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB300">
+        <v>2.15</v>
+      </c>
+      <c r="AC300">
+        <v>2.63</v>
+      </c>
+      <c r="AD300">
+        <v>1.4</v>
+      </c>
+      <c r="AE300">
+        <v>1.14</v>
+      </c>
+      <c r="AF300">
+        <v>1.5</v>
+      </c>
+      <c r="AG300">
         <v>2.25</v>
       </c>
-      <c r="AC300">
-        <v>2.62</v>
-      </c>
-      <c r="AD300">
-        <v>1.44</v>
-      </c>
-      <c r="AE300">
-        <v>1.15</v>
-      </c>
-      <c r="AF300">
-        <v>1.57</v>
-      </c>
-      <c r="AG300">
-        <v>2.16</v>
-      </c>
       <c r="AH300" t="inlineStr">
         <is>
           <t>[]</t>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK300">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="O301">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P301">
-        <v>3.75</v>
+        <v>4.58</v>
       </c>
       <c r="Q301">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="R301">
         <v>2.3</v>
       </c>
       <c r="S301">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T301">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U301">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="V301">
         <v>1.53</v>
       </c>
       <c r="W301">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X301">
         <v>1.03</v>
       </c>
       <c r="Y301">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z301">
         <v>4.5</v>
       </c>
       <c r="AA301">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB301">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC301">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD301">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE301">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF301">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG301">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK301">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AL301">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.15</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="Q31">
-        <v>4.65</v>
+        <v>2.5</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S31">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U31">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA31">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AB31">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AC31">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD31">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF31">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="O32">
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="R32">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.31</v>
+        <v>2.95</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA32">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AE32">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AG32">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AK32">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q33">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="R33">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="V33">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
         <v>1.04</v>
       </c>
-      <c r="X33">
-        <v>1</v>
-      </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,65 +12208,65 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="O73">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="Q73">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="R73">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T73">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U73">
+        <v>2.25</v>
+      </c>
+      <c r="V73">
+        <v>1.54</v>
+      </c>
+      <c r="W73">
+        <v>1.12</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>1.18</v>
+      </c>
+      <c r="Z73">
+        <v>3.9</v>
+      </c>
+      <c r="AA73">
+        <v>1.6</v>
+      </c>
+      <c r="AB73">
+        <v>2.18</v>
+      </c>
+      <c r="AC73">
+        <v>2.39</v>
+      </c>
+      <c r="AD73">
+        <v>1.44</v>
+      </c>
+      <c r="AE73">
+        <v>1.17</v>
+      </c>
+      <c r="AF73">
+        <v>1.5</v>
+      </c>
+      <c r="AG73">
         <v>2.38</v>
       </c>
-      <c r="V73">
-        <v>1.53</v>
-      </c>
-      <c r="W73">
-        <v>1.11</v>
-      </c>
-      <c r="X73">
-        <v>1</v>
-      </c>
-      <c r="Y73">
-        <v>1.19</v>
-      </c>
-      <c r="Z73">
-        <v>4.2</v>
-      </c>
-      <c r="AA73">
-        <v>1.66</v>
-      </c>
-      <c r="AB73">
-        <v>2.09</v>
-      </c>
-      <c r="AC73">
-        <v>2.6</v>
-      </c>
-      <c r="AD73">
-        <v>1.41</v>
-      </c>
-      <c r="AE73">
-        <v>1.13</v>
-      </c>
-      <c r="AF73">
-        <v>1.55</v>
-      </c>
-      <c r="AG73">
-        <v>2.3</v>
-      </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK73">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O74">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P74">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="Q74">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="R74">
+        <v>2.37</v>
+      </c>
+      <c r="S74">
+        <v>1.3</v>
+      </c>
+      <c r="T74">
+        <v>3.2</v>
+      </c>
+      <c r="U74">
         <v>2.38</v>
       </c>
-      <c r="S74">
-        <v>1.29</v>
-      </c>
-      <c r="T74">
-        <v>3.3</v>
-      </c>
-      <c r="U74">
-        <v>2.25</v>
-      </c>
       <c r="V74">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W74">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z74">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA74">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB74">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AC74">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AD74">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE74">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG74">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,61 +17098,61 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="O103">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="P103">
-        <v>2.12</v>
+        <v>3.7</v>
       </c>
       <c r="Q103">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="R103">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S103">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T103">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U103">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="V103">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W103">
         <v>1.05</v>
       </c>
       <c r="X103">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z103">
-        <v>3.08</v>
+        <v>3.53</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB103">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AC103">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF103">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG103">
         <v>2</v>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P104">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q104">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="R104">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S104">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="V104">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W104">
         <v>1.05</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y104">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="AA104">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB104">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC104">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="AD104">
+        <v>1.29</v>
+      </c>
+      <c r="AE104">
+        <v>1.06</v>
+      </c>
+      <c r="AF104">
+        <v>1.8</v>
+      </c>
+      <c r="AG104">
+        <v>2</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.3</v>
       </c>
-      <c r="AE104">
-        <v>1.09</v>
-      </c>
-      <c r="AF104">
-        <v>1.66</v>
-      </c>
-      <c r="AG104">
-        <v>2.06</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.33</v>
-      </c>
       <c r="AK104">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="O105">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="P105">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="Q105">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="R105">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="S105">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T105">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="U105">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="V105">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z105">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="AA105">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB105">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC105">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="AD105">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE105">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK105">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.36</v>
+        <v>4.22</v>
       </c>
       <c r="O106">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P106">
-        <v>7.4</v>
+        <v>1.82</v>
       </c>
       <c r="Q106">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="R106">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T106">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="U106">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V106">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA106">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AB106">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AC106">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AD106">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE106">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="AK106">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,65 +17750,65 @@
         </is>
       </c>
       <c r="N107">
-        <v>4.22</v>
+        <v>2.4</v>
       </c>
       <c r="O107">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P107">
-        <v>1.82</v>
+        <v>2.85</v>
       </c>
       <c r="Q107">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S107">
         <v>1.35</v>
       </c>
       <c r="T107">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U107">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="V107">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z107">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="AA107">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AB107">
+        <v>1.94</v>
+      </c>
+      <c r="AC107">
+        <v>2.99</v>
+      </c>
+      <c r="AD107">
+        <v>1.3</v>
+      </c>
+      <c r="AE107">
+        <v>1.09</v>
+      </c>
+      <c r="AF107">
+        <v>1.66</v>
+      </c>
+      <c r="AG107">
         <v>2.06</v>
       </c>
-      <c r="AC107">
-        <v>2.88</v>
-      </c>
-      <c r="AD107">
-        <v>1.35</v>
-      </c>
-      <c r="AE107">
-        <v>1.14</v>
-      </c>
-      <c r="AF107">
-        <v>1.67</v>
-      </c>
-      <c r="AG107">
-        <v>2.1</v>
-      </c>
       <c r="AH107" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="AK107">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -38454,7 +38454,7 @@
         <v>2.4</v>
       </c>
       <c r="O234">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P234">
         <v>2.8</v>
@@ -38632,7 +38632,7 @@
         <v>1.57</v>
       </c>
       <c r="T235">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U235">
         <v>4.2</v>
@@ -38668,7 +38668,7 @@
         <v>1.02</v>
       </c>
       <c r="AF235">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG235">
         <v>1.49</v>
@@ -38795,7 +38795,7 @@
         <v>1.76</v>
       </c>
       <c r="T236">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U236">
         <v>4.5</v>
@@ -38847,7 +38847,7 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AK236">
         <v>1.59</v>
@@ -38976,7 +38976,7 @@
         <v>1.7</v>
       </c>
       <c r="Z237">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AA237">
         <v>2.8</v>
@@ -42206,10 +42206,10 @@
         <v>4.5</v>
       </c>
       <c r="P257">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q257">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R257">
         <v>2.33</v>
@@ -42692,7 +42692,7 @@
         <v>2.2</v>
       </c>
       <c r="O260">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P260">
         <v>3.5</v>
@@ -42722,7 +42722,7 @@
         <v>1.14</v>
       </c>
       <c r="Y260">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="Z260">
         <v>2.09</v>
@@ -45840,7 +45840,7 @@
         <v>1.11</v>
       </c>
       <c r="AF279">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG279">
         <v>1.94</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R17">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U17">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG17">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.35</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P18">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y18">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z18">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AB18">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AG18">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q19">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z19">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC19">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -6035,7 +6035,7 @@
         <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V35">
         <v>1.5</v>
@@ -6062,16 +6062,16 @@
         <v>2.7</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
         <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="O51">
         <v>3.55</v>
       </c>
       <c r="P51">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q51">
         <v>2.9</v>
       </c>
       <c r="R51">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
         <v>1.2</v>
@@ -8824,10 +8824,10 @@
         <v>5.55</v>
       </c>
       <c r="AA52">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB52">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AC52">
         <v>2</v>
@@ -8858,7 +8858,7 @@
         <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="P53">
-        <v>2.46</v>
+        <v>5.25</v>
       </c>
       <c r="Q53">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="R53">
-        <v>2.21</v>
+        <v>2.85</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="U53">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="V53">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z53">
-        <v>4.25</v>
+        <v>7.3</v>
       </c>
       <c r="AA53">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AB53">
-        <v>2.25</v>
+        <v>3.51</v>
       </c>
       <c r="AC53">
-        <v>2.47</v>
+        <v>1.65</v>
       </c>
       <c r="AD53">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="AE53">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AF53">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG53">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="O54">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="Q54">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="R54">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="S54">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="T54">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="V54">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="W54">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="Z54">
-        <v>7.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA54">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB54">
-        <v>3.46</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="AD54">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="AE54">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG54">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.91</v>
+        <v>4.22</v>
       </c>
       <c r="O103">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P103">
-        <v>3.7</v>
+        <v>1.82</v>
       </c>
       <c r="Q103">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="R103">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S103">
         <v>1.35</v>
       </c>
       <c r="T103">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="U103">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="V103">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W103">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z103">
-        <v>3.53</v>
+        <v>3.8</v>
       </c>
       <c r="AA103">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB103">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AC103">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD103">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE103">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AK103">
-        <v>1.88</v>
+        <v>1.2</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="O104">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="Q104">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="R104">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T104">
+        <v>3</v>
+      </c>
+      <c r="U104">
         <v>2.8</v>
       </c>
-      <c r="U104">
-        <v>3.01</v>
-      </c>
       <c r="V104">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
         <v>1.05</v>
       </c>
       <c r="X104">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y104">
+        <v>1.27</v>
+      </c>
+      <c r="Z104">
+        <v>3.77</v>
+      </c>
+      <c r="AA104">
+        <v>1.91</v>
+      </c>
+      <c r="AB104">
+        <v>1.94</v>
+      </c>
+      <c r="AC104">
+        <v>2.99</v>
+      </c>
+      <c r="AD104">
         <v>1.3</v>
       </c>
-      <c r="Z104">
-        <v>3.08</v>
-      </c>
-      <c r="AA104">
-        <v>2</v>
-      </c>
-      <c r="AB104">
-        <v>1.79</v>
-      </c>
-      <c r="AC104">
-        <v>3.5</v>
-      </c>
-      <c r="AD104">
-        <v>1.29</v>
-      </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF104">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG104">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>4.22</v>
+        <v>3.25</v>
       </c>
       <c r="O106">
+        <v>3.35</v>
+      </c>
+      <c r="P106">
+        <v>2.12</v>
+      </c>
+      <c r="Q106">
         <v>3.7</v>
       </c>
-      <c r="P106">
-        <v>1.82</v>
-      </c>
-      <c r="Q106">
-        <v>4.4</v>
-      </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S106">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T106">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U106">
-        <v>2.55</v>
+        <v>3.01</v>
       </c>
       <c r="V106">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W106">
+        <v>1.05</v>
+      </c>
+      <c r="X106">
         <v>1.06</v>
       </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
       <c r="Y106">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA106">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB106">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AC106">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AD106">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE106">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF106">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG106">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,31 +17750,31 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="O107">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="P107">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q107">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="R107">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S107">
         <v>1.35</v>
       </c>
       <c r="T107">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U107">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W107">
         <v>1.05</v>
@@ -17783,31 +17783,31 @@
         <v>1</v>
       </c>
       <c r="Y107">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z107">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="AA107">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB107">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC107">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AD107">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE107">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G112">
@@ -18561,68 +18561,68 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N112">
+        <v>1.34</v>
+      </c>
+      <c r="O112">
+        <v>5.25</v>
+      </c>
+      <c r="P112">
+        <v>8</v>
+      </c>
+      <c r="Q112">
+        <v>1.75</v>
+      </c>
+      <c r="R112">
+        <v>2.55</v>
+      </c>
+      <c r="S112">
+        <v>1.28</v>
+      </c>
+      <c r="T112">
+        <v>3.34</v>
+      </c>
+      <c r="U112">
+        <v>2.34</v>
+      </c>
+      <c r="V112">
+        <v>1.53</v>
+      </c>
+      <c r="W112">
+        <v>1.1</v>
+      </c>
+      <c r="X112">
+        <v>1.03</v>
+      </c>
+      <c r="Y112">
+        <v>1.17</v>
+      </c>
+      <c r="Z112">
+        <v>5</v>
+      </c>
+      <c r="AA112">
+        <v>1.54</v>
+      </c>
+      <c r="AB112">
+        <v>2.3</v>
+      </c>
+      <c r="AC112">
+        <v>2.41</v>
+      </c>
+      <c r="AD112">
         <v>1.57</v>
       </c>
-      <c r="O112">
-        <v>4</v>
-      </c>
-      <c r="P112">
-        <v>5</v>
-      </c>
-      <c r="Q112">
-        <v>2.11</v>
-      </c>
-      <c r="R112">
-        <v>2.3</v>
-      </c>
-      <c r="S112">
-        <v>1.3</v>
-      </c>
-      <c r="T112">
-        <v>3.2</v>
-      </c>
-      <c r="U112">
-        <v>2.4</v>
-      </c>
-      <c r="V112">
-        <v>1.5</v>
-      </c>
-      <c r="W112">
-        <v>1.07</v>
-      </c>
-      <c r="X112">
-        <v>1.01</v>
-      </c>
-      <c r="Y112">
-        <v>1.22</v>
-      </c>
-      <c r="Z112">
-        <v>4.21</v>
-      </c>
-      <c r="AA112">
-        <v>1.73</v>
-      </c>
-      <c r="AB112">
-        <v>2.02</v>
-      </c>
-      <c r="AC112">
-        <v>2.76</v>
-      </c>
-      <c r="AD112">
-        <v>1.39</v>
-      </c>
       <c r="AE112">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF112">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG112">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AK112">
-        <v>2.2</v>
+        <v>2.93</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G113">
@@ -18724,68 +18724,68 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N113">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="O113">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="P113">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q113">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="R113">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="S113">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T113">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U113">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V113">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W113">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X113">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>5</v>
+        <v>4.21</v>
       </c>
       <c r="AA113">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AB113">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC113">
-        <v>2.41</v>
+        <v>2.76</v>
       </c>
       <c r="AD113">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AE113">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF113">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="O219">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P219">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q219">
         <v>2.5</v>
@@ -38303,7 +38303,7 @@
         <v>1.9</v>
       </c>
       <c r="S233">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="T233">
         <v>2.3</v>
@@ -38457,7 +38457,7 @@
         <v>2.9</v>
       </c>
       <c r="P234">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q234">
         <v>3.08</v>
@@ -38478,7 +38478,7 @@
         <v>1.3</v>
       </c>
       <c r="W234">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X234">
         <v>1.07</v>
@@ -38508,7 +38508,7 @@
         <v>1.94</v>
       </c>
       <c r="AG234">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>1.57</v>
       </c>
       <c r="T235">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U235">
         <v>4.2</v>
@@ -38671,7 +38671,7 @@
         <v>2.38</v>
       </c>
       <c r="AG235">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38789,19 +38789,19 @@
         <v>3.02</v>
       </c>
       <c r="R236">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="S236">
         <v>1.76</v>
       </c>
       <c r="T236">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U236">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="V236">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W236">
         <v>1.02</v>
@@ -38982,13 +38982,13 @@
         <v>2.8</v>
       </c>
       <c r="AB237">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AC237">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AD237">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE237">
         <v>1.02</v>
@@ -39010,7 +39010,7 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK237">
         <v>1.44</v>
@@ -42689,7 +42689,7 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O260">
         <v>2.75</v>
@@ -42701,13 +42701,13 @@
         <v>3.2</v>
       </c>
       <c r="R260">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="S260">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T260">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U260">
         <v>4.25</v>
@@ -42734,10 +42734,10 @@
         <v>1.33</v>
       </c>
       <c r="AC260">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AD260">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE260">
         <v>1.02</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
         <v>3.1</v>
       </c>
       <c r="P20">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U20">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
         <v>1.38</v>
@@ -3608,10 +3608,10 @@
         <v>3.61</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC20">
         <v>3.08</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>1.36</v>
       </c>
       <c r="Q38">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="R38">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U38">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="V38">
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z38">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA38">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB38">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AC38">
         <v>2.65</v>
       </c>
       <c r="AD38">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG38">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O39">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="P39">
-        <v>3.45</v>
+        <v>3.27</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -6681,16 +6681,16 @@
         <v>1.98</v>
       </c>
       <c r="S39">
+        <v>1.44</v>
+      </c>
+      <c r="T39">
+        <v>2.54</v>
+      </c>
+      <c r="U39">
+        <v>2.82</v>
+      </c>
+      <c r="V39">
         <v>1.36</v>
-      </c>
-      <c r="T39">
-        <v>2.88</v>
-      </c>
-      <c r="U39">
-        <v>2.76</v>
-      </c>
-      <c r="V39">
-        <v>1.33</v>
       </c>
       <c r="W39">
         <v>1.05</v>
@@ -6705,10 +6705,10 @@
         <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AB39">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
         <v>3.7</v>
@@ -6720,7 +6720,7 @@
         <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG39">
         <v>1.91</v>
@@ -6844,25 +6844,25 @@
         <v>2.12</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
         <v>2.8</v>
       </c>
       <c r="U40">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="V40">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
         <v>1.06</v>
       </c>
       <c r="Y40">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
         <v>3</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O41">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P41">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.03</v>
+        <v>2.82</v>
       </c>
       <c r="U41">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
         <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.05</v>
@@ -7031,10 +7031,10 @@
         <v>3.75</v>
       </c>
       <c r="AA41">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC41">
         <v>2.97</v>
@@ -7046,10 +7046,10 @@
         <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG41">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7161,10 +7161,10 @@
         <v>3.35</v>
       </c>
       <c r="P42">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q42">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="R42">
         <v>2.2</v>
@@ -7176,10 +7176,10 @@
         <v>3.02</v>
       </c>
       <c r="U42">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W42">
         <v>1.09</v>
@@ -7212,7 +7212,7 @@
         <v>1.7</v>
       </c>
       <c r="AG42">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -7363,13 +7363,13 @@
         <v>1.97</v>
       </c>
       <c r="AC43">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
         <v>1.67</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="O44">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="P44">
         <v>3</v>
@@ -7493,7 +7493,7 @@
         <v>2.7</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S44">
         <v>1.39</v>
@@ -7523,13 +7523,13 @@
         <v>1.92</v>
       </c>
       <c r="AB44">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC44">
         <v>3.3</v>
       </c>
       <c r="AD44">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
         <v>1.08</v>
@@ -8305,13 +8305,13 @@
         <v>5</v>
       </c>
       <c r="Q49">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="R49">
         <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T49">
         <v>3.25</v>
@@ -8320,7 +8320,7 @@
         <v>2.55</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
         <v>1.08</v>
@@ -8329,28 +8329,28 @@
         <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>3.75</v>
+        <v>4.06</v>
       </c>
       <c r="AA49">
         <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC49">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD49">
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
         <v>2</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
         <v>2.08</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P50">
         <v>3.4</v>
@@ -8474,16 +8474,16 @@
         <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V50">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
         <v>1.08</v>
@@ -8513,7 +8513,7 @@
         <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG50">
         <v>2.16</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>5.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q53">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="R53">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="S53">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="T53">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="V53">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="W53">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="Z53">
-        <v>7.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA53">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
-        <v>3.51</v>
+        <v>2.3</v>
       </c>
       <c r="AC53">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="AD53">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AE53">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG53">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="P54">
-        <v>2.44</v>
+        <v>5.25</v>
       </c>
       <c r="Q54">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="R54">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="S54">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="T54">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="U54">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="V54">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z54">
-        <v>4.25</v>
+        <v>7.3</v>
       </c>
       <c r="AA54">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AB54">
-        <v>2.3</v>
+        <v>3.51</v>
       </c>
       <c r="AC54">
-        <v>2.47</v>
+        <v>1.65</v>
       </c>
       <c r="AD54">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AF54">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG54">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK54">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10309,7 +10309,7 @@
         <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,25 +10415,25 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="O62">
         <v>3.15</v>
       </c>
       <c r="P62">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="Q62">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="R62">
         <v>2.13</v>
       </c>
       <c r="S62">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T62">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U62">
         <v>3.18</v>
@@ -10445,22 +10445,22 @@
         <v>1.03</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
         <v>1.36</v>
       </c>
       <c r="Z62">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA62">
         <v>2.17</v>
       </c>
       <c r="AB62">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC62">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="AD62">
         <v>1.25</v>
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG62">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.29</v>
       </c>
       <c r="AK62">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10744,10 +10744,10 @@
         <v>1.85</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q64">
         <v>2.41</v>
@@ -10756,19 +10756,19 @@
         <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U64">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="V64">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
         <v>1.06</v>
@@ -10780,22 +10780,22 @@
         <v>3.13</v>
       </c>
       <c r="AA64">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AB64">
         <v>1.71</v>
       </c>
       <c r="AC64">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD64">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE64">
         <v>1.04</v>
       </c>
       <c r="AF64">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG64">
         <v>1.85</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="O65">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P65">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="Q65">
         <v>2.85</v>
       </c>
       <c r="R65">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="S65">
         <v>1.41</v>
@@ -10925,7 +10925,7 @@
         <v>2.66</v>
       </c>
       <c r="U65">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="V65">
         <v>1.34</v>
@@ -10946,7 +10946,7 @@
         <v>2.05</v>
       </c>
       <c r="AB65">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC65">
         <v>3.5</v>
@@ -12054,7 +12054,7 @@
         <v>3.5</v>
       </c>
       <c r="Q72">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R72">
         <v>2.26</v>
@@ -12063,7 +12063,7 @@
         <v>1.35</v>
       </c>
       <c r="T72">
-        <v>3.07</v>
+        <v>2.82</v>
       </c>
       <c r="U72">
         <v>2.77</v>
@@ -12084,22 +12084,22 @@
         <v>3.42</v>
       </c>
       <c r="AA72">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AB72">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="AD72">
         <v>1.34</v>
       </c>
       <c r="AE72">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG72">
         <v>2.06</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK72">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12223,16 +12223,16 @@
         <v>2.38</v>
       </c>
       <c r="S73">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
         <v>2.25</v>
       </c>
       <c r="V73">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W73">
         <v>1.12</v>
@@ -12244,10 +12244,10 @@
         <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA73">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB73">
         <v>2.18</v>
@@ -12259,7 +12259,7 @@
         <v>1.44</v>
       </c>
       <c r="AE73">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
         <v>1.5</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12389,13 +12389,13 @@
         <v>1.3</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U74">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V74">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W74">
         <v>1.11</v>
@@ -12404,28 +12404,28 @@
         <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z74">
         <v>4.2</v>
       </c>
       <c r="AA74">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB74">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AC74">
         <v>2.6</v>
       </c>
       <c r="AD74">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE74">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG74">
         <v>2.3</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK74">
         <v>1.4</v>
@@ -12534,28 +12534,28 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O75">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
         <v>2.25</v>
       </c>
       <c r="Q75">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="R75">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S75">
         <v>1.25</v>
       </c>
       <c r="T75">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="U75">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V75">
         <v>1.53</v>
@@ -12564,34 +12564,34 @@
         <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA75">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB75">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC75">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD75">
         <v>1.45</v>
       </c>
       <c r="AE75">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF75">
         <v>1.53</v>
       </c>
       <c r="AG75">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>2.13</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
         <v>3.15</v>
@@ -12709,7 +12709,7 @@
         <v>2.58</v>
       </c>
       <c r="R76">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="S76">
         <v>1.3</v>
@@ -12718,13 +12718,13 @@
         <v>3.08</v>
       </c>
       <c r="U76">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V76">
         <v>1.52</v>
       </c>
       <c r="W76">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X76">
         <v>1.01</v>
@@ -12748,13 +12748,13 @@
         <v>1.49</v>
       </c>
       <c r="AE76">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF76">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG76">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
         <v>1.59</v>
@@ -12866,7 +12866,7 @@
         <v>3.25</v>
       </c>
       <c r="P77">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q77">
         <v>3.3</v>
@@ -12890,34 +12890,34 @@
         <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y77">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z77">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="AA77">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB77">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC77">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD77">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE77">
         <v>1.06</v>
       </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O78">
         <v>3.35</v>
@@ -13038,7 +13038,7 @@
         <v>2.25</v>
       </c>
       <c r="S78">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T78">
         <v>3</v>
@@ -13062,16 +13062,16 @@
         <v>3.4</v>
       </c>
       <c r="AA78">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB78">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC78">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AD78">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
         <v>1.09</v>
@@ -13186,25 +13186,25 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O79">
         <v>3.38</v>
       </c>
       <c r="P79">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="Q79">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="R79">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S79">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T79">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U79">
         <v>2.89</v>
@@ -13216,10 +13216,10 @@
         <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
         <v>3.4</v>
@@ -13237,13 +13237,13 @@
         <v>1.3</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF79">
         <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK79">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13367,7 +13367,7 @@
         <v>1.22</v>
       </c>
       <c r="T80">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U80">
         <v>2.2</v>
@@ -13376,7 +13376,7 @@
         <v>1.62</v>
       </c>
       <c r="W80">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X80">
         <v>1.02</v>
@@ -13385,13 +13385,13 @@
         <v>1.15</v>
       </c>
       <c r="Z80">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="AA80">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB80">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AC80">
         <v>2.3</v>
@@ -13530,7 +13530,7 @@
         <v>1.3</v>
       </c>
       <c r="T81">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U81">
         <v>2.5</v>
@@ -13548,10 +13548,10 @@
         <v>1.22</v>
       </c>
       <c r="Z81">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA81">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB81">
         <v>2.06</v>
@@ -13560,16 +13560,16 @@
         <v>2.8</v>
       </c>
       <c r="AD81">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE81">
         <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG81">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>3.5</v>
       </c>
       <c r="O82">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
         <v>1.79</v>
@@ -13693,7 +13693,7 @@
         <v>1.32</v>
       </c>
       <c r="T82">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U82">
         <v>2.5</v>
@@ -13708,7 +13708,7 @@
         <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z82">
         <v>4.1</v>
@@ -13726,7 +13726,7 @@
         <v>1.44</v>
       </c>
       <c r="AE82">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF82">
         <v>1.58</v>
@@ -13748,7 +13748,7 @@
         <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14022,7 +14022,7 @@
         <v>2.1</v>
       </c>
       <c r="U84">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="V84">
         <v>1.15</v>
@@ -14034,13 +14034,13 @@
         <v>1.16</v>
       </c>
       <c r="Y84">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Z84">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AA84">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AB84">
         <v>1.28</v>
@@ -14058,7 +14058,7 @@
         <v>2.4</v>
       </c>
       <c r="AG84">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O85">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="Q85">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R85">
         <v>2.15</v>
@@ -14194,7 +14194,7 @@
         <v>1.05</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y85">
         <v>1.29</v>
@@ -14203,19 +14203,19 @@
         <v>3.41</v>
       </c>
       <c r="AA85">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB85">
         <v>1.8</v>
       </c>
       <c r="AC85">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD85">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE85">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
         <v>1.8</v>
@@ -14339,13 +14339,13 @@
         <v>2.5</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S86">
         <v>1.4</v>
       </c>
       <c r="T86">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U86">
         <v>2.91</v>
@@ -14357,10 +14357,10 @@
         <v>1.08</v>
       </c>
       <c r="X86">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y86">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z86">
         <v>3</v>
@@ -14375,16 +14375,16 @@
         <v>3.8</v>
       </c>
       <c r="AD86">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE86">
         <v>1.05</v>
       </c>
       <c r="AF86">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG86">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="O87">
         <v>3.15</v>
@@ -14514,16 +14514,16 @@
         <v>3.12</v>
       </c>
       <c r="V87">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z87">
         <v>3</v>
@@ -14535,7 +14535,7 @@
         <v>1.68</v>
       </c>
       <c r="AC87">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="AD87">
         <v>1.22</v>
@@ -14547,7 +14547,7 @@
         <v>1.8</v>
       </c>
       <c r="AG87">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
+        <v>1.27</v>
+      </c>
+      <c r="AK87">
         <v>1.3</v>
-      </c>
-      <c r="AK87">
-        <v>1.35</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>2.2</v>
       </c>
       <c r="O88">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P88">
         <v>2.9</v>
@@ -14695,19 +14695,19 @@
         <v>2.06</v>
       </c>
       <c r="AB88">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC88">
         <v>3.78</v>
       </c>
       <c r="AD88">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE88">
         <v>1.06</v>
       </c>
       <c r="AF88">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG88">
         <v>1.85</v>
@@ -14816,25 +14816,25 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="O89">
         <v>3.25</v>
       </c>
       <c r="P89">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q89">
         <v>2.7</v>
       </c>
       <c r="R89">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S89">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T89">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U89">
         <v>2.77</v>
@@ -14870,7 +14870,7 @@
         <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG89">
         <v>1.91</v>
@@ -14979,16 +14979,16 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O90">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P90">
         <v>3.8</v>
       </c>
       <c r="Q90">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R90">
         <v>2.12</v>
@@ -15009,7 +15009,7 @@
         <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y90">
         <v>1.26</v>
@@ -15021,10 +15021,10 @@
         <v>1.93</v>
       </c>
       <c r="AB90">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC90">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD90">
         <v>1.28</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -15169,7 +15169,7 @@
         <v>1.41</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15178,7 +15178,7 @@
         <v>1.28</v>
       </c>
       <c r="Z91">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="AA91">
         <v>1.93</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
         <v>1.9</v>
@@ -15317,13 +15317,13 @@
         <v>4.58</v>
       </c>
       <c r="R92">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
         <v>1.36</v>
       </c>
       <c r="T92">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U92">
         <v>2.73</v>
@@ -15332,7 +15332,7 @@
         <v>1.39</v>
       </c>
       <c r="W92">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X92">
         <v>1.03</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
         <v>1.25</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O93">
         <v>3.5</v>
       </c>
       <c r="P93">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q93">
         <v>2.55</v>
@@ -15486,46 +15486,46 @@
         <v>1.34</v>
       </c>
       <c r="T93">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U93">
         <v>2.75</v>
       </c>
       <c r="V93">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W93">
         <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z93">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA93">
         <v>1.95</v>
       </c>
       <c r="AB93">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC93">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="AD93">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE93">
         <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG93">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P94">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -15664,16 +15664,16 @@
         <v>1.04</v>
       </c>
       <c r="Y94">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z94">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AA94">
         <v>1.75</v>
       </c>
       <c r="AB94">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC94">
         <v>2.9</v>
@@ -15797,7 +15797,7 @@
         <v>2</v>
       </c>
       <c r="O95">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
         <v>3.6</v>
@@ -15812,7 +15812,7 @@
         <v>1.38</v>
       </c>
       <c r="T95">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U95">
         <v>2.75</v>
@@ -15821,19 +15821,19 @@
         <v>1.42</v>
       </c>
       <c r="W95">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X95">
         <v>1.05</v>
       </c>
       <c r="Y95">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z95">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA95">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB95">
         <v>1.85</v>
@@ -15842,7 +15842,7 @@
         <v>3.2</v>
       </c>
       <c r="AD95">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE95">
         <v>1.09</v>
@@ -15957,43 +15957,43 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="O96">
         <v>3.6</v>
       </c>
       <c r="P96">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q96">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="R96">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S96">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T96">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="U96">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="V96">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W96">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
         <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z96">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA96">
         <v>2.05</v>
@@ -16008,7 +16008,7 @@
         <v>1.22</v>
       </c>
       <c r="AE96">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF96">
         <v>1.91</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
         <v>2</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O97">
         <v>3.4</v>
@@ -16135,19 +16135,19 @@
         <v>2.14</v>
       </c>
       <c r="S97">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U97">
         <v>2.73</v>
       </c>
       <c r="V97">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W97">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
         <v>1</v>
@@ -16156,13 +16156,13 @@
         <v>1.29</v>
       </c>
       <c r="Z97">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA97">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB97">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC97">
         <v>3.25</v>
@@ -16609,25 +16609,25 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="O100">
         <v>4</v>
       </c>
       <c r="P100">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="Q100">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R100">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S100">
         <v>1.31</v>
       </c>
       <c r="T100">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U100">
         <v>2.4</v>
@@ -16642,10 +16642,10 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA100">
         <v>1.68</v>
@@ -16663,7 +16663,7 @@
         <v>1.16</v>
       </c>
       <c r="AF100">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG100">
         <v>2.1</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
         <v>2.21</v>
@@ -16778,43 +16778,43 @@
         <v>3.6</v>
       </c>
       <c r="P101">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="Q101">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R101">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S101">
         <v>1.36</v>
       </c>
       <c r="T101">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U101">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="V101">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X101">
         <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z101">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA101">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB101">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC101">
         <v>3.1</v>
@@ -16823,13 +16823,13 @@
         <v>1.33</v>
       </c>
       <c r="AE101">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF101">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG101">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16941,22 +16941,22 @@
         <v>3.5</v>
       </c>
       <c r="P102">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
       </c>
       <c r="R102">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T102">
+        <v>2.92</v>
+      </c>
+      <c r="U102">
         <v>2.9</v>
-      </c>
-      <c r="U102">
-        <v>2.7</v>
       </c>
       <c r="V102">
         <v>1.39</v>
@@ -16965,7 +16965,7 @@
         <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
         <v>1.28</v>
@@ -16974,16 +16974,16 @@
         <v>3.3</v>
       </c>
       <c r="AA102">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB102">
         <v>1.8</v>
       </c>
       <c r="AC102">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD102">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
         <v>1.06</v>
@@ -17101,13 +17101,13 @@
         <v>4.22</v>
       </c>
       <c r="O103">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q103">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="R103">
         <v>2.25</v>
@@ -17119,7 +17119,7 @@
         <v>2.86</v>
       </c>
       <c r="U103">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="V103">
         <v>1.44</v>
@@ -17128,13 +17128,13 @@
         <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y103">
         <v>1.25</v>
       </c>
       <c r="Z103">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA103">
         <v>1.78</v>
@@ -17143,10 +17143,10 @@
         <v>2.06</v>
       </c>
       <c r="AC103">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD103">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE103">
         <v>1.14</v>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O104">
         <v>3.4</v>
       </c>
       <c r="P104">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="Q104">
         <v>2.95</v>
@@ -17285,10 +17285,10 @@
         <v>2.8</v>
       </c>
       <c r="V104">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
         <v>1</v>
@@ -17315,10 +17315,10 @@
         <v>1.09</v>
       </c>
       <c r="AF104">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG104">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O105">
         <v>5</v>
       </c>
       <c r="P105">
-        <v>7.4</v>
+        <v>8.35</v>
       </c>
       <c r="Q105">
         <v>1.8</v>
@@ -17442,34 +17442,34 @@
         <v>1.3</v>
       </c>
       <c r="T105">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U105">
         <v>2.34</v>
       </c>
       <c r="V105">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z105">
         <v>4.2</v>
       </c>
       <c r="AA105">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB105">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC105">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AD105">
         <v>1.41</v>
@@ -17481,7 +17481,7 @@
         <v>1.85</v>
       </c>
       <c r="AG105">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17587,25 +17587,25 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="O106">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P106">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q106">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R106">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S106">
         <v>1.4</v>
       </c>
       <c r="T106">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U106">
         <v>3.01</v>
@@ -17614,7 +17614,7 @@
         <v>1.37</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
         <v>1.06</v>
@@ -17632,7 +17632,7 @@
         <v>1.79</v>
       </c>
       <c r="AC106">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD106">
         <v>1.29</v>
@@ -17644,7 +17644,7 @@
         <v>1.8</v>
       </c>
       <c r="AG106">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
+        <v>1.25</v>
+      </c>
+      <c r="AK106">
         <v>1.3</v>
-      </c>
-      <c r="AK106">
-        <v>1.28</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O107">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P107">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q107">
         <v>2.42</v>
@@ -17768,7 +17768,7 @@
         <v>1.35</v>
       </c>
       <c r="T107">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U107">
         <v>2.77</v>
@@ -17777,37 +17777,37 @@
         <v>1.39</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
         <v>1</v>
       </c>
       <c r="Y107">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z107">
         <v>3.53</v>
       </c>
       <c r="AA107">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB107">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC107">
         <v>3.3</v>
       </c>
       <c r="AD107">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
         <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -18076,19 +18076,19 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="O109">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P109">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q109">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R109">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S109">
         <v>1.33</v>
@@ -18115,16 +18115,16 @@
         <v>3.6</v>
       </c>
       <c r="AA109">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB109">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC109">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD109">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE109">
         <v>1.1</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK109">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,10 +18248,10 @@
         <v>1.5</v>
       </c>
       <c r="Q110">
-        <v>5.6</v>
+        <v>5.78</v>
       </c>
       <c r="R110">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="S110">
         <v>1.25</v>
@@ -18269,7 +18269,7 @@
         <v>1.15</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
         <v>1.15</v>
@@ -18281,22 +18281,22 @@
         <v>1.57</v>
       </c>
       <c r="AB110">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AC110">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD110">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE110">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF110">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG110">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.18</v>
       </c>
       <c r="AK110">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18408,16 +18408,16 @@
         <v>3.4</v>
       </c>
       <c r="P111">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q111">
-        <v>3.55</v>
+        <v>4.16</v>
       </c>
       <c r="R111">
         <v>2.14</v>
       </c>
       <c r="S111">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
         <v>3.08</v>
@@ -18429,10 +18429,10 @@
         <v>1.41</v>
       </c>
       <c r="W111">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
         <v>1.26</v>
@@ -18444,16 +18444,16 @@
         <v>1.9</v>
       </c>
       <c r="AB111">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC111">
-        <v>2.94</v>
+        <v>3.16</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE111">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF111">
         <v>1.69</v>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK111">
         <v>1.29</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G112">
@@ -18561,68 +18561,68 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N112">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="O112">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>8</v>
+        <v>5.02</v>
       </c>
       <c r="Q112">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="R112">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T112">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U112">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V112">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W112">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z112">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA112">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AB112">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC112">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AD112">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AE112">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF112">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG112">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G113">
@@ -18724,68 +18724,68 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N113">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="O113">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P113">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q113">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="R113">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="S113">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U113">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V113">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W113">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z113">
-        <v>4.21</v>
+        <v>4.75</v>
       </c>
       <c r="AA113">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AB113">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC113">
-        <v>2.76</v>
+        <v>2.41</v>
       </c>
       <c r="AD113">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AE113">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF113">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG113">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK113">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,34 +18891,34 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P114">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q114">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R114">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S114">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U114">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="V114">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
         <v>1.04</v>
@@ -18933,13 +18933,13 @@
         <v>2</v>
       </c>
       <c r="AB114">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC114">
         <v>3.6</v>
       </c>
       <c r="AD114">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE114">
         <v>1.09</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK114">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="O115">
         <v>3.4</v>
@@ -19069,7 +19069,7 @@
         <v>2.05</v>
       </c>
       <c r="S115">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
         <v>2.73</v>
@@ -19084,28 +19084,28 @@
         <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y115">
         <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA115">
         <v>2</v>
       </c>
       <c r="AB115">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC115">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD115">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE115">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF115">
         <v>1.75</v>
@@ -19220,10 +19220,10 @@
         <v>2.45</v>
       </c>
       <c r="O116">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P116">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -19232,13 +19232,13 @@
         <v>2.2</v>
       </c>
       <c r="S116">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T116">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="U116">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V116">
         <v>1.44</v>
@@ -19247,7 +19247,7 @@
         <v>1.07</v>
       </c>
       <c r="X116">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y116">
         <v>1.27</v>
@@ -19256,10 +19256,10 @@
         <v>3.54</v>
       </c>
       <c r="AA116">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB116">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC116">
         <v>3</v>
@@ -19274,7 +19274,7 @@
         <v>1.62</v>
       </c>
       <c r="AG116">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
         <v>1.5</v>
@@ -19398,16 +19398,16 @@
         <v>1.41</v>
       </c>
       <c r="T117">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="U117">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V117">
         <v>1.35</v>
       </c>
       <c r="W117">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
         <v>1.06</v>
@@ -19422,7 +19422,7 @@
         <v>2.14</v>
       </c>
       <c r="AB117">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC117">
         <v>4</v>
@@ -19434,7 +19434,7 @@
         <v>1.05</v>
       </c>
       <c r="AF117">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG117">
         <v>1.84</v>
@@ -19561,19 +19561,19 @@
         <v>1.3</v>
       </c>
       <c r="T118">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U118">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V118">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W118">
         <v>1.11</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y118">
         <v>1.16</v>
@@ -19582,10 +19582,10 @@
         <v>4.15</v>
       </c>
       <c r="AA118">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB118">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AC118">
         <v>2.63</v>
@@ -19594,10 +19594,10 @@
         <v>1.44</v>
       </c>
       <c r="AE118">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF118">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG118">
         <v>2</v>
@@ -19709,13 +19709,13 @@
         <v>2.25</v>
       </c>
       <c r="O119">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P119">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="Q119">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R119">
         <v>2</v>
@@ -19733,37 +19733,37 @@
         <v>1.33</v>
       </c>
       <c r="W119">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
         <v>1.36</v>
       </c>
       <c r="Z119">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AA119">
         <v>2.08</v>
       </c>
       <c r="AB119">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC119">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AD119">
         <v>1.26</v>
       </c>
       <c r="AE119">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF119">
         <v>1.77</v>
       </c>
       <c r="AG119">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19872,10 +19872,10 @@
         <v>1.59</v>
       </c>
       <c r="O120">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P120">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="Q120">
         <v>2.13</v>
@@ -19887,7 +19887,7 @@
         <v>1.33</v>
       </c>
       <c r="T120">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U120">
         <v>2.62</v>
@@ -19896,10 +19896,10 @@
         <v>1.43</v>
       </c>
       <c r="W120">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X120">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
         <v>1.26</v>
@@ -19908,7 +19908,7 @@
         <v>3.55</v>
       </c>
       <c r="AA120">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB120">
         <v>1.95</v>
@@ -19942,7 +19942,7 @@
         <v>1.22</v>
       </c>
       <c r="AK120">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,31 +20032,31 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="O121">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="P121">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q121">
         <v>3</v>
       </c>
       <c r="R121">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S121">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T121">
         <v>3.5</v>
       </c>
       <c r="U121">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V121">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W121">
         <v>1.14</v>
@@ -20071,10 +20071,10 @@
         <v>4.25</v>
       </c>
       <c r="AA121">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB121">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC121">
         <v>2.45</v>
@@ -20083,7 +20083,7 @@
         <v>1.52</v>
       </c>
       <c r="AE121">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF121">
         <v>1.5</v>
@@ -20105,7 +20105,7 @@
         <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,7 +20195,7 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O122">
         <v>3.28</v>
@@ -20204,19 +20204,19 @@
         <v>2.55</v>
       </c>
       <c r="Q122">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R122">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="S122">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T122">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U122">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="V122">
         <v>1.42</v>
@@ -20225,31 +20225,31 @@
         <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
         <v>1.22</v>
       </c>
       <c r="Z122">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AA122">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB122">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC122">
         <v>3.1</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE122">
         <v>1.11</v>
       </c>
       <c r="AF122">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG122">
         <v>2.1</v>
@@ -20847,43 +20847,43 @@
         </is>
       </c>
       <c r="N126">
+        <v>2.15</v>
+      </c>
+      <c r="O126">
+        <v>3.25</v>
+      </c>
+      <c r="P126">
+        <v>2.97</v>
+      </c>
+      <c r="Q126">
+        <v>2.7</v>
+      </c>
+      <c r="R126">
         <v>2.2</v>
       </c>
-      <c r="O126">
-        <v>3.4</v>
-      </c>
-      <c r="P126">
-        <v>2.87</v>
-      </c>
-      <c r="Q126">
-        <v>2.85</v>
-      </c>
-      <c r="R126">
-        <v>2.27</v>
-      </c>
       <c r="S126">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T126">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U126">
         <v>2.68</v>
       </c>
       <c r="V126">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X126">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y126">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z126">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AA126">
         <v>1.82</v>
@@ -20892,10 +20892,10 @@
         <v>1.93</v>
       </c>
       <c r="AC126">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AD126">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE126">
         <v>1.13</v>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK126">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O129">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P129">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21378,7 +21378,7 @@
         <v>1.85</v>
       </c>
       <c r="AB129">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="O132">
         <v>3.64</v>
@@ -21837,13 +21837,13 @@
         <v>3.25</v>
       </c>
       <c r="R132">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S132">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T132">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U132">
         <v>2.1</v>
@@ -21864,16 +21864,16 @@
         <v>5</v>
       </c>
       <c r="AA132">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB132">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC132">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD132">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE132">
         <v>1.2</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O136">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P136">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q136">
         <v>2.63</v>
@@ -22492,16 +22492,16 @@
         <v>2.01</v>
       </c>
       <c r="S136">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T136">
         <v>2.62</v>
       </c>
       <c r="U136">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="V136">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W136">
         <v>1.02</v>
@@ -22510,31 +22510,31 @@
         <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z136">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="AA136">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AB136">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC136">
         <v>3.8</v>
       </c>
       <c r="AD136">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE136">
         <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG136">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O138">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P138">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Q138">
         <v>4.5</v>
@@ -22821,16 +22821,16 @@
         <v>1.24</v>
       </c>
       <c r="T138">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="U138">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V138">
         <v>1.67</v>
       </c>
       <c r="W138">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X138">
         <v>1.02</v>
@@ -22848,19 +22848,19 @@
         <v>2.5</v>
       </c>
       <c r="AC138">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD138">
         <v>1.67</v>
       </c>
       <c r="AE138">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF138">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG138">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22972,13 +22972,13 @@
         <v>6</v>
       </c>
       <c r="P139">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Q139">
         <v>1.53</v>
       </c>
       <c r="R139">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="S139">
         <v>1.14</v>
@@ -22999,31 +22999,31 @@
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z139">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA139">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB139">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AC139">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD139">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AE139">
         <v>1.36</v>
       </c>
       <c r="AF139">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG139">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK139">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23455,37 +23455,37 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O142">
         <v>3.22</v>
       </c>
       <c r="P142">
-        <v>4</v>
+        <v>4.56</v>
       </c>
       <c r="Q142">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="R142">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S142">
         <v>1.45</v>
       </c>
       <c r="T142">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="U142">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="V142">
         <v>1.33</v>
       </c>
       <c r="W142">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X142">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y142">
         <v>1.42</v>
@@ -23494,13 +23494,13 @@
         <v>2.75</v>
       </c>
       <c r="AA142">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB142">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC142">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD142">
         <v>1.19</v>
@@ -23528,7 +23528,7 @@
         <v>1.33</v>
       </c>
       <c r="AK142">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,16 +23618,16 @@
         </is>
       </c>
       <c r="N143">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O143">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P143">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q143">
-        <v>6.76</v>
+        <v>7.07</v>
       </c>
       <c r="R143">
         <v>2.45</v>
@@ -23636,13 +23636,13 @@
         <v>1.25</v>
       </c>
       <c r="T143">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="U143">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V143">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W143">
         <v>1.12</v>
@@ -23651,19 +23651,19 @@
         <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z143">
-        <v>4.45</v>
+        <v>4.72</v>
       </c>
       <c r="AA143">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AB143">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC143">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD143">
         <v>1.5</v>
@@ -23675,7 +23675,7 @@
         <v>1.75</v>
       </c>
       <c r="AG143">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AK143">
         <v>1.1</v>
@@ -23781,10 +23781,10 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="O144">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
         <v>4.45</v>
@@ -23799,46 +23799,46 @@
         <v>1.34</v>
       </c>
       <c r="T144">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U144">
         <v>2.39</v>
       </c>
       <c r="V144">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W144">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X144">
         <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z144">
         <v>4.2</v>
       </c>
       <c r="AA144">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB144">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC144">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AD144">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE144">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF144">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG144">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="O145">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P145">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q145">
         <v>4.2</v>
@@ -23962,43 +23962,43 @@
         <v>1.4</v>
       </c>
       <c r="T145">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U145">
         <v>3.02</v>
       </c>
       <c r="V145">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W145">
         <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y145">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z145">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AA145">
         <v>1.95</v>
       </c>
       <c r="AB145">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC145">
         <v>3.4</v>
       </c>
       <c r="AD145">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE145">
         <v>1.07</v>
       </c>
       <c r="AF145">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG145">
         <v>1.95</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="O146">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P146">
-        <v>4.43</v>
+        <v>5.25</v>
       </c>
       <c r="Q146">
         <v>2.25</v>
@@ -24125,10 +24125,10 @@
         <v>1.47</v>
       </c>
       <c r="T146">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U146">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="V146">
         <v>1.33</v>
@@ -24140,10 +24140,10 @@
         <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z146">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA146">
         <v>2.31</v>
@@ -24164,7 +24164,7 @@
         <v>2.05</v>
       </c>
       <c r="AG146">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK146">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24285,16 +24285,16 @@
         <v>2.15</v>
       </c>
       <c r="S147">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T147">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U147">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V147">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W147">
         <v>1.04</v>
@@ -24324,10 +24324,10 @@
         <v>1.06</v>
       </c>
       <c r="AF147">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG147">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK147">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24436,16 +24436,16 @@
         <v>2.35</v>
       </c>
       <c r="O148">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="P148">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="Q148">
         <v>3.14</v>
       </c>
       <c r="R148">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S148">
         <v>1.5</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK148">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24768,10 +24768,10 @@
         <v>3.1</v>
       </c>
       <c r="Q150">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R150">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S150">
         <v>1.25</v>
@@ -24937,16 +24937,16 @@
         <v>2.23</v>
       </c>
       <c r="S151">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T151">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U151">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="V151">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W151">
         <v>1.1</v>
@@ -24955,7 +24955,7 @@
         <v>1.04</v>
       </c>
       <c r="Y151">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z151">
         <v>4.1</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="O153">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P153">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q153">
         <v>2.85</v>
@@ -25266,7 +25266,7 @@
         <v>1.29</v>
       </c>
       <c r="T153">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U153">
         <v>2.41</v>
@@ -25296,13 +25296,13 @@
         <v>2.63</v>
       </c>
       <c r="AD153">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE153">
         <v>1.18</v>
       </c>
       <c r="AF153">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG153">
         <v>2.34</v>
@@ -26078,19 +26078,19 @@
         <v>2.05</v>
       </c>
       <c r="S158">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T158">
         <v>2.76</v>
       </c>
       <c r="U158">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V158">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W158">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X158">
         <v>1.06</v>
@@ -26120,7 +26120,7 @@
         <v>1.83</v>
       </c>
       <c r="AG158">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O167">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P167">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q167">
         <v>2.6</v>
@@ -27548,7 +27548,7 @@
         <v>1.22</v>
       </c>
       <c r="T167">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U167">
         <v>2.22</v>
@@ -27566,13 +27566,13 @@
         <v>1.18</v>
       </c>
       <c r="Z167">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="AA167">
         <v>1.48</v>
       </c>
       <c r="AB167">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC167">
         <v>2.25</v>
@@ -27584,10 +27584,10 @@
         <v>1.2</v>
       </c>
       <c r="AF167">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG167">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.26</v>
       </c>
       <c r="AK167">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27693,34 +27693,34 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="O168">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P168">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q168">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R168">
         <v>1.91</v>
       </c>
       <c r="S168">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T168">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="U168">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="V168">
         <v>1.29</v>
       </c>
       <c r="W168">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X168">
         <v>1.04</v>
@@ -27738,19 +27738,19 @@
         <v>1.54</v>
       </c>
       <c r="AC168">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD168">
         <v>1.15</v>
       </c>
       <c r="AE168">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF168">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG168">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK168">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27856,19 +27856,19 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="O169">
+        <v>3.05</v>
+      </c>
+      <c r="P169">
         <v>3.4</v>
-      </c>
-      <c r="P169">
-        <v>3.25</v>
       </c>
       <c r="Q169">
         <v>2.7</v>
       </c>
       <c r="R169">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S169">
         <v>1.37</v>
@@ -27877,16 +27877,16 @@
         <v>2.65</v>
       </c>
       <c r="U169">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V169">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W169">
         <v>1.06</v>
       </c>
       <c r="X169">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
         <v>1.25</v>
@@ -27895,10 +27895,10 @@
         <v>3.92</v>
       </c>
       <c r="AA169">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB169">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC169">
         <v>3.1</v>
@@ -27907,13 +27907,13 @@
         <v>1.39</v>
       </c>
       <c r="AE169">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF169">
         <v>1.65</v>
       </c>
       <c r="AG169">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>2.88</v>
       </c>
       <c r="R170">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="S170">
         <v>1.36</v>
@@ -28040,7 +28040,7 @@
         <v>2.88</v>
       </c>
       <c r="U170">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V170">
         <v>1.42</v>
@@ -28067,13 +28067,13 @@
         <v>3.05</v>
       </c>
       <c r="AD170">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE170">
         <v>1.07</v>
       </c>
       <c r="AF170">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG170">
         <v>2.05</v>
@@ -28092,7 +28092,7 @@
         <v>1.32</v>
       </c>
       <c r="AK170">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O171">
         <v>3.8</v>
       </c>
       <c r="P171">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q171">
         <v>2.45</v>
@@ -28200,16 +28200,16 @@
         <v>1.22</v>
       </c>
       <c r="T171">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U171">
         <v>2.15</v>
       </c>
       <c r="V171">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W171">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X171">
         <v>1.03</v>
@@ -28224,16 +28224,16 @@
         <v>1.5</v>
       </c>
       <c r="AB171">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC171">
         <v>2.25</v>
       </c>
       <c r="AD171">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE171">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF171">
         <v>1.44</v>
@@ -29160,28 +29160,28 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O177">
         <v>3.4</v>
       </c>
       <c r="P177">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q177">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="R177">
         <v>2.25</v>
       </c>
       <c r="S177">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T177">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="U177">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="V177">
         <v>1.4</v>
@@ -29190,7 +29190,7 @@
         <v>1.05</v>
       </c>
       <c r="X177">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y177">
         <v>1.21</v>
@@ -29205,7 +29205,7 @@
         <v>1.95</v>
       </c>
       <c r="AC177">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD177">
         <v>1.33</v>
@@ -29489,22 +29489,22 @@
         <v>1.33</v>
       </c>
       <c r="O179">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P179">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="Q179">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R179">
         <v>2.45</v>
       </c>
       <c r="S179">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T179">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="U179">
         <v>2.43</v>
@@ -29559,7 +29559,7 @@
         <v>1.05</v>
       </c>
       <c r="AK179">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29818,16 +29818,16 @@
         <v>3.7</v>
       </c>
       <c r="P181">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="Q181">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R181">
         <v>2.14</v>
       </c>
       <c r="S181">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T181">
         <v>2.67</v>
@@ -29839,22 +29839,22 @@
         <v>1.33</v>
       </c>
       <c r="W181">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z181">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA181">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB181">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC181">
         <v>3.42</v>
@@ -29869,7 +29869,7 @@
         <v>2</v>
       </c>
       <c r="AG181">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>1.27</v>
       </c>
       <c r="W182">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X182">
         <v>1.04</v>
@@ -30138,7 +30138,7 @@
         </is>
       </c>
       <c r="N183">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O183">
         <v>3.45</v>
@@ -30150,49 +30150,49 @@
         <v>3.3</v>
       </c>
       <c r="R183">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S183">
         <v>1.32</v>
       </c>
       <c r="T183">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="U183">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V183">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W183">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X183">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y183">
         <v>1.21</v>
       </c>
       <c r="Z183">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AA183">
         <v>1.8</v>
       </c>
       <c r="AB183">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC183">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD183">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE183">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF183">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG183">
         <v>2.15</v>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AK183">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB184">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30642,7 +30642,7 @@
         <v>2.3</v>
       </c>
       <c r="S186">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T186">
         <v>3.25</v>
@@ -30654,13 +30654,13 @@
         <v>1.53</v>
       </c>
       <c r="W186">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X186">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y186">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z186">
         <v>4.33</v>
@@ -30684,7 +30684,7 @@
         <v>1.5</v>
       </c>
       <c r="AG186">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30799,10 +30799,10 @@
         <v>2.36</v>
       </c>
       <c r="Q187">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R187">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S187">
         <v>1.36</v>
@@ -30811,13 +30811,13 @@
         <v>2.88</v>
       </c>
       <c r="U187">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V187">
         <v>1.33</v>
       </c>
       <c r="W187">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X187">
         <v>1.02</v>
@@ -30829,7 +30829,7 @@
         <v>3.1</v>
       </c>
       <c r="AA187">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB187">
         <v>1.71</v>
@@ -30841,13 +30841,13 @@
         <v>1.25</v>
       </c>
       <c r="AE187">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF187">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG187">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AK187">
         <v>1.34</v>
@@ -31128,7 +31128,7 @@
         <v>1.62</v>
       </c>
       <c r="R189">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="S189">
         <v>1.18</v>
@@ -31155,16 +31155,16 @@
         <v>7.1</v>
       </c>
       <c r="AA189">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB189">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AC189">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD189">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE189">
         <v>1.36</v>
@@ -31173,7 +31173,7 @@
         <v>1.53</v>
       </c>
       <c r="AG189">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31279,16 +31279,16 @@
         </is>
       </c>
       <c r="N190">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O190">
         <v>3.4</v>
       </c>
       <c r="P190">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q190">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R190">
         <v>1.97</v>
@@ -31297,10 +31297,10 @@
         <v>1.46</v>
       </c>
       <c r="T190">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U190">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="V190">
         <v>1.34</v>
@@ -31324,7 +31324,7 @@
         <v>1.67</v>
       </c>
       <c r="AC190">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD190">
         <v>1.21</v>
@@ -31442,22 +31442,22 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O191">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="P191">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q191">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="R191">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="S191">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T191">
         <v>3.4</v>
@@ -31466,7 +31466,7 @@
         <v>2.4</v>
       </c>
       <c r="V191">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W191">
         <v>1.12</v>
@@ -31478,13 +31478,13 @@
         <v>1.2</v>
       </c>
       <c r="Z191">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA191">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AB191">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC191">
         <v>2.47</v>
@@ -31614,19 +31614,19 @@
         <v>9.6</v>
       </c>
       <c r="Q192">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R192">
         <v>2.77</v>
       </c>
       <c r="S192">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T192">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U192">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V192">
         <v>1.63</v>
@@ -31635,31 +31635,31 @@
         <v>1.12</v>
       </c>
       <c r="X192">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z192">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="AA192">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB192">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC192">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD192">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE192">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF192">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG192">
         <v>1.78</v>
@@ -31678,7 +31678,7 @@
         <v>1.11</v>
       </c>
       <c r="AK192">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="O194">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P194">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="Q194">
         <v>2.4</v>
@@ -31946,19 +31946,19 @@
         <v>2.15</v>
       </c>
       <c r="S194">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T194">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U194">
         <v>2.65</v>
       </c>
       <c r="V194">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W194">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X194">
         <v>1.03</v>
@@ -31979,7 +31979,7 @@
         <v>3.1</v>
       </c>
       <c r="AD194">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE194">
         <v>1.08</v>
@@ -32004,7 +32004,7 @@
         <v>1.2</v>
       </c>
       <c r="AK194">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,16 +32094,16 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="O195">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P195">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q195">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="R195">
         <v>2.14</v>
@@ -32112,40 +32112,40 @@
         <v>1.31</v>
       </c>
       <c r="T195">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U195">
         <v>2.35</v>
       </c>
       <c r="V195">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W195">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X195">
         <v>1</v>
       </c>
       <c r="Y195">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z195">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA195">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB195">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC195">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="AD195">
         <v>1.38</v>
       </c>
       <c r="AE195">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF195">
         <v>1.57</v>
@@ -32167,7 +32167,7 @@
         <v>1.49</v>
       </c>
       <c r="AK195">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O196">
         <v>3.1</v>
       </c>
       <c r="P196">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q196">
         <v>2.5</v>
@@ -32275,7 +32275,7 @@
         <v>1.45</v>
       </c>
       <c r="T196">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U196">
         <v>3.6</v>
@@ -32287,28 +32287,28 @@
         <v>1.03</v>
       </c>
       <c r="X196">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y196">
         <v>1.41</v>
       </c>
       <c r="Z196">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AA196">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB196">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AC196">
         <v>4.5</v>
       </c>
       <c r="AD196">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE196">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF196">
         <v>2.05</v>
@@ -32420,7 +32420,7 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="O197">
         <v>3.25</v>
@@ -32438,19 +32438,19 @@
         <v>1.4</v>
       </c>
       <c r="T197">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U197">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V197">
         <v>1.4</v>
       </c>
       <c r="W197">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X197">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y197">
         <v>1.24</v>
@@ -32465,7 +32465,7 @@
         <v>1.8</v>
       </c>
       <c r="AC197">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD197">
         <v>1.29</v>
@@ -32474,10 +32474,10 @@
         <v>1.06</v>
       </c>
       <c r="AF197">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG197">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>2.9</v>
       </c>
       <c r="R198">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S198">
         <v>1.35</v>
@@ -32619,13 +32619,13 @@
         <v>1.25</v>
       </c>
       <c r="Z198">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA198">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB198">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC198">
         <v>2.88</v>
@@ -32637,7 +32637,7 @@
         <v>1.09</v>
       </c>
       <c r="AF198">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG198">
         <v>2.1</v>
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O200">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P200">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q200">
         <v>2.5</v>
@@ -32924,16 +32924,16 @@
         <v>1.91</v>
       </c>
       <c r="S200">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T200">
         <v>2.22</v>
       </c>
       <c r="U200">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="V200">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W200">
         <v>1.02</v>
@@ -32942,7 +32942,7 @@
         <v>1.11</v>
       </c>
       <c r="Y200">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z200">
         <v>2.41</v>
@@ -33078,7 +33078,7 @@
         <v>3.65</v>
       </c>
       <c r="P201">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q201">
         <v>6.5</v>
@@ -33087,19 +33087,19 @@
         <v>2.21</v>
       </c>
       <c r="S201">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T201">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U201">
         <v>3.08</v>
       </c>
       <c r="V201">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W201">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X201">
         <v>1.07</v>
@@ -33123,7 +33123,7 @@
         <v>1.2</v>
       </c>
       <c r="AE201">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF201">
         <v>2.21</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O202">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P202">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q202">
         <v>3.65</v>
@@ -33250,19 +33250,19 @@
         <v>2.14</v>
       </c>
       <c r="S202">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T202">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="U202">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="V202">
         <v>1.35</v>
       </c>
       <c r="W202">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X202">
         <v>1.02</v>
@@ -33277,7 +33277,7 @@
         <v>2.06</v>
       </c>
       <c r="AB202">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC202">
         <v>3.5</v>
@@ -33289,7 +33289,7 @@
         <v>1.05</v>
       </c>
       <c r="AF202">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG202">
         <v>1.91</v>
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AK202">
         <v>1.33</v>
@@ -33410,7 +33410,7 @@
         <v>2.85</v>
       </c>
       <c r="R203">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S203">
         <v>1.41</v>
@@ -33425,7 +33425,7 @@
         <v>1.32</v>
       </c>
       <c r="W203">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X203">
         <v>1.01</v>
@@ -33437,7 +33437,7 @@
         <v>2.92</v>
       </c>
       <c r="AA203">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB203">
         <v>1.68</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O204">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="P204">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33730,7 +33730,7 @@
         <v>3.1</v>
       </c>
       <c r="P205">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q205">
         <v>3.78</v>
@@ -33745,7 +33745,7 @@
         <v>2.59</v>
       </c>
       <c r="U205">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="V205">
         <v>1.36</v>
@@ -33757,19 +33757,19 @@
         <v>1.04</v>
       </c>
       <c r="Y205">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z205">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AA205">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB205">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC205">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD205">
         <v>1.25</v>
@@ -34050,28 +34050,28 @@
         </is>
       </c>
       <c r="N207">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O207">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="P207">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q207">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R207">
         <v>2.01</v>
       </c>
       <c r="S207">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T207">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="U207">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="V207">
         <v>1.3</v>
@@ -34080,19 +34080,19 @@
         <v>1</v>
       </c>
       <c r="X207">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y207">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z207">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AA207">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB207">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC207">
         <v>4.45</v>
@@ -34107,7 +34107,7 @@
         <v>1.95</v>
       </c>
       <c r="AG207">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AK207">
         <v>1.26</v>
@@ -34222,19 +34222,19 @@
         <v>11</v>
       </c>
       <c r="Q208">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R208">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S208">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T208">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U208">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V208">
         <v>1.59</v>
@@ -34246,25 +34246,25 @@
         <v>1.02</v>
       </c>
       <c r="Y208">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z208">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA208">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB208">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AC208">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD208">
         <v>1.57</v>
       </c>
       <c r="AE208">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF208">
         <v>2.05</v>
@@ -34286,7 +34286,7 @@
         <v>1.13</v>
       </c>
       <c r="AK208">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O209">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P209">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O211">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P211">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q211">
         <v>2.5</v>
@@ -34726,10 +34726,10 @@
         <v>2.45</v>
       </c>
       <c r="V211">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W211">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X211">
         <v>1.05</v>
@@ -34738,16 +34738,16 @@
         <v>1.25</v>
       </c>
       <c r="Z211">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA211">
         <v>1.75</v>
       </c>
       <c r="AB211">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC211">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD211">
         <v>1.38</v>
@@ -34756,7 +34756,7 @@
         <v>1.14</v>
       </c>
       <c r="AF211">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG211">
         <v>2.05</v>
@@ -34772,7 +34772,7 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK211">
         <v>1.88</v>
@@ -35031,25 +35031,25 @@
         <v>1.88</v>
       </c>
       <c r="O213">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="P213">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="Q213">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="R213">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="S213">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T213">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U213">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="V213">
         <v>1.5</v>
@@ -35061,31 +35061,31 @@
         <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z213">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="AA213">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB213">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC213">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AD213">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE213">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF213">
         <v>1.59</v>
       </c>
       <c r="AG213">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.21</v>
       </c>
       <c r="AK213">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35191,19 +35191,19 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O214">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P214">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q214">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="R214">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S214">
         <v>1.5</v>
@@ -35212,7 +35212,7 @@
         <v>2.57</v>
       </c>
       <c r="U214">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V214">
         <v>1.3</v>
@@ -35221,31 +35221,31 @@
         <v>1.03</v>
       </c>
       <c r="X214">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y214">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z214">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AA214">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AB214">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC214">
         <v>4.2</v>
       </c>
       <c r="AD214">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE214">
         <v>1.04</v>
       </c>
       <c r="AF214">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG214">
         <v>1.85</v>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK214">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35357,13 +35357,13 @@
         <v>1.35</v>
       </c>
       <c r="O215">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P215">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q215">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R215">
         <v>2.5</v>
@@ -35396,7 +35396,7 @@
         <v>1.44</v>
       </c>
       <c r="AB215">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AC215">
         <v>2.3</v>
@@ -35405,7 +35405,7 @@
         <v>1.6</v>
       </c>
       <c r="AE215">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF215">
         <v>1.76</v>
@@ -35680,7 +35680,7 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="O217">
         <v>6.71</v>
@@ -35692,22 +35692,22 @@
         <v>1.57</v>
       </c>
       <c r="R217">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="S217">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T217">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U217">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V217">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W217">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X217">
         <v>1.01</v>
@@ -35716,10 +35716,10 @@
         <v>1.08</v>
       </c>
       <c r="Z217">
-        <v>5.45</v>
+        <v>5.8</v>
       </c>
       <c r="AA217">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB217">
         <v>2.7</v>
@@ -35734,7 +35734,7 @@
         <v>1.3</v>
       </c>
       <c r="AF217">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AG217">
         <v>1.87</v>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK217">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="O218">
-        <v>3.69</v>
+        <v>3.8</v>
       </c>
       <c r="P218">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q218">
         <v>3</v>
@@ -35858,25 +35858,25 @@
         <v>2.38</v>
       </c>
       <c r="S218">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T218">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U218">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V218">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="W218">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X218">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y218">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z218">
         <v>4.69</v>
@@ -35888,19 +35888,19 @@
         <v>2.35</v>
       </c>
       <c r="AC218">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD218">
         <v>1.5</v>
       </c>
       <c r="AE218">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF218">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG218">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK218">
         <v>1.36</v>
@@ -36169,37 +36169,37 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="O220">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="P220">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q220">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R220">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="S220">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T220">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="U220">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="V220">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="W220">
         <v>1.13</v>
       </c>
       <c r="X220">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y220">
         <v>1.16</v>
@@ -36217,16 +36217,16 @@
         <v>2.32</v>
       </c>
       <c r="AD220">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE220">
         <v>1.22</v>
       </c>
       <c r="AF220">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG220">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK220">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36821,10 +36821,10 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="O224">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P224">
         <v>5.35</v>
@@ -36845,7 +36845,7 @@
         <v>2.13</v>
       </c>
       <c r="V224">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W224">
         <v>1.17</v>
@@ -36857,13 +36857,13 @@
         <v>1.14</v>
       </c>
       <c r="Z224">
-        <v>5.72</v>
+        <v>6</v>
       </c>
       <c r="AA224">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB224">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC224">
         <v>2.15</v>
@@ -37310,19 +37310,19 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O227">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="P227">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q227">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="R227">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S227">
         <v>1.2</v>
@@ -37331,10 +37331,10 @@
         <v>4</v>
       </c>
       <c r="U227">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="V227">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W227">
         <v>1.2</v>
@@ -37343,22 +37343,22 @@
         <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z227">
         <v>5.65</v>
       </c>
       <c r="AA227">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB227">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AC227">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="AD227">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE227">
         <v>1.28</v>
@@ -37383,7 +37383,7 @@
         <v>1.18</v>
       </c>
       <c r="AK227">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37636,16 +37636,16 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="O229">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="P229">
         <v>9.5</v>
       </c>
       <c r="Q229">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R229">
         <v>2.6</v>
@@ -37654,16 +37654,16 @@
         <v>1.29</v>
       </c>
       <c r="T229">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U229">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="V229">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W229">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X229">
         <v>1.03</v>
@@ -37672,19 +37672,19 @@
         <v>1.17</v>
       </c>
       <c r="Z229">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA229">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB229">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AC229">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD229">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE229">
         <v>1.14</v>
@@ -37709,7 +37709,7 @@
         <v>1.12</v>
       </c>
       <c r="AK229">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37799,7 +37799,7 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="O230">
         <v>6</v>
@@ -37811,22 +37811,22 @@
         <v>1.66</v>
       </c>
       <c r="R230">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S230">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T230">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U230">
         <v>2.2</v>
       </c>
       <c r="V230">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W230">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X230">
         <v>1.02</v>
@@ -37835,19 +37835,19 @@
         <v>1.13</v>
       </c>
       <c r="Z230">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA230">
         <v>1.49</v>
       </c>
       <c r="AB230">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC230">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD230">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AE230">
         <v>1.22</v>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AK230">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O231">
         <v>3.6</v>
       </c>
       <c r="P231">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="Q231">
         <v>3.75</v>
@@ -37983,7 +37983,7 @@
         <v>3.34</v>
       </c>
       <c r="U231">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V231">
         <v>1.57</v>
@@ -37992,7 +37992,7 @@
         <v>1.11</v>
       </c>
       <c r="X231">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y231">
         <v>1.18</v>
@@ -38013,7 +38013,7 @@
         <v>1.5</v>
       </c>
       <c r="AE231">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF231">
         <v>1.5</v>
@@ -38032,7 +38032,7 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AK231">
         <v>1.3</v>
@@ -39106,16 +39106,16 @@
         <v>1.26</v>
       </c>
       <c r="O238">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P238">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q238">
         <v>1.7</v>
       </c>
       <c r="R238">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="S238">
         <v>1.32</v>
@@ -39127,13 +39127,13 @@
         <v>2.4</v>
       </c>
       <c r="V238">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W238">
         <v>1.08</v>
       </c>
       <c r="X238">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y238">
         <v>1.24</v>
@@ -39148,7 +39148,7 @@
         <v>2.1</v>
       </c>
       <c r="AC238">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AD238">
         <v>1.37</v>
@@ -39157,10 +39157,10 @@
         <v>1.12</v>
       </c>
       <c r="AF238">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG238">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK238">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39592,7 +39592,7 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="O241">
         <v>3.5</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O247">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P247">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q247">
         <v>4.6</v>
@@ -40591,7 +40591,7 @@
         <v>2.62</v>
       </c>
       <c r="U247">
-        <v>3.43</v>
+        <v>2.88</v>
       </c>
       <c r="V247">
         <v>1.33</v>
@@ -40603,16 +40603,16 @@
         <v>1.06</v>
       </c>
       <c r="Y247">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z247">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AA247">
         <v>2.16</v>
       </c>
       <c r="AB247">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC247">
         <v>4.05</v>
@@ -40621,7 +40621,7 @@
         <v>1.22</v>
       </c>
       <c r="AE247">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF247">
         <v>2</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="O248">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P248">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q248">
         <v>3.2</v>
@@ -40751,7 +40751,7 @@
         <v>1.52</v>
       </c>
       <c r="T248">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="U248">
         <v>3.54</v>
@@ -40766,10 +40766,10 @@
         <v>1.06</v>
       </c>
       <c r="Y248">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z248">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AA248">
         <v>2.38</v>
@@ -40784,7 +40784,7 @@
         <v>1.18</v>
       </c>
       <c r="AE248">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF248">
         <v>1.95</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O249">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P249">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB249">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -41222,19 +41222,19 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="O251">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P251">
-        <v>3.09</v>
+        <v>2.98</v>
       </c>
       <c r="Q251">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="R251">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S251">
         <v>1.37</v>
@@ -41243,25 +41243,25 @@
         <v>2.88</v>
       </c>
       <c r="U251">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V251">
         <v>1.38</v>
       </c>
       <c r="W251">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X251">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y251">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z251">
         <v>3.3</v>
       </c>
       <c r="AA251">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB251">
         <v>1.78</v>
@@ -41276,10 +41276,10 @@
         <v>1.06</v>
       </c>
       <c r="AF251">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG251">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41406,22 +41406,22 @@
         <v>2.62</v>
       </c>
       <c r="U252">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="V252">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W252">
         <v>1.02</v>
       </c>
       <c r="X252">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z252">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AA252">
         <v>2.1</v>
@@ -41439,10 +41439,10 @@
         <v>1.06</v>
       </c>
       <c r="AF252">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG252">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK252">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41548,25 +41548,25 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O253">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P253">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="Q253">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="R253">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S253">
         <v>1.4</v>
       </c>
       <c r="T253">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U253">
         <v>2.85</v>
@@ -41618,7 +41618,7 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK253">
         <v>1.42</v>
@@ -42559,7 +42559,7 @@
         <v>1.05</v>
       </c>
       <c r="Y259">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z259">
         <v>3.42</v>
@@ -42571,7 +42571,7 @@
         <v>1.87</v>
       </c>
       <c r="AC259">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AD259">
         <v>1.29</v>
@@ -42583,7 +42583,7 @@
         <v>1.92</v>
       </c>
       <c r="AG259">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AK259">
         <v>2.36</v>
@@ -43018,10 +43018,10 @@
         <v>2.55</v>
       </c>
       <c r="O262">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="P262">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43504,16 +43504,16 @@
         </is>
       </c>
       <c r="N265">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="O265">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P265">
-        <v>4.45</v>
+        <v>4.85</v>
       </c>
       <c r="Q265">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="R265">
         <v>2.5</v>
@@ -43528,10 +43528,10 @@
         <v>2.1</v>
       </c>
       <c r="V265">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W265">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X265">
         <v>1.02</v>
@@ -43546,10 +43546,10 @@
         <v>1.41</v>
       </c>
       <c r="AB265">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AC265">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AD265">
         <v>1.7</v>
@@ -43561,7 +43561,7 @@
         <v>1.5</v>
       </c>
       <c r="AG265">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK265">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O266">
         <v>2.9</v>
@@ -43676,10 +43676,10 @@
         <v>2.9</v>
       </c>
       <c r="Q266">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="R266">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="S266">
         <v>1.49</v>
@@ -43740,7 +43740,7 @@
         <v>1.33</v>
       </c>
       <c r="AK266">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43830,25 +43830,25 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O267">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P267">
         <v>4</v>
       </c>
       <c r="Q267">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R267">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S267">
         <v>1.42</v>
       </c>
       <c r="T267">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U267">
         <v>2.97</v>
@@ -43869,16 +43869,16 @@
         <v>2.92</v>
       </c>
       <c r="AA267">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB267">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC267">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD267">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE267">
         <v>1.04</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK267">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43993,19 +43993,19 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O268">
         <v>3.1</v>
       </c>
       <c r="P268">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q268">
         <v>2.88</v>
       </c>
       <c r="R268">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S268">
         <v>1.44</v>
@@ -44014,7 +44014,7 @@
         <v>2.59</v>
       </c>
       <c r="U268">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V268">
         <v>1.34</v>
@@ -44023,28 +44023,28 @@
         <v>1.06</v>
       </c>
       <c r="X268">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y268">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z268">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="AA268">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AB268">
         <v>1.67</v>
       </c>
       <c r="AC268">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD268">
         <v>1.22</v>
       </c>
       <c r="AE268">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF268">
         <v>1.77</v>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK268">
         <v>1.6</v>
@@ -44322,13 +44322,13 @@
         <v>7</v>
       </c>
       <c r="O270">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P270">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q270">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
       <c r="R270">
         <v>2.36</v>
@@ -44376,7 +44376,7 @@
         <v>1.9</v>
       </c>
       <c r="AG270">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44482,19 +44482,19 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="O271">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="P271">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q271">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R271">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S271">
         <v>1.22</v>
@@ -44503,13 +44503,13 @@
         <v>3.75</v>
       </c>
       <c r="U271">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V271">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W271">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X271">
         <v>1.01</v>
@@ -44518,28 +44518,28 @@
         <v>1.14</v>
       </c>
       <c r="Z271">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA271">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB271">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="AC271">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD271">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE271">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF271">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG271">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>1.05</v>
       </c>
       <c r="AK271">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -45297,16 +45297,16 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O276">
         <v>3.4</v>
       </c>
       <c r="P276">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q276">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R276">
         <v>2.05</v>
@@ -45330,10 +45330,10 @@
         <v>1.07</v>
       </c>
       <c r="Y276">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z276">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA276">
         <v>2.04</v>
@@ -45342,19 +45342,19 @@
         <v>1.75</v>
       </c>
       <c r="AC276">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD276">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE276">
         <v>1.09</v>
       </c>
       <c r="AF276">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG276">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK276">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -46302,7 +46302,7 @@
         <v>1.24</v>
       </c>
       <c r="W282">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X282">
         <v>1.06</v>
@@ -46311,28 +46311,28 @@
         <v>1.52</v>
       </c>
       <c r="Z282">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AA282">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AB282">
         <v>1.48</v>
       </c>
       <c r="AC282">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD282">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE282">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF282">
         <v>2.1</v>
       </c>
       <c r="AG282">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -644,16 +644,16 @@
         <v>2.3</v>
       </c>
       <c r="Q2">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="R2">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U2">
         <v>2.56</v>
@@ -665,7 +665,7 @@
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.2</v>
@@ -677,7 +677,7 @@
         <v>1.74</v>
       </c>
       <c r="AB2">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC2">
         <v>2.74</v>
@@ -686,7 +686,7 @@
         <v>1.35</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
         <v>1.6</v>
@@ -708,7 +708,7 @@
         <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="O3">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="O4">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>3.16</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R5">
         <v>2.25</v>
@@ -1145,10 +1145,10 @@
         <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
         <v>1.1</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
         <v>1.61</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>1.52</v>
       </c>
       <c r="AG5">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,61 +1290,61 @@
         <v>3.7</v>
       </c>
       <c r="O6">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
         <v>4.5</v>
       </c>
       <c r="R6">
+        <v>2.05</v>
+      </c>
+      <c r="S6">
+        <v>1.4</v>
+      </c>
+      <c r="T6">
+        <v>2.62</v>
+      </c>
+      <c r="U6">
+        <v>3.02</v>
+      </c>
+      <c r="V6">
+        <v>1.31</v>
+      </c>
+      <c r="W6">
+        <v>1.02</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.31</v>
+      </c>
+      <c r="Z6">
+        <v>2.92</v>
+      </c>
+      <c r="AA6">
         <v>2.1</v>
       </c>
-      <c r="S6">
-        <v>1.38</v>
-      </c>
-      <c r="T6">
-        <v>2.78</v>
-      </c>
-      <c r="U6">
-        <v>2.7</v>
-      </c>
-      <c r="V6">
-        <v>1.39</v>
-      </c>
-      <c r="W6">
+      <c r="AB6">
+        <v>1.67</v>
+      </c>
+      <c r="AC6">
+        <v>3.7</v>
+      </c>
+      <c r="AD6">
+        <v>1.2</v>
+      </c>
+      <c r="AE6">
         <v>1.05</v>
       </c>
-      <c r="X6">
-        <v>1.05</v>
-      </c>
-      <c r="Y6">
-        <v>1.26</v>
-      </c>
-      <c r="Z6">
-        <v>3.2</v>
-      </c>
-      <c r="AA6">
+      <c r="AF6">
         <v>1.91</v>
       </c>
-      <c r="AB6">
-        <v>1.8</v>
-      </c>
-      <c r="AC6">
-        <v>3.45</v>
-      </c>
-      <c r="AD6">
-        <v>1.28</v>
-      </c>
-      <c r="AE6">
-        <v>1.04</v>
-      </c>
-      <c r="AF6">
-        <v>1.85</v>
-      </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
         <v>1.22</v>
@@ -1462,13 +1462,13 @@
         <v>3.84</v>
       </c>
       <c r="R7">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
         <v>2.29</v>
@@ -1489,10 +1489,10 @@
         <v>4.55</v>
       </c>
       <c r="AA7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC7">
         <v>2.42</v>
@@ -1504,10 +1504,10 @@
         <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG7">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
         <v>1.25</v>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O8">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="P8">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R8">
         <v>1.95</v>
       </c>
       <c r="S8">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T8">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U8">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V8">
         <v>1.29</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y8">
         <v>1.44</v>
@@ -1652,25 +1652,25 @@
         <v>2.61</v>
       </c>
       <c r="AA8">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AB8">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC8">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE8">
         <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -1791,10 +1791,10 @@
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U9">
         <v>3.2</v>
@@ -1809,19 +1809,19 @@
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z9">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AA9">
         <v>2.25</v>
       </c>
       <c r="AB9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AD9">
         <v>1.2</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
         <v>3.27</v>
@@ -2120,7 +2120,7 @@
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
         <v>2.74</v>
@@ -2129,16 +2129,16 @@
         <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA11">
         <v>1.95</v>
@@ -2156,7 +2156,7 @@
         <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
         <v>1.83</v>
@@ -2434,25 +2434,25 @@
         <v>2.9</v>
       </c>
       <c r="P13">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="Q13">
         <v>2.85</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S13">
         <v>1.6</v>
       </c>
       <c r="T13">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U13">
         <v>3.8</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
         <v>1.02</v>
@@ -2464,10 +2464,10 @@
         <v>1.5</v>
       </c>
       <c r="Z13">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AA13">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB13">
         <v>1.47</v>
@@ -2482,7 +2482,7 @@
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AG13">
         <v>1.65</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
         <v>1.62</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
         <v>3.4</v>
       </c>
       <c r="Q14">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S14">
         <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
         <v>2.82</v>
@@ -2618,7 +2618,7 @@
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -2630,16 +2630,16 @@
         <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB14">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC14">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
         <v>1.1</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O15">
         <v>3.1</v>
       </c>
       <c r="P15">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="Q15">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <v>2.05</v>
@@ -2778,7 +2778,7 @@
         <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2787,7 +2787,7 @@
         <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z15">
         <v>2.5</v>
@@ -2796,7 +2796,7 @@
         <v>2.44</v>
       </c>
       <c r="AB15">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AC15">
         <v>4.6</v>
@@ -2808,10 +2808,10 @@
         <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
         <v>1.2</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
         <v>2.8</v>
@@ -2959,7 +2959,7 @@
         <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
         <v>4</v>
@@ -3095,19 +3095,19 @@
         <v>2.05</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T17">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.04</v>
@@ -3119,10 +3119,10 @@
         <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC17">
         <v>3.6</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
         <v>1.3</v>
@@ -3243,40 +3243,40 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="Q18">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.08</v>
       </c>
       <c r="Y18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
         <v>2.7</v>
@@ -3288,7 +3288,7 @@
         <v>1.61</v>
       </c>
       <c r="AC18">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD18">
         <v>1.22</v>
@@ -3300,7 +3300,7 @@
         <v>1.88</v>
       </c>
       <c r="AG18">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q19">
         <v>3</v>
       </c>
       <c r="R19">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
         <v>1.42</v>
@@ -3436,7 +3436,7 @@
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
         <v>1.32</v>
@@ -3454,13 +3454,13 @@
         <v>3.74</v>
       </c>
       <c r="AD19">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
         <v>1.85</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
       </c>
       <c r="R22">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
         <v>1.3</v>
@@ -3931,10 +3931,10 @@
         <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AA22">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
         <v>1.91</v>
@@ -3952,7 +3952,7 @@
         <v>1.64</v>
       </c>
       <c r="AG22">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>3.44</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
         <v>2.7</v>
@@ -4076,7 +4076,7 @@
         <v>1.43</v>
       </c>
       <c r="T23">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U23">
         <v>2.95</v>
@@ -4097,25 +4097,25 @@
         <v>2.85</v>
       </c>
       <c r="AA23">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC23">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="AD23">
         <v>1.24</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="O24">
         <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="Q24">
         <v>2.85</v>
       </c>
       <c r="R24">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V24">
         <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4260,7 +4260,7 @@
         <v>3.44</v>
       </c>
       <c r="AA24">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB24">
         <v>1.86</v>
@@ -4269,7 +4269,7 @@
         <v>2.99</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE24">
         <v>1.13</v>
@@ -4390,13 +4390,13 @@
         <v>3.8</v>
       </c>
       <c r="P25">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q25">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R25">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S25">
         <v>1.27</v>
@@ -4405,10 +4405,10 @@
         <v>3.4</v>
       </c>
       <c r="U25">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V25">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
         <v>1.09</v>
@@ -4417,28 +4417,28 @@
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z25">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
         <v>1.62</v>
       </c>
       <c r="AB25">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AC25">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE25">
         <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG25">
         <v>2.15</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
+        <v>3.25</v>
+      </c>
+      <c r="Q26">
         <v>2.45</v>
       </c>
-      <c r="Q26">
-        <v>3.6</v>
-      </c>
       <c r="R26">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T26">
-        <v>2.43</v>
+        <v>3.15</v>
       </c>
       <c r="U26">
-        <v>3.3</v>
+        <v>2.47</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="Z26">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="AB26">
-        <v>1.55</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q27">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
+        <v>1.4</v>
+      </c>
+      <c r="T27">
+        <v>2.88</v>
+      </c>
+      <c r="U27">
+        <v>2.66</v>
+      </c>
+      <c r="V27">
+        <v>1.4</v>
+      </c>
+      <c r="W27">
+        <v>1.04</v>
+      </c>
+      <c r="X27">
+        <v>1.06</v>
+      </c>
+      <c r="Y27">
         <v>1.31</v>
       </c>
-      <c r="T27">
-        <v>3.3</v>
-      </c>
-      <c r="U27">
-        <v>2.4</v>
-      </c>
-      <c r="V27">
-        <v>1.5</v>
-      </c>
-      <c r="W27">
-        <v>1.08</v>
-      </c>
-      <c r="X27">
-        <v>1.03</v>
-      </c>
-      <c r="Y27">
-        <v>1.16</v>
-      </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA27">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AC27">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="O28">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U28">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="V28">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z28">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
+        <v>2.4</v>
+      </c>
+      <c r="AB28">
+        <v>1.55</v>
+      </c>
+      <c r="AC28">
+        <v>4.5</v>
+      </c>
+      <c r="AD28">
+        <v>1.18</v>
+      </c>
+      <c r="AE28">
+        <v>1.05</v>
+      </c>
+      <c r="AF28">
         <v>1.95</v>
       </c>
-      <c r="AB28">
-        <v>1.8</v>
-      </c>
-      <c r="AC28">
-        <v>3.18</v>
-      </c>
-      <c r="AD28">
-        <v>1.3</v>
-      </c>
-      <c r="AE28">
-        <v>1.06</v>
-      </c>
-      <c r="AF28">
-        <v>1.7</v>
-      </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,22 +5036,22 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O29">
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q29">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R29">
         <v>2.02</v>
       </c>
       <c r="S29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
         <v>2.56</v>
@@ -5090,7 +5090,7 @@
         <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
         <v>1.95</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q30">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R30">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
         <v>3.5</v>
@@ -5229,7 +5229,7 @@
         <v>1.14</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.13</v>
@@ -5238,13 +5238,13 @@
         <v>4.6</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB30">
         <v>2.3</v>
       </c>
       <c r="AC30">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD30">
         <v>1.46</v>
@@ -5256,7 +5256,7 @@
         <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
         <v>2.5</v>
@@ -5368,7 +5368,7 @@
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="Q31">
         <v>2.5</v>
@@ -5392,7 +5392,7 @@
         <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.18</v>
@@ -5401,13 +5401,13 @@
         <v>4.5</v>
       </c>
       <c r="AA31">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AB31">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AD31">
         <v>1.5</v>
@@ -5416,7 +5416,7 @@
         <v>1.2</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG31">
         <v>2.4</v>
@@ -5435,7 +5435,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
+        <v>4.4</v>
+      </c>
+      <c r="O32">
+        <v>3.8</v>
+      </c>
+      <c r="P32">
+        <v>1.62</v>
+      </c>
+      <c r="Q32">
+        <v>4.65</v>
+      </c>
+      <c r="R32">
+        <v>2.3</v>
+      </c>
+      <c r="S32">
+        <v>1.28</v>
+      </c>
+      <c r="T32">
+        <v>3.25</v>
+      </c>
+      <c r="U32">
+        <v>2.33</v>
+      </c>
+      <c r="V32">
+        <v>1.46</v>
+      </c>
+      <c r="W32">
+        <v>1.08</v>
+      </c>
+      <c r="X32">
+        <v>1.04</v>
+      </c>
+      <c r="Y32">
+        <v>1.17</v>
+      </c>
+      <c r="Z32">
         <v>4.2</v>
       </c>
-      <c r="O32">
-        <v>3.5</v>
-      </c>
-      <c r="P32">
-        <v>1.69</v>
-      </c>
-      <c r="Q32">
-        <v>4.5</v>
-      </c>
-      <c r="R32">
-        <v>2.12</v>
-      </c>
-      <c r="S32">
-        <v>1.38</v>
-      </c>
-      <c r="T32">
-        <v>2.88</v>
-      </c>
-      <c r="U32">
-        <v>2.95</v>
-      </c>
-      <c r="V32">
-        <v>1.37</v>
-      </c>
-      <c r="W32">
-        <v>1.04</v>
-      </c>
-      <c r="X32">
-        <v>1</v>
-      </c>
-      <c r="Y32">
-        <v>1.3</v>
-      </c>
-      <c r="Z32">
-        <v>3.3</v>
-      </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="P33">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Q33">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.94</v>
       </c>
       <c r="AK33">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,16 +5854,16 @@
         <v>3.3</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q34">
         <v>4.2</v>
       </c>
       <c r="R34">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S34">
         <v>1.41</v>
@@ -5872,43 +5872,43 @@
         <v>2.84</v>
       </c>
       <c r="U34">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="V34">
+        <v>1.33</v>
+      </c>
+      <c r="W34">
+        <v>1.02</v>
+      </c>
+      <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
         <v>1.34</v>
       </c>
-      <c r="W34">
-        <v>1.05</v>
-      </c>
-      <c r="X34">
-        <v>1</v>
-      </c>
-      <c r="Y34">
-        <v>1.33</v>
-      </c>
       <c r="Z34">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="AA34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB34">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC34">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
         <v>1.28</v>
@@ -6017,7 +6017,7 @@
         <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P35">
         <v>2.8</v>
@@ -6035,10 +6035,10 @@
         <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6062,7 +6062,7 @@
         <v>2.7</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE35">
         <v>1.1</v>
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="P51">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="Q51">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="R51">
         <v>2.4</v>
@@ -8643,13 +8643,13 @@
         <v>4</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
         <v>1.64</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8664,7 +8664,7 @@
         <v>1.45</v>
       </c>
       <c r="AB51">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AC51">
         <v>2.25</v>
@@ -8676,10 +8676,10 @@
         <v>1.22</v>
       </c>
       <c r="AF51">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG51">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O52">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P52">
         <v>3.45</v>
@@ -8815,22 +8815,22 @@
         <v>1.18</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z52">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA52">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC52">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD52">
         <v>1.77</v>
@@ -8842,7 +8842,7 @@
         <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="Q53">
         <v>2.95</v>
@@ -8963,40 +8963,40 @@
         <v>2.32</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="U53">
         <v>2.25</v>
       </c>
       <c r="V53">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W53">
         <v>1.1</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA53">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB53">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC53">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD53">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE53">
         <v>1.18</v>
@@ -9114,13 +9114,13 @@
         <v>1.44</v>
       </c>
       <c r="O54">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="P54">
         <v>5.25</v>
       </c>
       <c r="Q54">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R54">
         <v>2.85</v>
@@ -9129,7 +9129,7 @@
         <v>1.14</v>
       </c>
       <c r="T54">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="U54">
         <v>1.77</v>
@@ -9138,28 +9138,28 @@
         <v>1.91</v>
       </c>
       <c r="W54">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z54">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA54">
         <v>1.24</v>
       </c>
       <c r="AB54">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="AC54">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD54">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AE54">
         <v>1.44</v>
@@ -9168,7 +9168,7 @@
         <v>1.38</v>
       </c>
       <c r="AG54">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="O58">
         <v>3.5</v>
       </c>
       <c r="P58">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="Q58">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="R58">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="S58">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T58">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="U58">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="AA58">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB58">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC58">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD58">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,61 +9926,61 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="O59">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>3.51</v>
+        <v>4</v>
       </c>
       <c r="Q59">
+        <v>2.22</v>
+      </c>
+      <c r="R59">
         <v>2.34</v>
       </c>
-      <c r="R59">
-        <v>2.15</v>
-      </c>
       <c r="S59">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T59">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U59">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="V59">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W59">
         <v>1.06</v>
       </c>
       <c r="X59">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z59">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="AA59">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB59">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC59">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AD59">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE59">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF59">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
         <v>1.95</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK59">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10128,16 +10128,16 @@
         <v>3.84</v>
       </c>
       <c r="AA60">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB60">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC60">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD60">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE60">
         <v>1.12</v>
@@ -10146,7 +10146,7 @@
         <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O63">
         <v>3.58</v>
       </c>
       <c r="P63">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="Q63">
         <v>2.4</v>
@@ -10599,7 +10599,7 @@
         <v>3.05</v>
       </c>
       <c r="U63">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V63">
         <v>1.45</v>
@@ -10611,22 +10611,22 @@
         <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z63">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA63">
         <v>1.73</v>
       </c>
       <c r="AB63">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC63">
         <v>2.7</v>
       </c>
       <c r="AD63">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE63">
         <v>1.14</v>
@@ -10635,7 +10635,7 @@
         <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
         <v>1.52</v>
@@ -11559,22 +11559,22 @@
         <v>1.95</v>
       </c>
       <c r="O69">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="P69">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
       </c>
       <c r="R69">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
         <v>1.29</v>
       </c>
       <c r="T69">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U69">
         <v>2.45</v>
@@ -11586,22 +11586,22 @@
         <v>1.12</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
         <v>4.2</v>
       </c>
       <c r="AA69">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB69">
         <v>2.2</v>
       </c>
       <c r="AC69">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD69">
         <v>1.44</v>
@@ -11613,7 +11613,7 @@
         <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P86">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q86">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R86">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S86">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T86">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="U86">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="V86">
         <v>1.36</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X86">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z86">
         <v>3</v>
       </c>
       <c r="AA86">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB86">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC86">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD86">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE86">
         <v>1.05</v>
       </c>
       <c r="AF86">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG86">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
+        <v>1.27</v>
+      </c>
+      <c r="AK86">
         <v>1.3</v>
-      </c>
-      <c r="AK86">
-        <v>1.7</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,61 +14490,61 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="O87">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P87">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q87">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="R87">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="S87">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T87">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U87">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="V87">
         <v>1.36</v>
       </c>
       <c r="W87">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z87">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA87">
         <v>2.06</v>
       </c>
       <c r="AB87">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC87">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AD87">
         <v>1.22</v>
       </c>
       <c r="AE87">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG87">
         <v>1.85</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="O88">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P88">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q88">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R88">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S88">
         <v>1.4</v>
       </c>
       <c r="T88">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U88">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V88">
         <v>1.36</v>
       </c>
       <c r="W88">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y88">
         <v>1.33</v>
       </c>
       <c r="Z88">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA88">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB88">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC88">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD88">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE88">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF88">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG88">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK88">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O99">
         <v>3.6</v>
@@ -16497,13 +16497,13 @@
         <v>1.44</v>
       </c>
       <c r="AE99">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF99">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG99">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
         <v>1.83</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.28</v>
+        <v>3.44</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P104">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="Q104">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="R104">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S104">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U104">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="V104">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W104">
+        <v>1.04</v>
+      </c>
+      <c r="X104">
         <v>1.06</v>
       </c>
-      <c r="X104">
-        <v>1</v>
-      </c>
       <c r="Y104">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="AA104">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB104">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC104">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AD104">
+        <v>1.29</v>
+      </c>
+      <c r="AE104">
+        <v>1.06</v>
+      </c>
+      <c r="AF104">
+        <v>1.8</v>
+      </c>
+      <c r="AG104">
+        <v>1.92</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
+        <v>1.25</v>
+      </c>
+      <c r="AK104">
         <v>1.3</v>
-      </c>
-      <c r="AE104">
-        <v>1.09</v>
-      </c>
-      <c r="AF104">
-        <v>1.67</v>
-      </c>
-      <c r="AG104">
-        <v>2.1</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.33</v>
-      </c>
-      <c r="AK104">
-        <v>1.55</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="O105">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P105">
-        <v>8.35</v>
+        <v>4</v>
       </c>
       <c r="Q105">
-        <v>1.8</v>
+        <v>2.42</v>
       </c>
       <c r="R105">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="S105">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T105">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U105">
-        <v>2.34</v>
+        <v>2.77</v>
       </c>
       <c r="V105">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="W105">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z105">
-        <v>4.2</v>
+        <v>3.53</v>
       </c>
       <c r="AA105">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AB105">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="AC105">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="AD105">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE105">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF105">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.44</v>
+        <v>1.34</v>
       </c>
       <c r="O106">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="P106">
-        <v>2.08</v>
+        <v>8.35</v>
       </c>
       <c r="Q106">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="R106">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="S106">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U106">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="V106">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W106">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z106">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AA106">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB106">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AC106">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="AD106">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE106">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF106">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK106">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="O107">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="Q107">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="R107">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S107">
         <v>1.35</v>
@@ -17771,10 +17771,10 @@
         <v>3</v>
       </c>
       <c r="U107">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V107">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
         <v>1.06</v>
@@ -17783,31 +17783,31 @@
         <v>1</v>
       </c>
       <c r="Y107">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z107">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="AA107">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AB107">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AC107">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AD107">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK107">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17922,7 +17922,7 @@
         <v>1.8</v>
       </c>
       <c r="Q108">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="R108">
         <v>2.22</v>
@@ -17949,28 +17949,28 @@
         <v>1.18</v>
       </c>
       <c r="Z108">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="AA108">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB108">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC108">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD108">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
         <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG108">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.82</v>
+        <v>1.2</v>
       </c>
       <c r="AK108">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -21010,16 +21010,16 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="O127">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P127">
         <v>2.19</v>
       </c>
       <c r="Q127">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="R127">
         <v>2.39</v>
@@ -21028,13 +21028,13 @@
         <v>1.29</v>
       </c>
       <c r="T127">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U127">
         <v>2.42</v>
       </c>
       <c r="V127">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W127">
         <v>1.11</v>
@@ -21049,10 +21049,10 @@
         <v>4.2</v>
       </c>
       <c r="AA127">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB127">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC127">
         <v>2.3</v>
@@ -21064,10 +21064,10 @@
         <v>1.14</v>
       </c>
       <c r="AF127">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AG127">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.87</v>
+        <v>3.94</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P144">
-        <v>4.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q144">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="R144">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S144">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T144">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U144">
-        <v>2.39</v>
+        <v>3.02</v>
       </c>
       <c r="V144">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W144">
         <v>1.08</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y144">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z144">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA144">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AB144">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AC144">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="AD144">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE144">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF144">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AG144">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK144">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>3.94</v>
+        <v>1.87</v>
       </c>
       <c r="O145">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>1.91</v>
+        <v>4.45</v>
       </c>
       <c r="Q145">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="R145">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S145">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T145">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U145">
-        <v>3.02</v>
+        <v>2.39</v>
       </c>
       <c r="V145">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W145">
         <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z145">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA145">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AB145">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AC145">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="AD145">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE145">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF145">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24596,80 +24596,80 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O149">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P149">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Q149">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="R149">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S149">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T149">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U149">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="V149">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W149">
         <v>1.11</v>
       </c>
       <c r="X149">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y149">
         <v>1.2</v>
       </c>
       <c r="Z149">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA149">
         <v>1.61</v>
       </c>
       <c r="AB149">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC149">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AD149">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE149">
+        <v>1.15</v>
+      </c>
+      <c r="AF149">
+        <v>1.65</v>
+      </c>
+      <c r="AG149">
+        <v>2.15</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ149">
         <v>1.14</v>
       </c>
-      <c r="AF149">
-        <v>1.62</v>
-      </c>
-      <c r="AG149">
-        <v>2.2</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ149">
-        <v>1.18</v>
-      </c>
       <c r="AK149">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O152">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P152">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q152">
         <v>4</v>
@@ -25100,7 +25100,7 @@
         <v>2.15</v>
       </c>
       <c r="S152">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T152">
         <v>3.1</v>
@@ -25124,7 +25124,7 @@
         <v>3.5</v>
       </c>
       <c r="AA152">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB152">
         <v>1.95</v>
@@ -25133,13 +25133,13 @@
         <v>3.1</v>
       </c>
       <c r="AD152">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE152">
         <v>1.13</v>
       </c>
       <c r="AF152">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG152">
         <v>2</v>
@@ -28834,19 +28834,19 @@
         </is>
       </c>
       <c r="N175">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O175">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P175">
         <v>1.61</v>
       </c>
       <c r="Q175">
-        <v>4.6</v>
+        <v>4.77</v>
       </c>
       <c r="R175">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S175">
         <v>1.23</v>
@@ -28861,7 +28861,7 @@
         <v>1.59</v>
       </c>
       <c r="W175">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X175">
         <v>1</v>
@@ -28876,7 +28876,7 @@
         <v>1.47</v>
       </c>
       <c r="AB175">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC175">
         <v>2.25</v>
@@ -28904,7 +28904,7 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>2.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK175">
         <v>1.13</v>
@@ -30983,25 +30983,25 @@
         <v>1.08</v>
       </c>
       <c r="X188">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y188">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z188">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AA188">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB188">
         <v>1.91</v>
       </c>
       <c r="AC188">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="AD188">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE188">
         <v>1.12</v>
@@ -31010,7 +31010,7 @@
         <v>1.62</v>
       </c>
       <c r="AG188">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>3.6</v>
+        <v>1.23</v>
       </c>
       <c r="O207">
-        <v>3.02</v>
+        <v>6.5</v>
       </c>
       <c r="P207">
-        <v>2.18</v>
+        <v>11</v>
       </c>
       <c r="Q207">
+        <v>1.59</v>
+      </c>
+      <c r="R207">
+        <v>2.8</v>
+      </c>
+      <c r="S207">
+        <v>1.25</v>
+      </c>
+      <c r="T207">
+        <v>3.42</v>
+      </c>
+      <c r="U207">
+        <v>2.14</v>
+      </c>
+      <c r="V207">
+        <v>1.59</v>
+      </c>
+      <c r="W207">
+        <v>1.13</v>
+      </c>
+      <c r="X207">
+        <v>1.02</v>
+      </c>
+      <c r="Y207">
+        <v>1.11</v>
+      </c>
+      <c r="Z207">
+        <v>4.6</v>
+      </c>
+      <c r="AA207">
+        <v>1.53</v>
+      </c>
+      <c r="AB207">
+        <v>2.4</v>
+      </c>
+      <c r="AC207">
+        <v>2.29</v>
+      </c>
+      <c r="AD207">
+        <v>1.57</v>
+      </c>
+      <c r="AE207">
+        <v>1.19</v>
+      </c>
+      <c r="AF207">
+        <v>2.05</v>
+      </c>
+      <c r="AG207">
+        <v>1.73</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
+        <v>1.13</v>
+      </c>
+      <c r="AK207">
         <v>4.2</v>
-      </c>
-      <c r="R207">
-        <v>2.01</v>
-      </c>
-      <c r="S207">
-        <v>1.56</v>
-      </c>
-      <c r="T207">
-        <v>2.45</v>
-      </c>
-      <c r="U207">
-        <v>3.6</v>
-      </c>
-      <c r="V207">
-        <v>1.3</v>
-      </c>
-      <c r="W207">
-        <v>1</v>
-      </c>
-      <c r="X207">
-        <v>1.1</v>
-      </c>
-      <c r="Y207">
-        <v>1.45</v>
-      </c>
-      <c r="Z207">
-        <v>2.6</v>
-      </c>
-      <c r="AA207">
-        <v>2.4</v>
-      </c>
-      <c r="AB207">
-        <v>1.5</v>
-      </c>
-      <c r="AC207">
-        <v>4.45</v>
-      </c>
-      <c r="AD207">
-        <v>1.14</v>
-      </c>
-      <c r="AE207">
-        <v>1.05</v>
-      </c>
-      <c r="AF207">
-        <v>1.95</v>
-      </c>
-      <c r="AG207">
-        <v>1.7</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.65</v>
-      </c>
-      <c r="AK207">
-        <v>1.26</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.23</v>
+        <v>3.6</v>
       </c>
       <c r="O208">
-        <v>6.5</v>
+        <v>3.02</v>
       </c>
       <c r="P208">
-        <v>11</v>
+        <v>2.18</v>
       </c>
       <c r="Q208">
-        <v>1.59</v>
+        <v>4.2</v>
       </c>
       <c r="R208">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="S208">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="T208">
-        <v>3.42</v>
+        <v>2.45</v>
       </c>
       <c r="U208">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="V208">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="W208">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="X208">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y208">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="Z208">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA208">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AB208">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC208">
-        <v>2.29</v>
+        <v>4.45</v>
       </c>
       <c r="AD208">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AE208">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF208">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG208">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="AK208">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O219">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P219">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q219">
         <v>2.5</v>
@@ -36024,7 +36024,7 @@
         <v>1.63</v>
       </c>
       <c r="T219">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="U219">
         <v>3.8</v>
@@ -36060,7 +36060,7 @@
         <v>1.03</v>
       </c>
       <c r="AF219">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AG219">
         <v>1.53</v>
@@ -36332,31 +36332,31 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="O221">
         <v>4.3</v>
       </c>
       <c r="P221">
-        <v>7.37</v>
+        <v>5.9</v>
       </c>
       <c r="Q221">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R221">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S221">
         <v>1.3</v>
       </c>
       <c r="T221">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U221">
         <v>2.34</v>
       </c>
       <c r="V221">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W221">
         <v>1.09</v>
@@ -36365,13 +36365,13 @@
         <v>1.04</v>
       </c>
       <c r="Y221">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z221">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA221">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB221">
         <v>2.27</v>
@@ -36380,10 +36380,10 @@
         <v>2.7</v>
       </c>
       <c r="AD221">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE221">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF221">
         <v>1.85</v>
@@ -36405,7 +36405,7 @@
         <v>1.15</v>
       </c>
       <c r="AK221">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -37473,43 +37473,43 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O228">
+        <v>3.44</v>
+      </c>
+      <c r="P228">
+        <v>2.36</v>
+      </c>
+      <c r="Q228">
+        <v>3.4</v>
+      </c>
+      <c r="R228">
+        <v>2.15</v>
+      </c>
+      <c r="S228">
+        <v>1.35</v>
+      </c>
+      <c r="T228">
         <v>3.25</v>
       </c>
-      <c r="P228">
-        <v>2.37</v>
-      </c>
-      <c r="Q228">
-        <v>3.04</v>
-      </c>
-      <c r="R228">
-        <v>2.12</v>
-      </c>
-      <c r="S228">
-        <v>1.36</v>
-      </c>
-      <c r="T228">
-        <v>2.99</v>
-      </c>
       <c r="U228">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V228">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W228">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X228">
         <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z228">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA228">
         <v>1.78</v>
@@ -37518,19 +37518,19 @@
         <v>1.98</v>
       </c>
       <c r="AC228">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD228">
         <v>1.33</v>
       </c>
       <c r="AE228">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF228">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG228">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AK228">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -38164,10 +38164,10 @@
         <v>2.2</v>
       </c>
       <c r="AA232">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB232">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC232">
         <v>0</v>
@@ -38297,16 +38297,16 @@
         <v>4.15</v>
       </c>
       <c r="Q233">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="R233">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="S233">
         <v>1.61</v>
       </c>
       <c r="T233">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="U233">
         <v>3.7</v>
@@ -38315,7 +38315,7 @@
         <v>1.19</v>
       </c>
       <c r="W233">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X233">
         <v>1.08</v>
@@ -38327,7 +38327,7 @@
         <v>2.4</v>
       </c>
       <c r="AA233">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="AB233">
         <v>1.36</v>
@@ -38361,7 +38361,7 @@
         <v>1.36</v>
       </c>
       <c r="AK233">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38451,16 +38451,16 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O234">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P234">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q234">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R234">
         <v>1.89</v>
@@ -38469,37 +38469,37 @@
         <v>1.49</v>
       </c>
       <c r="T234">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="U234">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="V234">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W234">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X234">
         <v>1.07</v>
       </c>
       <c r="Y234">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z234">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AA234">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AB234">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC234">
         <v>4.25</v>
       </c>
       <c r="AD234">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE234">
         <v>1.01</v>
@@ -38508,7 +38508,7 @@
         <v>1.94</v>
       </c>
       <c r="AG234">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>1.31</v>
       </c>
       <c r="AK234">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38614,31 +38614,31 @@
         </is>
       </c>
       <c r="N235">
+        <v>2.62</v>
+      </c>
+      <c r="O235">
         <v>2.7</v>
       </c>
-      <c r="O235">
-        <v>2.62</v>
-      </c>
       <c r="P235">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q235">
         <v>3.64</v>
       </c>
       <c r="R235">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S235">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T235">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U235">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="V235">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W235">
         <v>1.03</v>
@@ -38647,31 +38647,31 @@
         <v>1.1</v>
       </c>
       <c r="Y235">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z235">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AA235">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AB235">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AC235">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="AD235">
         <v>1.06</v>
       </c>
       <c r="AE235">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF235">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AG235">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>1.36</v>
       </c>
       <c r="AK235">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O236">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P236">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q236">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="R236">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="S236">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="T236">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="U236">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="V236">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W236">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X236">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y236">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="Z236">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AA236">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB236">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC236">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD236">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE236">
         <v>1.02</v>
       </c>
       <c r="AF236">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="AG236">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
+        <v>1.36</v>
+      </c>
+      <c r="AK236">
         <v>1.44</v>
-      </c>
-      <c r="AK236">
-        <v>1.59</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,52 +38940,52 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O237">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P237">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="Q237">
-        <v>3.81</v>
+        <v>2.8</v>
       </c>
       <c r="R237">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S237">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="T237">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="U237">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="V237">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W237">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X237">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Y237">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z237">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AA237">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB237">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC237">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD237">
         <v>1.08</v>
@@ -38994,10 +38994,10 @@
         <v>1.02</v>
       </c>
       <c r="AF237">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AG237">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK237">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39758,61 +39758,61 @@
         <v>3.05</v>
       </c>
       <c r="O242">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P242">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q242">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="R242">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S242">
         <v>1.29</v>
       </c>
       <c r="T242">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U242">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V242">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W242">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X242">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y242">
+        <v>1.16</v>
+      </c>
+      <c r="Z242">
+        <v>3.65</v>
+      </c>
+      <c r="AA242">
+        <v>1.64</v>
+      </c>
+      <c r="AB242">
+        <v>2.23</v>
+      </c>
+      <c r="AC242">
+        <v>2.55</v>
+      </c>
+      <c r="AD242">
+        <v>1.44</v>
+      </c>
+      <c r="AE242">
         <v>1.17</v>
       </c>
-      <c r="Z242">
-        <v>3.98</v>
-      </c>
-      <c r="AA242">
-        <v>1.66</v>
-      </c>
-      <c r="AB242">
-        <v>2.18</v>
-      </c>
-      <c r="AC242">
-        <v>2.61</v>
-      </c>
-      <c r="AD242">
-        <v>1.42</v>
-      </c>
-      <c r="AE242">
-        <v>1.14</v>
-      </c>
       <c r="AF242">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG242">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>1.22</v>
       </c>
       <c r="AK242">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39918,19 +39918,19 @@
         </is>
       </c>
       <c r="N243">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O243">
         <v>3.55</v>
       </c>
       <c r="P243">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="Q243">
         <v>2.66</v>
       </c>
       <c r="R243">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S243">
         <v>1.35</v>
@@ -39948,7 +39948,7 @@
         <v>1.07</v>
       </c>
       <c r="X243">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
         <v>1.22</v>
@@ -39957,25 +39957,25 @@
         <v>3.9</v>
       </c>
       <c r="AA243">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB243">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC243">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="AD243">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE243">
         <v>1.08</v>
       </c>
       <c r="AF243">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG243">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         </is>
       </c>
       <c r="N244">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="O244">
         <v>3.6</v>
@@ -40093,7 +40093,7 @@
         <v>3.4</v>
       </c>
       <c r="R244">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S244">
         <v>1.33</v>
@@ -40102,7 +40102,7 @@
         <v>3.34</v>
       </c>
       <c r="U244">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V244">
         <v>1.49</v>
@@ -40111,13 +40111,13 @@
         <v>1.09</v>
       </c>
       <c r="X244">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y244">
         <v>1.22</v>
       </c>
       <c r="Z244">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA244">
         <v>1.83</v>
@@ -40126,7 +40126,7 @@
         <v>2</v>
       </c>
       <c r="AC244">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD244">
         <v>1.4</v>
@@ -40135,7 +40135,7 @@
         <v>1.15</v>
       </c>
       <c r="AF244">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG244">
         <v>2.25</v>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK244">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,25 +40244,25 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O245">
         <v>3.45</v>
       </c>
       <c r="P245">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q245">
         <v>2.88</v>
       </c>
       <c r="R245">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S245">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T245">
-        <v>3.28</v>
+        <v>2.86</v>
       </c>
       <c r="U245">
         <v>2.6</v>
@@ -40274,7 +40274,7 @@
         <v>1.08</v>
       </c>
       <c r="X245">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y245">
         <v>1.25</v>
@@ -40283,22 +40283,22 @@
         <v>3.9</v>
       </c>
       <c r="AA245">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB245">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC245">
         <v>2.83</v>
       </c>
       <c r="AD245">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE245">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF245">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG245">
         <v>2.25</v>
@@ -40317,7 +40317,7 @@
         <v>1.3</v>
       </c>
       <c r="AK245">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40416,13 +40416,13 @@
         <v>2.34</v>
       </c>
       <c r="Q246">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R246">
         <v>2.19</v>
       </c>
       <c r="S246">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T246">
         <v>3.3</v>
@@ -40434,28 +40434,28 @@
         <v>1.52</v>
       </c>
       <c r="W246">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X246">
         <v>1.05</v>
       </c>
       <c r="Y246">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z246">
         <v>4.15</v>
       </c>
       <c r="AA246">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AB246">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="AC246">
         <v>2.64</v>
       </c>
       <c r="AD246">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE246">
         <v>1.12</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AK246">
         <v>1.44</v>
@@ -41781,7 +41781,7 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK254">
         <v>1.85</v>
@@ -42200,16 +42200,16 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O257">
         <v>4.5</v>
       </c>
       <c r="P257">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q257">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R257">
         <v>2.33</v>
@@ -42230,19 +42230,19 @@
         <v>1.11</v>
       </c>
       <c r="X257">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y257">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z257">
-        <v>3.62</v>
+        <v>3.84</v>
       </c>
       <c r="AA257">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB257">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC257">
         <v>2.85</v>
@@ -42251,13 +42251,13 @@
         <v>1.36</v>
       </c>
       <c r="AE257">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF257">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG257">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>1.1</v>
       </c>
       <c r="AK257">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42689,7 +42689,7 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O260">
         <v>2.75</v>
@@ -42698,7 +42698,7 @@
         <v>3.5</v>
       </c>
       <c r="Q260">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R260">
         <v>1.9</v>
@@ -42710,7 +42710,7 @@
         <v>2.08</v>
       </c>
       <c r="U260">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V260">
         <v>1.15</v>
@@ -42722,25 +42722,25 @@
         <v>1.14</v>
       </c>
       <c r="Y260">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Z260">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AA260">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB260">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC260">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AD260">
         <v>1.05</v>
       </c>
       <c r="AE260">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF260">
         <v>2.4</v>
@@ -42762,7 +42762,7 @@
         <v>1.25</v>
       </c>
       <c r="AK260">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O261">
         <v>4.6</v>
       </c>
       <c r="P261">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="Q261">
         <v>1.77</v>
@@ -42873,28 +42873,28 @@
         <v>2.88</v>
       </c>
       <c r="U261">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="V261">
         <v>1.42</v>
       </c>
       <c r="W261">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X261">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y261">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z261">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AA261">
         <v>1.8</v>
       </c>
       <c r="AB261">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC261">
         <v>2.81</v>
@@ -42903,10 +42903,10 @@
         <v>1.36</v>
       </c>
       <c r="AE261">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF261">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AG261">
         <v>1.67</v>
@@ -42922,7 +42922,7 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK261">
         <v>3.05</v>
@@ -43341,31 +43341,31 @@
         </is>
       </c>
       <c r="N264">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O264">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="P264">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="Q264">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R264">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S264">
         <v>1.22</v>
       </c>
       <c r="T264">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U264">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V264">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W264">
         <v>1.15</v>
@@ -43374,31 +43374,31 @@
         <v>1.03</v>
       </c>
       <c r="Y264">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z264">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA264">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB264">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC264">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD264">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE264">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF264">
         <v>1.85</v>
       </c>
       <c r="AG264">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK264">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -44654,10 +44654,10 @@
         <v>2.75</v>
       </c>
       <c r="Q272">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R272">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="S272">
         <v>1.34</v>
@@ -44672,10 +44672,10 @@
         <v>1.37</v>
       </c>
       <c r="W272">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X272">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y272">
         <v>1.23</v>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK272">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44811,10 +44811,10 @@
         <v>1.95</v>
       </c>
       <c r="O273">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P273">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q273">
         <v>2.71</v>
@@ -44823,10 +44823,10 @@
         <v>1.83</v>
       </c>
       <c r="S273">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T273">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U273">
         <v>3.7</v>
@@ -44835,7 +44835,7 @@
         <v>1.2</v>
       </c>
       <c r="W273">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X273">
         <v>1.05</v>
@@ -44853,19 +44853,19 @@
         <v>1.41</v>
       </c>
       <c r="AC273">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AD273">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE273">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF273">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AG273">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O274">
         <v>3.2</v>
       </c>
       <c r="P274">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -44989,7 +44989,7 @@
         <v>1.33</v>
       </c>
       <c r="T274">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U274">
         <v>2.6</v>
@@ -44998,7 +44998,7 @@
         <v>1.42</v>
       </c>
       <c r="W274">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X274">
         <v>1.01</v>
@@ -45137,10 +45137,10 @@
         <v>1.44</v>
       </c>
       <c r="O275">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P275">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45801,13 +45801,13 @@
         <v>2.1</v>
       </c>
       <c r="S279">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T279">
         <v>2.9</v>
       </c>
       <c r="U279">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="V279">
         <v>1.33</v>
@@ -45816,22 +45816,22 @@
         <v>1.05</v>
       </c>
       <c r="X279">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y279">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z279">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA279">
         <v>2</v>
       </c>
       <c r="AB279">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC279">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="AD279">
         <v>1.3</v>
@@ -45856,7 +45856,7 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK279">
         <v>1.7</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O280">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P280">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q280">
         <v>2.82</v>
@@ -45970,7 +45970,7 @@
         <v>3.3</v>
       </c>
       <c r="U280">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="V280">
         <v>1.53</v>
@@ -45985,28 +45985,28 @@
         <v>1.2</v>
       </c>
       <c r="Z280">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA280">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB280">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AC280">
         <v>2.5</v>
       </c>
       <c r="AD280">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE280">
         <v>1.12</v>
       </c>
       <c r="AF280">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG280">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46112,10 +46112,10 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O281">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P281">
         <v>4.05</v>
@@ -46124,16 +46124,16 @@
         <v>2.5</v>
       </c>
       <c r="R281">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S281">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T281">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U281">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V281">
         <v>1.23</v>
@@ -46142,16 +46142,16 @@
         <v>1.05</v>
       </c>
       <c r="X281">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y281">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z281">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AA281">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB281">
         <v>1.53</v>
@@ -46160,10 +46160,10 @@
         <v>4.78</v>
       </c>
       <c r="AD281">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE281">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF281">
         <v>2.02</v>
@@ -46441,7 +46441,7 @@
         <v>2.25</v>
       </c>
       <c r="O283">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P283">
         <v>2.75</v>
@@ -46489,7 +46489,7 @@
         <v>1.32</v>
       </c>
       <c r="AE283">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF283">
         <v>1.6</v>
@@ -46610,16 +46610,16 @@
         <v>3.65</v>
       </c>
       <c r="Q284">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R284">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="S284">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T284">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="U284">
         <v>3.34</v>
@@ -46640,13 +46640,13 @@
         <v>2.52</v>
       </c>
       <c r="AA284">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AB284">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC284">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AD284">
         <v>1.14</v>
@@ -46658,7 +46658,7 @@
         <v>2.01</v>
       </c>
       <c r="AG284">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK284">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46773,7 +46773,7 @@
         <v>3</v>
       </c>
       <c r="Q285">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R285">
         <v>2.2</v>
@@ -46785,7 +46785,7 @@
         <v>3.08</v>
       </c>
       <c r="U285">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="V285">
         <v>1.49</v>
@@ -46803,7 +46803,7 @@
         <v>3.95</v>
       </c>
       <c r="AA285">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AB285">
         <v>2.25</v>
@@ -47090,19 +47090,19 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="O287">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P287">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="Q287">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R287">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="S287">
         <v>1.39</v>
@@ -47111,10 +47111,10 @@
         <v>2.66</v>
       </c>
       <c r="U287">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="V287">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W287">
         <v>1.05</v>
@@ -47123,22 +47123,22 @@
         <v>1.02</v>
       </c>
       <c r="Y287">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z287">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA287">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB287">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC287">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AD287">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE287">
         <v>1.06</v>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AK287">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47253,34 +47253,34 @@
         </is>
       </c>
       <c r="N288">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="O288">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P288">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q288">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R288">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S288">
         <v>1.25</v>
       </c>
       <c r="T288">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U288">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V288">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W288">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X288">
         <v>1.02</v>
@@ -47295,22 +47295,22 @@
         <v>1.66</v>
       </c>
       <c r="AB288">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AC288">
         <v>2.56</v>
       </c>
       <c r="AD288">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE288">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF288">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG288">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK288">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47425,19 +47425,19 @@
         <v>4.99</v>
       </c>
       <c r="Q289">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R289">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S289">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T289">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U289">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="V289">
         <v>1.47</v>
@@ -47452,16 +47452,16 @@
         <v>1.22</v>
       </c>
       <c r="Z289">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="AA289">
         <v>1.7</v>
       </c>
       <c r="AB289">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AC289">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="AD289">
         <v>1.42</v>
@@ -47470,10 +47470,10 @@
         <v>1.12</v>
       </c>
       <c r="AF289">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AG289">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47579,34 +47579,34 @@
         </is>
       </c>
       <c r="N290">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="O290">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P290">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="Q290">
         <v>3.94</v>
       </c>
       <c r="R290">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S290">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T290">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U290">
         <v>2.9</v>
       </c>
       <c r="V290">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W290">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X290">
         <v>1.04</v>
@@ -47618,7 +47618,7 @@
         <v>2.92</v>
       </c>
       <c r="AA290">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB290">
         <v>1.7</v>
@@ -47636,7 +47636,7 @@
         <v>1.77</v>
       </c>
       <c r="AG290">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47742,10 +47742,10 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="O291">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="P291">
         <v>7.6</v>
@@ -47920,7 +47920,7 @@
         <v>2.1</v>
       </c>
       <c r="S292">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T292">
         <v>2.7</v>
@@ -47935,22 +47935,22 @@
         <v>1.05</v>
       </c>
       <c r="X292">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y292">
         <v>1.32</v>
       </c>
       <c r="Z292">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA292">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB292">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC292">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="AD292">
         <v>1.25</v>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK292">
         <v>1.38</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O293">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P293">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q293">
         <v>1.85</v>
@@ -48089,10 +48089,10 @@
         <v>3.75</v>
       </c>
       <c r="U293">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V293">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W293">
         <v>1.12</v>
@@ -48107,25 +48107,25 @@
         <v>4.69</v>
       </c>
       <c r="AA293">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AB293">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AC293">
         <v>2.1</v>
       </c>
       <c r="AD293">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE293">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF293">
         <v>1.68</v>
       </c>
       <c r="AG293">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>1.18</v>
       </c>
       <c r="AK293">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48231,10 +48231,10 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O294">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P294">
         <v>5.95</v>
@@ -48246,16 +48246,16 @@
         <v>2.38</v>
       </c>
       <c r="S294">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T294">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U294">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V294">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W294">
         <v>1.1</v>
@@ -48264,16 +48264,16 @@
         <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z294">
         <v>4.15</v>
       </c>
       <c r="AA294">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB294">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AC294">
         <v>2.46</v>
@@ -48285,10 +48285,10 @@
         <v>1.15</v>
       </c>
       <c r="AF294">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG294">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK294">
         <v>2.53</v>
@@ -48720,7 +48720,7 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="O297">
         <v>3.9</v>
@@ -48732,19 +48732,19 @@
         <v>2.62</v>
       </c>
       <c r="R297">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S297">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T297">
         <v>4.8</v>
       </c>
       <c r="U297">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="V297">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W297">
         <v>1.2</v>
@@ -48753,16 +48753,16 @@
         <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z297">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA297">
         <v>1.4</v>
       </c>
       <c r="AB297">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AC297">
         <v>1.81</v>
@@ -48771,7 +48771,7 @@
         <v>1.94</v>
       </c>
       <c r="AE297">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF297">
         <v>1.36</v>
@@ -48883,22 +48883,22 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O298">
         <v>3.4</v>
       </c>
       <c r="P298">
+        <v>2.8</v>
+      </c>
+      <c r="Q298">
         <v>2.7</v>
-      </c>
-      <c r="Q298">
-        <v>2.76</v>
       </c>
       <c r="R298">
         <v>2.38</v>
       </c>
       <c r="S298">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T298">
         <v>3.5</v>
@@ -48910,7 +48910,7 @@
         <v>1.55</v>
       </c>
       <c r="W298">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X298">
         <v>1.03</v>
@@ -48922,7 +48922,7 @@
         <v>5</v>
       </c>
       <c r="AA298">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB298">
         <v>2.25</v>
@@ -48931,10 +48931,10 @@
         <v>2.38</v>
       </c>
       <c r="AD298">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE298">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF298">
         <v>1.53</v>
@@ -48956,7 +48956,7 @@
         <v>1.25</v>
       </c>
       <c r="AK298">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49049,16 +49049,16 @@
         <v>1.3</v>
       </c>
       <c r="O299">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P299">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q299">
         <v>1.7</v>
       </c>
       <c r="R299">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S299">
         <v>1.14</v>
@@ -49085,25 +49085,25 @@
         <v>7</v>
       </c>
       <c r="AA299">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB299">
         <v>3.25</v>
       </c>
       <c r="AC299">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AD299">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AE299">
         <v>1.36</v>
       </c>
       <c r="AF299">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG299">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49209,19 +49209,19 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O300">
-        <v>4.43</v>
+        <v>3.8</v>
       </c>
       <c r="P300">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q300">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R300">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S300">
         <v>1.17</v>
@@ -49230,13 +49230,13 @@
         <v>4.5</v>
       </c>
       <c r="U300">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V300">
         <v>1.74</v>
       </c>
       <c r="W300">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X300">
         <v>1.01</v>
@@ -49257,13 +49257,13 @@
         <v>1.95</v>
       </c>
       <c r="AD300">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE300">
         <v>1.33</v>
       </c>
       <c r="AF300">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG300">
         <v>3</v>
@@ -49375,16 +49375,16 @@
         <v>1.8</v>
       </c>
       <c r="O301">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="P301">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="Q301">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R301">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S301">
         <v>1.29</v>
@@ -49393,10 +49393,10 @@
         <v>3.28</v>
       </c>
       <c r="U301">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V301">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W301">
         <v>1.11</v>
@@ -49405,7 +49405,7 @@
         <v>1.03</v>
       </c>
       <c r="Y301">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z301">
         <v>4.5</v>
@@ -49414,22 +49414,22 @@
         <v>1.62</v>
       </c>
       <c r="AB301">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC301">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD301">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE301">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF301">
         <v>1.57</v>
       </c>
       <c r="AG301">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>1.22</v>
       </c>
       <c r="AK301">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49556,10 +49556,10 @@
         <v>4.33</v>
       </c>
       <c r="U302">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V302">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="W302">
         <v>1.2</v>
@@ -49577,7 +49577,7 @@
         <v>1.33</v>
       </c>
       <c r="AB302">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AC302">
         <v>2</v>
@@ -49592,7 +49592,7 @@
         <v>1.4</v>
       </c>
       <c r="AG302">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49698,34 +49698,34 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O303">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P303">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="Q303">
         <v>2.04</v>
       </c>
       <c r="R303">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="S303">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T303">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="U303">
         <v>2.05</v>
       </c>
       <c r="V303">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W303">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X303">
         <v>1.01</v>
@@ -49749,13 +49749,13 @@
         <v>1.66</v>
       </c>
       <c r="AE303">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF303">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG303">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49861,25 +49861,25 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O304">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P304">
         <v>4.5</v>
       </c>
       <c r="Q304">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R304">
         <v>2.25</v>
       </c>
       <c r="S304">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T304">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U304">
         <v>2.5</v>
@@ -49894,16 +49894,16 @@
         <v>1.04</v>
       </c>
       <c r="Y304">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z304">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA304">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB304">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC304">
         <v>2.8</v>
@@ -49912,7 +49912,7 @@
         <v>1.36</v>
       </c>
       <c r="AE304">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF304">
         <v>1.75</v>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK304">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50024,16 +50024,16 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O305">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P305">
         <v>4.5</v>
       </c>
       <c r="Q305">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="R305">
         <v>2.06</v>
@@ -50051,16 +50051,16 @@
         <v>1.32</v>
       </c>
       <c r="W305">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X305">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y305">
         <v>1.35</v>
       </c>
       <c r="Z305">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA305">
         <v>1.96</v>
@@ -50069,10 +50069,10 @@
         <v>1.7</v>
       </c>
       <c r="AC305">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="AD305">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE305">
         <v>1.04</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="O306">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P306">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q306">
         <v>3.54</v>
@@ -50223,10 +50223,10 @@
         <v>1.2</v>
       </c>
       <c r="Z306">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA306">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB306">
         <v>2.05</v>
@@ -50238,7 +50238,7 @@
         <v>1.42</v>
       </c>
       <c r="AE306">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF306">
         <v>1.55</v>
@@ -50353,10 +50353,10 @@
         <v>2</v>
       </c>
       <c r="O307">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P307">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q307">
         <v>2.5</v>
@@ -50365,22 +50365,22 @@
         <v>2.3</v>
       </c>
       <c r="S307">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T307">
         <v>3.5</v>
       </c>
       <c r="U307">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="V307">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W307">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X307">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y307">
         <v>1.18</v>
@@ -50389,7 +50389,7 @@
         <v>4.5</v>
       </c>
       <c r="AA307">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB307">
         <v>2.1</v>
@@ -50513,19 +50513,19 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O308">
+        <v>3.7</v>
+      </c>
+      <c r="P308">
         <v>3.9</v>
-      </c>
-      <c r="P308">
-        <v>4.1</v>
       </c>
       <c r="Q308">
         <v>2.24</v>
       </c>
       <c r="R308">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S308">
         <v>1.29</v>
@@ -50546,7 +50546,7 @@
         <v>1.03</v>
       </c>
       <c r="Y308">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z308">
         <v>4.15</v>
@@ -50570,7 +50570,7 @@
         <v>1.6</v>
       </c>
       <c r="AG308">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK308">
         <v>2.05</v>
@@ -50709,10 +50709,10 @@
         <v>1.03</v>
       </c>
       <c r="Y309">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z309">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA309">
         <v>1.56</v>
@@ -50724,7 +50724,7 @@
         <v>2.03</v>
       </c>
       <c r="AD309">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AE309">
         <v>1.13</v>
@@ -50848,22 +50848,22 @@
         <v>3.85</v>
       </c>
       <c r="Q310">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="R310">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S310">
         <v>1.28</v>
       </c>
       <c r="T310">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U310">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="V310">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W310">
         <v>1.11</v>
@@ -50875,19 +50875,19 @@
         <v>1.17</v>
       </c>
       <c r="Z310">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA310">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB310">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC310">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AD310">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE310">
         <v>1.14</v>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK310">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,31 +51002,31 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O311">
+        <v>3.25</v>
+      </c>
+      <c r="P311">
         <v>3.4</v>
       </c>
-      <c r="P311">
-        <v>3.65</v>
-      </c>
       <c r="Q311">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R311">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S311">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T311">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U311">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V311">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W311">
         <v>1.1</v>
@@ -51041,25 +51041,25 @@
         <v>3.85</v>
       </c>
       <c r="AA311">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB311">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC311">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="AD311">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE311">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF311">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG311">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK311">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51331,10 +51331,10 @@
         <v>1.44</v>
       </c>
       <c r="O313">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P313">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="Q313">
         <v>1.87</v>
@@ -51346,10 +51346,10 @@
         <v>1.22</v>
       </c>
       <c r="T313">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="U313">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V313">
         <v>1.7</v>
@@ -51361,16 +51361,16 @@
         <v>1.02</v>
       </c>
       <c r="Y313">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z313">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA313">
         <v>1.44</v>
       </c>
       <c r="AB313">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC313">
         <v>2.16</v>
@@ -51379,7 +51379,7 @@
         <v>1.75</v>
       </c>
       <c r="AE313">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF313">
         <v>1.6</v>
@@ -51401,7 +51401,7 @@
         <v>1.11</v>
       </c>
       <c r="AK313">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51497,13 +51497,13 @@
         <v>3.25</v>
       </c>
       <c r="P314">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="Q314">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="R314">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S314">
         <v>1.36</v>
@@ -51512,13 +51512,13 @@
         <v>2.78</v>
       </c>
       <c r="U314">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="V314">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W314">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X314">
         <v>1</v>
@@ -51533,7 +51533,7 @@
         <v>1.96</v>
       </c>
       <c r="AB314">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC314">
         <v>3.34</v>
@@ -51561,7 +51561,7 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK314">
         <v>1.5</v>
@@ -51654,34 +51654,34 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O315">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P315">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="Q315">
+        <v>2.3</v>
+      </c>
+      <c r="R315">
         <v>2.4</v>
-      </c>
-      <c r="R315">
-        <v>2.38</v>
       </c>
       <c r="S315">
         <v>1.21</v>
       </c>
       <c r="T315">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U315">
         <v>2.1</v>
       </c>
       <c r="V315">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W315">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X315">
         <v>1.03</v>
@@ -51690,25 +51690,25 @@
         <v>1.12</v>
       </c>
       <c r="Z315">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA315">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB315">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AC315">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD315">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE315">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF315">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG315">
         <v>2.45</v>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK315">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51820,13 +51820,13 @@
         <v>1.5</v>
       </c>
       <c r="O316">
-        <v>4.5</v>
+        <v>5.17</v>
       </c>
       <c r="P316">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q316">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="R316">
         <v>2.7</v>
@@ -51853,13 +51853,13 @@
         <v>1.11</v>
       </c>
       <c r="Z316">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AA316">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB316">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AC316">
         <v>2</v>
@@ -51871,10 +51871,10 @@
         <v>1.3</v>
       </c>
       <c r="AF316">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG316">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51980,10 +51980,10 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O317">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="P317">
         <v>3</v>
@@ -51998,7 +51998,7 @@
         <v>1.22</v>
       </c>
       <c r="T317">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U317">
         <v>2.1</v>
@@ -52007,7 +52007,7 @@
         <v>1.65</v>
       </c>
       <c r="W317">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X317">
         <v>1.02</v>
@@ -52016,28 +52016,28 @@
         <v>1.15</v>
       </c>
       <c r="Z317">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA317">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB317">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AC317">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD317">
         <v>1.67</v>
       </c>
       <c r="AE317">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF317">
         <v>1.44</v>
       </c>
       <c r="AG317">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
         <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q28">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="U28">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
         <v>1.05</v>
@@ -4906,31 +4906,31 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AA28">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AB28">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC28">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD28">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE28">
         <v>1.05</v>
       </c>
       <c r="AF28">
+        <v>1.75</v>
+      </c>
+      <c r="AG28">
         <v>1.95</v>
-      </c>
-      <c r="AG28">
-        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="O29">
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="Q29">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="R29">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="U29">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
         <v>1.05</v>
@@ -5069,31 +5069,31 @@
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Z29">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AA29">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AB29">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AC29">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
       </c>
       <c r="AF29">
+        <v>1.95</v>
+      </c>
+      <c r="AG29">
         <v>1.75</v>
-      </c>
-      <c r="AG29">
-        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="P53">
-        <v>2.13</v>
+        <v>5.25</v>
       </c>
       <c r="Q53">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="R53">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T53">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="U53">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="V53">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="W53">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
         <v>1.03</v>
       </c>
-      <c r="Y53">
-        <v>1.18</v>
-      </c>
       <c r="Z53">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA53">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AB53">
-        <v>2.2</v>
+        <v>3.54</v>
       </c>
       <c r="AC53">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD53">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="AE53">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AF53">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG53">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O54">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>5.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q54">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="R54">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="S54">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
+        <v>3.35</v>
+      </c>
+      <c r="U54">
+        <v>2.25</v>
+      </c>
+      <c r="V54">
+        <v>1.57</v>
+      </c>
+      <c r="W54">
+        <v>1.1</v>
+      </c>
+      <c r="X54">
+        <v>1.03</v>
+      </c>
+      <c r="Y54">
+        <v>1.18</v>
+      </c>
+      <c r="Z54">
         <v>4.5</v>
       </c>
-      <c r="U54">
-        <v>1.77</v>
-      </c>
-      <c r="V54">
-        <v>1.91</v>
-      </c>
-      <c r="W54">
-        <v>1.24</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.03</v>
-      </c>
-      <c r="Z54">
-        <v>8.5</v>
-      </c>
       <c r="AA54">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AB54">
-        <v>3.54</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AD54">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="AE54">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG54">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,80 +17098,80 @@
         </is>
       </c>
       <c r="N103">
-        <v>4.22</v>
+        <v>3.44</v>
       </c>
       <c r="O103">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P103">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="Q103">
-        <v>4.78</v>
+        <v>3.9</v>
       </c>
       <c r="R103">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S103">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="U103">
-        <v>2.66</v>
+        <v>3.01</v>
       </c>
       <c r="V103">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W103">
+        <v>1.04</v>
+      </c>
+      <c r="X103">
         <v>1.06</v>
       </c>
-      <c r="X103">
-        <v>1.05</v>
-      </c>
       <c r="Y103">
+        <v>1.3</v>
+      </c>
+      <c r="Z103">
+        <v>3.08</v>
+      </c>
+      <c r="AA103">
+        <v>2</v>
+      </c>
+      <c r="AB103">
+        <v>1.79</v>
+      </c>
+      <c r="AC103">
+        <v>3.3</v>
+      </c>
+      <c r="AD103">
+        <v>1.29</v>
+      </c>
+      <c r="AE103">
+        <v>1.06</v>
+      </c>
+      <c r="AF103">
+        <v>1.8</v>
+      </c>
+      <c r="AG103">
+        <v>1.92</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103">
         <v>1.25</v>
       </c>
-      <c r="Z103">
-        <v>3.95</v>
-      </c>
-      <c r="AA103">
-        <v>1.78</v>
-      </c>
-      <c r="AB103">
-        <v>2.06</v>
-      </c>
-      <c r="AC103">
-        <v>2.8</v>
-      </c>
-      <c r="AD103">
-        <v>1.34</v>
-      </c>
-      <c r="AE103">
-        <v>1.14</v>
-      </c>
-      <c r="AF103">
-        <v>1.67</v>
-      </c>
-      <c r="AG103">
-        <v>2.1</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>1.22</v>
-      </c>
       <c r="AK103">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.44</v>
+        <v>2.28</v>
       </c>
       <c r="O104">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="Q104">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="R104">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T104">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U104">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="V104">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W104">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y104">
+        <v>1.27</v>
+      </c>
+      <c r="Z104">
+        <v>3.77</v>
+      </c>
+      <c r="AA104">
+        <v>1.91</v>
+      </c>
+      <c r="AB104">
+        <v>1.94</v>
+      </c>
+      <c r="AC104">
+        <v>2.99</v>
+      </c>
+      <c r="AD104">
         <v>1.3</v>
       </c>
-      <c r="Z104">
-        <v>3.08</v>
-      </c>
-      <c r="AA104">
-        <v>2</v>
-      </c>
-      <c r="AB104">
-        <v>1.79</v>
-      </c>
-      <c r="AC104">
-        <v>3.3</v>
-      </c>
-      <c r="AD104">
-        <v>1.29</v>
-      </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF104">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG104">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="O105">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P105">
-        <v>4</v>
+        <v>8.35</v>
       </c>
       <c r="Q105">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="R105">
+        <v>2.45</v>
+      </c>
+      <c r="S105">
+        <v>1.3</v>
+      </c>
+      <c r="T105">
+        <v>3.2</v>
+      </c>
+      <c r="U105">
+        <v>2.34</v>
+      </c>
+      <c r="V105">
+        <v>1.49</v>
+      </c>
+      <c r="W105">
+        <v>1.12</v>
+      </c>
+      <c r="X105">
+        <v>1.03</v>
+      </c>
+      <c r="Y105">
+        <v>1.2</v>
+      </c>
+      <c r="Z105">
+        <v>4.2</v>
+      </c>
+      <c r="AA105">
+        <v>1.66</v>
+      </c>
+      <c r="AB105">
         <v>2.21</v>
       </c>
-      <c r="S105">
-        <v>1.35</v>
-      </c>
-      <c r="T105">
-        <v>3</v>
-      </c>
-      <c r="U105">
-        <v>2.77</v>
-      </c>
-      <c r="V105">
-        <v>1.39</v>
-      </c>
-      <c r="W105">
-        <v>1.06</v>
-      </c>
-      <c r="X105">
-        <v>1</v>
-      </c>
-      <c r="Y105">
-        <v>1.26</v>
-      </c>
-      <c r="Z105">
-        <v>3.53</v>
-      </c>
-      <c r="AA105">
-        <v>1.86</v>
-      </c>
-      <c r="AB105">
-        <v>1.89</v>
-      </c>
       <c r="AC105">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="AD105">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE105">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG105">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK105">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
+        <v>4.22</v>
+      </c>
+      <c r="O106">
+        <v>3.6</v>
+      </c>
+      <c r="P106">
+        <v>1.81</v>
+      </c>
+      <c r="Q106">
+        <v>4.78</v>
+      </c>
+      <c r="R106">
+        <v>2.25</v>
+      </c>
+      <c r="S106">
+        <v>1.35</v>
+      </c>
+      <c r="T106">
+        <v>2.86</v>
+      </c>
+      <c r="U106">
+        <v>2.66</v>
+      </c>
+      <c r="V106">
+        <v>1.44</v>
+      </c>
+      <c r="W106">
+        <v>1.06</v>
+      </c>
+      <c r="X106">
+        <v>1.05</v>
+      </c>
+      <c r="Y106">
+        <v>1.25</v>
+      </c>
+      <c r="Z106">
+        <v>3.95</v>
+      </c>
+      <c r="AA106">
+        <v>1.78</v>
+      </c>
+      <c r="AB106">
+        <v>2.06</v>
+      </c>
+      <c r="AC106">
+        <v>2.8</v>
+      </c>
+      <c r="AD106">
         <v>1.34</v>
       </c>
-      <c r="O106">
-        <v>5</v>
-      </c>
-      <c r="P106">
-        <v>8.35</v>
-      </c>
-      <c r="Q106">
-        <v>1.8</v>
-      </c>
-      <c r="R106">
-        <v>2.45</v>
-      </c>
-      <c r="S106">
-        <v>1.3</v>
-      </c>
-      <c r="T106">
-        <v>3.2</v>
-      </c>
-      <c r="U106">
-        <v>2.34</v>
-      </c>
-      <c r="V106">
-        <v>1.49</v>
-      </c>
-      <c r="W106">
-        <v>1.12</v>
-      </c>
-      <c r="X106">
-        <v>1.03</v>
-      </c>
-      <c r="Y106">
-        <v>1.2</v>
-      </c>
-      <c r="Z106">
-        <v>4.2</v>
-      </c>
-      <c r="AA106">
-        <v>1.66</v>
-      </c>
-      <c r="AB106">
-        <v>2.21</v>
-      </c>
-      <c r="AC106">
-        <v>2.54</v>
-      </c>
-      <c r="AD106">
-        <v>1.41</v>
-      </c>
       <c r="AE106">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>3.1</v>
+        <v>1.16</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="O107">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P107">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="Q107">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="R107">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S107">
         <v>1.35</v>
@@ -17771,10 +17771,10 @@
         <v>3</v>
       </c>
       <c r="U107">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V107">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W107">
         <v>1.06</v>
@@ -17783,31 +17783,31 @@
         <v>1</v>
       </c>
       <c r="Y107">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z107">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="AA107">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AB107">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AC107">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AD107">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE107">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -24116,7 +24116,7 @@
         <v>5.25</v>
       </c>
       <c r="Q146">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R146">
         <v>2.07</v>
@@ -24128,10 +24128,10 @@
         <v>2.6</v>
       </c>
       <c r="U146">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V146">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W146">
         <v>1.04</v>
@@ -24140,16 +24140,16 @@
         <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z146">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AA146">
         <v>2.31</v>
       </c>
       <c r="AB146">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC146">
         <v>3.94</v>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK146">
         <v>2.05</v>
@@ -35191,7 +35191,7 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O214">
         <v>3.25</v>
@@ -35200,22 +35200,22 @@
         <v>3.25</v>
       </c>
       <c r="Q214">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="R214">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S214">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T214">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="U214">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="V214">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W214">
         <v>1.03</v>
@@ -35239,10 +35239,10 @@
         <v>4.2</v>
       </c>
       <c r="AD214">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE214">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF214">
         <v>1.91</v>
@@ -35264,7 +35264,7 @@
         <v>1.33</v>
       </c>
       <c r="AK214">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="O236">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P236">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="Q236">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="R236">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S236">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="T236">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="U236">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="V236">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W236">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X236">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Y236">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z236">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AA236">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB236">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC236">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD236">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE236">
         <v>1.02</v>
       </c>
       <c r="AF236">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AG236">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK236">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O237">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P237">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="Q237">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R237">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="S237">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="T237">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="U237">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="V237">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W237">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X237">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Y237">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Z237">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AA237">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB237">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC237">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD237">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE237">
         <v>1.02</v>
       </c>
       <c r="AF237">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="AG237">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK237">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -44328,7 +44328,7 @@
         <v>1.44</v>
       </c>
       <c r="Q270">
-        <v>6.79</v>
+        <v>6.88</v>
       </c>
       <c r="R270">
         <v>2.36</v>
@@ -44352,7 +44352,7 @@
         <v>1</v>
       </c>
       <c r="Y270">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z270">
         <v>4.35</v>
@@ -44361,22 +44361,22 @@
         <v>1.75</v>
       </c>
       <c r="AB270">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC270">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD270">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE270">
         <v>1.12</v>
       </c>
       <c r="AF270">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG270">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O272">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P272">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="Q272">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="R272">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="S272">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="T272">
-        <v>2.83</v>
+        <v>2.26</v>
       </c>
       <c r="U272">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="V272">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W272">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X272">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y272">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="Z272">
-        <v>3.42</v>
+        <v>2.38</v>
       </c>
       <c r="AA272">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="AB272">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AC272">
-        <v>3.08</v>
+        <v>5.2</v>
       </c>
       <c r="AD272">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AE272">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF272">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="AG272">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK272">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,80 +44808,80 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O273">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P273">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="Q273">
+        <v>2.9</v>
+      </c>
+      <c r="R273">
+        <v>2.07</v>
+      </c>
+      <c r="S273">
+        <v>1.34</v>
+      </c>
+      <c r="T273">
+        <v>2.83</v>
+      </c>
+      <c r="U273">
         <v>2.71</v>
       </c>
-      <c r="R273">
+      <c r="V273">
+        <v>1.37</v>
+      </c>
+      <c r="W273">
+        <v>1.07</v>
+      </c>
+      <c r="X273">
+        <v>1</v>
+      </c>
+      <c r="Y273">
+        <v>1.23</v>
+      </c>
+      <c r="Z273">
+        <v>3.42</v>
+      </c>
+      <c r="AA273">
         <v>1.83</v>
       </c>
-      <c r="S273">
-        <v>1.55</v>
-      </c>
-      <c r="T273">
-        <v>2.26</v>
-      </c>
-      <c r="U273">
-        <v>3.7</v>
-      </c>
-      <c r="V273">
-        <v>1.2</v>
-      </c>
-      <c r="W273">
-        <v>1.01</v>
-      </c>
-      <c r="X273">
-        <v>1.05</v>
-      </c>
-      <c r="Y273">
-        <v>1.5</v>
-      </c>
-      <c r="Z273">
-        <v>2.38</v>
-      </c>
-      <c r="AA273">
-        <v>2.52</v>
-      </c>
       <c r="AB273">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AC273">
-        <v>5.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD273">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AE273">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF273">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="AG273">
+        <v>2.07</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ273">
+        <v>1.34</v>
+      </c>
+      <c r="AK273">
         <v>1.57</v>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ273">
-        <v>1.29</v>
-      </c>
-      <c r="AK273">
-        <v>1.67</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45306,7 +45306,7 @@
         <v>3.9</v>
       </c>
       <c r="Q276">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="R276">
         <v>2.05</v>
@@ -45330,10 +45330,10 @@
         <v>1.07</v>
       </c>
       <c r="Y276">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z276">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA276">
         <v>2.04</v>
@@ -45342,7 +45342,7 @@
         <v>1.75</v>
       </c>
       <c r="AC276">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD276">
         <v>1.25</v>
@@ -45351,10 +45351,10 @@
         <v>1.09</v>
       </c>
       <c r="AF276">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG276">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O282">
         <v>3</v>
       </c>
       <c r="P282">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q282">
         <v>3</v>
@@ -46305,31 +46305,31 @@
         <v>1.02</v>
       </c>
       <c r="X282">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y282">
         <v>1.52</v>
       </c>
       <c r="Z282">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AA282">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AB282">
         <v>1.48</v>
       </c>
       <c r="AC282">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD282">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE282">
         <v>1.04</v>
       </c>
       <c r="AF282">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG282">
         <v>1.65</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O283">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P283">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="Q283">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R283">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="S283">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T283">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U283">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="V283">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W283">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X283">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y283">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="Z283">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="AA283">
-        <v>1.77</v>
+        <v>2.33</v>
       </c>
       <c r="AB283">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AC283">
-        <v>2.88</v>
+        <v>4.25</v>
       </c>
       <c r="AD283">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AE283">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AF283">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AG283">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK283">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O284">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P284">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q284">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R284">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="S284">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T284">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U284">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="V284">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W284">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X284">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y284">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="Z284">
-        <v>2.52</v>
+        <v>3.58</v>
       </c>
       <c r="AA284">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="AB284">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AC284">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD284">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AE284">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AF284">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="AG284">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK284">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AL284">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P73">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="Q73">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="R73">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="S73">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U73">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="V73">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W73">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA73">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AB73">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC73">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AD73">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE73">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF73">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG73">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK73">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="O74">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P74">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="Q74">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="R74">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U74">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="V74">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z74">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA74">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AB74">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC74">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AD74">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK74">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S84">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
+        <v>4.22</v>
+      </c>
+      <c r="O105">
+        <v>3.6</v>
+      </c>
+      <c r="P105">
+        <v>1.81</v>
+      </c>
+      <c r="Q105">
+        <v>4.78</v>
+      </c>
+      <c r="R105">
+        <v>2.25</v>
+      </c>
+      <c r="S105">
+        <v>1.35</v>
+      </c>
+      <c r="T105">
+        <v>2.86</v>
+      </c>
+      <c r="U105">
+        <v>2.66</v>
+      </c>
+      <c r="V105">
+        <v>1.44</v>
+      </c>
+      <c r="W105">
+        <v>1.06</v>
+      </c>
+      <c r="X105">
+        <v>1.05</v>
+      </c>
+      <c r="Y105">
+        <v>1.25</v>
+      </c>
+      <c r="Z105">
+        <v>3.95</v>
+      </c>
+      <c r="AA105">
+        <v>1.78</v>
+      </c>
+      <c r="AB105">
+        <v>2.06</v>
+      </c>
+      <c r="AC105">
+        <v>2.8</v>
+      </c>
+      <c r="AD105">
         <v>1.34</v>
       </c>
-      <c r="O105">
-        <v>5</v>
-      </c>
-      <c r="P105">
-        <v>8.35</v>
-      </c>
-      <c r="Q105">
-        <v>1.8</v>
-      </c>
-      <c r="R105">
-        <v>2.45</v>
-      </c>
-      <c r="S105">
-        <v>1.3</v>
-      </c>
-      <c r="T105">
-        <v>3.2</v>
-      </c>
-      <c r="U105">
-        <v>2.34</v>
-      </c>
-      <c r="V105">
-        <v>1.49</v>
-      </c>
-      <c r="W105">
-        <v>1.12</v>
-      </c>
-      <c r="X105">
-        <v>1.03</v>
-      </c>
-      <c r="Y105">
-        <v>1.2</v>
-      </c>
-      <c r="Z105">
-        <v>4.2</v>
-      </c>
-      <c r="AA105">
-        <v>1.66</v>
-      </c>
-      <c r="AB105">
-        <v>2.21</v>
-      </c>
-      <c r="AC105">
-        <v>2.54</v>
-      </c>
-      <c r="AD105">
-        <v>1.41</v>
-      </c>
       <c r="AE105">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF105">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>3.1</v>
+        <v>1.16</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>4.22</v>
+        <v>1.9</v>
       </c>
       <c r="O106">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P106">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="Q106">
-        <v>4.78</v>
+        <v>2.42</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S106">
         <v>1.35</v>
       </c>
       <c r="T106">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U106">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V106">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W106">
         <v>1.06</v>
       </c>
       <c r="X106">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y106">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z106">
-        <v>3.95</v>
+        <v>3.53</v>
       </c>
       <c r="AA106">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB106">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AC106">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD106">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE106">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG106">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.16</v>
+        <v>1.88</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="O107">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>8.35</v>
       </c>
       <c r="Q107">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="R107">
+        <v>2.45</v>
+      </c>
+      <c r="S107">
+        <v>1.3</v>
+      </c>
+      <c r="T107">
+        <v>3.2</v>
+      </c>
+      <c r="U107">
+        <v>2.34</v>
+      </c>
+      <c r="V107">
+        <v>1.49</v>
+      </c>
+      <c r="W107">
+        <v>1.12</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.2</v>
+      </c>
+      <c r="Z107">
+        <v>4.2</v>
+      </c>
+      <c r="AA107">
+        <v>1.66</v>
+      </c>
+      <c r="AB107">
         <v>2.21</v>
       </c>
-      <c r="S107">
-        <v>1.35</v>
-      </c>
-      <c r="T107">
-        <v>3</v>
-      </c>
-      <c r="U107">
-        <v>2.77</v>
-      </c>
-      <c r="V107">
-        <v>1.39</v>
-      </c>
-      <c r="W107">
-        <v>1.06</v>
-      </c>
-      <c r="X107">
-        <v>1</v>
-      </c>
-      <c r="Y107">
-        <v>1.26</v>
-      </c>
-      <c r="Z107">
-        <v>3.53</v>
-      </c>
-      <c r="AA107">
-        <v>1.86</v>
-      </c>
-      <c r="AB107">
-        <v>1.89</v>
-      </c>
       <c r="AC107">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="AD107">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF107">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK107">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -29824,7 +29824,7 @@
         <v>2.12</v>
       </c>
       <c r="R181">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S181">
         <v>1.38</v>
@@ -29833,28 +29833,28 @@
         <v>2.67</v>
       </c>
       <c r="U181">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V181">
         <v>1.33</v>
       </c>
       <c r="W181">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z181">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA181">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB181">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC181">
         <v>3.42</v>
@@ -29866,10 +29866,10 @@
         <v>1.05</v>
       </c>
       <c r="AF181">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG181">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK181">
         <v>2.21</v>
@@ -29984,16 +29984,16 @@
         <v>2.9</v>
       </c>
       <c r="Q182">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R182">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="S182">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T182">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="U182">
         <v>3.2</v>
@@ -30014,7 +30014,7 @@
         <v>2.66</v>
       </c>
       <c r="AA182">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AB182">
         <v>1.57</v>
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O266">
         <v>2.9</v>
@@ -43706,10 +43706,10 @@
         <v>2.62</v>
       </c>
       <c r="AA266">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB266">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC266">
         <v>3.98</v>
@@ -43833,7 +43833,7 @@
         <v>1.77</v>
       </c>
       <c r="O267">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P267">
         <v>4</v>
@@ -43845,10 +43845,10 @@
         <v>2</v>
       </c>
       <c r="S267">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T267">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U267">
         <v>2.97</v>
@@ -43857,7 +43857,7 @@
         <v>1.31</v>
       </c>
       <c r="W267">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X267">
         <v>1.02</v>
@@ -43869,7 +43869,7 @@
         <v>2.92</v>
       </c>
       <c r="AA267">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB267">
         <v>1.67</v>
@@ -43900,7 +43900,7 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK267">
         <v>2</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O273">
         <v>3.2</v>
       </c>
       <c r="P273">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q273">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R273">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S273">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T273">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="U273">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V273">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W273">
+        <v>1.08</v>
+      </c>
+      <c r="X273">
+        <v>1.01</v>
+      </c>
+      <c r="Y273">
+        <v>1.22</v>
+      </c>
+      <c r="Z273">
+        <v>3.5</v>
+      </c>
+      <c r="AA273">
+        <v>1.8</v>
+      </c>
+      <c r="AB273">
+        <v>1.89</v>
+      </c>
+      <c r="AC273">
+        <v>2.97</v>
+      </c>
+      <c r="AD273">
+        <v>1.3</v>
+      </c>
+      <c r="AE273">
         <v>1.07</v>
       </c>
-      <c r="X273">
-        <v>1</v>
-      </c>
-      <c r="Y273">
-        <v>1.23</v>
-      </c>
-      <c r="Z273">
-        <v>3.42</v>
-      </c>
-      <c r="AA273">
-        <v>1.83</v>
-      </c>
-      <c r="AB273">
-        <v>1.85</v>
-      </c>
-      <c r="AC273">
-        <v>3.08</v>
-      </c>
-      <c r="AD273">
-        <v>1.28</v>
-      </c>
-      <c r="AE273">
-        <v>1.06</v>
-      </c>
       <c r="AF273">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG273">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AK273">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O274">
         <v>3.2</v>
       </c>
       <c r="P274">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q274">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R274">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S274">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T274">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="U274">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="V274">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W274">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X274">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y274">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z274">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA274">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB274">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC274">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD274">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE274">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF274">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG274">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AK274">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45140,7 +45140,7 @@
         <v>4.3</v>
       </c>
       <c r="P275">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="O291">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="P291">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -48732,7 +48732,7 @@
         <v>2.62</v>
       </c>
       <c r="R297">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S297">
         <v>1.14</v>
@@ -48741,7 +48741,7 @@
         <v>4.8</v>
       </c>
       <c r="U297">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="V297">
         <v>1.7</v>
@@ -48753,10 +48753,10 @@
         <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z297">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA297">
         <v>1.4</v>
@@ -48765,19 +48765,19 @@
         <v>3</v>
       </c>
       <c r="AC297">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD297">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AE297">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF297">
         <v>1.36</v>
       </c>
       <c r="AG297">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK297">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48883,19 +48883,19 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="O298">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P298">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="Q298">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R298">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S298">
         <v>1.29</v>
@@ -48910,7 +48910,7 @@
         <v>1.55</v>
       </c>
       <c r="W298">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X298">
         <v>1.03</v>
@@ -48922,7 +48922,7 @@
         <v>5</v>
       </c>
       <c r="AA298">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB298">
         <v>2.25</v>
@@ -48931,7 +48931,7 @@
         <v>2.38</v>
       </c>
       <c r="AD298">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE298">
         <v>1.22</v>
@@ -48956,7 +48956,7 @@
         <v>1.25</v>
       </c>
       <c r="AK298">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49055,7 +49055,7 @@
         <v>7</v>
       </c>
       <c r="Q299">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R299">
         <v>2.88</v>
@@ -49070,7 +49070,7 @@
         <v>1.85</v>
       </c>
       <c r="V299">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W299">
         <v>1.22</v>
@@ -49079,13 +49079,13 @@
         <v>1.01</v>
       </c>
       <c r="Y299">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z299">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA299">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB299">
         <v>3.25</v>
@@ -49218,22 +49218,22 @@
         <v>2.1</v>
       </c>
       <c r="Q300">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R300">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S300">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T300">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U300">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V300">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W300">
         <v>1.2</v>
@@ -49254,10 +49254,10 @@
         <v>3</v>
       </c>
       <c r="AC300">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD300">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE300">
         <v>1.33</v>
@@ -49266,7 +49266,7 @@
         <v>1.36</v>
       </c>
       <c r="AG300">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK300">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O301">
-        <v>4.14</v>
+        <v>4.24</v>
       </c>
       <c r="P301">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q301">
         <v>2.38</v>
@@ -49393,16 +49393,16 @@
         <v>3.28</v>
       </c>
       <c r="U301">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V301">
         <v>1.57</v>
       </c>
       <c r="W301">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X301">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y301">
         <v>1.18</v>
@@ -49417,10 +49417,10 @@
         <v>2.25</v>
       </c>
       <c r="AC301">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD301">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE301">
         <v>1.15</v>
@@ -49538,10 +49538,10 @@
         <v>1.8</v>
       </c>
       <c r="O302">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P302">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q302">
         <v>2.2</v>
@@ -49556,10 +49556,10 @@
         <v>4.33</v>
       </c>
       <c r="U302">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V302">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W302">
         <v>1.2</v>
@@ -49571,10 +49571,10 @@
         <v>1.11</v>
       </c>
       <c r="Z302">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AA302">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB302">
         <v>2.87</v>
@@ -49586,7 +49586,7 @@
         <v>1.75</v>
       </c>
       <c r="AE302">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF302">
         <v>1.4</v>
@@ -50196,7 +50196,7 @@
         <v>2.1</v>
       </c>
       <c r="Q306">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="R306">
         <v>2.3</v>
@@ -50208,13 +50208,13 @@
         <v>3.4</v>
       </c>
       <c r="U306">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V306">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W306">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X306">
         <v>1.04</v>
@@ -50223,28 +50223,28 @@
         <v>1.2</v>
       </c>
       <c r="Z306">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA306">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB306">
         <v>2.05</v>
       </c>
       <c r="AC306">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD306">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE306">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF306">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG306">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>1.62</v>
       </c>
       <c r="AK306">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50356,7 +50356,7 @@
         <v>3.6</v>
       </c>
       <c r="P307">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q307">
         <v>2.5</v>
@@ -50371,7 +50371,7 @@
         <v>3.5</v>
       </c>
       <c r="U307">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V307">
         <v>1.5</v>
@@ -50380,7 +50380,7 @@
         <v>1.11</v>
       </c>
       <c r="X307">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y307">
         <v>1.18</v>
@@ -50395,13 +50395,13 @@
         <v>2.1</v>
       </c>
       <c r="AC307">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AD307">
         <v>1.5</v>
       </c>
       <c r="AE307">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF307">
         <v>1.57</v>
@@ -50516,13 +50516,13 @@
         <v>1.7</v>
       </c>
       <c r="O308">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P308">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q308">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="R308">
         <v>2.3</v>
@@ -50534,22 +50534,22 @@
         <v>3.5</v>
       </c>
       <c r="U308">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="V308">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W308">
         <v>1.09</v>
       </c>
       <c r="X308">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y308">
         <v>1.18</v>
       </c>
       <c r="Z308">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA308">
         <v>1.61</v>
@@ -50558,7 +50558,7 @@
         <v>2.13</v>
       </c>
       <c r="AC308">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD308">
         <v>1.44</v>
@@ -50570,7 +50570,7 @@
         <v>1.6</v>
       </c>
       <c r="AG308">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK308">
         <v>2.05</v>
@@ -50691,16 +50691,16 @@
         <v>2.27</v>
       </c>
       <c r="S309">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T309">
         <v>3.6</v>
       </c>
       <c r="U309">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="V309">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W309">
         <v>1.11</v>
@@ -50709,31 +50709,31 @@
         <v>1.03</v>
       </c>
       <c r="Y309">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z309">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA309">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB309">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="AC309">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="AD309">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE309">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF309">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG309">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -51328,31 +51328,31 @@
         </is>
       </c>
       <c r="N313">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O313">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P313">
-        <v>5.25</v>
+        <v>6.01</v>
       </c>
       <c r="Q313">
         <v>1.87</v>
       </c>
       <c r="R313">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S313">
         <v>1.22</v>
       </c>
       <c r="T313">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="U313">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="V313">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W313">
         <v>1.15</v>
@@ -51364,25 +51364,25 @@
         <v>1.11</v>
       </c>
       <c r="Z313">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA313">
         <v>1.44</v>
       </c>
       <c r="AB313">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC313">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AD313">
         <v>1.75</v>
       </c>
       <c r="AE313">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF313">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG313">
         <v>2.25</v>
@@ -51401,7 +51401,7 @@
         <v>1.11</v>
       </c>
       <c r="AK313">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51657,22 +51657,22 @@
         <v>1.91</v>
       </c>
       <c r="O315">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P315">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q315">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R315">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S315">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T315">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U315">
         <v>2.1</v>
@@ -51681,34 +51681,34 @@
         <v>1.66</v>
       </c>
       <c r="W315">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X315">
         <v>1.03</v>
       </c>
       <c r="Y315">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z315">
         <v>4.8</v>
       </c>
       <c r="AA315">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB315">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC315">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AD315">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE315">
         <v>1.2</v>
       </c>
       <c r="AF315">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG315">
         <v>2.45</v>
@@ -51727,7 +51727,7 @@
         <v>1.22</v>
       </c>
       <c r="AK315">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51826,7 +51826,7 @@
         <v>4.6</v>
       </c>
       <c r="Q316">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R316">
         <v>2.7</v>
@@ -51841,7 +51841,7 @@
         <v>1.95</v>
       </c>
       <c r="V316">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W316">
         <v>1.2</v>
@@ -51850,31 +51850,31 @@
         <v>1.01</v>
       </c>
       <c r="Y316">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z316">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="AA316">
         <v>1.36</v>
       </c>
       <c r="AB316">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AC316">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD316">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE316">
         <v>1.3</v>
       </c>
       <c r="AF316">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG316">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK316">
         <v>2.45</v>
@@ -51986,25 +51986,25 @@
         <v>4.22</v>
       </c>
       <c r="P317">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="Q317">
         <v>2.4</v>
       </c>
       <c r="R317">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S317">
         <v>1.22</v>
       </c>
       <c r="T317">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U317">
         <v>2.1</v>
       </c>
       <c r="V317">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W317">
         <v>1.17</v>
@@ -52016,28 +52016,28 @@
         <v>1.15</v>
       </c>
       <c r="Z317">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA317">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB317">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC317">
         <v>2.16</v>
       </c>
       <c r="AD317">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AE317">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF317">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG317">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
         <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q28">
-        <v>3.44</v>
+        <v>2.98</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="U28">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AA28">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="AB28">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC28">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD28">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.36</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="O29">
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="Q29">
-        <v>2.98</v>
+        <v>3.44</v>
       </c>
       <c r="R29">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="U29">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Z29">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AA29">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AB29">
+        <v>1.55</v>
+      </c>
+      <c r="AC29">
+        <v>4.5</v>
+      </c>
+      <c r="AD29">
+        <v>1.13</v>
+      </c>
+      <c r="AE29">
+        <v>1.02</v>
+      </c>
+      <c r="AF29">
+        <v>1.95</v>
+      </c>
+      <c r="AG29">
         <v>1.73</v>
-      </c>
-      <c r="AC29">
-        <v>3.72</v>
-      </c>
-      <c r="AD29">
-        <v>1.23</v>
-      </c>
-      <c r="AE29">
-        <v>1.05</v>
-      </c>
-      <c r="AF29">
-        <v>1.77</v>
-      </c>
-      <c r="AG29">
-        <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>5.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q53">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="R53">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="S53">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="U53">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="V53">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="W53">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="Z53">
-        <v>8.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA53">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC53">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD53">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AE53">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG53">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="P54">
-        <v>2.13</v>
+        <v>5.25</v>
       </c>
       <c r="Q54">
-        <v>2.95</v>
+        <v>1.85</v>
       </c>
       <c r="R54">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="S54">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T54">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="U54">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="V54">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Z54">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="AA54">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AB54">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC54">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AD54">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AF54">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG54">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK54">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="O106">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P106">
-        <v>8</v>
+        <v>3.65</v>
       </c>
       <c r="Q106">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R106">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T106">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U106">
-        <v>2.34</v>
+        <v>2.87</v>
       </c>
       <c r="V106">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z106">
-        <v>4.24</v>
+        <v>3.24</v>
       </c>
       <c r="AA106">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AB106">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AC106">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="AD106">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE106">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AG106">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="O107">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P107">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="Q107">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="R107">
+        <v>2.36</v>
+      </c>
+      <c r="S107">
+        <v>1.3</v>
+      </c>
+      <c r="T107">
+        <v>3.4</v>
+      </c>
+      <c r="U107">
+        <v>2.34</v>
+      </c>
+      <c r="V107">
+        <v>1.5</v>
+      </c>
+      <c r="W107">
+        <v>1.1</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.2</v>
+      </c>
+      <c r="Z107">
+        <v>4.24</v>
+      </c>
+      <c r="AA107">
+        <v>1.68</v>
+      </c>
+      <c r="AB107">
         <v>2.21</v>
       </c>
-      <c r="S107">
-        <v>1.35</v>
-      </c>
-      <c r="T107">
-        <v>2.7</v>
-      </c>
-      <c r="U107">
-        <v>2.87</v>
-      </c>
-      <c r="V107">
-        <v>1.4</v>
-      </c>
-      <c r="W107">
-        <v>1.06</v>
-      </c>
-      <c r="X107">
-        <v>1.05</v>
-      </c>
-      <c r="Y107">
-        <v>1.28</v>
-      </c>
-      <c r="Z107">
-        <v>3.24</v>
-      </c>
-      <c r="AA107">
-        <v>1.9</v>
-      </c>
-      <c r="AB107">
-        <v>1.85</v>
-      </c>
       <c r="AC107">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF107">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK107">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G111">
@@ -18398,84 +18398,84 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N111">
+        <v>2.02</v>
+      </c>
+      <c r="O111">
+        <v>3.45</v>
+      </c>
+      <c r="P111">
+        <v>3.25</v>
+      </c>
+      <c r="Q111">
+        <v>2.63</v>
+      </c>
+      <c r="R111">
+        <v>2.14</v>
+      </c>
+      <c r="S111">
+        <v>1.33</v>
+      </c>
+      <c r="T111">
+        <v>3.2</v>
+      </c>
+      <c r="U111">
+        <v>2.65</v>
+      </c>
+      <c r="V111">
+        <v>1.42</v>
+      </c>
+      <c r="W111">
+        <v>1.08</v>
+      </c>
+      <c r="X111">
+        <v>1.05</v>
+      </c>
+      <c r="Y111">
+        <v>1.25</v>
+      </c>
+      <c r="Z111">
+        <v>3.6</v>
+      </c>
+      <c r="AA111">
+        <v>1.85</v>
+      </c>
+      <c r="AB111">
+        <v>1.9</v>
+      </c>
+      <c r="AC111">
+        <v>3.1</v>
+      </c>
+      <c r="AD111">
+        <v>1.33</v>
+      </c>
+      <c r="AE111">
+        <v>1.1</v>
+      </c>
+      <c r="AF111">
+        <v>1.65</v>
+      </c>
+      <c r="AG111">
+        <v>2.06</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
         <v>1.35</v>
       </c>
-      <c r="O111">
-        <v>5.25</v>
-      </c>
-      <c r="P111">
-        <v>8</v>
-      </c>
-      <c r="Q111">
-        <v>1.75</v>
-      </c>
-      <c r="R111">
-        <v>2.6</v>
-      </c>
-      <c r="S111">
-        <v>1.25</v>
-      </c>
-      <c r="T111">
-        <v>3.4</v>
-      </c>
-      <c r="U111">
-        <v>2.3</v>
-      </c>
-      <c r="V111">
-        <v>1.55</v>
-      </c>
-      <c r="W111">
-        <v>1.15</v>
-      </c>
-      <c r="X111">
-        <v>1.03</v>
-      </c>
-      <c r="Y111">
-        <v>1.14</v>
-      </c>
-      <c r="Z111">
-        <v>5</v>
-      </c>
-      <c r="AA111">
-        <v>1.54</v>
-      </c>
-      <c r="AB111">
-        <v>2.26</v>
-      </c>
-      <c r="AC111">
-        <v>2.29</v>
-      </c>
-      <c r="AD111">
-        <v>1.57</v>
-      </c>
-      <c r="AE111">
-        <v>1.15</v>
-      </c>
-      <c r="AF111">
-        <v>1.83</v>
-      </c>
-      <c r="AG111">
-        <v>1.95</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.16</v>
-      </c>
       <c r="AK111">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G113">
@@ -18724,68 +18724,68 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N113">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="O113">
-        <v>3.45</v>
+        <v>5.25</v>
       </c>
       <c r="P113">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="Q113">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="R113">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="S113">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T113">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U113">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="V113">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W113">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z113">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="AA113">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AB113">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AC113">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="AD113">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF113">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG113">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AK113">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O236">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P236">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q236">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="R236">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="S236">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="T236">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U236">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="V236">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W236">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X236">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Y236">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="Z236">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AA236">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB236">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC236">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD236">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE236">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF236">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AG236">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>1.44</v>
       </c>
       <c r="AK236">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="O237">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P237">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q237">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R237">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S237">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="T237">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U237">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="V237">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W237">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X237">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Y237">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z237">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AA237">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB237">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC237">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD237">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE237">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF237">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AG237">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>1.44</v>
       </c>
       <c r="AK237">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL237">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -2265,58 +2265,58 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O12">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Q12">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="U12">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AB12">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
         <v>2.33</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="P32">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Q32">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AC32">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.94</v>
       </c>
       <c r="AK32">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="O33">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q33">
-        <v>5.1</v>
+        <v>4.65</v>
       </c>
       <c r="R33">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="V33">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O65">
         <v>3.08</v>
@@ -10913,7 +10913,7 @@
         <v>2.6</v>
       </c>
       <c r="Q65">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="R65">
         <v>2.13</v>
@@ -10925,43 +10925,43 @@
         <v>2.79</v>
       </c>
       <c r="U65">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="V65">
         <v>1.34</v>
       </c>
       <c r="W65">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z65">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA65">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB65">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC65">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE65">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG65">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK65">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G112">
@@ -18561,84 +18561,84 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N112">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="O112">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P112">
-        <v>5.02</v>
+        <v>8</v>
       </c>
       <c r="Q112">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R112">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S112">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T112">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U112">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V112">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA112">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AB112">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AC112">
+        <v>2.29</v>
+      </c>
+      <c r="AD112">
+        <v>1.57</v>
+      </c>
+      <c r="AE112">
+        <v>1.15</v>
+      </c>
+      <c r="AF112">
+        <v>1.83</v>
+      </c>
+      <c r="AG112">
+        <v>1.95</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>1.16</v>
+      </c>
+      <c r="AK112">
         <v>2.8</v>
-      </c>
-      <c r="AD112">
-        <v>1.39</v>
-      </c>
-      <c r="AE112">
-        <v>1.11</v>
-      </c>
-      <c r="AF112">
-        <v>1.73</v>
-      </c>
-      <c r="AG112">
-        <v>1.98</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.25</v>
-      </c>
-      <c r="AK112">
-        <v>2.2</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G113">
@@ -18724,84 +18724,84 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N113">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="O113">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P113">
-        <v>8</v>
+        <v>5.02</v>
       </c>
       <c r="Q113">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R113">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S113">
+        <v>1.3</v>
+      </c>
+      <c r="T113">
+        <v>3.2</v>
+      </c>
+      <c r="U113">
+        <v>2.4</v>
+      </c>
+      <c r="V113">
+        <v>1.5</v>
+      </c>
+      <c r="W113">
+        <v>1.07</v>
+      </c>
+      <c r="X113">
+        <v>1.01</v>
+      </c>
+      <c r="Y113">
+        <v>1.2</v>
+      </c>
+      <c r="Z113">
+        <v>4.2</v>
+      </c>
+      <c r="AA113">
+        <v>1.73</v>
+      </c>
+      <c r="AB113">
+        <v>2.05</v>
+      </c>
+      <c r="AC113">
+        <v>2.8</v>
+      </c>
+      <c r="AD113">
+        <v>1.39</v>
+      </c>
+      <c r="AE113">
+        <v>1.11</v>
+      </c>
+      <c r="AF113">
+        <v>1.73</v>
+      </c>
+      <c r="AG113">
+        <v>1.98</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
         <v>1.25</v>
       </c>
-      <c r="T113">
-        <v>3.4</v>
-      </c>
-      <c r="U113">
-        <v>2.3</v>
-      </c>
-      <c r="V113">
-        <v>1.55</v>
-      </c>
-      <c r="W113">
-        <v>1.15</v>
-      </c>
-      <c r="X113">
-        <v>1.03</v>
-      </c>
-      <c r="Y113">
-        <v>1.14</v>
-      </c>
-      <c r="Z113">
-        <v>5</v>
-      </c>
-      <c r="AA113">
-        <v>1.54</v>
-      </c>
-      <c r="AB113">
-        <v>2.26</v>
-      </c>
-      <c r="AC113">
-        <v>2.29</v>
-      </c>
-      <c r="AD113">
-        <v>1.57</v>
-      </c>
-      <c r="AE113">
-        <v>1.15</v>
-      </c>
-      <c r="AF113">
-        <v>1.83</v>
-      </c>
-      <c r="AG113">
-        <v>1.95</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.16</v>
-      </c>
       <c r="AK113">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -29658,55 +29658,55 @@
         <v>3.19</v>
       </c>
       <c r="Q180">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="R180">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U180">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="V180">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W180">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y180">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z180">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AA180">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AB180">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC180">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD180">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF180">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG180">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29821,7 +29821,7 @@
         <v>5.04</v>
       </c>
       <c r="Q181">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R181">
         <v>2.2</v>
@@ -29848,19 +29848,19 @@
         <v>1.3</v>
       </c>
       <c r="Z181">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA181">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB181">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC181">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD181">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE181">
         <v>1.05</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK181">
         <v>2.21</v>
@@ -29987,13 +29987,13 @@
         <v>3.1</v>
       </c>
       <c r="R182">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="S182">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T182">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="U182">
         <v>3.2</v>
@@ -30002,7 +30002,7 @@
         <v>1.27</v>
       </c>
       <c r="W182">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X182">
         <v>1.04</v>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK182">
         <v>1.47</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="O236">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P236">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q236">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="R236">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S236">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="T236">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U236">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="V236">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W236">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X236">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Y236">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z236">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AA236">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB236">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC236">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD236">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE236">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF236">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AG236">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>1.44</v>
       </c>
       <c r="AK236">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O237">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P237">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q237">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="R237">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="S237">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="T237">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U237">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="V237">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W237">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X237">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Y237">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="Z237">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AA237">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB237">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC237">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD237">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE237">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF237">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AG237">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>1.44</v>
       </c>
       <c r="AK237">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -43993,7 +43993,7 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O268">
         <v>2.9</v>
@@ -44002,7 +44002,7 @@
         <v>2.9</v>
       </c>
       <c r="Q268">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="R268">
         <v>1.91</v>
@@ -44026,10 +44026,10 @@
         <v>1.05</v>
       </c>
       <c r="Y268">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z268">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA268">
         <v>2.38</v>
@@ -44038,7 +44038,7 @@
         <v>1.57</v>
       </c>
       <c r="AC268">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AD268">
         <v>1.17</v>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK268">
         <v>1.47</v>
@@ -44165,16 +44165,16 @@
         <v>4</v>
       </c>
       <c r="Q269">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R269">
         <v>2</v>
       </c>
       <c r="S269">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T269">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U269">
         <v>2.97</v>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK269">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AL269">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="O28">
         <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>2.98</v>
+        <v>3.44</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U28">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Z28">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC28">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AD28">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.36</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="O29">
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q29">
-        <v>3.44</v>
+        <v>2.98</v>
       </c>
       <c r="R29">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U29">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AA29">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC29">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD29">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE29">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG29">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="Q32">
-        <v>5.05</v>
+        <v>4.65</v>
       </c>
       <c r="R32">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U32">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="V32">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="Q33">
-        <v>4.65</v>
+        <v>5.05</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="V33">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AB33">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AC33">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.94</v>
       </c>
       <c r="AK33">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
+        <v>5.1</v>
+      </c>
+      <c r="O47">
+        <v>3.9</v>
+      </c>
+      <c r="P47">
+        <v>1.53</v>
+      </c>
+      <c r="Q47">
+        <v>5.39</v>
+      </c>
+      <c r="R47">
+        <v>2.3</v>
+      </c>
+      <c r="S47">
+        <v>1.29</v>
+      </c>
+      <c r="T47">
+        <v>3.3</v>
+      </c>
+      <c r="U47">
+        <v>2.3</v>
+      </c>
+      <c r="V47">
+        <v>1.5</v>
+      </c>
+      <c r="W47">
+        <v>1.07</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.16</v>
+      </c>
+      <c r="Z47">
+        <v>4.5</v>
+      </c>
+      <c r="AA47">
+        <v>1.65</v>
+      </c>
+      <c r="AB47">
+        <v>2.15</v>
+      </c>
+      <c r="AC47">
+        <v>2.63</v>
+      </c>
+      <c r="AD47">
+        <v>1.45</v>
+      </c>
+      <c r="AE47">
+        <v>1.12</v>
+      </c>
+      <c r="AF47">
         <v>1.52</v>
       </c>
-      <c r="O47">
-        <v>3.75</v>
-      </c>
-      <c r="P47">
-        <v>5.55</v>
-      </c>
-      <c r="Q47">
-        <v>2.03</v>
-      </c>
-      <c r="R47">
-        <v>2.2</v>
-      </c>
-      <c r="S47">
-        <v>1.33</v>
-      </c>
-      <c r="T47">
-        <v>2.88</v>
-      </c>
-      <c r="U47">
-        <v>2.67</v>
-      </c>
-      <c r="V47">
-        <v>1.38</v>
-      </c>
-      <c r="W47">
-        <v>1.04</v>
-      </c>
-      <c r="X47">
-        <v>1.05</v>
-      </c>
-      <c r="Y47">
-        <v>1.29</v>
-      </c>
-      <c r="Z47">
-        <v>3.5</v>
-      </c>
-      <c r="AA47">
-        <v>1.88</v>
-      </c>
-      <c r="AB47">
-        <v>1.92</v>
-      </c>
-      <c r="AC47">
-        <v>3.05</v>
-      </c>
-      <c r="AD47">
-        <v>1.28</v>
-      </c>
-      <c r="AE47">
-        <v>1.1</v>
-      </c>
-      <c r="AF47">
-        <v>1.87</v>
-      </c>
       <c r="AG47">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
-        <v>2.35</v>
+        <v>1.12</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>5.1</v>
+        <v>2.07</v>
       </c>
       <c r="O48">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="P48">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="Q48">
-        <v>5.39</v>
+        <v>2.62</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="U48">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="V48">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="W48">
+        <v>1.03</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.35</v>
+      </c>
+      <c r="Z48">
+        <v>3.03</v>
+      </c>
+      <c r="AA48">
+        <v>2.1</v>
+      </c>
+      <c r="AB48">
+        <v>1.7</v>
+      </c>
+      <c r="AC48">
+        <v>3.58</v>
+      </c>
+      <c r="AD48">
+        <v>1.21</v>
+      </c>
+      <c r="AE48">
         <v>1.07</v>
       </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.16</v>
-      </c>
-      <c r="Z48">
-        <v>4.5</v>
-      </c>
-      <c r="AA48">
+      <c r="AF48">
+        <v>1.83</v>
+      </c>
+      <c r="AG48">
+        <v>1.8</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.25</v>
+      </c>
+      <c r="AK48">
         <v>1.65</v>
-      </c>
-      <c r="AB48">
-        <v>2.15</v>
-      </c>
-      <c r="AC48">
-        <v>2.63</v>
-      </c>
-      <c r="AD48">
-        <v>1.45</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.52</v>
-      </c>
-      <c r="AG48">
-        <v>2.1</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.18</v>
-      </c>
-      <c r="AK48">
-        <v>1.12</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,25 +8305,25 @@
         <v>5</v>
       </c>
       <c r="Q49">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8341,10 +8341,10 @@
         <v>2.01</v>
       </c>
       <c r="AC49">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD49">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE49">
         <v>1.13</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O50">
         <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
         <v>2.56</v>
@@ -8474,10 +8474,10 @@
         <v>2.37</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U50">
         <v>2.45</v>
@@ -8486,7 +8486,7 @@
         <v>1.48</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8510,13 +8510,13 @@
         <v>1.37</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
         <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.44</v>
+        <v>1.38</v>
       </c>
       <c r="O53">
+        <v>4.25</v>
+      </c>
+      <c r="P53">
+        <v>4.6</v>
+      </c>
+      <c r="Q53">
+        <v>1.85</v>
+      </c>
+      <c r="R53">
+        <v>2.85</v>
+      </c>
+      <c r="S53">
+        <v>1.17</v>
+      </c>
+      <c r="T53">
+        <v>4.5</v>
+      </c>
+      <c r="U53">
+        <v>1.77</v>
+      </c>
+      <c r="V53">
+        <v>1.95</v>
+      </c>
+      <c r="W53">
+        <v>1.24</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.03</v>
+      </c>
+      <c r="Z53">
+        <v>8</v>
+      </c>
+      <c r="AA53">
+        <v>1.24</v>
+      </c>
+      <c r="AB53">
         <v>3.4</v>
       </c>
-      <c r="P53">
-        <v>2.5</v>
-      </c>
-      <c r="Q53">
-        <v>2.9</v>
-      </c>
-      <c r="R53">
-        <v>2.4</v>
-      </c>
-      <c r="S53">
-        <v>1.28</v>
-      </c>
-      <c r="T53">
-        <v>3.45</v>
-      </c>
-      <c r="U53">
-        <v>2.2</v>
-      </c>
-      <c r="V53">
-        <v>1.54</v>
-      </c>
-      <c r="W53">
-        <v>1.1</v>
-      </c>
-      <c r="X53">
-        <v>1.03</v>
-      </c>
-      <c r="Y53">
-        <v>1.15</v>
-      </c>
-      <c r="Z53">
-        <v>4.5</v>
-      </c>
-      <c r="AA53">
-        <v>1.57</v>
-      </c>
-      <c r="AB53">
-        <v>2.2</v>
-      </c>
       <c r="AC53">
-        <v>2.53</v>
+        <v>1.69</v>
       </c>
       <c r="AD53">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AE53">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AF53">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG53">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.38</v>
+        <v>2.44</v>
       </c>
       <c r="O54">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q54">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="R54">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="S54">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="T54">
+        <v>3.45</v>
+      </c>
+      <c r="U54">
+        <v>2.2</v>
+      </c>
+      <c r="V54">
+        <v>1.54</v>
+      </c>
+      <c r="W54">
+        <v>1.1</v>
+      </c>
+      <c r="X54">
+        <v>1.03</v>
+      </c>
+      <c r="Y54">
+        <v>1.15</v>
+      </c>
+      <c r="Z54">
         <v>4.5</v>
       </c>
-      <c r="U54">
-        <v>1.77</v>
-      </c>
-      <c r="V54">
-        <v>1.95</v>
-      </c>
-      <c r="W54">
-        <v>1.24</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.03</v>
-      </c>
-      <c r="Z54">
-        <v>8</v>
-      </c>
       <c r="AA54">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AB54">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
-        <v>1.69</v>
+        <v>2.53</v>
       </c>
       <c r="AD54">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AE54">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG54">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="O58">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q58">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R58">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S58">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T58">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="U58">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W58">
+        <v>1.1</v>
+      </c>
+      <c r="X58">
         <v>1.05</v>
       </c>
-      <c r="X58">
-        <v>1.03</v>
-      </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="AA58">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB58">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="AC58">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AD58">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,80 +9926,80 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="O59">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P59">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q59">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R59">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S59">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T59">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="U59">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W59">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
+        <v>1.3</v>
+      </c>
+      <c r="Z59">
+        <v>3.3</v>
+      </c>
+      <c r="AA59">
+        <v>1.98</v>
+      </c>
+      <c r="AB59">
+        <v>1.84</v>
+      </c>
+      <c r="AC59">
+        <v>3.5</v>
+      </c>
+      <c r="AD59">
+        <v>1.3</v>
+      </c>
+      <c r="AE59">
+        <v>1.06</v>
+      </c>
+      <c r="AF59">
+        <v>1.88</v>
+      </c>
+      <c r="AG59">
+        <v>1.77</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
         <v>1.22</v>
       </c>
-      <c r="Z59">
-        <v>3.77</v>
-      </c>
-      <c r="AA59">
-        <v>1.8</v>
-      </c>
-      <c r="AB59">
-        <v>2.04</v>
-      </c>
-      <c r="AC59">
-        <v>3</v>
-      </c>
-      <c r="AD59">
-        <v>1.33</v>
-      </c>
-      <c r="AE59">
-        <v>1.12</v>
-      </c>
-      <c r="AF59">
-        <v>1.75</v>
-      </c>
-      <c r="AG59">
-        <v>2.01</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59">
-        <v>1.25</v>
-      </c>
       <c r="AK59">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="O105">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="Q105">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="R105">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="S105">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U105">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="V105">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z105">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA105">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB105">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AC105">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="AD105">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AE105">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF105">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AG105">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,65 +17750,65 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="O107">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>7.7</v>
       </c>
       <c r="Q107">
+        <v>1.78</v>
+      </c>
+      <c r="R107">
         <v>2.5</v>
       </c>
-      <c r="R107">
-        <v>2.08</v>
-      </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="V107">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA107">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB107">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AC107">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="AD107">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF107">
+        <v>1.94</v>
+      </c>
+      <c r="AG107">
         <v>1.77</v>
       </c>
-      <c r="AG107">
-        <v>2</v>
-      </c>
       <c r="AH107" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK107">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18906,19 +18906,19 @@
         <v>1.98</v>
       </c>
       <c r="S114">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T114">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U114">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V114">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X114">
         <v>1.06</v>
@@ -18933,13 +18933,13 @@
         <v>2</v>
       </c>
       <c r="AB114">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC114">
         <v>3.25</v>
       </c>
       <c r="AD114">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE114">
         <v>1.09</v>
@@ -19069,19 +19069,19 @@
         <v>2.05</v>
       </c>
       <c r="S115">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T115">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U115">
         <v>2.8</v>
       </c>
       <c r="V115">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
         <v>1.06</v>
@@ -19111,7 +19111,7 @@
         <v>1.75</v>
       </c>
       <c r="AG115">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>2.2</v>
       </c>
       <c r="S116">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T116">
         <v>3.22</v>
@@ -19241,10 +19241,10 @@
         <v>2.45</v>
       </c>
       <c r="V116">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X116">
         <v>1.05</v>
@@ -19274,7 +19274,7 @@
         <v>1.62</v>
       </c>
       <c r="AG116">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O117">
         <v>3.25</v>
@@ -19395,13 +19395,13 @@
         <v>2.1</v>
       </c>
       <c r="S117">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T117">
         <v>2.88</v>
       </c>
       <c r="U117">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V117">
         <v>1.36</v>
@@ -19419,7 +19419,7 @@
         <v>2.85</v>
       </c>
       <c r="AA117">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB117">
         <v>1.66</v>
@@ -19431,7 +19431,7 @@
         <v>1.22</v>
       </c>
       <c r="AE117">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF117">
         <v>1.8</v>
@@ -19453,7 +19453,7 @@
         <v>1.29</v>
       </c>
       <c r="AK117">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O118">
         <v>4.15</v>
@@ -19552,10 +19552,10 @@
         <v>5.25</v>
       </c>
       <c r="Q118">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="R118">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S118">
         <v>1.3</v>
@@ -19564,10 +19564,10 @@
         <v>3.35</v>
       </c>
       <c r="U118">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V118">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W118">
         <v>1.08</v>
@@ -19576,10 +19576,10 @@
         <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z118">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA118">
         <v>1.65</v>
@@ -19594,7 +19594,7 @@
         <v>1.4</v>
       </c>
       <c r="AE118">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF118">
         <v>1.75</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK118">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,7 +19706,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="O119">
         <v>3.08</v>
@@ -19727,13 +19727,13 @@
         <v>2.63</v>
       </c>
       <c r="U119">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V119">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W119">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
         <v>1.01</v>
@@ -19748,7 +19748,7 @@
         <v>2.08</v>
       </c>
       <c r="AB119">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC119">
         <v>3.54</v>
@@ -19779,7 +19779,7 @@
         <v>1.36</v>
       </c>
       <c r="AK119">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19872,16 +19872,16 @@
         <v>1.59</v>
       </c>
       <c r="O120">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P120">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q120">
         <v>2.13</v>
       </c>
       <c r="R120">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S120">
         <v>1.33</v>
@@ -19899,7 +19899,7 @@
         <v>1.11</v>
       </c>
       <c r="X120">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
         <v>1.26</v>
@@ -19923,7 +19923,7 @@
         <v>1.13</v>
       </c>
       <c r="AF120">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG120">
         <v>1.95</v>
@@ -20047,7 +20047,7 @@
         <v>2.4</v>
       </c>
       <c r="S121">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T121">
         <v>3.5</v>
@@ -20056,7 +20056,7 @@
         <v>2.3</v>
       </c>
       <c r="V121">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W121">
         <v>1.11</v>
@@ -20068,7 +20068,7 @@
         <v>1.19</v>
       </c>
       <c r="Z121">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA121">
         <v>1.63</v>
@@ -20198,10 +20198,10 @@
         <v>2.6</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -20210,7 +20210,7 @@
         <v>2.06</v>
       </c>
       <c r="S122">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
         <v>2.73</v>
@@ -20222,7 +20222,7 @@
         <v>1.42</v>
       </c>
       <c r="W122">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X122">
         <v>1.03</v>
@@ -20243,7 +20243,7 @@
         <v>3.25</v>
       </c>
       <c r="AD122">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE122">
         <v>1.11</v>
@@ -24107,10 +24107,10 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O146">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="P146">
         <v>5.25</v>
@@ -24128,7 +24128,7 @@
         <v>2.65</v>
       </c>
       <c r="U146">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V146">
         <v>1.33</v>
@@ -24143,7 +24143,7 @@
         <v>1.36</v>
       </c>
       <c r="Z146">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AA146">
         <v>2.32</v>
@@ -24152,10 +24152,10 @@
         <v>1.65</v>
       </c>
       <c r="AC146">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD146">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE146">
         <v>1.02</v>
@@ -24164,7 +24164,7 @@
         <v>2.05</v>
       </c>
       <c r="AG146">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -27530,19 +27530,19 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="O167">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P167">
         <v>2.87</v>
       </c>
       <c r="Q167">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="R167">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S167">
         <v>1.22</v>
@@ -27554,7 +27554,7 @@
         <v>2.26</v>
       </c>
       <c r="V167">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W167">
         <v>1.15</v>
@@ -27572,7 +27572,7 @@
         <v>1.49</v>
       </c>
       <c r="AB167">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC167">
         <v>2.35</v>
@@ -27603,7 +27603,7 @@
         <v>1.25</v>
       </c>
       <c r="AK167">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -30138,10 +30138,10 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O183">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P183">
         <v>2.25</v>
@@ -30156,7 +30156,7 @@
         <v>1.32</v>
       </c>
       <c r="T183">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="U183">
         <v>2.6</v>
@@ -30165,7 +30165,7 @@
         <v>1.42</v>
       </c>
       <c r="W183">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X183">
         <v>1.04</v>
@@ -30174,7 +30174,7 @@
         <v>1.21</v>
       </c>
       <c r="Z183">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA183">
         <v>1.81</v>
@@ -30189,7 +30189,7 @@
         <v>1.32</v>
       </c>
       <c r="AE183">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF183">
         <v>1.6</v>
@@ -35215,7 +35215,7 @@
         <v>3.3</v>
       </c>
       <c r="V214">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W214">
         <v>1.04</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="O217">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="P217">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="Q217">
         <v>1.53</v>
@@ -35707,7 +35707,7 @@
         <v>1.75</v>
       </c>
       <c r="W217">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X217">
         <v>1.01</v>
@@ -35716,7 +35716,7 @@
         <v>1.08</v>
       </c>
       <c r="Z217">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA217">
         <v>1.37</v>
@@ -35731,13 +35731,13 @@
         <v>1.76</v>
       </c>
       <c r="AE217">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF217">
         <v>1.83</v>
       </c>
       <c r="AG217">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35846,10 +35846,10 @@
         <v>2.62</v>
       </c>
       <c r="O218">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P218">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q218">
         <v>3</v>
@@ -35864,7 +35864,7 @@
         <v>3.5</v>
       </c>
       <c r="U218">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V218">
         <v>1.6</v>
@@ -35879,7 +35879,7 @@
         <v>1.14</v>
       </c>
       <c r="Z218">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA218">
         <v>1.6</v>
@@ -35897,7 +35897,7 @@
         <v>1.2</v>
       </c>
       <c r="AF218">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG218">
         <v>2.4</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O219">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P219">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q219">
         <v>2.5</v>
@@ -36060,7 +36060,7 @@
         <v>1.03</v>
       </c>
       <c r="AF219">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="AG219">
         <v>1.53</v>
@@ -38164,10 +38164,10 @@
         <v>2.2</v>
       </c>
       <c r="AA232">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB232">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC232">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         <v>1.62</v>
       </c>
       <c r="T233">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="U233">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="V233">
         <v>1.19</v>
@@ -38327,13 +38327,13 @@
         <v>2.4</v>
       </c>
       <c r="AA233">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AB233">
         <v>1.4</v>
       </c>
       <c r="AC233">
-        <v>5.81</v>
+        <v>5.84</v>
       </c>
       <c r="AD233">
         <v>1.13</v>
@@ -38345,7 +38345,7 @@
         <v>2.3</v>
       </c>
       <c r="AG233">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>1.36</v>
       </c>
       <c r="AK233">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38457,10 +38457,10 @@
         <v>3</v>
       </c>
       <c r="P234">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q234">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="R234">
         <v>2.05</v>
@@ -38481,10 +38481,10 @@
         <v>1.01</v>
       </c>
       <c r="X234">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z234">
         <v>2.69</v>
@@ -38493,16 +38493,16 @@
         <v>2.3</v>
       </c>
       <c r="AB234">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC234">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD234">
         <v>1.16</v>
       </c>
       <c r="AE234">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF234">
         <v>1.94</v>
@@ -38521,7 +38521,7 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK234">
         <v>1.49</v>
@@ -38614,28 +38614,28 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O235">
         <v>2.75</v>
       </c>
       <c r="P235">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="Q235">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R235">
         <v>1.73</v>
       </c>
       <c r="S235">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="T235">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U235">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="V235">
         <v>1.2</v>
@@ -38653,13 +38653,13 @@
         <v>2.25</v>
       </c>
       <c r="AA235">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AB235">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC235">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AD235">
         <v>1.11</v>
@@ -38671,7 +38671,7 @@
         <v>2.15</v>
       </c>
       <c r="AG235">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38786,10 +38786,10 @@
         <v>4.1</v>
       </c>
       <c r="Q236">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R236">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="S236">
         <v>1.76</v>
@@ -38798,7 +38798,7 @@
         <v>2.1</v>
       </c>
       <c r="U236">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="V236">
         <v>1.17</v>
@@ -38807,22 +38807,22 @@
         <v>1.02</v>
       </c>
       <c r="X236">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Y236">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Z236">
         <v>2.02</v>
       </c>
       <c r="AA236">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AB236">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC236">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD236">
         <v>1.08</v>
@@ -38850,7 +38850,7 @@
         <v>1.44</v>
       </c>
       <c r="AK236">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38943,13 +38943,13 @@
         <v>2.6</v>
       </c>
       <c r="O237">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P237">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q237">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R237">
         <v>1.73</v>
@@ -38970,13 +38970,13 @@
         <v>1.03</v>
       </c>
       <c r="X237">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Y237">
         <v>1.67</v>
       </c>
       <c r="Z237">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA237">
         <v>2.8</v>
@@ -42547,7 +42547,7 @@
         <v>3</v>
       </c>
       <c r="U259">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V259">
         <v>1.44</v>
@@ -42577,7 +42577,7 @@
         <v>1.36</v>
       </c>
       <c r="AE259">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF259">
         <v>1.97</v>
@@ -43018,16 +43018,16 @@
         <v>2.2</v>
       </c>
       <c r="O262">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P262">
         <v>3.5</v>
       </c>
       <c r="Q262">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R262">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="S262">
         <v>1.62</v>
@@ -43051,7 +43051,7 @@
         <v>1.67</v>
       </c>
       <c r="Z262">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AA262">
         <v>2.88</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="O272">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P272">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q272">
         <v>6.94</v>
@@ -44672,7 +44672,7 @@
         <v>1.45</v>
       </c>
       <c r="W272">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X272">
         <v>1.01</v>
@@ -44684,13 +44684,13 @@
         <v>3.95</v>
       </c>
       <c r="AA272">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB272">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC272">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="AD272">
         <v>1.41</v>
@@ -45632,10 +45632,10 @@
         <v>3.75</v>
       </c>
       <c r="Q278">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="R278">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S278">
         <v>1.36</v>
@@ -45647,7 +45647,7 @@
         <v>2.8</v>
       </c>
       <c r="V278">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W278">
         <v>1.06</v>
@@ -45665,7 +45665,7 @@
         <v>2.05</v>
       </c>
       <c r="AB278">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC278">
         <v>3.75</v>
@@ -46112,7 +46112,7 @@
         </is>
       </c>
       <c r="N281">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="O281">
         <v>3.3</v>
@@ -46157,7 +46157,7 @@
         <v>1.83</v>
       </c>
       <c r="AC281">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD281">
         <v>1.27</v>
@@ -46166,7 +46166,7 @@
         <v>1.11</v>
       </c>
       <c r="AF281">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG281">
         <v>1.94</v>
@@ -46185,7 +46185,7 @@
         <v>1.3</v>
       </c>
       <c r="AK281">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46631,16 +46631,16 @@
         <v>1.02</v>
       </c>
       <c r="X284">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y284">
         <v>1.54</v>
       </c>
       <c r="Z284">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AA284">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AB284">
         <v>1.48</v>
@@ -46674,7 +46674,7 @@
         <v>1.3</v>
       </c>
       <c r="AK284">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -47090,10 +47090,10 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O287">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P287">
         <v>3</v>
@@ -47102,52 +47102,52 @@
         <v>2.7</v>
       </c>
       <c r="R287">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S287">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T287">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U287">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V287">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W287">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X287">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y287">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z287">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="AA287">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AB287">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AC287">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD287">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE287">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF287">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG287">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK287">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47416,10 +47416,10 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O289">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P289">
         <v>2.44</v>
@@ -47428,16 +47428,16 @@
         <v>3.24</v>
       </c>
       <c r="R289">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S289">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T289">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U289">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="V289">
         <v>1.4</v>
@@ -47446,7 +47446,7 @@
         <v>1.08</v>
       </c>
       <c r="X289">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y289">
         <v>1.27</v>
@@ -47455,13 +47455,13 @@
         <v>3.2</v>
       </c>
       <c r="AA289">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB289">
         <v>1.78</v>
       </c>
       <c r="AC289">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="AD289">
         <v>1.26</v>
@@ -47579,22 +47579,22 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="O290">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P290">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q290">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="R290">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="S290">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T290">
         <v>3.4</v>
@@ -47603,40 +47603,40 @@
         <v>2.3</v>
       </c>
       <c r="V290">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W290">
         <v>1.09</v>
       </c>
       <c r="X290">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y290">
         <v>1.16</v>
       </c>
       <c r="Z290">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="AA290">
         <v>1.66</v>
       </c>
       <c r="AB290">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC290">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD290">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE290">
         <v>1.12</v>
       </c>
       <c r="AF290">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG290">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>1.18</v>
       </c>
       <c r="AK290">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47754,13 +47754,13 @@
         <v>2</v>
       </c>
       <c r="R291">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S291">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T291">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U291">
         <v>2.41</v>
@@ -47772,13 +47772,13 @@
         <v>1.11</v>
       </c>
       <c r="X291">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z291">
-        <v>3.94</v>
+        <v>4.03</v>
       </c>
       <c r="AA291">
         <v>1.7</v>
@@ -47787,13 +47787,13 @@
         <v>2.07</v>
       </c>
       <c r="AC291">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD291">
         <v>1.42</v>
       </c>
       <c r="AE291">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF291">
         <v>1.7</v>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="O292">
         <v>3</v>
@@ -47923,7 +47923,7 @@
         <v>1.34</v>
       </c>
       <c r="T292">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U292">
         <v>3</v>
@@ -47938,22 +47938,22 @@
         <v>1.04</v>
       </c>
       <c r="Y292">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z292">
         <v>2.92</v>
       </c>
       <c r="AA292">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AB292">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC292">
         <v>3.48</v>
       </c>
       <c r="AD292">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE292">
         <v>1.04</v>
@@ -47962,7 +47962,7 @@
         <v>1.68</v>
       </c>
       <c r="AG292">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>3.3</v>
       </c>
       <c r="P294">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="Q294">
         <v>3.6</v>
@@ -48246,16 +48246,16 @@
         <v>2.1</v>
       </c>
       <c r="S294">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T294">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U294">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="V294">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W294">
         <v>1.03</v>
@@ -48288,7 +48288,7 @@
         <v>1.73</v>
       </c>
       <c r="AG294">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48412,19 +48412,19 @@
         <v>1.22</v>
       </c>
       <c r="T295">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U295">
         <v>2.2</v>
       </c>
       <c r="V295">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="W295">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X295">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y295">
         <v>1.13</v>
@@ -48439,10 +48439,10 @@
         <v>2.3</v>
       </c>
       <c r="AC295">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AD295">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE295">
         <v>1.23</v>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK295">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48557,7 +48557,7 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O296">
         <v>4.25</v>
@@ -48587,16 +48587,16 @@
         <v>1.1</v>
       </c>
       <c r="X296">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y296">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z296">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="AA296">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB296">
         <v>2.24</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,31 +49698,31 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.69</v>
+        <v>2.6</v>
       </c>
       <c r="O303">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P303">
-        <v>4.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q303">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="R303">
         <v>2.5</v>
       </c>
       <c r="S303">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T303">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U303">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V303">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W303">
         <v>1.2</v>
@@ -49731,31 +49731,31 @@
         <v>1.01</v>
       </c>
       <c r="Y303">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z303">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA303">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB303">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC303">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD303">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE303">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF303">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG303">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK303">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,31 +49861,31 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="O304">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P304">
-        <v>2.15</v>
+        <v>4.06</v>
       </c>
       <c r="Q304">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R304">
         <v>2.5</v>
       </c>
       <c r="S304">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T304">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U304">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V304">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W304">
         <v>1.2</v>
@@ -49894,31 +49894,31 @@
         <v>1.01</v>
       </c>
       <c r="Y304">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z304">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA304">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB304">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC304">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD304">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AE304">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF304">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG304">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK304">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50024,10 +50024,10 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O305">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P305">
         <v>4.15</v>
@@ -50039,7 +50039,7 @@
         <v>2.47</v>
       </c>
       <c r="S305">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T305">
         <v>3.82</v>
@@ -50048,7 +50048,7 @@
         <v>2.05</v>
       </c>
       <c r="V305">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W305">
         <v>1.18</v>
@@ -51165,19 +51165,19 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O312">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P312">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="Q312">
         <v>2.15</v>
       </c>
       <c r="R312">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S312">
         <v>1.31</v>
@@ -51192,10 +51192,10 @@
         <v>1.46</v>
       </c>
       <c r="W312">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X312">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y312">
         <v>1.17</v>
@@ -51210,19 +51210,19 @@
         <v>2.14</v>
       </c>
       <c r="AC312">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD312">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE312">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF312">
         <v>1.6</v>
       </c>
       <c r="AG312">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>1.2</v>
       </c>
       <c r="AK312">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51331,25 +51331,25 @@
         <v>1.85</v>
       </c>
       <c r="O313">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P313">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q313">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R313">
         <v>2.28</v>
       </c>
       <c r="S313">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T313">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="U313">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="V313">
         <v>1.44</v>
@@ -51367,7 +51367,7 @@
         <v>3.64</v>
       </c>
       <c r="AA313">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB313">
         <v>1.9</v>
@@ -51385,7 +51385,7 @@
         <v>1.68</v>
       </c>
       <c r="AG313">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51829,7 +51829,7 @@
         <v>2.9</v>
       </c>
       <c r="R316">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S316">
         <v>1.36</v>
@@ -51859,13 +51859,13 @@
         <v>1.96</v>
       </c>
       <c r="AB316">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC316">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD316">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE316">
         <v>1.05</v>
@@ -51874,7 +51874,7 @@
         <v>1.67</v>
       </c>
       <c r="AG316">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK316">
         <v>1.5</v>
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G318">
@@ -52143,80 +52143,80 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="O318">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="P318">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="Q318">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R318">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="S318">
+        <v>1.2</v>
+      </c>
+      <c r="T318">
+        <v>4</v>
+      </c>
+      <c r="U318">
+        <v>2.05</v>
+      </c>
+      <c r="V318">
+        <v>1.74</v>
+      </c>
+      <c r="W318">
+        <v>1.2</v>
+      </c>
+      <c r="X318">
+        <v>1.01</v>
+      </c>
+      <c r="Y318">
+        <v>1.07</v>
+      </c>
+      <c r="Z318">
+        <v>5.75</v>
+      </c>
+      <c r="AA318">
+        <v>1.36</v>
+      </c>
+      <c r="AB318">
+        <v>2.9</v>
+      </c>
+      <c r="AC318">
+        <v>2.03</v>
+      </c>
+      <c r="AD318">
+        <v>1.72</v>
+      </c>
+      <c r="AE318">
+        <v>1.3</v>
+      </c>
+      <c r="AF318">
+        <v>1.43</v>
+      </c>
+      <c r="AG318">
+        <v>2.58</v>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ318">
         <v>1.22</v>
       </c>
-      <c r="T318">
-        <v>3.8</v>
-      </c>
-      <c r="U318">
+      <c r="AK318">
         <v>2.2</v>
-      </c>
-      <c r="V318">
-        <v>1.6</v>
-      </c>
-      <c r="W318">
-        <v>1.18</v>
-      </c>
-      <c r="X318">
-        <v>1.02</v>
-      </c>
-      <c r="Y318">
-        <v>1.15</v>
-      </c>
-      <c r="Z318">
-        <v>5.5</v>
-      </c>
-      <c r="AA318">
-        <v>1.45</v>
-      </c>
-      <c r="AB318">
-        <v>2.5</v>
-      </c>
-      <c r="AC318">
-        <v>2.1</v>
-      </c>
-      <c r="AD318">
-        <v>1.63</v>
-      </c>
-      <c r="AE318">
-        <v>1.26</v>
-      </c>
-      <c r="AF318">
-        <v>1.42</v>
-      </c>
-      <c r="AG318">
-        <v>2.64</v>
-      </c>
-      <c r="AH318" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI318" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ318">
-        <v>1.25</v>
-      </c>
-      <c r="AK318">
-        <v>1.65</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G319">
@@ -52306,64 +52306,64 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O319">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="P319">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="Q319">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R319">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="S319">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T319">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U319">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V319">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="W319">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X319">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y319">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z319">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA319">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AB319">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC319">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD319">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AE319">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF319">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG319">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK319">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AL319">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="O84">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="P84">
         <v>2.9</v>
       </c>
       <c r="Q84">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="R84">
         <v>1.82</v>
       </c>
       <c r="S84">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T84">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="U84">
         <v>4.2</v>
@@ -14028,7 +14028,7 @@
         <v>1.15</v>
       </c>
       <c r="W84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X84">
         <v>1.16</v>
@@ -14037,13 +14037,13 @@
         <v>1.73</v>
       </c>
       <c r="Z84">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AA84">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AB84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC84">
         <v>6.3</v>
@@ -14074,7 +14074,7 @@
         <v>1.41</v>
       </c>
       <c r="AK84">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.9</v>
+        <v>3.42</v>
       </c>
       <c r="O106">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="Q106">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="R106">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S106">
+        <v>1.35</v>
+      </c>
+      <c r="T106">
+        <v>2.88</v>
+      </c>
+      <c r="U106">
+        <v>2.73</v>
+      </c>
+      <c r="V106">
         <v>1.36</v>
       </c>
-      <c r="T106">
-        <v>2.7</v>
-      </c>
-      <c r="U106">
-        <v>2.7</v>
-      </c>
-      <c r="V106">
-        <v>1.39</v>
-      </c>
       <c r="W106">
+        <v>1.06</v>
+      </c>
+      <c r="X106">
+        <v>1.06</v>
+      </c>
+      <c r="Y106">
+        <v>1.29</v>
+      </c>
+      <c r="Z106">
+        <v>3.05</v>
+      </c>
+      <c r="AA106">
+        <v>2</v>
+      </c>
+      <c r="AB106">
+        <v>1.78</v>
+      </c>
+      <c r="AC106">
+        <v>3.3</v>
+      </c>
+      <c r="AD106">
+        <v>1.3</v>
+      </c>
+      <c r="AE106">
         <v>1.08</v>
       </c>
-      <c r="X106">
-        <v>1.03</v>
-      </c>
-      <c r="Y106">
-        <v>1.25</v>
-      </c>
-      <c r="Z106">
-        <v>3.3</v>
-      </c>
-      <c r="AA106">
-        <v>1.85</v>
-      </c>
-      <c r="AB106">
-        <v>1.89</v>
-      </c>
-      <c r="AC106">
-        <v>3</v>
-      </c>
-      <c r="AD106">
-        <v>1.32</v>
-      </c>
-      <c r="AE106">
-        <v>1.11</v>
-      </c>
       <c r="AF106">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG106">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>3.42</v>
+        <v>1.9</v>
       </c>
       <c r="O107">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P107">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="Q107">
-        <v>3.81</v>
+        <v>2.5</v>
       </c>
       <c r="R107">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S107">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U107">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z107">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA107">
+        <v>1.85</v>
+      </c>
+      <c r="AB107">
+        <v>1.89</v>
+      </c>
+      <c r="AC107">
+        <v>3</v>
+      </c>
+      <c r="AD107">
+        <v>1.32</v>
+      </c>
+      <c r="AE107">
+        <v>1.11</v>
+      </c>
+      <c r="AF107">
+        <v>1.77</v>
+      </c>
+      <c r="AG107">
         <v>2</v>
-      </c>
-      <c r="AB107">
-        <v>1.78</v>
-      </c>
-      <c r="AC107">
-        <v>3.3</v>
-      </c>
-      <c r="AD107">
-        <v>1.3</v>
-      </c>
-      <c r="AE107">
-        <v>1.08</v>
-      </c>
-      <c r="AF107">
-        <v>1.8</v>
-      </c>
-      <c r="AG107">
-        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P121">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q121">
         <v>3</v>
       </c>
       <c r="R121">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T121">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="U121">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="V121">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W121">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X121">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z121">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="AA121">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AB121">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AC121">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD121">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AE121">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF121">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG121">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AK121">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="O122">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q122">
         <v>3</v>
       </c>
       <c r="R122">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S122">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="U122">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="V122">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W122">
+        <v>1.04</v>
+      </c>
+      <c r="X122">
+        <v>1.03</v>
+      </c>
+      <c r="Y122">
+        <v>1.22</v>
+      </c>
+      <c r="Z122">
+        <v>3.54</v>
+      </c>
+      <c r="AA122">
+        <v>1.93</v>
+      </c>
+      <c r="AB122">
+        <v>1.83</v>
+      </c>
+      <c r="AC122">
+        <v>3.25</v>
+      </c>
+      <c r="AD122">
+        <v>1.31</v>
+      </c>
+      <c r="AE122">
         <v>1.11</v>
       </c>
-      <c r="X122">
-        <v>1.01</v>
-      </c>
-      <c r="Y122">
-        <v>1.19</v>
-      </c>
-      <c r="Z122">
-        <v>4.25</v>
-      </c>
-      <c r="AA122">
-        <v>1.63</v>
-      </c>
-      <c r="AB122">
-        <v>2.13</v>
-      </c>
-      <c r="AC122">
-        <v>2.45</v>
-      </c>
-      <c r="AD122">
-        <v>1.52</v>
-      </c>
-      <c r="AE122">
-        <v>1.2</v>
-      </c>
       <c r="AF122">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG122">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AK122">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O129">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P129">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21499,10 +21499,10 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="O130">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P130">
         <v>6</v>
@@ -21520,10 +21520,10 @@
         <v>3.75</v>
       </c>
       <c r="U130">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V130">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W130">
         <v>1.12</v>
@@ -21535,7 +21535,7 @@
         <v>1.1</v>
       </c>
       <c r="Z130">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA130">
         <v>1.44</v>
@@ -21572,7 +21572,7 @@
         <v>1.06</v>
       </c>
       <c r="AK130">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="O138">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P138">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q138">
         <v>4.5</v>
@@ -22824,13 +22824,13 @@
         <v>3.64</v>
       </c>
       <c r="U138">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V138">
         <v>1.67</v>
       </c>
       <c r="W138">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X138">
         <v>1.02</v>
@@ -22848,7 +22848,7 @@
         <v>2.5</v>
       </c>
       <c r="AC138">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AD138">
         <v>1.67</v>
@@ -22857,10 +22857,10 @@
         <v>1.24</v>
       </c>
       <c r="AF138">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG138">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22969,10 +22969,10 @@
         <v>1.21</v>
       </c>
       <c r="O139">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="P139">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Q139">
         <v>1.53</v>
@@ -22987,13 +22987,13 @@
         <v>4.8</v>
       </c>
       <c r="U139">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V139">
         <v>1.85</v>
       </c>
       <c r="W139">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X139">
         <v>1.01</v>
@@ -23008,13 +23008,13 @@
         <v>1.33</v>
       </c>
       <c r="AB139">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AC139">
         <v>1.8</v>
       </c>
       <c r="AD139">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE139">
         <v>1.36</v>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK139">
         <v>3.6</v>
@@ -23125,7 +23125,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N140">
@@ -26398,7 +26398,7 @@
         <v>2.8</v>
       </c>
       <c r="Q160">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R160">
         <v>2.13</v>
@@ -26419,7 +26419,7 @@
         <v>1.03</v>
       </c>
       <c r="X160">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y160">
         <v>1.32</v>
@@ -26443,7 +26443,7 @@
         <v>1.07</v>
       </c>
       <c r="AF160">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG160">
         <v>1.87</v>
@@ -26878,16 +26878,16 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q163">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="R163">
         <v>2.13</v>
@@ -26917,16 +26917,16 @@
         <v>3.42</v>
       </c>
       <c r="AA163">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB163">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC163">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD163">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE163">
         <v>1.09</v>
@@ -26948,7 +26948,7 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AK163">
         <v>1.36</v>
@@ -27080,10 +27080,10 @@
         <v>0</v>
       </c>
       <c r="AA164">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB164">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC164">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q165">
         <v>2.66</v>
@@ -27222,16 +27222,16 @@
         <v>1.44</v>
       </c>
       <c r="T165">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U165">
         <v>3.28</v>
       </c>
       <c r="V165">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W165">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X165">
         <v>1.02</v>
@@ -27376,10 +27376,10 @@
         <v>0</v>
       </c>
       <c r="Q166">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R166">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S166">
         <v>1.44</v>
@@ -27406,10 +27406,10 @@
         <v>2.7</v>
       </c>
       <c r="AA166">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AB166">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC166">
         <v>4</v>
@@ -27424,7 +27424,7 @@
         <v>1.87</v>
       </c>
       <c r="AG166">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>1.28</v>
       </c>
       <c r="AK166">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27542,7 +27542,7 @@
         <v>2.88</v>
       </c>
       <c r="R167">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S167">
         <v>1.43</v>
@@ -27551,13 +27551,13 @@
         <v>2.5</v>
       </c>
       <c r="U167">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="V167">
         <v>1.29</v>
       </c>
       <c r="W167">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X167">
         <v>1.02</v>
@@ -27569,16 +27569,16 @@
         <v>2.74</v>
       </c>
       <c r="AA167">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB167">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC167">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AD167">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE167">
         <v>1.02</v>
@@ -27587,7 +27587,7 @@
         <v>1.86</v>
       </c>
       <c r="AG167">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27693,34 +27693,34 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q168">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="R168">
         <v>2.07</v>
       </c>
       <c r="S168">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T168">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U168">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V168">
         <v>1.36</v>
       </c>
       <c r="W168">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X168">
         <v>1</v>
@@ -27735,7 +27735,7 @@
         <v>1.89</v>
       </c>
       <c r="AB168">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC168">
         <v>3.2</v>
@@ -27747,10 +27747,10 @@
         <v>1.06</v>
       </c>
       <c r="AF168">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG168">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK168">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27856,31 +27856,31 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O169">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="P169">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q169">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="R169">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S169">
         <v>1.22</v>
       </c>
       <c r="T169">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U169">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V169">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W169">
         <v>1.15</v>
@@ -27892,10 +27892,10 @@
         <v>1.18</v>
       </c>
       <c r="Z169">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AA169">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB169">
         <v>2.4</v>
@@ -27929,7 +27929,7 @@
         <v>1.25</v>
       </c>
       <c r="AK169">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28028,22 +28028,22 @@
         <v>3.3</v>
       </c>
       <c r="Q170">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R170">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S170">
         <v>1.44</v>
       </c>
       <c r="T170">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="U170">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V170">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W170">
         <v>1.04</v>
@@ -28052,31 +28052,31 @@
         <v>1.04</v>
       </c>
       <c r="Y170">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z170">
         <v>2.62</v>
       </c>
       <c r="AA170">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AB170">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC170">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD170">
         <v>1.15</v>
       </c>
       <c r="AE170">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF170">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG170">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -29975,19 +29975,19 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="O182">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P182">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="Q182">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R182">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S182">
         <v>1.42</v>
@@ -30011,19 +30011,19 @@
         <v>1.38</v>
       </c>
       <c r="Z182">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA182">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB182">
         <v>1.57</v>
       </c>
       <c r="AC182">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD182">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE182">
         <v>1.05</v>
@@ -30138,16 +30138,16 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O183">
         <v>3.7</v>
       </c>
       <c r="P183">
-        <v>5.04</v>
+        <v>4.8</v>
       </c>
       <c r="Q183">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R183">
         <v>2.2</v>
@@ -30162,7 +30162,7 @@
         <v>2.88</v>
       </c>
       <c r="V183">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W183">
         <v>1.04</v>
@@ -30171,19 +30171,19 @@
         <v>1.01</v>
       </c>
       <c r="Y183">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z183">
         <v>3.04</v>
       </c>
       <c r="AA183">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB183">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC183">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AD183">
         <v>1.24</v>
@@ -30192,10 +30192,10 @@
         <v>1.05</v>
       </c>
       <c r="AF183">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AG183">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>1.08</v>
       </c>
       <c r="AK183">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>3.2</v>
       </c>
       <c r="V184">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W184">
         <v>1.01</v>
@@ -30334,10 +30334,10 @@
         <v>1.04</v>
       </c>
       <c r="Y184">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z184">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA184">
         <v>2.38</v>
@@ -30346,7 +30346,7 @@
         <v>1.57</v>
       </c>
       <c r="AC184">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AD184">
         <v>1.17</v>
@@ -30355,10 +30355,10 @@
         <v>1.02</v>
       </c>
       <c r="AF184">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG184">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30464,43 +30464,43 @@
         </is>
       </c>
       <c r="N185">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O185">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P185">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q185">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="R185">
         <v>2.25</v>
       </c>
       <c r="S185">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T185">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U185">
         <v>2.6</v>
       </c>
       <c r="V185">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W185">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X185">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y185">
         <v>1.21</v>
       </c>
       <c r="Z185">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA185">
         <v>1.81</v>
@@ -30509,10 +30509,10 @@
         <v>1.94</v>
       </c>
       <c r="AC185">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD185">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE185">
         <v>1.13</v>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK185">
         <v>1.4</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O191">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="P191">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="Q191">
         <v>1.69</v>
@@ -31478,22 +31478,22 @@
         <v>1.08</v>
       </c>
       <c r="Z191">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA191">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB191">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AC191">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AD191">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AE191">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF191">
         <v>1.53</v>
@@ -31515,7 +31515,7 @@
         <v>1.15</v>
       </c>
       <c r="AK191">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31931,19 +31931,19 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="O194">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P194">
         <v>10</v>
       </c>
       <c r="Q194">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R194">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="S194">
         <v>1.22</v>
@@ -31952,13 +31952,13 @@
         <v>3.9</v>
       </c>
       <c r="U194">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V194">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W194">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X194">
         <v>1.01</v>
@@ -31967,10 +31967,10 @@
         <v>1.13</v>
       </c>
       <c r="Z194">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA194">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB194">
         <v>2.62</v>
@@ -31979,7 +31979,7 @@
         <v>2.14</v>
       </c>
       <c r="AD194">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE194">
         <v>1.25</v>
@@ -31988,7 +31988,7 @@
         <v>1.91</v>
       </c>
       <c r="AG194">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32103,25 +32103,25 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R195">
         <v>2.1</v>
       </c>
       <c r="S195">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T195">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="U195">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="V195">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W195">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
         <v>1.06</v>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK195">
         <v>2.5</v>
@@ -32426,16 +32426,16 @@
         <v>3.5</v>
       </c>
       <c r="P197">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="Q197">
         <v>3</v>
       </c>
       <c r="R197">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S197">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T197">
         <v>3.25</v>
@@ -32450,13 +32450,13 @@
         <v>1.08</v>
       </c>
       <c r="X197">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
         <v>1.22</v>
       </c>
       <c r="Z197">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="AA197">
         <v>1.73</v>
@@ -32468,7 +32468,7 @@
         <v>2.57</v>
       </c>
       <c r="AD197">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE197">
         <v>1.17</v>
@@ -32477,7 +32477,7 @@
         <v>1.57</v>
       </c>
       <c r="AG197">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AK197">
         <v>1.49</v>
@@ -32583,19 +32583,19 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O198">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P198">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
       </c>
       <c r="R198">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S198">
         <v>1.45</v>
@@ -32604,19 +32604,19 @@
         <v>2.38</v>
       </c>
       <c r="U198">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="V198">
         <v>1.25</v>
       </c>
       <c r="W198">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X198">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y198">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z198">
         <v>2.57</v>
@@ -32625,10 +32625,10 @@
         <v>2.43</v>
       </c>
       <c r="AB198">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC198">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AD198">
         <v>1.14</v>
@@ -32640,7 +32640,7 @@
         <v>2.05</v>
       </c>
       <c r="AG198">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32749,10 +32749,10 @@
         <v>2.25</v>
       </c>
       <c r="O199">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P199">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q199">
         <v>2.88</v>
@@ -32776,19 +32776,19 @@
         <v>1.08</v>
       </c>
       <c r="X199">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y199">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z199">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA199">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB199">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC199">
         <v>3.25</v>
@@ -32803,7 +32803,7 @@
         <v>1.73</v>
       </c>
       <c r="AG199">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -33235,10 +33235,10 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O202">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P202">
         <v>3.8</v>
@@ -33250,37 +33250,37 @@
         <v>1.98</v>
       </c>
       <c r="S202">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T202">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U202">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="V202">
         <v>1.22</v>
       </c>
       <c r="W202">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X202">
         <v>1.11</v>
       </c>
       <c r="Y202">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Z202">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AA202">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AB202">
         <v>1.45</v>
       </c>
       <c r="AC202">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
       <c r="AD202">
         <v>1.1</v>
@@ -33292,7 +33292,7 @@
         <v>2.25</v>
       </c>
       <c r="AG202">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>1.3</v>
       </c>
       <c r="AK202">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="N203">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
       <c r="O203">
         <v>3.65</v>
@@ -33410,52 +33410,52 @@
         <v>6.5</v>
       </c>
       <c r="R203">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S203">
         <v>1.44</v>
       </c>
       <c r="T203">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U203">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="V203">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W203">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X203">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y203">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z203">
         <v>2.8</v>
       </c>
       <c r="AA203">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB203">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC203">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AD203">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE203">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF203">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AG203">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>1.22</v>
       </c>
       <c r="AK203">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -36006,16 +36006,16 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O219">
         <v>7</v>
       </c>
       <c r="P219">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q219">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R219">
         <v>2.8</v>
@@ -36030,7 +36030,7 @@
         <v>1.95</v>
       </c>
       <c r="V219">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W219">
         <v>1.15</v>
@@ -36054,7 +36054,7 @@
         <v>1.97</v>
       </c>
       <c r="AD219">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE219">
         <v>1.33</v>
@@ -36063,7 +36063,7 @@
         <v>1.83</v>
       </c>
       <c r="AG219">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>1.04</v>
       </c>
       <c r="AK219">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36169,7 +36169,7 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O220">
         <v>3.55</v>
@@ -36187,7 +36187,7 @@
         <v>1.25</v>
       </c>
       <c r="T220">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U220">
         <v>2.34</v>
@@ -36196,34 +36196,34 @@
         <v>1.6</v>
       </c>
       <c r="W220">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X220">
         <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z220">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA220">
         <v>1.6</v>
       </c>
       <c r="AB220">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC220">
         <v>2.6</v>
       </c>
       <c r="AD220">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE220">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF220">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG220">
         <v>2.4</v>
@@ -36239,7 +36239,7 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AK220">
         <v>1.44</v>
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O226">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="P226">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q226">
         <v>1.85</v>
@@ -37168,16 +37168,16 @@
         <v>3.66</v>
       </c>
       <c r="U226">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V226">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W226">
         <v>1.16</v>
       </c>
       <c r="X226">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
         <v>1.13</v>
@@ -37186,7 +37186,7 @@
         <v>6</v>
       </c>
       <c r="AA226">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB226">
         <v>2.7</v>
@@ -37195,13 +37195,13 @@
         <v>2.03</v>
       </c>
       <c r="AD226">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AE226">
         <v>1.29</v>
       </c>
       <c r="AF226">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG226">
         <v>2.38</v>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK226">
         <v>2.55</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
+        <v>2.6</v>
+      </c>
+      <c r="O238">
+        <v>2.7</v>
+      </c>
+      <c r="P238">
+        <v>2.8</v>
+      </c>
+      <c r="Q238">
+        <v>3.3</v>
+      </c>
+      <c r="R238">
+        <v>1.73</v>
+      </c>
+      <c r="S238">
+        <v>1.62</v>
+      </c>
+      <c r="T238">
+        <v>2.2</v>
+      </c>
+      <c r="U238">
+        <v>4</v>
+      </c>
+      <c r="V238">
+        <v>1.2</v>
+      </c>
+      <c r="W238">
+        <v>1.03</v>
+      </c>
+      <c r="X238">
+        <v>1.15</v>
+      </c>
+      <c r="Y238">
+        <v>1.67</v>
+      </c>
+      <c r="Z238">
         <v>2.1</v>
       </c>
-      <c r="O238">
-        <v>2.65</v>
-      </c>
-      <c r="P238">
-        <v>4.1</v>
-      </c>
-      <c r="Q238">
-        <v>3</v>
-      </c>
-      <c r="R238">
-        <v>1.78</v>
-      </c>
-      <c r="S238">
-        <v>1.76</v>
-      </c>
-      <c r="T238">
-        <v>2.1</v>
-      </c>
-      <c r="U238">
-        <v>4.33</v>
-      </c>
-      <c r="V238">
-        <v>1.17</v>
-      </c>
-      <c r="W238">
-        <v>1.02</v>
-      </c>
-      <c r="X238">
-        <v>1.16</v>
-      </c>
-      <c r="Y238">
-        <v>1.74</v>
-      </c>
-      <c r="Z238">
-        <v>2.02</v>
-      </c>
       <c r="AA238">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="AB238">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC238">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD238">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE238">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF238">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AG238">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>1.44</v>
       </c>
       <c r="AK238">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="O239">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P239">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q239">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R239">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="S239">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="T239">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U239">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V239">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W239">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X239">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Y239">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Z239">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA239">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AB239">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC239">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD239">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE239">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF239">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AG239">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>1.44</v>
       </c>
       <c r="AK239">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39921,10 +39921,10 @@
         <v>1.8</v>
       </c>
       <c r="O243">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P243">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="O253">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P253">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41877,10 +41877,10 @@
         <v>2.3</v>
       </c>
       <c r="O255">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P255">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q255">
         <v>2.8</v>
@@ -41895,7 +41895,7 @@
         <v>2.88</v>
       </c>
       <c r="U255">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V255">
         <v>1.38</v>
@@ -41910,7 +41910,7 @@
         <v>1.3</v>
       </c>
       <c r="Z255">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA255">
         <v>1.89</v>
@@ -41925,13 +41925,13 @@
         <v>1.3</v>
       </c>
       <c r="AE255">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF255">
         <v>1.68</v>
       </c>
       <c r="AG255">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="O256">
         <v>3.2</v>
@@ -42067,7 +42067,7 @@
         <v>1.02</v>
       </c>
       <c r="X256">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y256">
         <v>1.38</v>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK256">
         <v>1.65</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O257">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="P257">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="Q257">
         <v>3.4</v>
@@ -42215,16 +42215,16 @@
         <v>2.05</v>
       </c>
       <c r="S257">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T257">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U257">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="V257">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W257">
         <v>1.04</v>
@@ -42257,7 +42257,7 @@
         <v>1.78</v>
       </c>
       <c r="AG257">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>1.36</v>
       </c>
       <c r="AK257">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42701,7 +42701,7 @@
         <v>1.98</v>
       </c>
       <c r="R260">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S260">
         <v>1.36</v>
@@ -42725,7 +42725,7 @@
         <v>1.3</v>
       </c>
       <c r="Z260">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA260">
         <v>2</v>
@@ -42746,7 +42746,7 @@
         <v>2.2</v>
       </c>
       <c r="AG260">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="O266">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="P266">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R266">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T266">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U266">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V266">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X266">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y266">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z266">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE266">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF266">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG266">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK266">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44156,7 +44156,7 @@
         </is>
       </c>
       <c r="N269">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="O269">
         <v>4.33</v>
@@ -44177,10 +44177,10 @@
         <v>3.75</v>
       </c>
       <c r="U269">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V269">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W269">
         <v>1.18</v>
@@ -44192,28 +44192,28 @@
         <v>1.13</v>
       </c>
       <c r="Z269">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA269">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB269">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AC269">
         <v>2.1</v>
       </c>
       <c r="AD269">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE269">
         <v>1.25</v>
       </c>
       <c r="AF269">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG269">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O270">
         <v>2.9</v>
@@ -44328,7 +44328,7 @@
         <v>2.9</v>
       </c>
       <c r="Q270">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="R270">
         <v>1.91</v>
@@ -44352,10 +44352,10 @@
         <v>1.05</v>
       </c>
       <c r="Y270">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z270">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA270">
         <v>2.38</v>
@@ -44364,7 +44364,7 @@
         <v>1.57</v>
       </c>
       <c r="AC270">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD270">
         <v>1.17</v>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK270">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44488,10 +44488,10 @@
         <v>3.3</v>
       </c>
       <c r="P271">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="Q271">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="R271">
         <v>2</v>
@@ -44524,13 +44524,13 @@
         <v>2.1</v>
       </c>
       <c r="AB271">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC271">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AD271">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE271">
         <v>1.04</v>
@@ -44539,7 +44539,7 @@
         <v>1.88</v>
       </c>
       <c r="AG271">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,31 +45460,31 @@
         </is>
       </c>
       <c r="N277">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O277">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P277">
         <v>3.25</v>
       </c>
       <c r="Q277">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="R277">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S277">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T277">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U277">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V277">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W277">
         <v>1.08</v>
@@ -45493,47 +45493,47 @@
         <v>1</v>
       </c>
       <c r="Y277">
+        <v>1.21</v>
+      </c>
+      <c r="Z277">
+        <v>3.58</v>
+      </c>
+      <c r="AA277">
+        <v>1.79</v>
+      </c>
+      <c r="AB277">
+        <v>1.9</v>
+      </c>
+      <c r="AC277">
+        <v>2.95</v>
+      </c>
+      <c r="AD277">
+        <v>1.31</v>
+      </c>
+      <c r="AE277">
+        <v>1.1</v>
+      </c>
+      <c r="AF277">
+        <v>1.63</v>
+      </c>
+      <c r="AG277">
+        <v>2.1</v>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ277">
         <v>1.25</v>
       </c>
-      <c r="Z277">
-        <v>3.2</v>
-      </c>
-      <c r="AA277">
-        <v>1.91</v>
-      </c>
-      <c r="AB277">
-        <v>1.78</v>
-      </c>
-      <c r="AC277">
-        <v>3.28</v>
-      </c>
-      <c r="AD277">
-        <v>1.3</v>
-      </c>
-      <c r="AE277">
-        <v>1.05</v>
-      </c>
-      <c r="AF277">
-        <v>1.73</v>
-      </c>
-      <c r="AG277">
-        <v>1.92</v>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ277">
-        <v>1.23</v>
-      </c>
       <c r="AK277">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,31 +45623,31 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O278">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P278">
         <v>3.25</v>
       </c>
       <c r="Q278">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="R278">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S278">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T278">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U278">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V278">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W278">
         <v>1.08</v>
@@ -45656,31 +45656,31 @@
         <v>1</v>
       </c>
       <c r="Y278">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z278">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AA278">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AB278">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC278">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AD278">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE278">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF278">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG278">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK278">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O289">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P289">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q289">
         <v>2.7</v>
@@ -47431,13 +47431,13 @@
         <v>2.31</v>
       </c>
       <c r="S289">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T289">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U289">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="V289">
         <v>1.45</v>
@@ -47449,10 +47449,10 @@
         <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z289">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="AA289">
         <v>1.77</v>
@@ -47464,13 +47464,13 @@
         <v>2.7</v>
       </c>
       <c r="AD289">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE289">
         <v>1.15</v>
       </c>
       <c r="AF289">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AG289">
         <v>2.15</v>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK289">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47742,25 +47742,25 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="O291">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P291">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="Q291">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="R291">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S291">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T291">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U291">
         <v>2.55</v>
@@ -47772,22 +47772,22 @@
         <v>1.08</v>
       </c>
       <c r="X291">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
         <v>1.27</v>
       </c>
       <c r="Z291">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA291">
         <v>1.95</v>
       </c>
       <c r="AB291">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC291">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="AD291">
         <v>1.26</v>
@@ -47796,10 +47796,10 @@
         <v>1.06</v>
       </c>
       <c r="AF291">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG291">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>1.5</v>
       </c>
       <c r="AK291">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47905,16 +47905,16 @@
         </is>
       </c>
       <c r="N292">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="O292">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P292">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="Q292">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R292">
         <v>2.44</v>
@@ -47926,13 +47926,13 @@
         <v>3.4</v>
       </c>
       <c r="U292">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V292">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W292">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X292">
         <v>1.02</v>
@@ -47947,16 +47947,16 @@
         <v>1.66</v>
       </c>
       <c r="AB292">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AC292">
         <v>2.38</v>
       </c>
       <c r="AD292">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE292">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF292">
         <v>1.55</v>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK292">
         <v>1.3</v>
@@ -48086,7 +48086,7 @@
         <v>1.3</v>
       </c>
       <c r="T293">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U293">
         <v>2.41</v>
@@ -48101,28 +48101,28 @@
         <v>1.02</v>
       </c>
       <c r="Y293">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z293">
-        <v>4.03</v>
+        <v>3.95</v>
       </c>
       <c r="AA293">
         <v>1.7</v>
       </c>
       <c r="AB293">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AC293">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD293">
         <v>1.42</v>
       </c>
       <c r="AE293">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF293">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG293">
         <v>2.18</v>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK293">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48234,10 +48234,10 @@
         <v>2.71</v>
       </c>
       <c r="O294">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P294">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="Q294">
         <v>3.2</v>
@@ -48264,31 +48264,31 @@
         <v>1.04</v>
       </c>
       <c r="Y294">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z294">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="AA294">
         <v>1.85</v>
       </c>
       <c r="AB294">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC294">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="AD294">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE294">
         <v>1.04</v>
       </c>
       <c r="AF294">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG294">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48720,16 +48720,16 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="O297">
         <v>4.8</v>
       </c>
       <c r="P297">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="Q297">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R297">
         <v>2.66</v>
@@ -48738,13 +48738,13 @@
         <v>1.22</v>
       </c>
       <c r="T297">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U297">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V297">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W297">
         <v>1.15</v>
@@ -48774,10 +48774,10 @@
         <v>1.23</v>
       </c>
       <c r="AF297">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG297">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AK297">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O298">
         <v>4.25</v>
       </c>
       <c r="P298">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="Q298">
         <v>1.83</v>
@@ -48901,13 +48901,13 @@
         <v>1.26</v>
       </c>
       <c r="T298">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U298">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V298">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W298">
         <v>1.1</v>
@@ -48916,16 +48916,16 @@
         <v>1.01</v>
       </c>
       <c r="Y298">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z298">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA298">
         <v>1.61</v>
       </c>
       <c r="AB298">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AC298">
         <v>2.46</v>
@@ -48934,13 +48934,13 @@
         <v>1.43</v>
       </c>
       <c r="AE298">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF298">
         <v>1.78</v>
       </c>
       <c r="AG298">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>1.09</v>
       </c>
       <c r="AK298">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49372,7 +49372,7 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O301">
         <v>3.8</v>
@@ -49408,7 +49408,7 @@
         <v>1.07</v>
       </c>
       <c r="Z301">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="AA301">
         <v>1.36</v>
@@ -49544,19 +49544,19 @@
         <v>2.8</v>
       </c>
       <c r="Q302">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="R302">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S302">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T302">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U302">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V302">
         <v>1.57</v>
@@ -49707,10 +49707,10 @@
         <v>6.5</v>
       </c>
       <c r="Q303">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R303">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="S303">
         <v>1.13</v>
@@ -49719,10 +49719,10 @@
         <v>5.2</v>
       </c>
       <c r="U303">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V303">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="W303">
         <v>1.25</v>
@@ -49771,7 +49771,7 @@
         <v>1.08</v>
       </c>
       <c r="AK303">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="O304">
         <v>3.7</v>
@@ -49873,7 +49873,7 @@
         <v>2.25</v>
       </c>
       <c r="R304">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="S304">
         <v>1.25</v>
@@ -49882,19 +49882,19 @@
         <v>3.6</v>
       </c>
       <c r="U304">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V304">
         <v>1.5</v>
       </c>
       <c r="W304">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X304">
         <v>1.01</v>
       </c>
       <c r="Y304">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z304">
         <v>4.6</v>
@@ -49906,7 +49906,7 @@
         <v>2.3</v>
       </c>
       <c r="AC304">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AD304">
         <v>1.51</v>
@@ -50030,7 +50030,7 @@
         <v>3.75</v>
       </c>
       <c r="P305">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q305">
         <v>3</v>
@@ -50069,7 +50069,7 @@
         <v>3.1</v>
       </c>
       <c r="AC305">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD305">
         <v>1.91</v>
@@ -50193,7 +50193,7 @@
         <v>4</v>
       </c>
       <c r="P306">
-        <v>3.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q306">
         <v>2.2</v>
@@ -50229,7 +50229,7 @@
         <v>1.31</v>
       </c>
       <c r="AB306">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC306">
         <v>1.95</v>
@@ -50350,10 +50350,10 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O307">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P307">
         <v>4.15</v>
@@ -50365,7 +50365,7 @@
         <v>2.47</v>
       </c>
       <c r="S307">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T307">
         <v>3.82</v>
@@ -50374,7 +50374,7 @@
         <v>2.05</v>
       </c>
       <c r="V307">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W307">
         <v>1.18</v>
@@ -50386,13 +50386,13 @@
         <v>1.08</v>
       </c>
       <c r="Z307">
-        <v>5.39</v>
+        <v>5.34</v>
       </c>
       <c r="AA307">
         <v>1.45</v>
       </c>
       <c r="AB307">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AC307">
         <v>2.04</v>
@@ -50407,7 +50407,7 @@
         <v>1.5</v>
       </c>
       <c r="AG307">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>1.15</v>
       </c>
       <c r="AK307">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O310">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P310">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q310">
         <v>3.7</v>
@@ -50860,10 +50860,10 @@
         <v>3.5</v>
       </c>
       <c r="U310">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V310">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W310">
         <v>1.13</v>
@@ -50912,7 +50912,7 @@
         <v>1.62</v>
       </c>
       <c r="AK310">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51075,7 +51075,7 @@
         <v>1.29</v>
       </c>
       <c r="AK311">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51168,7 +51168,7 @@
         <v>1.73</v>
       </c>
       <c r="O312">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P312">
         <v>4.5</v>
@@ -51201,22 +51201,22 @@
         <v>1.22</v>
       </c>
       <c r="Z312">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AA312">
         <v>1.7</v>
       </c>
       <c r="AB312">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC312">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AD312">
         <v>1.48</v>
       </c>
       <c r="AE312">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF312">
         <v>1.67</v>
@@ -51235,7 +51235,7 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK312">
         <v>2.09</v>
@@ -51491,25 +51491,25 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O314">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P314">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q314">
         <v>2.15</v>
       </c>
       <c r="R314">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S314">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T314">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U314">
         <v>2.44</v>
@@ -51518,10 +51518,10 @@
         <v>1.46</v>
       </c>
       <c r="W314">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X314">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y314">
         <v>1.17</v>
@@ -51536,19 +51536,19 @@
         <v>2.14</v>
       </c>
       <c r="AC314">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD314">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE314">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF314">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG314">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK314">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51657,58 +51657,58 @@
         <v>1.85</v>
       </c>
       <c r="O315">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P315">
         <v>3.4</v>
       </c>
       <c r="Q315">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R315">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="S315">
         <v>1.32</v>
       </c>
       <c r="T315">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U315">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="V315">
         <v>1.44</v>
       </c>
       <c r="W315">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X315">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y315">
         <v>1.26</v>
       </c>
       <c r="Z315">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AA315">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB315">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC315">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD315">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE315">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF315">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG315">
         <v>2.05</v>
@@ -51727,7 +51727,7 @@
         <v>1.22</v>
       </c>
       <c r="AK315">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51980,19 +51980,19 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O317">
         <v>4.33</v>
       </c>
       <c r="P317">
-        <v>6.12</v>
+        <v>5.25</v>
       </c>
       <c r="Q317">
         <v>1.87</v>
       </c>
       <c r="R317">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="S317">
         <v>1.21</v>
@@ -52016,7 +52016,7 @@
         <v>1.11</v>
       </c>
       <c r="Z317">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA317">
         <v>1.44</v>
@@ -52031,7 +52031,7 @@
         <v>1.75</v>
       </c>
       <c r="AE317">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF317">
         <v>1.5</v>
@@ -52143,7 +52143,7 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O318">
         <v>3.25</v>
@@ -52152,16 +52152,16 @@
         <v>2.56</v>
       </c>
       <c r="Q318">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R318">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S318">
         <v>1.36</v>
       </c>
       <c r="T318">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U318">
         <v>2.8</v>
@@ -52170,10 +52170,10 @@
         <v>1.36</v>
       </c>
       <c r="W318">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X318">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y318">
         <v>1.28</v>
@@ -52182,10 +52182,10 @@
         <v>3.08</v>
       </c>
       <c r="AA318">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB318">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AC318">
         <v>3.42</v>
@@ -52194,13 +52194,13 @@
         <v>1.23</v>
       </c>
       <c r="AE318">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF318">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG318">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>4</v>
       </c>
       <c r="P319">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="Q319">
         <v>2.05</v>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK319">
         <v>2.2</v>
@@ -52472,19 +52472,19 @@
         <v>1.91</v>
       </c>
       <c r="O320">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P320">
         <v>3.2</v>
       </c>
       <c r="Q320">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="R320">
         <v>2.45</v>
       </c>
       <c r="S320">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T320">
         <v>3.6</v>
@@ -52496,7 +52496,7 @@
         <v>1.61</v>
       </c>
       <c r="W320">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X320">
         <v>1.03</v>
@@ -52505,7 +52505,7 @@
         <v>1.15</v>
       </c>
       <c r="Z320">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA320">
         <v>1.5</v>
@@ -52517,7 +52517,7 @@
         <v>2.36</v>
       </c>
       <c r="AD320">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE320">
         <v>1.22</v>
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O321">
         <v>4.18</v>
       </c>
       <c r="P321">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="Q321">
         <v>2.49</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.37</v>
       </c>
       <c r="P32">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q32">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="R32">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>2.28</v>
+        <v>2.97</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE32">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.96</v>
       </c>
       <c r="AK32">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O33">
-        <v>3.37</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Q33">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.97</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.96</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>2.05</v>
       </c>
       <c r="Q60">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R60">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T60">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U60">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V60">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AA60">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB60">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC60">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD60">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE60">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF60">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
         <v>1.3</v>
@@ -16452,7 +16452,7 @@
         <v>3.6</v>
       </c>
       <c r="P99">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="Q99">
         <v>2.33</v>
@@ -16482,7 +16482,7 @@
         <v>1.16</v>
       </c>
       <c r="Z99">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA99">
         <v>1.66</v>
@@ -16503,7 +16503,7 @@
         <v>1.57</v>
       </c>
       <c r="AG99">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="O105">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="Q105">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R105">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="S105">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U105">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="V105">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z105">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA105">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB105">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="AC105">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="AD105">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AE105">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG105">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK105">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.42</v>
+        <v>1.37</v>
       </c>
       <c r="O106">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="P106">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="Q106">
-        <v>3.81</v>
+        <v>1.8</v>
       </c>
       <c r="R106">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U106">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AA106">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB106">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="AC106">
-        <v>3.24</v>
+        <v>2.57</v>
       </c>
       <c r="AD106">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AE106">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF106">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AK106">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>3.42</v>
       </c>
       <c r="O107">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q107">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="R107">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S107">
         <v>1.36</v>
       </c>
       <c r="T107">
+        <v>2.88</v>
+      </c>
+      <c r="U107">
         <v>2.7</v>
       </c>
-      <c r="U107">
-        <v>2.77</v>
-      </c>
       <c r="V107">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
         <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z107">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="AA107">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB107">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC107">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AD107">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17916,61 +17916,61 @@
         <v>3.5</v>
       </c>
       <c r="O108">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
         <v>1.82</v>
       </c>
       <c r="Q108">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="R108">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S108">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U108">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V108">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W108">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z108">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AA108">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB108">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC108">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AD108">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG108">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.48</v>
+        <v>2.69</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P121">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q121">
         <v>3</v>
       </c>
       <c r="R121">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S121">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T121">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U121">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="V121">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="W121">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X121">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z121">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="AA121">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="AB121">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AC121">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AE121">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF121">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG121">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.69</v>
+        <v>2.48</v>
       </c>
       <c r="O122">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q122">
         <v>3</v>
       </c>
       <c r="R122">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S122">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T122">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U122">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="V122">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="W122">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z122">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA122">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AB122">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC122">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="AD122">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AE122">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG122">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AK122">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -21701,10 +21701,10 @@
         <v>0</v>
       </c>
       <c r="AA131">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AB131">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC131">
         <v>0</v>
@@ -23125,23 +23125,23 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N140">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="O140">
-        <v>7.15</v>
+        <v>6.15</v>
       </c>
       <c r="P140">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q140">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="R140">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="S140">
         <v>1.19</v>
@@ -23159,28 +23159,28 @@
         <v>1.19</v>
       </c>
       <c r="X140">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
         <v>1.1</v>
       </c>
       <c r="Z140">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA140">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB140">
         <v>2.88</v>
       </c>
       <c r="AC140">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD140">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE140">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF140">
         <v>2.05</v>
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK140">
         <v>5</v>
@@ -23288,17 +23288,17 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N141">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="O141">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="P141">
-        <v>5.4</v>
+        <v>7.25</v>
       </c>
       <c r="Q141">
         <v>1.91</v>
@@ -23307,19 +23307,19 @@
         <v>2.4</v>
       </c>
       <c r="S141">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T141">
         <v>3.45</v>
       </c>
       <c r="U141">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V141">
         <v>1.53</v>
       </c>
       <c r="W141">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X141">
         <v>1.02</v>
@@ -23328,7 +23328,7 @@
         <v>1.18</v>
       </c>
       <c r="Z141">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA141">
         <v>1.62</v>
@@ -23337,16 +23337,16 @@
         <v>2.15</v>
       </c>
       <c r="AC141">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AD141">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AE141">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF141">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG141">
         <v>2</v>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK141">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O142">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P142">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -23488,22 +23488,22 @@
         <v>1.03</v>
       </c>
       <c r="Y142">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z142">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA142">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AB142">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AC142">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD142">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE142">
         <v>1.08</v>
@@ -23528,7 +23528,7 @@
         <v>1.24</v>
       </c>
       <c r="AK142">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23947,10 +23947,10 @@
         <v>6.5</v>
       </c>
       <c r="O145">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P145">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Q145">
         <v>6</v>
@@ -23962,10 +23962,10 @@
         <v>1.22</v>
       </c>
       <c r="T145">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="U145">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V145">
         <v>1.56</v>
@@ -23977,7 +23977,7 @@
         <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z145">
         <v>4.5</v>
@@ -24014,7 +24014,7 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AK145">
         <v>1.08</v>
@@ -24119,7 +24119,7 @@
         <v>4.4</v>
       </c>
       <c r="R146">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S146">
         <v>1.38</v>
@@ -24270,19 +24270,19 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="O147">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P147">
         <v>4.45</v>
       </c>
       <c r="Q147">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R147">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S147">
         <v>1.34</v>
@@ -24306,7 +24306,7 @@
         <v>1.23</v>
       </c>
       <c r="Z147">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA147">
         <v>1.67</v>
@@ -24315,7 +24315,7 @@
         <v>2.15</v>
       </c>
       <c r="AC147">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD147">
         <v>1.44</v>
@@ -24343,7 +24343,7 @@
         <v>1.25</v>
       </c>
       <c r="AK147">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O151">
         <v>4.2</v>
@@ -24946,10 +24946,10 @@
         <v>2.33</v>
       </c>
       <c r="V151">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W151">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X151">
         <v>1.01</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK151">
         <v>2.25</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O177">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P177">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q177">
         <v>4.5</v>
@@ -29181,13 +29181,13 @@
         <v>3.8</v>
       </c>
       <c r="U177">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V177">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W177">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
         <v>1.01</v>
@@ -29196,16 +29196,16 @@
         <v>1.09</v>
       </c>
       <c r="Z177">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA177">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB177">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AC177">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AD177">
         <v>1.6</v>
@@ -29217,7 +29217,7 @@
         <v>1.45</v>
       </c>
       <c r="AG177">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R195">
         <v>2.2</v>
@@ -32112,7 +32112,7 @@
         <v>1.4</v>
       </c>
       <c r="T195">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="U195">
         <v>3.2</v>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK195">
         <v>2.63</v>
@@ -36830,19 +36830,19 @@
         <v>2.14</v>
       </c>
       <c r="Q224">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R224">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S224">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T224">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U224">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V224">
         <v>1.51</v>
@@ -36851,31 +36851,31 @@
         <v>1.1</v>
       </c>
       <c r="X224">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y224">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z224">
         <v>3.9</v>
       </c>
       <c r="AA224">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB224">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC224">
         <v>2.75</v>
       </c>
       <c r="AD224">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE224">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF224">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG224">
         <v>2.25</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O238">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P238">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q238">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="R238">
         <v>1.73</v>
       </c>
       <c r="S238">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="T238">
         <v>2.1</v>
       </c>
       <c r="U238">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="V238">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W238">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X238">
         <v>1.15</v>
       </c>
       <c r="Y238">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="Z238">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA238">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AB238">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC238">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD238">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE238">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF238">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="AG238">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AK238">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
+        <v>2.1</v>
+      </c>
+      <c r="O239">
+        <v>2.65</v>
+      </c>
+      <c r="P239">
+        <v>4.55</v>
+      </c>
+      <c r="Q239">
         <v>2.6</v>
-      </c>
-      <c r="O239">
-        <v>2.7</v>
-      </c>
-      <c r="P239">
-        <v>2.8</v>
-      </c>
-      <c r="Q239">
-        <v>3.3</v>
       </c>
       <c r="R239">
         <v>1.73</v>
       </c>
       <c r="S239">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="T239">
         <v>2.1</v>
       </c>
       <c r="U239">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="V239">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W239">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X239">
         <v>1.15</v>
       </c>
       <c r="Y239">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z239">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA239">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB239">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC239">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD239">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE239">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF239">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="AG239">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AK239">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="O258">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P258">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q258">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="R258">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S258">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T258">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="U258">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="V258">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W258">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X258">
         <v>1.02</v>
       </c>
       <c r="Y258">
+        <v>1.3</v>
+      </c>
+      <c r="Z258">
+        <v>2.97</v>
+      </c>
+      <c r="AA258">
+        <v>2.02</v>
+      </c>
+      <c r="AB258">
+        <v>1.71</v>
+      </c>
+      <c r="AC258">
+        <v>3.48</v>
+      </c>
+      <c r="AD258">
         <v>1.22</v>
       </c>
-      <c r="Z258">
-        <v>4.2</v>
-      </c>
-      <c r="AA258">
-        <v>1.77</v>
-      </c>
-      <c r="AB258">
-        <v>2.05</v>
-      </c>
-      <c r="AC258">
-        <v>2.88</v>
-      </c>
-      <c r="AD258">
-        <v>1.36</v>
-      </c>
       <c r="AE258">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF258">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG258">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK258">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
+        <v>1.83</v>
+      </c>
+      <c r="O259">
+        <v>3.4</v>
+      </c>
+      <c r="P259">
+        <v>3.6</v>
+      </c>
+      <c r="Q259">
         <v>2.25</v>
       </c>
-      <c r="O259">
+      <c r="R259">
+        <v>2.25</v>
+      </c>
+      <c r="S259">
+        <v>1.3</v>
+      </c>
+      <c r="T259">
         <v>3.1</v>
       </c>
-      <c r="P259">
-        <v>2.7</v>
-      </c>
-      <c r="Q259">
-        <v>2.99</v>
-      </c>
-      <c r="R259">
-        <v>2.05</v>
-      </c>
-      <c r="S259">
-        <v>1.39</v>
-      </c>
-      <c r="T259">
-        <v>2.66</v>
-      </c>
       <c r="U259">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="V259">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W259">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X259">
         <v>1.02</v>
       </c>
       <c r="Y259">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z259">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="AA259">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB259">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AC259">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD259">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE259">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF259">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG259">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK259">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -43504,10 +43504,10 @@
         </is>
       </c>
       <c r="N265">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O265">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="P265">
         <v>8</v>
@@ -43525,13 +43525,13 @@
         <v>2.91</v>
       </c>
       <c r="U265">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V265">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W265">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X265">
         <v>1.03</v>
@@ -43549,10 +43549,10 @@
         <v>2</v>
       </c>
       <c r="AC265">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD265">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE265">
         <v>1.11</v>
@@ -43577,7 +43577,7 @@
         <v>1.13</v>
       </c>
       <c r="AK265">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,31 +45460,31 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O277">
         <v>3.25</v>
       </c>
       <c r="P277">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q277">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R277">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="S277">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T277">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U277">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V277">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W277">
         <v>1.06</v>
@@ -45496,28 +45496,28 @@
         <v>1.25</v>
       </c>
       <c r="Z277">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA277">
+        <v>1.93</v>
+      </c>
+      <c r="AB277">
         <v>1.84</v>
       </c>
-      <c r="AB277">
-        <v>1.85</v>
-      </c>
       <c r="AC277">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AD277">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE277">
         <v>1.1</v>
       </c>
       <c r="AF277">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG277">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK277">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,31 +45623,31 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O278">
         <v>3.25</v>
       </c>
       <c r="P278">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q278">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R278">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="S278">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T278">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="U278">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V278">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W278">
         <v>1.06</v>
@@ -45659,28 +45659,28 @@
         <v>1.25</v>
       </c>
       <c r="Z278">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA278">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AB278">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC278">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AD278">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE278">
         <v>1.1</v>
       </c>
       <c r="AF278">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG278">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK278">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O279">
         <v>3.9</v>
       </c>
       <c r="P279">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q279">
         <v>1.96</v>
@@ -45813,16 +45813,16 @@
         <v>1.56</v>
       </c>
       <c r="W279">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X279">
         <v>1.01</v>
       </c>
       <c r="Y279">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z279">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA279">
         <v>1.61</v>
@@ -45831,7 +45831,7 @@
         <v>2.25</v>
       </c>
       <c r="AC279">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AD279">
         <v>1.44</v>
@@ -45840,10 +45840,10 @@
         <v>1.17</v>
       </c>
       <c r="AF279">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG279">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O285">
         <v>3</v>
       </c>
       <c r="P285">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -46837,7 +46837,7 @@
         <v>1.3</v>
       </c>
       <c r="AK285">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47419,10 +47419,10 @@
         <v>2.1</v>
       </c>
       <c r="O289">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P289">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="Q289">
         <v>2.7</v>
@@ -47431,13 +47431,13 @@
         <v>2.31</v>
       </c>
       <c r="S289">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T289">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U289">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V289">
         <v>1.45</v>
@@ -47449,13 +47449,13 @@
         <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z289">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="AA289">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB289">
         <v>1.99</v>
@@ -47464,32 +47464,32 @@
         <v>2.7</v>
       </c>
       <c r="AD289">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE289">
         <v>1.15</v>
       </c>
       <c r="AF289">
+        <v>1.59</v>
+      </c>
+      <c r="AG289">
+        <v>2.38</v>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ289">
+        <v>1.33</v>
+      </c>
+      <c r="AK289">
         <v>1.56</v>
-      </c>
-      <c r="AG289">
-        <v>2.15</v>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ289">
-        <v>1.25</v>
-      </c>
-      <c r="AK289">
-        <v>1.53</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="O291">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P291">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="Q291">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="R291">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="S291">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="T291">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U291">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V291">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W291">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X291">
         <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Z291">
-        <v>3.08</v>
+        <v>4.28</v>
       </c>
       <c r="AA291">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AB291">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="AC291">
-        <v>3.47</v>
+        <v>2.52</v>
       </c>
       <c r="AD291">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE291">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF291">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG291">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AK291">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="O292">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="P292">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="Q292">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R292">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="S292">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="T292">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="U292">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="V292">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W292">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X292">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y292">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z292">
-        <v>4.28</v>
+        <v>3.18</v>
       </c>
       <c r="AA292">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB292">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="AC292">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AD292">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE292">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF292">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AG292">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK292">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48077,10 +48077,10 @@
         <v>4.99</v>
       </c>
       <c r="Q293">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R293">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S293">
         <v>1.3</v>
@@ -48089,10 +48089,10 @@
         <v>3.2</v>
       </c>
       <c r="U293">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V293">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W293">
         <v>1.11</v>
@@ -48101,31 +48101,31 @@
         <v>1.02</v>
       </c>
       <c r="Y293">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z293">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="AA293">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB293">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AC293">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AD293">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE293">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF293">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG293">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>1.11</v>
       </c>
       <c r="AK293">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="O294">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P294">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="Q294">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="R294">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S294">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T294">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="U294">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="V294">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W294">
+        <v>1.08</v>
+      </c>
+      <c r="X294">
         <v>1.02</v>
       </c>
-      <c r="X294">
-        <v>1.04</v>
-      </c>
       <c r="Y294">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z294">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AA294">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB294">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC294">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="AD294">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE294">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF294">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG294">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK294">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48394,25 +48394,25 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O295">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="P295">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="Q295">
         <v>1.67</v>
       </c>
       <c r="R295">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S295">
         <v>1.22</v>
       </c>
       <c r="T295">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U295">
         <v>2.1</v>
@@ -48427,10 +48427,10 @@
         <v>1.02</v>
       </c>
       <c r="Y295">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z295">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="AA295">
         <v>1.4</v>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AK295">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="O297">
         <v>4.8</v>
       </c>
       <c r="P297">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="Q297">
         <v>1.75</v>
@@ -48753,7 +48753,7 @@
         <v>1.01</v>
       </c>
       <c r="Y297">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z297">
         <v>4.69</v>
@@ -48762,7 +48762,7 @@
         <v>1.54</v>
       </c>
       <c r="AB297">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AC297">
         <v>2.32</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="O298">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="P298">
-        <v>5.9</v>
+        <v>5.35</v>
       </c>
       <c r="Q298">
         <v>1.83</v>
@@ -48901,7 +48901,7 @@
         <v>1.26</v>
       </c>
       <c r="T298">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U298">
         <v>2.38</v>
@@ -48910,7 +48910,7 @@
         <v>1.51</v>
       </c>
       <c r="W298">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X298">
         <v>1.01</v>
@@ -48919,13 +48919,13 @@
         <v>1.2</v>
       </c>
       <c r="Z298">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="AA298">
         <v>1.61</v>
       </c>
       <c r="AB298">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC298">
         <v>2.46</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O307">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P307">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="Q307">
         <v>2.04</v>
@@ -50374,10 +50374,10 @@
         <v>2.05</v>
       </c>
       <c r="V307">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W307">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X307">
         <v>1.01</v>
@@ -50688,7 +50688,7 @@
         <v>2.34</v>
       </c>
       <c r="R309">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S309">
         <v>1.4</v>
@@ -50733,7 +50733,7 @@
         <v>1.95</v>
       </c>
       <c r="AG309">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>3.75</v>
       </c>
       <c r="P314">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q314">
         <v>2.15</v>
@@ -51506,7 +51506,7 @@
         <v>2.24</v>
       </c>
       <c r="S314">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T314">
         <v>3.2</v>
@@ -51536,10 +51536,10 @@
         <v>2.14</v>
       </c>
       <c r="AC314">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD314">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE314">
         <v>1.12</v>
@@ -51548,7 +51548,7 @@
         <v>1.7</v>
       </c>
       <c r="AG314">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK314">
         <v>1.95</v>
@@ -51654,10 +51654,10 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="O315">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P315">
         <v>3.4</v>
@@ -51687,7 +51687,7 @@
         <v>1.01</v>
       </c>
       <c r="Y315">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z315">
         <v>3.5</v>
@@ -51708,7 +51708,7 @@
         <v>1.13</v>
       </c>
       <c r="AF315">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG315">
         <v>2.05</v>
@@ -52143,7 +52143,7 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O318">
         <v>3.25</v>
@@ -52152,10 +52152,10 @@
         <v>2.56</v>
       </c>
       <c r="Q318">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R318">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S318">
         <v>1.36</v>
@@ -52173,7 +52173,7 @@
         <v>1.08</v>
       </c>
       <c r="X318">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y318">
         <v>1.28</v>
@@ -52216,7 +52216,7 @@
         <v>1.29</v>
       </c>
       <c r="AK318">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,64 +52469,64 @@
         </is>
       </c>
       <c r="N320">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O320">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="P320">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q320">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="R320">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S320">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T320">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="U320">
         <v>2.18</v>
       </c>
       <c r="V320">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W320">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X320">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y320">
         <v>1.15</v>
       </c>
       <c r="Z320">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA320">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB320">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC320">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AD320">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AE320">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF320">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG320">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK320">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,64 +52632,64 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O321">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="P321">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Q321">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="R321">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S321">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T321">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="U321">
         <v>2.18</v>
       </c>
       <c r="V321">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W321">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X321">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y321">
         <v>1.15</v>
       </c>
       <c r="Z321">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA321">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB321">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC321">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AD321">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AE321">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF321">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG321">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK321">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL321">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O3">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="P3">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P4">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB4">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O5">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>3.05</v>
+        <v>3.47</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1157,28 +1157,28 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AA5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB5">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG5">
         <v>2.25</v>
@@ -1197,7 +1197,7 @@
         <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P7">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R7">
         <v>2.3</v>
@@ -1489,10 +1489,10 @@
         <v>4.45</v>
       </c>
       <c r="AA7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB7">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AC7">
         <v>2.46</v>
@@ -1501,10 +1501,10 @@
         <v>1.43</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
         <v>2.39</v>
@@ -1523,7 +1523,7 @@
         <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>3.46</v>
       </c>
       <c r="P9">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -1791,19 +1791,19 @@
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U9">
         <v>3.3</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1.08</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P13">
         <v>3.3</v>
@@ -2452,7 +2452,7 @@
         <v>3.65</v>
       </c>
       <c r="V13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
         <v>1.01</v>
@@ -2470,10 +2470,10 @@
         <v>2.39</v>
       </c>
       <c r="AB13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AD13">
         <v>1.17</v>
@@ -3898,16 +3898,16 @@
         <v>2.29</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q22">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.3</v>
@@ -3916,7 +3916,7 @@
         <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
         <v>1.42</v>
@@ -3946,7 +3946,7 @@
         <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
         <v>1.65</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
         <v>3.4</v>
@@ -4100,10 +4100,10 @@
         <v>2.08</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC23">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="AD23">
         <v>1.18</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
         <v>1.67</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
         <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="Q24">
         <v>2.8</v>
@@ -4236,7 +4236,7 @@
         <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
         <v>2.88</v>
@@ -4251,34 +4251,34 @@
         <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="AA24">
         <v>1.85</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AD24">
         <v>1.35</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4387,10 +4387,10 @@
         <v>1.58</v>
       </c>
       <c r="O25">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="P25">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -4405,13 +4405,13 @@
         <v>3.55</v>
       </c>
       <c r="U25">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P26">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q26">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z26">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AB26">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
-        <v>2.76</v>
+        <v>3.44</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="O27">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="Q27">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U27">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z27">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA27">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="AB27">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="AC27">
-        <v>3.44</v>
+        <v>4.5</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
+        <v>3.25</v>
+      </c>
+      <c r="Q29">
+        <v>2.5</v>
+      </c>
+      <c r="R29">
+        <v>2.3</v>
+      </c>
+      <c r="S29">
+        <v>1.33</v>
+      </c>
+      <c r="T29">
+        <v>3.04</v>
+      </c>
+      <c r="U29">
+        <v>2.4</v>
+      </c>
+      <c r="V29">
+        <v>1.46</v>
+      </c>
+      <c r="W29">
+        <v>1.08</v>
+      </c>
+      <c r="X29">
+        <v>1.03</v>
+      </c>
+      <c r="Y29">
+        <v>1.18</v>
+      </c>
+      <c r="Z29">
+        <v>4.2</v>
+      </c>
+      <c r="AA29">
+        <v>1.7</v>
+      </c>
+      <c r="AB29">
+        <v>2.21</v>
+      </c>
+      <c r="AC29">
+        <v>2.76</v>
+      </c>
+      <c r="AD29">
+        <v>1.4</v>
+      </c>
+      <c r="AE29">
+        <v>1.15</v>
+      </c>
+      <c r="AF29">
+        <v>1.6</v>
+      </c>
+      <c r="AG29">
         <v>2.25</v>
       </c>
-      <c r="Q29">
-        <v>3.4</v>
-      </c>
-      <c r="R29">
-        <v>1.9</v>
-      </c>
-      <c r="S29">
-        <v>1.44</v>
-      </c>
-      <c r="T29">
-        <v>2.63</v>
-      </c>
-      <c r="U29">
-        <v>3.2</v>
-      </c>
-      <c r="V29">
-        <v>1.3</v>
-      </c>
-      <c r="W29">
-        <v>1.06</v>
-      </c>
-      <c r="X29">
-        <v>1.07</v>
-      </c>
-      <c r="Y29">
-        <v>1.45</v>
-      </c>
-      <c r="Z29">
-        <v>2.7</v>
-      </c>
-      <c r="AA29">
-        <v>2.31</v>
-      </c>
-      <c r="AB29">
-        <v>1.59</v>
-      </c>
-      <c r="AC29">
-        <v>4.5</v>
-      </c>
-      <c r="AD29">
-        <v>1.18</v>
-      </c>
-      <c r="AE29">
-        <v>1.06</v>
-      </c>
-      <c r="AF29">
-        <v>1.95</v>
-      </c>
-      <c r="AG29">
-        <v>1.87</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O32">
-        <v>3.37</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Q32">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S32">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.97</v>
+        <v>2.28</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD32">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.96</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.37</v>
       </c>
       <c r="P33">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q33">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="R33">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>2.28</v>
+        <v>2.97</v>
       </c>
       <c r="V33">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC33">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.96</v>
       </c>
       <c r="AK33">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.18</v>
+        <v>3.43</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="Q34">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R34">
         <v>2.18</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U34">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="V34">
         <v>1.33</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5899,7 +5899,7 @@
         <v>3.75</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
@@ -5908,7 +5908,7 @@
         <v>1.82</v>
       </c>
       <c r="AG34">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.9</v>
+        <v>3.42</v>
       </c>
       <c r="O105">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q105">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="R105">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S105">
         <v>1.36</v>
       </c>
       <c r="T105">
+        <v>2.88</v>
+      </c>
+      <c r="U105">
         <v>2.7</v>
       </c>
-      <c r="U105">
-        <v>2.77</v>
-      </c>
       <c r="V105">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
         <v>1.05</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z105">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="AA105">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB105">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC105">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AD105">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,65 +17750,65 @@
         </is>
       </c>
       <c r="N107">
-        <v>3.42</v>
+        <v>1.9</v>
       </c>
       <c r="O107">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P107">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="Q107">
-        <v>3.81</v>
+        <v>2.5</v>
       </c>
       <c r="R107">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S107">
         <v>1.36</v>
       </c>
       <c r="T107">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U107">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W107">
         <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z107">
+        <v>3.65</v>
+      </c>
+      <c r="AA107">
+        <v>1.85</v>
+      </c>
+      <c r="AB107">
+        <v>1.89</v>
+      </c>
+      <c r="AC107">
         <v>3</v>
       </c>
-      <c r="AA107">
+      <c r="AD107">
+        <v>1.32</v>
+      </c>
+      <c r="AE107">
+        <v>1.07</v>
+      </c>
+      <c r="AF107">
+        <v>1.77</v>
+      </c>
+      <c r="AG107">
         <v>2</v>
       </c>
-      <c r="AB107">
-        <v>1.78</v>
-      </c>
-      <c r="AC107">
-        <v>3.24</v>
-      </c>
-      <c r="AD107">
-        <v>1.3</v>
-      </c>
-      <c r="AE107">
-        <v>1.06</v>
-      </c>
-      <c r="AF107">
-        <v>1.8</v>
-      </c>
-      <c r="AG107">
-        <v>1.95</v>
-      </c>
       <c r="AH107" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK107">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -23125,7 +23125,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N140">
@@ -23288,7 +23288,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N141">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,31 +45460,31 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O277">
         <v>3.25</v>
       </c>
       <c r="P277">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q277">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R277">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="S277">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T277">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="U277">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V277">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W277">
         <v>1.06</v>
@@ -45496,28 +45496,28 @@
         <v>1.25</v>
       </c>
       <c r="Z277">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA277">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AB277">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC277">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AD277">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE277">
         <v>1.1</v>
       </c>
       <c r="AF277">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG277">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK277">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,31 +45623,31 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O278">
         <v>3.25</v>
       </c>
       <c r="P278">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q278">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R278">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="S278">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T278">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U278">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V278">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W278">
         <v>1.06</v>
@@ -45659,28 +45659,28 @@
         <v>1.25</v>
       </c>
       <c r="Z278">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA278">
+        <v>1.93</v>
+      </c>
+      <c r="AB278">
         <v>1.84</v>
       </c>
-      <c r="AB278">
-        <v>1.85</v>
-      </c>
       <c r="AC278">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AD278">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE278">
         <v>1.1</v>
       </c>
       <c r="AF278">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG278">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK278">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.55</v>
+        <v>2.53</v>
       </c>
       <c r="O293">
-        <v>4.17</v>
+        <v>3</v>
       </c>
       <c r="P293">
-        <v>4.99</v>
+        <v>2.23</v>
       </c>
       <c r="Q293">
-        <v>2.1</v>
+        <v>3.54</v>
       </c>
       <c r="R293">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S293">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T293">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U293">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V293">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W293">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X293">
         <v>1.02</v>
       </c>
       <c r="Y293">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z293">
-        <v>3.84</v>
+        <v>3.08</v>
       </c>
       <c r="AA293">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB293">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AC293">
-        <v>2.48</v>
+        <v>3.47</v>
       </c>
       <c r="AD293">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE293">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF293">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG293">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AK293">
-        <v>2.16</v>
+        <v>1.35</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.53</v>
+        <v>1.55</v>
       </c>
       <c r="O294">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="P294">
-        <v>2.23</v>
+        <v>4.99</v>
       </c>
       <c r="Q294">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="R294">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S294">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T294">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U294">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V294">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W294">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X294">
         <v>1.02</v>
       </c>
       <c r="Y294">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z294">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="AA294">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AB294">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AC294">
-        <v>3.47</v>
+        <v>2.48</v>
       </c>
       <c r="AD294">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE294">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF294">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG294">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AK294">
-        <v>1.35</v>
+        <v>2.16</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G319">
@@ -52306,64 +52306,64 @@
         </is>
       </c>
       <c r="N319">
+        <v>1.91</v>
+      </c>
+      <c r="O319">
+        <v>3.5</v>
+      </c>
+      <c r="P319">
+        <v>3.2</v>
+      </c>
+      <c r="Q319">
+        <v>2.44</v>
+      </c>
+      <c r="R319">
+        <v>2.45</v>
+      </c>
+      <c r="S319">
+        <v>1.26</v>
+      </c>
+      <c r="T319">
+        <v>3.6</v>
+      </c>
+      <c r="U319">
+        <v>2.18</v>
+      </c>
+      <c r="V319">
         <v>1.61</v>
       </c>
-      <c r="O319">
-        <v>4</v>
-      </c>
-      <c r="P319">
-        <v>4.68</v>
-      </c>
-      <c r="Q319">
-        <v>2.05</v>
-      </c>
-      <c r="R319">
-        <v>2.7</v>
-      </c>
-      <c r="S319">
-        <v>1.2</v>
-      </c>
-      <c r="T319">
-        <v>4</v>
-      </c>
-      <c r="U319">
-        <v>2.05</v>
-      </c>
-      <c r="V319">
-        <v>1.74</v>
-      </c>
       <c r="W319">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X319">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y319">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z319">
-        <v>6.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA319">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB319">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC319">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AD319">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AE319">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF319">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG319">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK319">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,64 +52469,64 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="O320">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P320">
-        <v>3.2</v>
+        <v>4.68</v>
       </c>
       <c r="Q320">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="R320">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S320">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T320">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U320">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="V320">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="W320">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X320">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y320">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z320">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA320">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB320">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC320">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AD320">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AE320">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF320">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG320">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK320">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AL320">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O12">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="P12">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2286,10 +2286,10 @@
         <v>2.85</v>
       </c>
       <c r="U12">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2298,31 +2298,31 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AG12">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.98</v>
+        <v>2.45</v>
       </c>
       <c r="O27">
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="R27">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U27">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
         <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA27">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AB27">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AC27">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="AD27">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG27">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
         <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="U28">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>1.74</v>
+        <v>2.21</v>
       </c>
       <c r="AC28">
-        <v>3.76</v>
+        <v>2.76</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="V29">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
+        <v>1.45</v>
+      </c>
+      <c r="Z29">
+        <v>2.7</v>
+      </c>
+      <c r="AA29">
+        <v>2.31</v>
+      </c>
+      <c r="AB29">
+        <v>1.59</v>
+      </c>
+      <c r="AC29">
+        <v>4.5</v>
+      </c>
+      <c r="AD29">
         <v>1.18</v>
       </c>
-      <c r="Z29">
-        <v>4.2</v>
-      </c>
-      <c r="AA29">
-        <v>1.7</v>
-      </c>
-      <c r="AB29">
-        <v>2.21</v>
-      </c>
-      <c r="AC29">
-        <v>2.76</v>
-      </c>
-      <c r="AD29">
-        <v>1.4</v>
-      </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.37</v>
       </c>
       <c r="P32">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q32">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="R32">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>2.28</v>
+        <v>2.97</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE32">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.96</v>
       </c>
       <c r="AK32">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O33">
-        <v>3.37</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Q33">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.97</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.96</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="P65">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q65">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="R65">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
         <v>1.41</v>
@@ -10937,16 +10937,16 @@
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z65">
         <v>2.92</v>
       </c>
       <c r="AA65">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AB65">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC65">
         <v>3.5</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AK65">
         <v>1.54</v>
@@ -14001,16 +14001,16 @@
         </is>
       </c>
       <c r="N84">
+        <v>2.6</v>
+      </c>
+      <c r="O84">
         <v>2.7</v>
       </c>
-      <c r="O84">
-        <v>2.64</v>
-      </c>
       <c r="P84">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="Q84">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R84">
         <v>1.82</v>
@@ -14019,10 +14019,10 @@
         <v>1.72</v>
       </c>
       <c r="T84">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U84">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V84">
         <v>1.15</v>
@@ -14034,31 +14034,31 @@
         <v>1.16</v>
       </c>
       <c r="Y84">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z84">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AA84">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AB84">
         <v>1.36</v>
       </c>
       <c r="AC84">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="AD84">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF84">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG84">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AK84">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="O106">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="P106">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="Q106">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R106">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U106">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="V106">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W106">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X106">
         <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA106">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB106">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="AC106">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="AD106">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AE106">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG106">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK106">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O107">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="P107">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="Q107">
+        <v>1.8</v>
+      </c>
+      <c r="R107">
         <v>2.5</v>
       </c>
-      <c r="R107">
-        <v>2.08</v>
-      </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="U107">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="V107">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA107">
+        <v>1.65</v>
+      </c>
+      <c r="AB107">
+        <v>2.14</v>
+      </c>
+      <c r="AC107">
+        <v>2.57</v>
+      </c>
+      <c r="AD107">
+        <v>1.48</v>
+      </c>
+      <c r="AE107">
+        <v>1.17</v>
+      </c>
+      <c r="AF107">
         <v>1.85</v>
       </c>
-      <c r="AB107">
-        <v>1.89</v>
-      </c>
-      <c r="AC107">
-        <v>3</v>
-      </c>
-      <c r="AD107">
-        <v>1.32</v>
-      </c>
-      <c r="AE107">
-        <v>1.07</v>
-      </c>
-      <c r="AF107">
-        <v>1.77</v>
-      </c>
       <c r="AG107">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK107">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O129">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P129">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21499,43 +21499,43 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="O130">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P130">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
       </c>
       <c r="R130">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S130">
         <v>1.22</v>
       </c>
       <c r="T130">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U130">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V130">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W130">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X130">
         <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z130">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA130">
         <v>1.44</v>
@@ -21544,19 +21544,19 @@
         <v>2.63</v>
       </c>
       <c r="AC130">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD130">
         <v>1.6</v>
       </c>
       <c r="AE130">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF130">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG130">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -23125,68 +23125,68 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N140">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="O140">
-        <v>6.15</v>
+        <v>5.8</v>
       </c>
       <c r="P140">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q140">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="R140">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S140">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="U140">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="V140">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W140">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X140">
         <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z140">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA140">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB140">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC140">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD140">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE140">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF140">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG140">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK140">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23288,7 +23288,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N141">
@@ -23301,52 +23301,52 @@
         <v>7.25</v>
       </c>
       <c r="Q141">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="R141">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S141">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T141">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="U141">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V141">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W141">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X141">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z141">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA141">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AB141">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AC141">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AD141">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE141">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF141">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG141">
         <v>2</v>
@@ -23365,7 +23365,7 @@
         <v>1.14</v>
       </c>
       <c r="AK141">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23464,22 +23464,22 @@
         <v>2.7</v>
       </c>
       <c r="Q142">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R142">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S142">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T142">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U142">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V142">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W142">
         <v>1.1</v>
@@ -23494,10 +23494,10 @@
         <v>3.5</v>
       </c>
       <c r="AA142">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB142">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC142">
         <v>2.97</v>
@@ -23506,7 +23506,7 @@
         <v>1.3</v>
       </c>
       <c r="AE142">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF142">
         <v>1.54</v>
@@ -23528,7 +23528,7 @@
         <v>1.24</v>
       </c>
       <c r="AK142">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23621,10 +23621,10 @@
         <v>2.5</v>
       </c>
       <c r="O143">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P143">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -25746,55 +25746,55 @@
         <v>0</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE156">
         <v>0</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T157">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U157">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V157">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X157">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y157">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z157">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE157">
         <v>0</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AG157">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK157">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26398,19 +26398,19 @@
         <v>2.8</v>
       </c>
       <c r="Q160">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R160">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="S160">
         <v>1.44</v>
       </c>
       <c r="T160">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="U160">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="V160">
         <v>1.33</v>
@@ -26425,13 +26425,13 @@
         <v>1.32</v>
       </c>
       <c r="Z160">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA160">
         <v>2.08</v>
       </c>
       <c r="AB160">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC160">
         <v>3.5</v>
@@ -26440,7 +26440,7 @@
         <v>1.26</v>
       </c>
       <c r="AE160">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF160">
         <v>1.82</v>
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X162">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26887,16 +26887,16 @@
         <v>2.15</v>
       </c>
       <c r="Q163">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R163">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S163">
         <v>1.33</v>
       </c>
       <c r="T163">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="U163">
         <v>2.6</v>
@@ -26905,22 +26905,22 @@
         <v>1.4</v>
       </c>
       <c r="W163">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X163">
         <v>1</v>
       </c>
       <c r="Y163">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z163">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="AA163">
         <v>1.79</v>
       </c>
       <c r="AB163">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC163">
         <v>2.88</v>
@@ -26935,7 +26935,7 @@
         <v>1.64</v>
       </c>
       <c r="AG163">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK163">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27080,10 +27080,10 @@
         <v>0</v>
       </c>
       <c r="AA164">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB164">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC164">
         <v>0</v>
@@ -27216,7 +27216,7 @@
         <v>2.66</v>
       </c>
       <c r="R165">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S165">
         <v>1.44</v>
@@ -27376,16 +27376,16 @@
         <v>0</v>
       </c>
       <c r="Q166">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R166">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S166">
         <v>1.44</v>
       </c>
       <c r="T166">
-        <v>2.47</v>
+        <v>2.06</v>
       </c>
       <c r="U166">
         <v>3.14</v>
@@ -27397,7 +27397,7 @@
         <v>1.04</v>
       </c>
       <c r="X166">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y166">
         <v>1.36</v>
@@ -27406,16 +27406,16 @@
         <v>2.7</v>
       </c>
       <c r="AA166">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AB166">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC166">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD166">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE166">
         <v>1.02</v>
@@ -27440,7 +27440,7 @@
         <v>1.28</v>
       </c>
       <c r="AK166">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27539,16 +27539,16 @@
         <v>0</v>
       </c>
       <c r="Q167">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R167">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S167">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T167">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="U167">
         <v>3.12</v>
@@ -27557,10 +27557,10 @@
         <v>1.29</v>
       </c>
       <c r="W167">
+        <v>1.05</v>
+      </c>
+      <c r="X167">
         <v>1.04</v>
-      </c>
-      <c r="X167">
-        <v>1.02</v>
       </c>
       <c r="Y167">
         <v>1.35</v>
@@ -27569,19 +27569,19 @@
         <v>2.74</v>
       </c>
       <c r="AA167">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB167">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC167">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AD167">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE167">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF167">
         <v>1.86</v>
@@ -27702,22 +27702,22 @@
         <v>2.05</v>
       </c>
       <c r="Q168">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R168">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="S168">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T168">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U168">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="V168">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W168">
         <v>1.07</v>
@@ -27726,16 +27726,16 @@
         <v>1</v>
       </c>
       <c r="Y168">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z168">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AA168">
         <v>1.89</v>
       </c>
       <c r="AB168">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC168">
         <v>3.2</v>
@@ -27750,7 +27750,7 @@
         <v>1.7</v>
       </c>
       <c r="AG168">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AK168">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O169">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="P169">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q169">
         <v>2.6</v>
@@ -27877,13 +27877,13 @@
         <v>3.34</v>
       </c>
       <c r="U169">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V169">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W169">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X169">
         <v>1.03</v>
@@ -27895,13 +27895,13 @@
         <v>4.8</v>
       </c>
       <c r="AA169">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB169">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC169">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AD169">
         <v>1.57</v>
@@ -27913,7 +27913,7 @@
         <v>1.44</v>
       </c>
       <c r="AG169">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK169">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O170">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P170">
         <v>3.3</v>
       </c>
       <c r="Q170">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R170">
         <v>1.95</v>
       </c>
       <c r="S170">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T170">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="U170">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="V170">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W170">
         <v>1.04</v>
       </c>
       <c r="X170">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y170">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="Z170">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AA170">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="AB170">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AC170">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD170">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE170">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF170">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AG170">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK170">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="O182">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P182">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="Q182">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="R182">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="S182">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T182">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="U182">
         <v>3.2</v>
       </c>
       <c r="V182">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W182">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X182">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y182">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z182">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA182">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB182">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC182">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD182">
         <v>1.2</v>
       </c>
       <c r="AE182">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF182">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG182">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK182">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30138,61 +30138,61 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="O183">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P183">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="Q183">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R183">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S183">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T183">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="U183">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V183">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W183">
         <v>1.04</v>
       </c>
       <c r="X183">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z183">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AA183">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB183">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC183">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AD183">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE183">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF183">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AG183">
         <v>1.67</v>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK183">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30304,28 +30304,28 @@
         <v>2.3</v>
       </c>
       <c r="O184">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P184">
         <v>2.9</v>
       </c>
       <c r="Q184">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R184">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S184">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T184">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U184">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V184">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W184">
         <v>1.01</v>
@@ -30334,31 +30334,31 @@
         <v>1.04</v>
       </c>
       <c r="Y184">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z184">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="AA184">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AB184">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC184">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AD184">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE184">
         <v>1.02</v>
       </c>
       <c r="AF184">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG184">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK184">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30464,10 +30464,10 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O185">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P185">
         <v>2.2</v>
@@ -30476,43 +30476,43 @@
         <v>3.55</v>
       </c>
       <c r="R185">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S185">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T185">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U185">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="V185">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W185">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X185">
         <v>1.03</v>
       </c>
       <c r="Y185">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z185">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA185">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB185">
         <v>1.94</v>
       </c>
       <c r="AC185">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AD185">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE185">
         <v>1.13</v>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AK185">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -31442,16 +31442,16 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O191">
-        <v>5.1</v>
+        <v>5.55</v>
       </c>
       <c r="P191">
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="Q191">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R191">
         <v>3</v>
@@ -31460,16 +31460,16 @@
         <v>1.18</v>
       </c>
       <c r="T191">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U191">
         <v>1.85</v>
       </c>
       <c r="V191">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W191">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X191">
         <v>1.01</v>
@@ -31481,13 +31481,13 @@
         <v>7.5</v>
       </c>
       <c r="AA191">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB191">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AC191">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD191">
         <v>1.9</v>
@@ -31499,7 +31499,7 @@
         <v>1.53</v>
       </c>
       <c r="AG191">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AK191">
         <v>3.25</v>
@@ -31931,58 +31931,58 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O194">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="P194">
         <v>10</v>
       </c>
       <c r="Q194">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R194">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S194">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T194">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U194">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V194">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W194">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
         <v>1.13</v>
       </c>
       <c r="Z194">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA194">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB194">
         <v>2.62</v>
       </c>
       <c r="AC194">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AD194">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE194">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF194">
         <v>1.91</v>
@@ -32103,49 +32103,49 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="R195">
         <v>2.2</v>
       </c>
       <c r="S195">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T195">
         <v>2.53</v>
       </c>
       <c r="U195">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="V195">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W195">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X195">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
         <v>1.36</v>
       </c>
       <c r="Z195">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA195">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AB195">
         <v>1.63</v>
       </c>
       <c r="AC195">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD195">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE195">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF195">
         <v>2.25</v>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK195">
         <v>2.63</v>
@@ -33081,55 +33081,55 @@
         <v>0</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33235,7 +33235,7 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O202">
         <v>2.95</v>
@@ -33250,37 +33250,37 @@
         <v>1.98</v>
       </c>
       <c r="S202">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T202">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U202">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="V202">
         <v>1.22</v>
       </c>
       <c r="W202">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X202">
         <v>1.11</v>
       </c>
       <c r="Y202">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z202">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AA202">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AB202">
         <v>1.45</v>
       </c>
       <c r="AC202">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="AD202">
         <v>1.1</v>
@@ -33289,7 +33289,7 @@
         <v>1</v>
       </c>
       <c r="AF202">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG202">
         <v>1.59</v>
@@ -33308,7 +33308,7 @@
         <v>1.3</v>
       </c>
       <c r="AK202">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="O203">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P203">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q203">
         <v>6.5</v>
@@ -33416,43 +33416,43 @@
         <v>1.44</v>
       </c>
       <c r="T203">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="U203">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="V203">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W203">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X203">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y203">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z203">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA203">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AB203">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC203">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="AD203">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE203">
         <v>1.07</v>
       </c>
       <c r="AF203">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG203">
         <v>1.57</v>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK203">
         <v>1.04</v>
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -36006,58 +36006,58 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O219">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P219">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="Q219">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R219">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S219">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T219">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U219">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V219">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W219">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X219">
         <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z219">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA219">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB219">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AC219">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AD219">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE219">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF219">
         <v>1.83</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK219">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36169,19 +36169,19 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O220">
         <v>3.55</v>
       </c>
       <c r="P220">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q220">
         <v>3</v>
       </c>
       <c r="R220">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="S220">
         <v>1.25</v>
@@ -36190,56 +36190,56 @@
         <v>3.6</v>
       </c>
       <c r="U220">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V220">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W220">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X220">
         <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z220">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA220">
         <v>1.6</v>
       </c>
       <c r="AB220">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC220">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD220">
         <v>1.5</v>
       </c>
       <c r="AE220">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF220">
+        <v>1.44</v>
+      </c>
+      <c r="AG220">
+        <v>2.45</v>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ220">
         <v>1.5</v>
-      </c>
-      <c r="AG220">
-        <v>2.4</v>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ220">
-        <v>1.51</v>
       </c>
       <c r="AK220">
         <v>1.44</v>
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S227">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T227">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U227">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V227">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W227">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y227">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z227">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA227">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB227">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC227">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD227">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK227">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
+        <v>2.1</v>
+      </c>
+      <c r="O238">
+        <v>2.65</v>
+      </c>
+      <c r="P238">
+        <v>4.55</v>
+      </c>
+      <c r="Q238">
         <v>2.6</v>
-      </c>
-      <c r="O238">
-        <v>2.7</v>
-      </c>
-      <c r="P238">
-        <v>2.8</v>
-      </c>
-      <c r="Q238">
-        <v>3.3</v>
       </c>
       <c r="R238">
         <v>1.73</v>
       </c>
       <c r="S238">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="T238">
         <v>2.1</v>
       </c>
       <c r="U238">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="V238">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W238">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X238">
         <v>1.15</v>
       </c>
       <c r="Y238">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z238">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA238">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB238">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC238">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD238">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE238">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="AG238">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AK238">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O239">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P239">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q239">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="R239">
         <v>1.73</v>
       </c>
       <c r="S239">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="T239">
         <v>2.1</v>
       </c>
       <c r="U239">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="V239">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W239">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X239">
         <v>1.15</v>
       </c>
       <c r="Y239">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="Z239">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA239">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AB239">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC239">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD239">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE239">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF239">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="AG239">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AK239">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39918,10 +39918,10 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O243">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P243">
         <v>3.8</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="O253">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P253">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
+        <v>1.83</v>
+      </c>
+      <c r="O258">
+        <v>3.4</v>
+      </c>
+      <c r="P258">
+        <v>3.6</v>
+      </c>
+      <c r="Q258">
         <v>2.25</v>
       </c>
-      <c r="O258">
+      <c r="R258">
+        <v>2.25</v>
+      </c>
+      <c r="S258">
+        <v>1.3</v>
+      </c>
+      <c r="T258">
         <v>3.1</v>
       </c>
-      <c r="P258">
-        <v>2.7</v>
-      </c>
-      <c r="Q258">
-        <v>2.99</v>
-      </c>
-      <c r="R258">
-        <v>2.05</v>
-      </c>
-      <c r="S258">
-        <v>1.39</v>
-      </c>
-      <c r="T258">
-        <v>2.66</v>
-      </c>
       <c r="U258">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="V258">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W258">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X258">
         <v>1.02</v>
       </c>
       <c r="Y258">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z258">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="AA258">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB258">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AC258">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD258">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE258">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF258">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG258">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK258">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="O259">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P259">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q259">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="R259">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S259">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T259">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="U259">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="V259">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W259">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X259">
         <v>1.02</v>
       </c>
       <c r="Y259">
+        <v>1.3</v>
+      </c>
+      <c r="Z259">
+        <v>2.97</v>
+      </c>
+      <c r="AA259">
+        <v>2.02</v>
+      </c>
+      <c r="AB259">
+        <v>1.71</v>
+      </c>
+      <c r="AC259">
+        <v>3.48</v>
+      </c>
+      <c r="AD259">
         <v>1.22</v>
       </c>
-      <c r="Z259">
-        <v>4.2</v>
-      </c>
-      <c r="AA259">
-        <v>1.77</v>
-      </c>
-      <c r="AB259">
-        <v>2.05</v>
-      </c>
-      <c r="AC259">
-        <v>2.88</v>
-      </c>
-      <c r="AD259">
-        <v>1.36</v>
-      </c>
       <c r="AE259">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF259">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG259">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK259">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42689,31 +42689,31 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O260">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P260">
-        <v>6.54</v>
+        <v>5.5</v>
       </c>
       <c r="Q260">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R260">
         <v>2.25</v>
       </c>
       <c r="S260">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T260">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U260">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V260">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W260">
         <v>1.06</v>
@@ -42722,31 +42722,31 @@
         <v>1.03</v>
       </c>
       <c r="Y260">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z260">
         <v>3.3</v>
       </c>
       <c r="AA260">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB260">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC260">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD260">
         <v>1.25</v>
       </c>
       <c r="AE260">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF260">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG260">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK260">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43667,61 +43667,61 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O266">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="P266">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="Q266">
+        <v>3.16</v>
+      </c>
+      <c r="R266">
+        <v>1.88</v>
+      </c>
+      <c r="S266">
+        <v>1.45</v>
+      </c>
+      <c r="T266">
+        <v>2.58</v>
+      </c>
+      <c r="U266">
         <v>3.12</v>
-      </c>
-      <c r="R266">
-        <v>1.94</v>
-      </c>
-      <c r="S266">
-        <v>1.43</v>
-      </c>
-      <c r="T266">
-        <v>2.75</v>
-      </c>
-      <c r="U266">
-        <v>3.04</v>
       </c>
       <c r="V266">
         <v>1.3</v>
       </c>
       <c r="W266">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X266">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y266">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z266">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA266">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB266">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AC266">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AD266">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE266">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF266">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG266">
         <v>1.85</v>
@@ -43740,7 +43740,7 @@
         <v>1.3</v>
       </c>
       <c r="AK266">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43830,28 +43830,28 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O267">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P267">
-        <v>4.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q267">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R267">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S267">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T267">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U267">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V267">
         <v>1.33</v>
@@ -43860,34 +43860,34 @@
         <v>1.06</v>
       </c>
       <c r="X267">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y267">
         <v>1.3</v>
       </c>
       <c r="Z267">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA267">
         <v>2.1</v>
       </c>
       <c r="AB267">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC267">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD267">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE267">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF267">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG267">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK267">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44319,16 +44319,16 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O270">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P270">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="Q270">
-        <v>3.04</v>
+        <v>3.29</v>
       </c>
       <c r="R270">
         <v>1.91</v>
@@ -44340,22 +44340,22 @@
         <v>2.34</v>
       </c>
       <c r="U270">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V270">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X270">
         <v>1.05</v>
       </c>
       <c r="Y270">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Z270">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AA270">
         <v>2.38</v>
@@ -44364,19 +44364,19 @@
         <v>1.57</v>
       </c>
       <c r="AC270">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD270">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE270">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF270">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AG270">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK270">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="O271">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P271">
-        <v>4.55</v>
+        <v>3.65</v>
       </c>
       <c r="Q271">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="R271">
         <v>2</v>
       </c>
       <c r="S271">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="T271">
-        <v>2.53</v>
+        <v>2.29</v>
       </c>
       <c r="U271">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="V271">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W271">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X271">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y271">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z271">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="AA271">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB271">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AC271">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AD271">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE271">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF271">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AG271">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>1.25</v>
       </c>
       <c r="AK271">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="O291">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="P291">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="Q291">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R291">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="S291">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="T291">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="U291">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="V291">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W291">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X291">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y291">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z291">
-        <v>4.28</v>
+        <v>3.18</v>
       </c>
       <c r="AA291">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB291">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="AC291">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="AD291">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE291">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF291">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AG291">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK291">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="O292">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P292">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="Q292">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R292">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="S292">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="T292">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="U292">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="V292">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="W292">
+        <v>1.13</v>
+      </c>
+      <c r="X292">
         <v>1.02</v>
       </c>
-      <c r="X292">
-        <v>1.04</v>
-      </c>
       <c r="Y292">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z292">
-        <v>3.18</v>
+        <v>4.28</v>
       </c>
       <c r="AA292">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB292">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="AC292">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AD292">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE292">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF292">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AG292">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK292">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.53</v>
+        <v>1.55</v>
       </c>
       <c r="O293">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="P293">
-        <v>2.23</v>
+        <v>4.99</v>
       </c>
       <c r="Q293">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="R293">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S293">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T293">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U293">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V293">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W293">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X293">
         <v>1.02</v>
       </c>
       <c r="Y293">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z293">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="AA293">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AB293">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AC293">
-        <v>3.47</v>
+        <v>2.48</v>
       </c>
       <c r="AD293">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE293">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF293">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG293">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AK293">
-        <v>1.35</v>
+        <v>2.16</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.55</v>
+        <v>2.53</v>
       </c>
       <c r="O294">
-        <v>4.17</v>
+        <v>3</v>
       </c>
       <c r="P294">
-        <v>4.99</v>
+        <v>2.23</v>
       </c>
       <c r="Q294">
-        <v>2.1</v>
+        <v>3.54</v>
       </c>
       <c r="R294">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S294">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T294">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U294">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V294">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W294">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X294">
         <v>1.02</v>
       </c>
       <c r="Y294">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z294">
-        <v>3.84</v>
+        <v>3.08</v>
       </c>
       <c r="AA294">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB294">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AC294">
-        <v>2.48</v>
+        <v>3.47</v>
       </c>
       <c r="AD294">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE294">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF294">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG294">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AK294">
-        <v>2.16</v>
+        <v>1.35</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O297">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="P297">
-        <v>6.05</v>
+        <v>5.35</v>
       </c>
       <c r="Q297">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R297">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="S297">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T297">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U297">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V297">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="W297">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X297">
         <v>1.01</v>
       </c>
       <c r="Y297">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z297">
-        <v>4.69</v>
+        <v>4.28</v>
       </c>
       <c r="AA297">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AB297">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="AC297">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="AD297">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AE297">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF297">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG297">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK297">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="O298">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="P298">
-        <v>5.35</v>
+        <v>6.05</v>
       </c>
       <c r="Q298">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="R298">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="S298">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T298">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U298">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V298">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="W298">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X298">
         <v>1.01</v>
       </c>
       <c r="Y298">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z298">
-        <v>4.28</v>
+        <v>4.69</v>
       </c>
       <c r="AA298">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AB298">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="AC298">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AD298">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AE298">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF298">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AG298">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK298">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G319">
@@ -52306,64 +52306,64 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="O319">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P319">
-        <v>3.2</v>
+        <v>4.68</v>
       </c>
       <c r="Q319">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="R319">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S319">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T319">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U319">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="V319">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="W319">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X319">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y319">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z319">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA319">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB319">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC319">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AD319">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AE319">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF319">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG319">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK319">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,64 +52469,64 @@
         </is>
       </c>
       <c r="N320">
+        <v>1.91</v>
+      </c>
+      <c r="O320">
+        <v>3.5</v>
+      </c>
+      <c r="P320">
+        <v>3.2</v>
+      </c>
+      <c r="Q320">
+        <v>2.44</v>
+      </c>
+      <c r="R320">
+        <v>2.45</v>
+      </c>
+      <c r="S320">
+        <v>1.26</v>
+      </c>
+      <c r="T320">
+        <v>3.6</v>
+      </c>
+      <c r="U320">
+        <v>2.18</v>
+      </c>
+      <c r="V320">
         <v>1.61</v>
       </c>
-      <c r="O320">
-        <v>4</v>
-      </c>
-      <c r="P320">
-        <v>4.68</v>
-      </c>
-      <c r="Q320">
-        <v>2.05</v>
-      </c>
-      <c r="R320">
-        <v>2.7</v>
-      </c>
-      <c r="S320">
-        <v>1.2</v>
-      </c>
-      <c r="T320">
-        <v>4</v>
-      </c>
-      <c r="U320">
-        <v>2.05</v>
-      </c>
-      <c r="V320">
-        <v>1.74</v>
-      </c>
       <c r="W320">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X320">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y320">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z320">
-        <v>6.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA320">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB320">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC320">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AD320">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AE320">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF320">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG320">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK320">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL320">
         <v>0</v>

--- a/jogos_2026-08-22.xlsx
+++ b/jogos_2026-08-22.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
         <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q18">
         <v>3</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
         <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA18">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB18">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC18">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD18">
         <v>1.2</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
         <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
         <v>3</v>
       </c>
       <c r="R19">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z19">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA19">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AB19">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC19">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD19">
         <v>1.2</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK19">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>3</v>
       </c>
       <c r="Q20">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S20">
         <v>1.39</v>
@@ -3611,13 +3611,13 @@
         <v>1.88</v>
       </c>
       <c r="AB20">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC20">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD20">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE20">
         <v>1.07</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.93</v>
+        <v>4.2</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>3.1</v>
+        <v>1.58</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S31">
+        <v>1.4</v>
+      </c>
+      <c r="T31">
+        <v>3</v>
+      </c>
+      <c r="U31">
+        <v>2.98</v>
+      </c>
+      <c r="V31">
+        <v>1.38</v>
+      </c>
+      <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.3</v>
+      </c>
+      <c r="Z31">
+        <v>3.3</v>
+      </c>
+      <c r="AA31">
+        <v>1.92</v>
+      </c>
+      <c r="AB31">
+        <v>1.79</v>
+      </c>
+      <c r="AC31">
+        <v>3.28</v>
+      </c>
+      <c r="AD31">
         <v>1.25</v>
       </c>
-      <c r="T31">
-        <v>3.6</v>
-      </c>
-      <c r="U31">
-        <v>2.33</v>
-      </c>
-      <c r="V31">
-        <v>1.5</v>
-      </c>
-      <c r="W31">
-        <v>1.13</v>
-      </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.18</v>
-      </c>
-      <c r="Z31">
-        <v>4.5</v>
-      </c>
-      <c r="AA31">
-        <v>1.61</v>
-      </c>
-      <c r="AB31">
-        <v>2.25</v>
-      </c>
-      <c r="AC31">
-        <v>2.45</v>
-      </c>
-      <c r="AD31">
-        <v>1.5</v>
-      </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="AK31">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.2</v>
+        <v>1.93</v>
       </c>
       <c r="O32">
         <v>3.5</v>
       </c>
       <c r="P32">
+        <v>3.1</v>
+      </c>
+      <c r="Q32">
+        <v>2.5</v>
+      </c>
+      <c r="R32">
+        <v>2.4</v>
+      </c>
+      <c r="S32">
+        <v>1.25</v>
+      </c>
+      <c r="T32">
+        <v>3.6</v>
+      </c>
+      <c r="U32">
+        <v>2.33</v>
+      </c>
+      <c r="V32">
+        <v>1.5</v>
+      </c>
+      <c r="W32">
+        <v>1.13</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>1.18</v>
+      </c>
+      <c r="Z32">
+        <v>4.5</v>
+      </c>
+      <c r="AA32">
+        <v>1.61</v>
+      </c>
+      <c r="AB32">
+        <v>2.25</v>
+      </c>
+      <c r="AC32">
+        <v>2.45</v>
+      </c>
+      <c r="AD32">
+        <v>1.5</v>
+      </c>
+      <c r="AE32">
+        <v>1.14</v>
+      </c>
+      <c r="AF32">
         <v>1.58</v>
       </c>
-      <c r="Q32">
-        <v>5</v>
-      </c>
-      <c r="R32">
-        <v>2.13</v>
-      </c>
-      <c r="S32">
-        <v>1.4</v>
-      </c>
-      <c r="T32">
-        <v>3</v>
-      </c>
-      <c r="U32">
-        <v>2.98</v>
-      </c>
-      <c r="V32">
-        <v>1.38</v>
-      </c>
-      <c r="W32">
-        <v>1.04</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.3</v>
-      </c>
-      <c r="Z32">
-        <v>3.3</v>
-      </c>
-      <c r="AA32">
-        <v>1.92</v>
-      </c>
-      <c r="AB32">
-        <v>1.79</v>
-      </c>
-      <c r="AC32">
-        <v>3.28</v>
-      </c>
-      <c r="AD32">
-        <v>1.25</v>
-      </c>
-      <c r="AE32">
-        <v>1.1</v>
-      </c>
-      <c r="AF32">
-        <v>1.8</v>
-      </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.94</v>
+        <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6506,28 +6506,28 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O38">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="P38">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q38">
         <v>7.5</v>
       </c>
       <c r="R38">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="V38">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
         <v>1.13</v>
@@ -6554,13 +6554,13 @@
         <v>1.51</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
         <v>1.95</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="O45">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="R45">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S45">
+        <v>1.36</v>
+      </c>
+      <c r="T45">
+        <v>2.65</v>
+      </c>
+      <c r="U45">
+        <v>3.02</v>
+      </c>
+      <c r="V45">
+        <v>1.36</v>
+      </c>
+      <c r="W45">
+        <v>1.06</v>
+      </c>
+      <c r="X45">
+        <v>1.02</v>
+      </c>
+      <c r="Y45">
         <v>1.33</v>
       </c>
-      <c r="T45">
-        <v>2.88</v>
-      </c>
-      <c r="U45">
-        <v>2.67</v>
-      </c>
-      <c r="V45">
-        <v>1.4</v>
-      </c>
-      <c r="W45">
-        <v>1.04</v>
-      </c>
-      <c r="X45">
-        <v>1.05</v>
-      </c>
-      <c r="Y45">
+      <c r="Z45">
+        <v>2.9</v>
+      </c>
+      <c r="AA45">
+        <v>2.05</v>
+      </c>
+      <c r="AB45">
+        <v>1.67</v>
+      </c>
+      <c r="AC45">
+        <v>3.75</v>
+      </c>
+      <c r="AD45">
         <v>1.22</v>
       </c>
-      <c r="Z45">
-        <v>3.4</v>
-      </c>
-      <c r="AA45">
-        <v>1.85</v>
-      </c>
-      <c r="AB45">
-        <v>1.85</v>
-      </c>
-      <c r="AC45">
-        <v>3.05</v>
-      </c>
-      <c r="AD45">
-        <v>1.28</v>
-      </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG45">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O46">
         <v>3.1</v>
       </c>
       <c r="P46">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q46">
-        <v>2.58</v>
+        <v>2.83</v>
       </c>
       <c r="R46">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T46">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U46">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W46">
         <v>1.06</v>
@@ -7840,31 +7840,31 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z46">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA46">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB46">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC46">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE46">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG46">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>4.6</v>
+        <v>1.52</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>1.49</v>
+        <v>5</v>
       </c>
       <c r="Q47">
-        <v>5.15</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
+        <v>1.33</v>
+      </c>
+      <c r="T47">
+        <v>2.88</v>
+      </c>
+      <c r="U47">
+        <v>2.67</v>
+      </c>
+      <c r="V47">
+        <v>1.4</v>
+      </c>
+      <c r="W47">
+        <v>1.04</v>
+      </c>
+      <c r="X47">
+        <v>1.05</v>
+      </c>
+      <c r="Y47">
+        <v>1.22</v>
+      </c>
+      <c r="Z47">
+        <v>3.4</v>
+      </c>
+      <c r="AA47">
+        <v>1.85</v>
+      </c>
+      <c r="AB47">
+        <v>1.85</v>
+      </c>
+      <c r="AC47">
+        <v>3.05</v>
+      </c>
+      <c r="AD47">
+        <v>1.28</v>
+      </c>
+      <c r="AE47">
+        <v>1.07</v>
+      </c>
+      <c r="AF47">
+        <v>1.87</v>
+      </c>
+      <c r="AG47">
+        <v>1.8</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.25</v>
       </c>
-      <c r="T47">
-        <v>3.2</v>
-      </c>
-      <c r="U47">
-        <v>2.39</v>
-      </c>
-      <c r="V47">
-        <v>1.47</v>
-      </c>
-      <c r="W47">
-        <v>1.07</v>
-      </c>
-      <c r="X47">
-        <v>1.03</v>
-      </c>
-      <c r="Y47">
-        <v>1.2</v>
-      </c>
-      <c r="Z47">
-        <v>4.2</v>
-      </c>
-      <c r="AA47">
-        <v>1.6</v>
-      </c>
-      <c r="AB47">
-        <v>2.18</v>
-      </c>
-      <c r="AC47">
-        <v>2.56</v>
-      </c>
-      <c r="AD47">
-        <v>1.45</v>
-      </c>
-      <c r="AE47">
-        <v>1.2</v>
-      </c>
-      <c r="AF47">
-        <v>1.7</v>
-      </c>
-      <c r="AG47">
-        <v>2</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.22</v>
-      </c>
       <c r="AK47">
-        <v>1.09</v>
+        <v>2.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,65 +8133,65 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>2.9</v>
+        <v>1.49</v>
       </c>
       <c r="Q48">
-        <v>2.83</v>
+        <v>5.15</v>
       </c>
       <c r="R48">
+        <v>2.31</v>
+      </c>
+      <c r="S48">
+        <v>1.25</v>
+      </c>
+      <c r="T48">
+        <v>3.2</v>
+      </c>
+      <c r="U48">
+        <v>2.39</v>
+      </c>
+      <c r="V48">
+        <v>1.47</v>
+      </c>
+      <c r="W48">
+        <v>1.07</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.2</v>
+      </c>
+      <c r="Z48">
+        <v>4.2</v>
+      </c>
+      <c r="AA48">
+        <v>1.6</v>
+      </c>
+      <c r="AB48">
+        <v>2.18</v>
+      </c>
+      <c r="AC48">
+        <v>2.56</v>
+      </c>
+      <c r="AD48">
+        <v>1.45</v>
+      </c>
+      <c r="AE48">
+        <v>1.2</v>
+      </c>
+      <c r="AF48">
+        <v>1.7</v>
+      </c>
+      <c r="AG48">
         <v>2</v>
       </c>
-      <c r="S48">
-        <v>1.41</v>
-      </c>
-      <c r="T48">
-        <v>2.56</v>
-      </c>
-      <c r="U48">
-        <v>3.03</v>
-      </c>
-      <c r="V48">
-        <v>1.31</v>
-      </c>
-      <c r="W48">
-        <v>1.06</v>
-      </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.34</v>
-      </c>
-      <c r="Z48">
-        <v>3.1</v>
-      </c>
-      <c r="AA48">
-        <v>2.07</v>
-      </c>
-      <c r="AB48">
-        <v>1.66</v>
-      </c>
-      <c r="AC48">
-        <v>3.58</v>
-      </c>
-      <c r="AD48">
-        <v>1.23</v>
-      </c>
-      <c r="AE48">
-        <v>1.04</v>
-      </c>
-      <c r="AF48">
-        <v>1.82</v>
-      </c>
-      <c r="AG48">
-        <v>1.85</v>
-      </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -10264,7 +10264,7 @@
         <v>2.42</v>
       </c>
       <c r="R61">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="S61">
         <v>1.33</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK61">
         <v>1.81</v>
@@ -10584,7 +10584,7 @@
         <v>3.58</v>
       </c>
       <c r="P63">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="Q63">
         <v>2.4</v>
@@ -10605,10 +10605,10 @@
         <v>1.45</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
         <v>1.18</v>
@@ -10620,10 +10620,10 @@
         <v>1.72</v>
       </c>
       <c r="AB63">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AC63">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD63">
         <v>1.36</v>
@@ -10756,62 +10756,62 @@
         <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
         <v>2.8</v>
       </c>
       <c r="U64">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V64">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W64">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
         <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AA64">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB64">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC64">
         <v>3.8</v>
       </c>
       <c r="AD64">
+        <v>1.21</v>
+      </c>
+      <c r="AE64">
+        <v>1.08</v>
+      </c>
+      <c r="AF64">
+        <v>1.87</v>
+      </c>
+      <c r="AG64">
+        <v>1.81</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.25</v>
-      </c>
-      <c r="AE64">
-        <v>1.04</v>
-      </c>
-      <c r="AF64">
-        <v>1.85</v>
-      </c>
-      <c r="AG64">
-        <v>1.85</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.29</v>
       </c>
       <c r="AK64">
         <v>1.8</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="O72">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P72">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q72">
-        <v>2.35</v>
+        <v>3.13</v>
       </c>
       <c r="R72">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.77</v>
+        <v>3.25</v>
       </c>
       <c r="U72">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="V72">
+        <v>1.49</v>
+      </c>
+      <c r="W72">
+        <v>1.1</v>
+      </c>
+      <c r="X72">
+        <v>1</v>
+      </c>
+      <c r="Y72">
+        <v>1.2</v>
+      </c>
+      <c r="Z72">
+        <v>4.2</v>
+      </c>
+      <c r="AA72">
+        <v>1.65</v>
+      </c>
+      <c r="AB72">
+        <v>2.2</v>
+      </c>
+      <c r="AC72">
+        <v>2.49</v>
+      </c>
+      <c r="AD72">
+        <v>1.42</v>
+      </c>
+      <c r="AE72">
+        <v>1.17</v>
+      </c>
+      <c r="AF72">
+        <v>1.53</v>
+      </c>
+      <c r="AG72">
+        <v>2.32</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.43</v>
       </c>
-      <c r="W72">
-        <v>1.06</v>
-      </c>
-      <c r="X72">
-        <v>1.05</v>
-      </c>
-      <c r="Y72">
-        <v>1.21</v>
-      </c>
-      <c r="Z72">
-        <v>3.5</v>
-      </c>
-      <c r="AA72">
-        <v>1.81</v>
-      </c>
-      <c r="AB72">
-        <v>1.93</v>
-      </c>
-      <c r="AC72">
-        <v>3.1</v>
-      </c>
-      <c r="AD72">
-        <v>1.33</v>
-      </c>
-      <c r="AE72">
-        <v>1.11</v>
-      </c>
-      <c r="AF72">
-        <v>1.63</v>
-      </c>
-      <c r="AG72">
-        <v>2.06</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.27</v>
-      </c>
       <c r="AK72">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="O73">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P73">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q73">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="R73">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V73">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W73">
         <v>1.11</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA73">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB73">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC73">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD73">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE73">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF73">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG73">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O74">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
         <v>3.3</v>
       </c>
       <c r="Q74">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="S74">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U74">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="V74">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z74">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA74">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AB74">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AC74">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AD74">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE74">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF74">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK74">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="O75">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P75">
         <v>2.3</v>
@@ -12546,16 +12546,16 @@
         <v>3.35</v>
       </c>
       <c r="R75">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
         <v>1.25</v>
       </c>
       <c r="T75">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="U75">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="V75">
         <v>1.53</v>
@@ -12564,7 +12564,7 @@
         <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
         <v>1.2</v>
@@ -12576,10 +12576,10 @@
         <v>1.67</v>
       </c>
       <c r="AB75">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC75">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AD75">
         <v>1.45</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="O77">
         <v>3.21</v>
@@ -12869,10 +12869,10 @@
         <v>2.45</v>
       </c>
       <c r="Q77">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R77">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="S77">
         <v>1.36</v>
@@ -12881,34 +12881,34 @@
         <v>2.8</v>
       </c>
       <c r="U77">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="V77">
         <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z77">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA77">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB77">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AC77">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD77">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE77">
         <v>1.1</v>
@@ -12917,7 +12917,7 @@
         <v>1.75</v>
       </c>
       <c r="AG77">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13035,13 +13035,13 @@
         <v>2.75</v>
       </c>
       <c r="R78">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S78">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T78">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U78">
         <v>2.7</v>
@@ -13050,37 +13050,37 @@
         <v>1.42</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X78">
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z78">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA78">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB78">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC78">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="AD78">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE78">
         <v>1.09</v>
       </c>
       <c r="AF78">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG78">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AK78">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13192,7 +13192,7 @@
         <v>3.36</v>
       </c>
       <c r="P79">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="Q79">
         <v>2.8</v>
@@ -13201,7 +13201,7 @@
         <v>2.1</v>
       </c>
       <c r="S79">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T79">
         <v>2.85</v>
@@ -13213,16 +13213,16 @@
         <v>1.41</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y79">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z79">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="AA79">
         <v>1.96</v>
@@ -13370,13 +13370,13 @@
         <v>2.8</v>
       </c>
       <c r="U80">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="V80">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W80">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X80">
         <v>1.03</v>
@@ -13388,7 +13388,7 @@
         <v>4.8</v>
       </c>
       <c r="AA80">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB80">
         <v>2.3</v>
@@ -13397,16 +13397,16 @@
         <v>2.38</v>
       </c>
       <c r="AD80">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE80">
         <v>1.19</v>
       </c>
       <c r="AF80">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG80">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AK80">
         <v>3</v>
@@ -13530,25 +13530,25 @@
         <v>1.32</v>
       </c>
       <c r="T81">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="U81">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V81">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA81">
         <v>1.65</v>
@@ -13560,10 +13560,10 @@
         <v>2.63</v>
       </c>
       <c r="AD81">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE81">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF81">
         <v>1.6</v>
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O82">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q82">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T82">
         <v>3.2</v>
       </c>
       <c r="U82">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="V82">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W82">
         <v>1.12</v>
@@ -13720,16 +13720,16 @@
         <v>1.98</v>
       </c>
       <c r="AC82">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AD82">
         <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG82">
         <v>2.05</v>
@@ -13748,7 +13748,7 @@
         <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14164,25 +14164,25 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O85">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P85">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="Q85">
         <v>2.3</v>
       </c>
       <c r="R85">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S85">
         <v>1.36</v>
       </c>
       <c r="T85">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U85">
         <v>2.88</v>
@@ -14191,25 +14191,25 @@
         <v>1.36</v>
       </c>
       <c r="W85">
+        <v>1.08</v>
+      </c>
+      <c r="X85">
         <v>1.05</v>
       </c>
-      <c r="X85">
-        <v>1.01</v>
-      </c>
       <c r="Y85">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z85">
         <v>3.46</v>
       </c>
       <c r="AA85">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB85">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC85">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD85">
         <v>1.25</v>
@@ -14218,10 +14218,10 @@
         <v>1.07</v>
       </c>
       <c r="AF85">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG85">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14333,7 +14333,7 @@
         <v>3.3</v>
       </c>
       <c r="P86">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q86">
         <v>4.1</v>
@@ -14345,25 +14345,25 @@
         <v>1.38</v>
       </c>
       <c r="T86">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U86">
         <v>3.17</v>
       </c>
       <c r="V86">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W86">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X86">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z86">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="AA86">
         <v>2.06</v>
@@ -14378,13 +14378,13 @@
         <v>1.22</v>
       </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF86">
         <v>1.8</v>
       </c>
       <c r="AG86">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>2.9</v>
       </c>
       <c r="Q87">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R87">
         <v>2.1</v>
@@ -14508,31 +14508,31 @@
         <v>1.4</v>
       </c>
       <c r="T87">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="U87">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="V87">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
         <v>1.02</v>
       </c>
       <c r="X87">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y87">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z87">
         <v>3</v>
       </c>
       <c r="AA87">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB87">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC87">
         <v>3.8</v>
@@ -14544,10 +14544,10 @@
         <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG87">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O88">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P88">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -14668,31 +14668,31 @@
         <v>2.1</v>
       </c>
       <c r="S88">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T88">
         <v>2.62</v>
       </c>
       <c r="U88">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="V88">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X88">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y88">
         <v>1.33</v>
       </c>
       <c r="Z88">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA88">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AB88">
         <v>1.7</v>
@@ -14704,29 +14704,29 @@
         <v>1.22</v>
       </c>
       <c r="AE88">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF88">
         <v>1.85</v>
       </c>
       <c r="AG88">
+        <v>1.85</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
+        <v>1.25</v>
+      </c>
+      <c r="AK88">
         <v>1.83</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.33</v>
-      </c>
-      <c r="AK88">
-        <v>1.73</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,52 +17424,52 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="O105">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="Q105">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="R105">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S105">
+        <v>1.37</v>
+      </c>
+      <c r="T105">
+        <v>2.73</v>
+      </c>
+      <c r="U105">
+        <v>2.59</v>
+      </c>
+      <c r="V105">
         <v>1.41</v>
       </c>
-      <c r="T105">
-        <v>2.75</v>
-      </c>
-      <c r="U105">
-        <v>2.7</v>
-      </c>
-      <c r="V105">
-        <v>1.36</v>
-      </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z105">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AA105">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB105">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC105">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD105">
         <v>1.29</v>
@@ -17478,10 +17478,10 @@
         <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="AK105">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,52 +17750,52 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="O107">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P107">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="Q107">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="R107">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S107">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T107">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U107">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V107">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z107">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="AA107">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB107">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC107">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD107">
         <v>1.29</v>
@@ -17804,10 +17804,10 @@
         <v>1.08</v>
       </c>
       <c r="AF107">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AK107">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N128">
@@ -21179,19 +21179,19 @@
         <v>4.33</v>
       </c>
       <c r="P128">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q128">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R128">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="S128">
         <v>1.3</v>
       </c>
       <c r="T128">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="U128">
         <v>2.31</v>
@@ -21200,22 +21200,22 @@
         <v>1.51</v>
       </c>
       <c r="W128">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X128">
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z128">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA128">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB128">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC128">
         <v>2.33</v>
@@ -21224,13 +21224,13 @@
         <v>1.48</v>
       </c>
       <c r="AE128">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF128">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG128">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>1.13</v>
       </c>
       <c r="AK128">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O129">
         <v>3.45</v>
       </c>
       <c r="P129">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -23125,7 +23125,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N140">
@@ -23135,7 +23135,7 @@
         <v>5.5</v>
       </c>
       <c r="P140">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -23150,43 +23150,43 @@
         <v>3.75</v>
       </c>
       <c r="U140">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V140">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W140">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X140">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z140">
         <v>5.9</v>
       </c>
       <c r="AA140">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB140">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC140">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD140">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE140">
         <v>1.2</v>
       </c>
       <c r="AF140">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG140">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23292,31 +23292,31 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O141">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P141">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q141">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="R141">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S141">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T141">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U141">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V141">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W141">
         <v>1.17</v>
@@ -23328,44 +23328,44 @@
         <v>1.15</v>
       </c>
       <c r="Z141">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA141">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB141">
         <v>2.35</v>
       </c>
       <c r="AC141">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD141">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE141">
+        <v>1.15</v>
+      </c>
+      <c r="AF141">
+        <v>1.67</v>
+      </c>
+      <c r="AG141">
+        <v>1.96</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ141">
         <v>1.2</v>
       </c>
-      <c r="AF141">
-        <v>1.73</v>
-      </c>
-      <c r="AG141">
-        <v>2</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>1.14</v>
-      </c>
       <c r="AK141">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -24442,7 +24442,7 @@
         <v>5.3</v>
       </c>
       <c r="Q148">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="R148">
         <v>1.98</v>
@@ -24451,25 +24451,25 @@
         <v>1.48</v>
       </c>
       <c r="T148">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="U148">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V148">
         <v>1.33</v>
       </c>
       <c r="W148">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X148">
         <v>1.07</v>
       </c>
       <c r="Y148">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z148">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AA148">
         <v>2.32</v>
@@ -24478,7 +24478,7 @@
         <v>1.65</v>
       </c>
       <c r="AC148">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AD148">
         <v>1.22</v>
@@ -24490,7 +24490,7 @@
         <v>2.05</v>
       </c>
       <c r="AG148">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>2.9</v>
       </c>
       <c r="Q152">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="R152">
         <v>2.25</v>
@@ -25115,25 +25115,25 @@
         <v>1.12</v>
       </c>
       <c r="X152">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
         <v>1.11</v>
       </c>
       <c r="Z152">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA152">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB152">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC152">
         <v>2.3</v>
       </c>
       <c r="AD152">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE152">
         <v>1.2</v>
@@ -25142,7 +25142,7 @@
         <v>1.44</v>
       </c>
       <c r="AG152">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25254,22 +25254,22 @@
         <v>3.45</v>
       </c>
       <c r="P153">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q153">
         <v>3.8</v>
       </c>
       <c r="R153">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S153">
         <v>1.3</v>
       </c>
       <c r="T153">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U153">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V153">
         <v>1.46</v>
@@ -25278,13 +25278,13 @@
         <v>1.11</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z153">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="AA153">
         <v>1.8</v>
@@ -25293,19 +25293,19 @@
         <v>2.04</v>
       </c>
       <c r="AC153">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD153">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE153">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF153">
         <v>1.57</v>
       </c>
       <c r="AG153">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25420,13 +25420,13 @@
         <v>1.9</v>
       </c>
       <c r="Q154">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R154">
         <v>2.11</v>
       </c>
       <c r="S154">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T154">
         <v>3.1</v>
@@ -25450,10 +25450,10 @@
         <v>3.5</v>
       </c>
       <c r="AA154">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB154">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AC154">
         <v>3.1</v>
@@ -25468,7 +25468,7 @@
         <v>1.66</v>
       </c>
       <c r="AG154">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AK154">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -27856,22 +27856,22 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O169">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P169">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q169">
         <v>2.6</v>
       </c>
       <c r="R169">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S169">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T169">
         <v>3.34</v>
@@ -27880,10 +27880,10 @@
         <v>2.22</v>
       </c>
       <c r="V169">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W169">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X169">
         <v>1.03</v>
@@ -27892,16 +27892,16 @@
         <v>1.18</v>
       </c>
       <c r="Z169">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA169">
         <v>1.49</v>
       </c>
       <c r="AB169">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC169">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD169">
         <v>1.57</v>
@@ -27910,10 +27910,10 @@
         <v>1.2</v>
       </c>
       <c r="AF169">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG169">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -28019,19 +28019,19 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O170">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P170">
         <v>3.3</v>
       </c>
       <c r="Q170">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="R170">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S170">
         <v>1.57</v>
@@ -28049,31 +28049,31 @@
         <v>1.04</v>
       </c>
       <c r="X170">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y170">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Z170">
         <v>2.35</v>
       </c>
       <c r="AA170">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AB170">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC170">
         <v>5.4</v>
       </c>
       <c r="AD170">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE170">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF170">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AG170">
         <v>1.62</v>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK170">
         <v>1.57</v>
@@ -28182,28 +28182,28 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O171">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P171">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="Q171">
         <v>2.8</v>
       </c>
       <c r="R171">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S171">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T171">
         <v>2.73</v>
       </c>
       <c r="U171">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V171">
         <v>1.4</v>
@@ -28215,22 +28215,22 @@
         <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z171">
-        <v>3.75</v>
+        <v>4.04</v>
       </c>
       <c r="AA171">
         <v>1.9</v>
       </c>
       <c r="AB171">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC171">
         <v>2.8</v>
       </c>
       <c r="AD171">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE171">
         <v>1.1</v>
@@ -28239,7 +28239,7 @@
         <v>1.65</v>
       </c>
       <c r="AG171">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O172">
         <v>3.4</v>
@@ -28354,10 +28354,10 @@
         <v>2.9</v>
       </c>
       <c r="Q172">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R172">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="S172">
         <v>1.37</v>
@@ -28369,40 +28369,40 @@
         <v>2.6</v>
       </c>
       <c r="V172">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W172">
         <v>1.04</v>
       </c>
       <c r="X172">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y172">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z172">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA172">
         <v>1.94</v>
       </c>
       <c r="AB172">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AC172">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD172">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE172">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF172">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG172">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK172">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O178">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P178">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="Q178">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="R178">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S178">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T178">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U178">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="V178">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W178">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X178">
         <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z178">
         <v>4.15</v>
       </c>
       <c r="AA178">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB178">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC178">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="AD178">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE178">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF178">
         <v>1.5</v>
       </c>
       <c r="AG178">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK178">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29492,37 +29492,37 @@
         <v>3.3</v>
       </c>
       <c r="P179">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q179">
-        <v>4.31</v>
+        <v>4.13</v>
       </c>
       <c r="R179">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S179">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T179">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U179">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="V179">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W179">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X179">
         <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z179">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="AA179">
         <v>1.83</v>
@@ -29531,19 +29531,19 @@
         <v>1.86</v>
       </c>
       <c r="AC179">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD179">
         <v>1.29</v>
       </c>
       <c r="AE179">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF179">
         <v>1.67</v>
       </c>
       <c r="AG179">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29667,13 +29667,13 @@
         <v>1.38</v>
       </c>
       <c r="T180">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U180">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="V180">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W180">
         <v>1.04</v>
@@ -29688,10 +29688,10 @@
         <v>3.29</v>
       </c>
       <c r="AA180">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB180">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC180">
         <v>3.45</v>
@@ -29700,7 +29700,7 @@
         <v>1.28</v>
       </c>
       <c r="AE180">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF180">
         <v>1.74</v>
@@ -29821,7 +29821,7 @@
         <v>7</v>
       </c>
       <c r="Q181">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="R181">
         <v>2.45</v>
@@ -29833,10 +29833,10 @@
         <v>3.1</v>
       </c>
       <c r="U181">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="V181">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W181">
         <v>1.13</v>
@@ -29845,10 +29845,10 @@
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z181">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AA181">
         <v>1.67</v>
@@ -29860,7 +29860,7 @@
         <v>2.63</v>
       </c>
       <c r="AD181">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE181">
         <v>1.13</v>
@@ -29869,7 +29869,7 @@
         <v>1.85</v>
       </c>
       <c r="AG181">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>1.15</v>
       </c>
       <c r="AK181">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29993,7 +29993,7 @@
         <v>1.47</v>
       </c>
       <c r="T182">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U182">
         <v>3.2</v>
@@ -30008,22 +30008,22 @@
         <v>1.06</v>
       </c>
       <c r="Y182">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z182">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA182">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB182">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC182">
         <v>4.33</v>
       </c>
       <c r="AD182">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE182">
         <v>1.03</v>
@@ -30032,7 +30032,7 @@
         <v>1.85</v>
       </c>
       <c r="AG182">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK182">
         <v>1.44</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O183">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="P183">
-        <v>4.77</v>
+        <v>2.9</v>
       </c>
       <c r="Q183">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="R183">
         <v>2</v>
       </c>
       <c r="S183">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T183">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U183">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="V183">
         <v>1.3</v>
       </c>
       <c r="W183">
+        <v>1.06</v>
+      </c>
+      <c r="X183">
         <v>1.04</v>
       </c>
-      <c r="X183">
-        <v>1.03</v>
-      </c>
       <c r="Y183">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z183">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AA183">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB183">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC183">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AD183">
         <v>1.2</v>
       </c>
       <c r="AE183">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF183">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AG183">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK183">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O184">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="P184">
-        <v>2.9</v>
+        <v>4.77</v>
       </c>
       <c r="Q184">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R184">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="S184">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T184">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="U184">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="V184">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W184">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X184">
+        <v>1.06</v>
+      </c>
+      <c r="Y184">
+        <v>1.36</v>
+      </c>
+      <c r="Z184">
+        <v>2.83</v>
+      </c>
+      <c r="AA184">
+        <v>2</v>
+      </c>
+      <c r="AB184">
+        <v>1.75</v>
+      </c>
+      <c r="AC184">
+        <v>3.58</v>
+      </c>
+      <c r="AD184">
+        <v>1.21</v>
+      </c>
+      <c r="AE184">
         <v>1.04</v>
       </c>
-      <c r="Y184">
-        <v>1.39</v>
-      </c>
-      <c r="Z184">
-        <v>2.85</v>
-      </c>
-      <c r="AA184">
-        <v>2.27</v>
-      </c>
-      <c r="AB184">
-        <v>1.61</v>
-      </c>
-      <c r="AC184">
-        <v>3.95</v>
-      </c>
-      <c r="AD184">
-        <v>1.2</v>
-      </c>
-      <c r="AE184">
-        <v>1.02</v>
-      </c>
       <c r="AF184">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG184">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK184">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30467,52 +30467,52 @@
         <v>3</v>
       </c>
       <c r="O185">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P185">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q185">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R185">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S185">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T185">
         <v>2.91</v>
       </c>
       <c r="U185">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="V185">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W185">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X185">
         <v>1.03</v>
       </c>
       <c r="Y185">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z185">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA185">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB185">
         <v>1.94</v>
       </c>
       <c r="AC185">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AD185">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE185">
         <v>1.13</v>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK185">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30953,37 +30953,37 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O188">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P188">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q188">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R188">
+        <v>2.21</v>
+      </c>
+      <c r="S188">
+        <v>1.33</v>
+      </c>
+      <c r="T188">
+        <v>3.28</v>
+      </c>
+      <c r="U188">
         <v>2.4</v>
       </c>
-      <c r="S188">
-        <v>1.29</v>
-      </c>
-      <c r="T188">
-        <v>3.24</v>
-      </c>
-      <c r="U188">
-        <v>2.52</v>
-      </c>
       <c r="V188">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W188">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X188">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y188">
         <v>1.22</v>
@@ -30992,22 +30992,22 @@
         <v>3.7</v>
       </c>
       <c r="AA188">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB188">
         <v>2.07</v>
       </c>
       <c r="AC188">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD188">
         <v>1.5</v>
       </c>
       <c r="AE188">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF188">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG188">
         <v>2.3</v>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK188">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -32106,7 +32106,7 @@
         <v>1.91</v>
       </c>
       <c r="R195">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S195">
         <v>1.42</v>
@@ -32115,40 +32115,40 @@
         <v>2.75</v>
       </c>
       <c r="U195">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V195">
         <v>1.35</v>
       </c>
       <c r="W195">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X195">
         <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z195">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AA195">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB195">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC195">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="AD195">
         <v>1.18</v>
       </c>
       <c r="AE195">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF195">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG195">
         <v>1.57</v>
@@ -32583,19 +32583,19 @@
         </is>
       </c>
       <c r="N198">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="O198">
         <v>2.9</v>
       </c>
       <c r="P198">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
       </c>
       <c r="R198">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="S198">
         <v>1.45</v>
@@ -32607,31 +32607,31 @@
         <v>3.4</v>
       </c>
       <c r="V198">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W198">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X198">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y198">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="Z198">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AA198">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AB198">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC198">
-        <v>4.45</v>
+        <v>5.21</v>
       </c>
       <c r="AD198">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE198">
         <v>1.05</v>
@@ -32656,7 +32656,7 @@
         <v>1.36</v>
       </c>
       <c r="AK198">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32746,10 +32746,10 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O199">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P199">
         <v>2.95</v>
@@ -32758,10 +32758,10 @@
         <v>2.88</v>
       </c>
       <c r="R199">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S199">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T199">
         <v>2.8</v>
@@ -32773,10 +32773,10 @@
         <v>1.36</v>
       </c>
       <c r="W199">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X199">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y199">
         <v>1.25</v>
@@ -32785,10 +32785,10 @@
         <v>3.2</v>
       </c>
       <c r="AA199">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB199">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC199">
         <v>3.25</v>
@@ -32803,7 +32803,7 @@
         <v>1.73</v>
       </c>
       <c r="AG199">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK199">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32912,13 +32912,13 @@
         <v>2.35</v>
       </c>
       <c r="O200">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P200">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q200">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="R200">
         <v>1.95</v>
@@ -32927,7 +32927,7 @@
         <v>1.39</v>
       </c>
       <c r="T200">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U200">
         <v>2.26</v>
@@ -32939,25 +32939,25 @@
         <v>1.04</v>
       </c>
       <c r="X200">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y200">
         <v>1.31</v>
       </c>
       <c r="Z200">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA200">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AB200">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AC200">
         <v>2.63</v>
       </c>
       <c r="AD200">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE200">
         <v>1.11</v>
@@ -33573,10 +33573,10 @@
         <v>3.6</v>
       </c>
       <c r="R204">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S204">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T204">
         <v>2.56</v>
@@ -33585,10 +33585,10 @@
         <v>2.8</v>
       </c>
       <c r="V204">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W204">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X204">
         <v>1.06</v>
@@ -33597,10 +33597,10 @@
         <v>1.34</v>
       </c>
       <c r="Z204">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="AA204">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB204">
         <v>1.73</v>
@@ -33612,7 +33612,7 @@
         <v>1.25</v>
       </c>
       <c r="AE204">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF204">
         <v>1.8</v>
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AK204">
         <v>1.33</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="O206">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P206">
-        <v>3.67</v>
+        <v>3.85</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34059,43 +34059,43 @@
         <v>2.38</v>
       </c>
       <c r="Q207">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="R207">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S207">
         <v>1.4</v>
       </c>
       <c r="T207">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U207">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="V207">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W207">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X207">
         <v>1.06</v>
       </c>
       <c r="Y207">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z207">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AA207">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB207">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AC207">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AD207">
         <v>1.25</v>
@@ -34104,10 +34104,10 @@
         <v>1.1</v>
       </c>
       <c r="AF207">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AG207">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK207">
         <v>1.31</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O208">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="P208">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -35526,25 +35526,25 @@
         <v>3.1</v>
       </c>
       <c r="Q216">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R216">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S216">
         <v>1.5</v>
       </c>
       <c r="T216">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U216">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V216">
         <v>1.33</v>
       </c>
       <c r="W216">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X216">
         <v>1.04</v>
@@ -35556,7 +35556,7 @@
         <v>2.8</v>
       </c>
       <c r="AA216">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB216">
         <v>1.65</v>
@@ -35565,16 +35565,16 @@
         <v>4.2</v>
       </c>
       <c r="AD216">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE216">
         <v>1.06</v>
       </c>
       <c r="AF216">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG216">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>1.34</v>
       </c>
       <c r="AK216">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36006,22 +36006,22 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O219">
         <v>6.5</v>
       </c>
       <c r="P219">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q219">
         <v>1.55</v>
       </c>
       <c r="R219">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S219">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T219">
         <v>3.8</v>
@@ -36042,28 +36042,28 @@
         <v>1.09</v>
       </c>
       <c r="Z219">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA219">
         <v>1.4</v>
       </c>
       <c r="AB219">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AC219">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AD219">
         <v>1.71</v>
       </c>
       <c r="AE219">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF219">
         <v>1.83</v>
       </c>
       <c r="AG219">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK219">
         <v>4</v>
@@ -36172,16 +36172,16 @@
         <v>2.62</v>
       </c>
       <c r="O220">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P220">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q220">
         <v>3</v>
       </c>
       <c r="R220">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S220">
         <v>1.25</v>
@@ -36190,43 +36190,43 @@
         <v>3.6</v>
       </c>
       <c r="U220">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V220">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W220">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X220">
         <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z220">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA220">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB220">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AC220">
         <v>2.63</v>
       </c>
       <c r="AD220">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE220">
         <v>1.2</v>
       </c>
       <c r="AF220">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG220">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>1.5</v>
       </c>
       <c r="AK220">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36332,31 +36332,31 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="O221">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="P221">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q221">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R221">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="S221">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T221">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U221">
         <v>3.8</v>
       </c>
       <c r="V221">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W221">
         <v>1.03</v>
@@ -36374,7 +36374,7 @@
         <v>2.8</v>
       </c>
       <c r="AB221">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC221">
         <v>6</v>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK221">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O227">
         <v>2.95</v>
       </c>
       <c r="P227">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q227">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R227">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S227">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="T227">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="U227">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V227">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W227">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X227">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y227">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z227">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AA227">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AB227">
         <v>1.57</v>
       </c>
       <c r="AC227">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD227">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE227">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF227">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG227">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AK227">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O228">
         <v>2.95</v>
       </c>
       <c r="P228">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q228">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R228">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S228">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T228">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="U228">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V228">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W228">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X228">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y228">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z228">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA228">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB228">
         <v>1.57</v>
       </c>
       <c r="AC228">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD228">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE228">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF228">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG228">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AK228">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37645,7 +37645,7 @@
         <v>5.34</v>
       </c>
       <c r="Q229">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R229">
         <v>2.6</v>
@@ -37660,7 +37660,7 @@
         <v>2.02</v>
       </c>
       <c r="V229">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W229">
         <v>1.2</v>
@@ -37669,10 +37669,10 @@
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z229">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA229">
         <v>1.41</v>
@@ -37681,19 +37681,19 @@
         <v>2.79</v>
       </c>
       <c r="AC229">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD229">
         <v>1.69</v>
       </c>
       <c r="AE229">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF229">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG229">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>1.18</v>
       </c>
       <c r="AK229">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37799,19 +37799,19 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O230">
         <v>3.25</v>
       </c>
       <c r="P230">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q230">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="R230">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S230">
         <v>1.33</v>
@@ -37823,19 +37823,19 @@
         <v>2.62</v>
       </c>
       <c r="V230">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W230">
         <v>1.11</v>
       </c>
       <c r="X230">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y230">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z230">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AA230">
         <v>1.75</v>
@@ -37844,13 +37844,13 @@
         <v>2.05</v>
       </c>
       <c r="AC230">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD230">
         <v>1.32</v>
       </c>
       <c r="AE230">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF230">
         <v>1.65</v>
@@ -37968,19 +37968,19 @@
         <v>5.5</v>
       </c>
       <c r="P231">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q231">
         <v>1.65</v>
       </c>
       <c r="R231">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S231">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T231">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U231">
         <v>2.33</v>
@@ -37989,10 +37989,10 @@
         <v>1.47</v>
       </c>
       <c r="W231">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X231">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y231">
         <v>1.18</v>
@@ -38007,7 +38007,7 @@
         <v>2.2</v>
       </c>
       <c r="AC231">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AD231">
         <v>1.44</v>
@@ -38019,7 +38019,7 @@
         <v>2.38</v>
       </c>
       <c r="AG231">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>1.15</v>
       </c>
       <c r="AK231">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38137,19 +38137,19 @@
         <v>1.68</v>
       </c>
       <c r="R232">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S232">
         <v>1.24</v>
       </c>
       <c r="T232">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="U232">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="V232">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W232">
         <v>1.13</v>
@@ -38167,13 +38167,13 @@
         <v>1.5</v>
       </c>
       <c r="AB232">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC232">
         <v>2.25</v>
       </c>
       <c r="AD232">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE232">
         <v>1.2</v>
@@ -38182,7 +38182,7 @@
         <v>1.85</v>
       </c>
       <c r="AG232">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK232">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38632,10 +38632,10 @@
         <v>1.62</v>
       </c>
       <c r="T235">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="U235">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="V235">
         <v>1.19</v>
@@ -38644,22 +38644,22 @@
         <v>1.03</v>
       </c>
       <c r="X235">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y235">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z235">
         <v>2.38</v>
       </c>
       <c r="AA235">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AB235">
         <v>1.4</v>
       </c>
       <c r="AC235">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AD235">
         <v>1.14</v>
@@ -38668,7 +38668,7 @@
         <v>1.02</v>
       </c>
       <c r="AF235">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG235">
         <v>1.57</v>
@@ -38786,19 +38786,19 @@
         <v>2.9</v>
       </c>
       <c r="Q236">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="R236">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="S236">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T236">
         <v>2.61</v>
       </c>
       <c r="U236">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V236">
         <v>1.27</v>
@@ -38807,34 +38807,34 @@
         <v>1.05</v>
       </c>
       <c r="X236">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y236">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z236">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AA236">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AB236">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC236">
         <v>4.15</v>
       </c>
       <c r="AD236">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE236">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF236">
         <v>1.91</v>
       </c>
       <c r="AG236">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>1.33</v>
       </c>
       <c r="AK236">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38946,7 +38946,7 @@
         <v>2.75</v>
       </c>
       <c r="P237">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q237">
         <v>3.64</v>
@@ -38955,10 +38955,10 @@
         <v>1.73</v>
       </c>
       <c r="S237">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T237">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U237">
         <v>4.05</v>
@@ -38973,10 +38973,10 @@
         <v>1.15</v>
       </c>
       <c r="Y237">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Z237">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA237">
         <v>2.88</v>
@@ -38985,10 +38985,10 @@
         <v>1.36</v>
       </c>
       <c r="AC237">
-        <v>5.2</v>
+        <v>5.95</v>
       </c>
       <c r="AD237">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE237">
         <v>1.03</v>
@@ -38997,7 +38997,7 @@
         <v>2.2</v>
       </c>
       <c r="AG237">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,52 +39103,52 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="O238">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P238">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="Q238">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R238">
         <v>1.73</v>
       </c>
       <c r="S238">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="T238">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U238">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="V238">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W238">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X238">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Y238">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Z238">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AA238">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB238">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC238">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AD238">
         <v>1.05</v>
@@ -39157,10 +39157,10 @@
         <v>1.02</v>
       </c>
       <c r="AF238">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AG238">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>1.44</v>
       </c>
       <c r="AK238">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="O239">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P239">
+        <v>4.15</v>
+      </c>
+      <c r="Q239">
         <v>2.8</v>
-      </c>
-      <c r="Q239">
-        <v>3.3</v>
       </c>
       <c r="R239">
         <v>1.73</v>
       </c>
       <c r="S239">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="T239">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U239">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V239">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W239">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X239">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y239">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z239">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AA239">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB239">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC239">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AD239">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE239">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF239">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AG239">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>1.44</v>
       </c>
       <c r="AK239">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39601,46 +39601,46 @@
         <v>2.78</v>
       </c>
       <c r="Q241">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="R241">
         <v>2.22</v>
       </c>
       <c r="S241">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T241">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U241">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="V241">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W241">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X241">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z241">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="AA241">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB241">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AC241">
         <v>3.27</v>
       </c>
       <c r="AD241">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE241">
         <v>1.06</v>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK241">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="O242">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P242">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="Q242">
         <v>2.25</v>
@@ -39770,10 +39770,10 @@
         <v>2.1</v>
       </c>
       <c r="S242">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T242">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U242">
         <v>3.08</v>
@@ -39782,25 +39782,25 @@
         <v>1.3</v>
       </c>
       <c r="W242">
+        <v>1.04</v>
+      </c>
+      <c r="X242">
         <v>1.02</v>
-      </c>
-      <c r="X242">
-        <v>1.06</v>
       </c>
       <c r="Y242">
         <v>1.33</v>
       </c>
       <c r="Z242">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA242">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AB242">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC242">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AD242">
         <v>1.22</v>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK242">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -40081,10 +40081,10 @@
         </is>
       </c>
       <c r="N244">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O244">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P244">
         <v>2.05</v>
@@ -40105,40 +40105,40 @@
         <v>2.5</v>
       </c>
       <c r="V244">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W244">
         <v>1.09</v>
       </c>
       <c r="X244">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z244">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA244">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB244">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC244">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD244">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE244">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF244">
         <v>1.53</v>
       </c>
       <c r="AG244">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.3</v>
       </c>
       <c r="AK244">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="O245">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="P245">
-        <v>4.03</v>
+        <v>2.9</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40416,22 +40416,22 @@
         <v>5.25</v>
       </c>
       <c r="Q246">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="R246">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="S246">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="T246">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="U246">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V246">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W246">
         <v>1.01</v>
@@ -40440,28 +40440,28 @@
         <v>1.05</v>
       </c>
       <c r="Y246">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z246">
-        <v>2.63</v>
+        <v>2.03</v>
       </c>
       <c r="AA246">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AB246">
         <v>1.37</v>
       </c>
       <c r="AC246">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD246">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE246">
         <v>1.01</v>
       </c>
       <c r="AF246">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG246">
         <v>1.47</v>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK246">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40582,7 +40582,7 @@
         <v>2.63</v>
       </c>
       <c r="R247">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S247">
         <v>1.33</v>
@@ -40624,10 +40624,10 @@
         <v>1.08</v>
       </c>
       <c r="AF247">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG247">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK247">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O248">
         <v>3.4</v>
       </c>
       <c r="P248">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q248">
         <v>3.3</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S248">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T248">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U248">
         <v>2.45</v>
       </c>
       <c r="V248">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W248">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X248">
         <v>1.05</v>
       </c>
       <c r="Y248">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z248">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA248">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB248">
         <v>2</v>
       </c>
       <c r="AC248">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD248">
         <v>1.36</v>
       </c>
       <c r="AE248">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF248">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG248">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AK248">
         <v>1.4</v>
@@ -40911,13 +40911,13 @@
         <v>2.2</v>
       </c>
       <c r="S249">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T249">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="U249">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="V249">
         <v>1.43</v>
@@ -40932,13 +40932,13 @@
         <v>1.28</v>
       </c>
       <c r="Z249">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA249">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB249">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AC249">
         <v>3.22</v>
@@ -40950,10 +40950,10 @@
         <v>1.07</v>
       </c>
       <c r="AF249">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG249">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK249">
         <v>1.46</v>
@@ -41068,10 +41068,10 @@
         <v>2.31</v>
       </c>
       <c r="Q250">
-        <v>3.54</v>
+        <v>3.16</v>
       </c>
       <c r="R250">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="S250">
         <v>1.33</v>
@@ -41083,31 +41083,31 @@
         <v>2.54</v>
       </c>
       <c r="V250">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W250">
         <v>1.1</v>
       </c>
       <c r="X250">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y250">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z250">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA250">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AB250">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC250">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AD250">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE250">
         <v>1.11</v>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK250">
         <v>1.36</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="O253">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="P253">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O255">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P255">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="Q255">
         <v>2.8</v>
@@ -41889,49 +41889,49 @@
         <v>2.05</v>
       </c>
       <c r="S255">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T255">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="U255">
         <v>2.7</v>
       </c>
       <c r="V255">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W255">
         <v>1.05</v>
       </c>
       <c r="X255">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z255">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA255">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB255">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AC255">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AD255">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE255">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF255">
         <v>1.73</v>
       </c>
       <c r="AG255">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>1.33</v>
       </c>
       <c r="AK255">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42064,22 +42064,22 @@
         <v>1.33</v>
       </c>
       <c r="W256">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X256">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y256">
         <v>1.36</v>
       </c>
       <c r="Z256">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AA256">
         <v>2.1</v>
       </c>
       <c r="AB256">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC256">
         <v>4.1</v>
@@ -42091,10 +42091,10 @@
         <v>1.06</v>
       </c>
       <c r="AF256">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG256">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>1.3</v>
       </c>
       <c r="AK256">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42200,34 +42200,34 @@
         </is>
       </c>
       <c r="N257">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="O257">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="P257">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="Q257">
-        <v>3.3</v>
+        <v>3.81</v>
       </c>
       <c r="R257">
         <v>2.1</v>
       </c>
       <c r="S257">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T257">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U257">
-        <v>3.08</v>
+   